--- a/Design Files/IoT-Button-v1.2/BOM/eSpark-BOM-IoT-Button.xlsx
+++ b/Design Files/IoT-Button-v1.2/BOM/eSpark-BOM-IoT-Button.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="213">
   <si>
     <t>Component list</t>
   </si>
@@ -139,9 +139,6 @@
     <t>CAP CER 1UF 25V X5R 0603</t>
   </si>
   <si>
-    <t>CAP CER 0.1UF 50V X5R 0603</t>
-  </si>
-  <si>
     <t>CAP CER 10UF 16V X5R 0603</t>
   </si>
   <si>
@@ -238,9 +235,6 @@
     <t>CC0603KRX5R8BB105</t>
   </si>
   <si>
-    <t>CC0603KRX5R9BB104</t>
-  </si>
-  <si>
     <t>CC0603KRX5R7BB106</t>
   </si>
   <si>
@@ -331,9 +325,6 @@
     <t>C14664</t>
   </si>
   <si>
-    <t>C110022</t>
-  </si>
-  <si>
     <t>C2936601</t>
   </si>
   <si>
@@ -478,9 +469,6 @@
     <t>5V2A New AC 100V-240V Converter Adapter DC 5V 2A 2000mA Power Supply EU Plug DC 5.5mm x 2.1mm</t>
   </si>
   <si>
-    <t>C18, C20, C25, C26</t>
-  </si>
-  <si>
     <t>CAP CER 0.1UF 25V X5R 0402</t>
   </si>
   <si>
@@ -493,9 +481,6 @@
     <t>C106256</t>
   </si>
   <si>
-    <t>C1, C2, C5, C8, C10, C11, C12, C14, C15, C16, C17</t>
-  </si>
-  <si>
     <t>C3, C4, C7, C13, C19, C27</t>
   </si>
   <si>
@@ -574,9 +559,6 @@
     <t>R7</t>
   </si>
   <si>
-    <t>R3, R5</t>
-  </si>
-  <si>
     <t>RES 100K OHM 5% 1/10W 0603</t>
   </si>
   <si>
@@ -595,24 +577,9 @@
     <t>DNP</t>
   </si>
   <si>
-    <t>R12</t>
-  </si>
-  <si>
-    <t>RES SMD 100K OHM 5% 1/5W 0603</t>
-  </si>
-  <si>
-    <t>RES-0603</t>
-  </si>
-  <si>
-    <t>CRGH0603J100K</t>
-  </si>
-  <si>
     <t>TE Connectivity</t>
   </si>
   <si>
-    <t>C2074142</t>
-  </si>
-  <si>
     <t>Rx1, Rx2</t>
   </si>
   <si>
@@ -686,6 +653,12 @@
   </si>
   <si>
     <t>C266196</t>
+  </si>
+  <si>
+    <t>C1, C2, C5, C8, C10, C11, C12, C14, C15, C16, C17, C18, C20, C25, C26</t>
+  </si>
+  <si>
+    <t>R3, R5, R12</t>
   </si>
 </sst>
 </file>
@@ -1350,28 +1323,19 @@
     <xf numFmtId="166" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1382,20 +1346,29 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1842,7 +1815,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S45"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -1876,15 +1849,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="73"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="84"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1895,7 +1868,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="51" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1920,7 +1893,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="52" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1934,7 +1907,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="74"/>
+      <c r="S3" s="85"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1945,7 +1918,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="53" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1959,7 +1932,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="75"/>
+      <c r="S4" s="86"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1984,7 +1957,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="75"/>
+      <c r="S5" s="86"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2005,7 +1978,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="75"/>
+      <c r="S6" s="86"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2026,7 +1999,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="75"/>
+      <c r="S7" s="86"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2047,7 +2020,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="75"/>
+      <c r="S8" s="86"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2064,212 +2037,212 @@
         <v>37</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K9" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="O9" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="L9" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="M9" s="30" t="s">
+      <c r="P9" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="N9" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="O9" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>145</v>
-      </c>
       <c r="R9" s="30" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="S9" s="30" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="56"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="68" t="s">
+      <c r="C10" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="E10" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="49" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="H10" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="I10" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="J10" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="K10" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="L10" s="49">
-        <v>11</v>
+      <c r="D10" s="49" t="s">
+        <v>153</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="L10" s="37">
+        <v>6</v>
       </c>
       <c r="M10" s="37">
         <f>L10*2</f>
-        <v>22</v>
-      </c>
-      <c r="N10" s="37">
+        <v>12</v>
+      </c>
+      <c r="N10" s="49">
         <v>100</v>
       </c>
-      <c r="O10" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P10" s="50">
-        <v>3.7000000000000002E-3</v>
-      </c>
-      <c r="Q10" s="38">
-        <f>P10*N10</f>
-        <v>0.37</v>
-      </c>
-      <c r="R10" s="37"/>
-      <c r="S10" s="57"/>
+      <c r="O10" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P10" s="38">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="Q10" s="50">
+        <f t="shared" ref="Q10" si="0">P10*N10</f>
+        <v>0.52</v>
+      </c>
+      <c r="R10" s="49"/>
+      <c r="S10" s="55"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="56"/>
       <c r="B11" s="46">
-        <f>ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B41" si="1">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="49" t="s">
-        <v>158</v>
+      <c r="D11" s="37" t="s">
+        <v>154</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G11" s="37" t="s">
         <v>71</v>
       </c>
       <c r="H11" s="37" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I11" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J11" s="37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K11" s="37" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L11" s="37">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M11" s="37">
         <f>L11*2</f>
-        <v>12</v>
-      </c>
-      <c r="N11" s="49">
-        <v>100</v>
+        <v>4</v>
+      </c>
+      <c r="N11" s="37">
+        <v>5</v>
       </c>
       <c r="O11" s="59" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P11" s="38">
-        <v>5.1999999999999998E-3</v>
-      </c>
-      <c r="Q11" s="50">
-        <f t="shared" ref="Q11" si="0">P11*N11</f>
-        <v>0.52</v>
-      </c>
-      <c r="R11" s="49"/>
+        <v>0.15809999999999999</v>
+      </c>
+      <c r="Q11" s="38">
+        <f>P11*N11</f>
+        <v>0.79049999999999998</v>
+      </c>
+      <c r="R11" s="37"/>
       <c r="S11" s="55"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A12" s="56"/>
       <c r="B12" s="46">
-        <f t="shared" ref="B12:B43" si="1">ROW(B12) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="C12" s="67" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>159</v>
+        <v>211</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>40</v>
+        <v>149</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L12" s="37">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M12" s="37">
         <f>L12*2</f>
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="N12" s="37">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="O12" s="59" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P12" s="38">
-        <v>0.15809999999999999</v>
+        <v>1.8E-3</v>
       </c>
       <c r="Q12" s="38">
         <f>P12*N12</f>
-        <v>0.79049999999999998</v>
+        <v>0.18</v>
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="55"/>
@@ -2281,145 +2254,143 @@
         <v>4</v>
       </c>
       <c r="C13" s="67" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="70" t="s">
-        <v>152</v>
+        <v>22</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>153</v>
+        <v>40</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="G13" s="37" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="H13" s="37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I13" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J13" s="37" t="s">
-        <v>156</v>
+        <v>102</v>
       </c>
       <c r="K13" s="37" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="L13" s="37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M13" s="37">
-        <f>L13*2</f>
-        <v>8</v>
-      </c>
-      <c r="N13" s="37">
-        <v>100</v>
+        <f t="shared" ref="M13:M41" si="2">L13*2</f>
+        <v>2</v>
+      </c>
+      <c r="N13" s="49">
+        <v>10</v>
       </c>
       <c r="O13" s="59" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P13" s="38">
-        <v>1.8E-3</v>
-      </c>
-      <c r="Q13" s="38">
-        <f>P13*N13</f>
-        <v>0.18</v>
-      </c>
-      <c r="R13" s="37"/>
-      <c r="S13" s="55"/>
+        <v>6.4299999999999996E-2</v>
+      </c>
+      <c r="Q13" s="50">
+        <f t="shared" ref="Q13" si="3">P13*N13</f>
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="R13" s="49"/>
+      <c r="S13" s="49"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="56"/>
-      <c r="B14" s="46">
+      <c r="B14" s="72">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="C14" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="70" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="K14" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L14" s="37">
+      <c r="D14" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="F14" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>159</v>
+      </c>
+      <c r="I14" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J14" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="K14" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L14" s="49">
         <v>1</v>
       </c>
       <c r="M14" s="37">
-        <f t="shared" ref="M14:M45" si="2">L14*2</f>
+        <f>L14*2</f>
         <v>2</v>
       </c>
-      <c r="N14" s="49">
-        <v>10</v>
-      </c>
-      <c r="O14" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P14" s="38">
-        <v>6.4299999999999996E-2</v>
-      </c>
-      <c r="Q14" s="50">
-        <f t="shared" ref="Q14" si="3">P14*N14</f>
-        <v>0.64300000000000002</v>
-      </c>
-      <c r="R14" s="49"/>
-      <c r="S14" s="49"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N14" s="37">
+        <v>3</v>
+      </c>
+      <c r="O14" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P14" s="50">
+        <v>0.22550000000000001</v>
+      </c>
+      <c r="Q14" s="38">
+        <f>P14*N14</f>
+        <v>0.67649999999999999</v>
+      </c>
+      <c r="R14" s="37"/>
+      <c r="S14" s="55"/>
+    </row>
+    <row r="15" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="56"/>
-      <c r="B15" s="82">
+      <c r="B15" s="46">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="C15" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="49" t="s">
-        <v>160</v>
-      </c>
-      <c r="E15" s="49" t="s">
-        <v>161</v>
-      </c>
-      <c r="F15" s="49" t="s">
-        <v>162</v>
-      </c>
-      <c r="G15" s="49" t="s">
-        <v>163</v>
-      </c>
-      <c r="H15" s="49" t="s">
-        <v>164</v>
-      </c>
-      <c r="I15" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="J15" s="49" t="s">
-        <v>165</v>
-      </c>
-      <c r="K15" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="L15" s="49">
+        <v>11</v>
+      </c>
+      <c r="D15" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="K15" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L15" s="37">
         <v>1</v>
       </c>
       <c r="M15" s="37">
@@ -2427,241 +2398,243 @@
         <v>2</v>
       </c>
       <c r="N15" s="37">
-        <v>3</v>
-      </c>
-      <c r="O15" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P15" s="50">
-        <v>0.22550000000000001</v>
+        <v>5</v>
+      </c>
+      <c r="O15" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P15" s="38">
+        <v>9.5100000000000004E-2</v>
       </c>
       <c r="Q15" s="38">
         <f>P15*N15</f>
-        <v>0.67649999999999999</v>
+        <v>0.47550000000000003</v>
       </c>
       <c r="R15" s="37"/>
       <c r="S15" s="55"/>
     </row>
-    <row r="16" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="56"/>
       <c r="B16" s="46">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="C16" s="67" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="70" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="37" t="s">
+      <c r="C16" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="69" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="37" t="s">
+      <c r="F16" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="G16" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="H16" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37" t="s">
-        <v>106</v>
+      <c r="G16" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="49" t="s">
+        <v>89</v>
+      </c>
+      <c r="I16" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J16" s="49" t="s">
+        <v>104</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L16" s="37">
+        <v>134</v>
+      </c>
+      <c r="L16" s="49">
         <v>1</v>
       </c>
       <c r="M16" s="37">
-        <f>L16*2</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N16" s="37">
-        <v>5</v>
-      </c>
-      <c r="O16" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P16" s="38">
-        <v>9.5100000000000004E-2</v>
+        <v>20</v>
+      </c>
+      <c r="O16" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P16" s="50">
+        <v>3.1E-2</v>
       </c>
       <c r="Q16" s="38">
         <f>P16*N16</f>
-        <v>0.47550000000000003</v>
+        <v>0.62</v>
       </c>
       <c r="R16" s="37"/>
       <c r="S16" s="55"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A17" s="56"/>
       <c r="B17" s="46">
-        <f t="shared" si="1"/>
+        <f>ROW(B17) - ROW($B$9)</f>
         <v>8</v>
       </c>
-      <c r="C17" s="68" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="49" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="H17" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="I17" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="J17" s="49" t="s">
-        <v>107</v>
+      <c r="C17" s="67" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="F17" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G17" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="H17" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="I17" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J17" s="37" t="s">
+        <v>164</v>
       </c>
       <c r="K17" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L17" s="49">
+        <v>134</v>
+      </c>
+      <c r="L17" s="37">
         <v>1</v>
       </c>
       <c r="M17" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N17" s="37">
-        <v>20</v>
-      </c>
-      <c r="O17" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P17" s="50">
-        <v>3.1E-2</v>
-      </c>
-      <c r="Q17" s="38">
-        <f>P17*N17</f>
-        <v>0.62</v>
-      </c>
-      <c r="R17" s="37"/>
+      <c r="N17" s="49">
+        <v>5</v>
+      </c>
+      <c r="O17" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P17" s="38">
+        <v>0.1636</v>
+      </c>
+      <c r="Q17" s="50">
+        <f t="shared" ref="Q17" si="4">P17*N17</f>
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="R17" s="49"/>
       <c r="S17" s="55"/>
     </row>
     <row r="18" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A18" s="56"/>
       <c r="B18" s="46">
-        <f>ROW(B18) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="C18" s="67" t="s">
-        <v>166</v>
-      </c>
-      <c r="D18" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="37" t="s">
-        <v>167</v>
+      <c r="C18" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="69" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="49" t="s">
+        <v>43</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="G18" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="H18" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="I18" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J18" s="37" t="s">
-        <v>169</v>
+        <v>135</v>
+      </c>
+      <c r="G18" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="I18" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J18" s="49" t="s">
+        <v>105</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L18" s="37">
+        <v>134</v>
+      </c>
+      <c r="L18" s="49">
         <v>1</v>
       </c>
       <c r="M18" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N18" s="49">
-        <v>5</v>
-      </c>
-      <c r="O18" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P18" s="38">
-        <v>0.1636</v>
-      </c>
-      <c r="Q18" s="50">
-        <f t="shared" ref="Q18" si="4">P18*N18</f>
-        <v>0.81799999999999995</v>
-      </c>
-      <c r="R18" s="49"/>
+      <c r="N18" s="37">
+        <v>20</v>
+      </c>
+      <c r="O18" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P18" s="50">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="Q18" s="38">
+        <f>P18*N18</f>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="R18" s="37"/>
       <c r="S18" s="55"/>
     </row>
-    <row r="19" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A19" s="56"/>
       <c r="B19" s="46">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="C19" s="68" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="69" t="s">
-        <v>170</v>
-      </c>
-      <c r="E19" s="49" t="s">
+      <c r="C19" s="67" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="37" t="s">
         <v>44</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="G19" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="H19" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="I19" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="J19" s="49" t="s">
-        <v>108</v>
+        <v>135</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="I19" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J19" s="37" t="s">
+        <v>75</v>
       </c>
       <c r="K19" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L19" s="49">
+        <v>134</v>
+      </c>
+      <c r="L19" s="37">
         <v>1</v>
       </c>
       <c r="M19" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N19" s="37">
-        <v>20</v>
-      </c>
-      <c r="O19" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P19" s="50">
-        <v>2.2499999999999999E-2</v>
-      </c>
-      <c r="Q19" s="38">
-        <f>P19*N19</f>
-        <v>0.44999999999999996</v>
-      </c>
-      <c r="R19" s="37"/>
+      <c r="N19" s="49">
+        <v>12</v>
+      </c>
+      <c r="O19" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P19" s="38">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="Q19" s="50">
+        <f t="shared" ref="Q19" si="5">P19*N19</f>
+        <v>0.86399999999999988</v>
+      </c>
+      <c r="R19" s="49"/>
       <c r="S19" s="55"/>
     </row>
     <row r="20" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -2670,54 +2643,52 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="C20" s="67" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="70" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="37" t="s">
+      <c r="C20" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="69" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="49" t="s">
         <v>45</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="G20" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="H20" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="I20" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J20" s="37" t="s">
-        <v>77</v>
+        <v>135</v>
+      </c>
+      <c r="G20" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49" t="s">
+        <v>106</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L20" s="37">
+        <v>134</v>
+      </c>
+      <c r="L20" s="49">
         <v>1</v>
       </c>
       <c r="M20" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N20" s="49">
-        <v>12</v>
-      </c>
-      <c r="O20" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P20" s="38">
-        <v>7.1999999999999995E-2</v>
-      </c>
-      <c r="Q20" s="50">
-        <f t="shared" ref="Q20" si="5">P20*N20</f>
-        <v>0.86399999999999988</v>
-      </c>
-      <c r="R20" s="49"/>
+      <c r="N20" s="37">
+        <v>5</v>
+      </c>
+      <c r="O20" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P20" s="50">
+        <v>0.20130000000000001</v>
+      </c>
+      <c r="Q20" s="38">
+        <f>P20*N20</f>
+        <v>1.0065</v>
+      </c>
+      <c r="R20" s="37"/>
       <c r="S20" s="55"/>
     </row>
     <row r="21" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -2726,52 +2697,54 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="C21" s="68" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="49" t="s">
+      <c r="C21" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="37" t="s">
         <v>46</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="G21" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="H21" s="49" t="s">
-        <v>94</v>
-      </c>
-      <c r="I21" s="49"/>
-      <c r="J21" s="49" t="s">
-        <v>109</v>
+      <c r="G21" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J21" s="37" t="s">
+        <v>107</v>
       </c>
       <c r="K21" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L21" s="49">
+        <v>134</v>
+      </c>
+      <c r="L21" s="37">
         <v>1</v>
       </c>
       <c r="M21" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N21" s="37">
-        <v>5</v>
-      </c>
-      <c r="O21" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P21" s="50">
-        <v>0.20130000000000001</v>
-      </c>
-      <c r="Q21" s="38">
-        <f>P21*N21</f>
-        <v>1.0065</v>
-      </c>
-      <c r="R21" s="37"/>
+      <c r="N21" s="49">
+        <v>20</v>
+      </c>
+      <c r="O21" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P21" s="38">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="Q21" s="50">
+        <f t="shared" ref="Q21" si="6">P21*N21</f>
+        <v>0.53</v>
+      </c>
+      <c r="R21" s="49"/>
       <c r="S21" s="55"/>
     </row>
     <row r="22" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -2780,54 +2753,54 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="C22" s="67" t="s">
+      <c r="C22" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="70" t="s">
-        <v>28</v>
-      </c>
-      <c r="E22" s="37" t="s">
+      <c r="D22" s="69" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="G22" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="H22" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="I22" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J22" s="37" t="s">
-        <v>110</v>
+      <c r="F22" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J22" s="49" t="s">
+        <v>108</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L22" s="37">
+        <v>134</v>
+      </c>
+      <c r="L22" s="49">
         <v>1</v>
       </c>
       <c r="M22" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N22" s="49">
+      <c r="N22" s="37">
         <v>20</v>
       </c>
-      <c r="O22" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P22" s="38">
-        <v>2.6499999999999999E-2</v>
-      </c>
-      <c r="Q22" s="50">
-        <f t="shared" ref="Q22" si="6">P22*N22</f>
-        <v>0.53</v>
-      </c>
-      <c r="R22" s="49"/>
+      <c r="O22" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P22" s="50">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="Q22" s="38">
+        <f>P22*N22</f>
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="R22" s="37"/>
       <c r="S22" s="55"/>
     </row>
     <row r="23" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -2836,388 +2809,388 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="C23" s="68" t="s">
+      <c r="C23" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="69" t="s">
-        <v>29</v>
-      </c>
-      <c r="E23" s="49" t="s">
+      <c r="D23" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="G23" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="H23" s="49" t="s">
-        <v>95</v>
-      </c>
-      <c r="I23" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="J23" s="49" t="s">
-        <v>111</v>
+      <c r="F23" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I23" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J23" s="37" t="s">
+        <v>109</v>
       </c>
       <c r="K23" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L23" s="49">
+        <v>134</v>
+      </c>
+      <c r="L23" s="37">
         <v>1</v>
       </c>
       <c r="M23" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N23" s="37">
+      <c r="N23" s="49">
         <v>20</v>
       </c>
-      <c r="O23" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P23" s="50">
-        <v>2.3300000000000001E-2</v>
-      </c>
-      <c r="Q23" s="38">
-        <f>P23*N23</f>
-        <v>0.46600000000000003</v>
-      </c>
-      <c r="R23" s="37"/>
+      <c r="O23" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P23" s="38">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="Q23" s="50">
+        <f t="shared" ref="Q23" si="7">P23*N23</f>
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="R23" s="49"/>
       <c r="S23" s="55"/>
     </row>
     <row r="24" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A24" s="56"/>
       <c r="B24" s="46">
-        <f t="shared" si="1"/>
+        <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
       <c r="C24" s="67" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="70" t="s">
-        <v>30</v>
+        <v>166</v>
+      </c>
+      <c r="D24" s="37" t="s">
+        <v>167</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>49</v>
+        <v>168</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>64</v>
+        <v>135</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J24" s="37" t="s">
-        <v>112</v>
+        <v>171</v>
       </c>
       <c r="K24" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="L24" s="37">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M24" s="37">
         <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="N24" s="37">
+        <v>15</v>
+      </c>
+      <c r="O24" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P24" s="38">
+        <v>7.1300000000000002E-2</v>
+      </c>
+      <c r="Q24" s="38">
+        <f>P24*N24</f>
+        <v>1.0695000000000001</v>
+      </c>
+      <c r="R24" s="37"/>
+      <c r="S24" s="55"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="56"/>
+      <c r="B25" s="73">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="75" t="s">
+        <v>172</v>
+      </c>
+      <c r="E25" s="75" t="s">
+        <v>173</v>
+      </c>
+      <c r="F25" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" s="75" t="s">
+        <v>174</v>
+      </c>
+      <c r="H25" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="I25" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="75" t="s">
+        <v>176</v>
+      </c>
+      <c r="K25" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="L25" s="75">
         <v>2</v>
-      </c>
-      <c r="N24" s="49">
-        <v>20</v>
-      </c>
-      <c r="O24" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P24" s="38">
-        <v>3.2199999999999999E-2</v>
-      </c>
-      <c r="Q24" s="50">
-        <f t="shared" ref="Q24" si="7">P24*N24</f>
-        <v>0.64400000000000002</v>
-      </c>
-      <c r="R24" s="49"/>
-      <c r="S24" s="55"/>
-    </row>
-    <row r="25" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A25" s="56"/>
-      <c r="B25" s="46">
-        <f>ROW(B25) - ROW($B$9)</f>
-        <v>16</v>
-      </c>
-      <c r="C25" s="67" t="s">
-        <v>171</v>
-      </c>
-      <c r="D25" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="E25" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="F25" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="G25" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="H25" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="I25" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J25" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="K25" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L25" s="37">
-        <v>6</v>
       </c>
       <c r="M25" s="37">
         <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="N25" s="37">
-        <v>15</v>
-      </c>
-      <c r="O25" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P25" s="38">
-        <v>7.1300000000000002E-2</v>
-      </c>
-      <c r="Q25" s="38">
-        <f>P25*N25</f>
-        <v>1.0695000000000001</v>
-      </c>
-      <c r="R25" s="37"/>
+        <v>4</v>
+      </c>
+      <c r="N25" s="49">
+        <v>10</v>
+      </c>
+      <c r="O25" s="66" t="s">
+        <v>136</v>
+      </c>
+      <c r="P25" s="63">
+        <v>3.1E-2</v>
+      </c>
+      <c r="Q25" s="50">
+        <f t="shared" ref="Q25" si="8">P25*N25</f>
+        <v>0.31</v>
+      </c>
+      <c r="R25" s="49"/>
       <c r="S25" s="55"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="56"/>
-      <c r="B26" s="83">
-        <f t="shared" si="1"/>
+      <c r="B26" s="46">
+        <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="84" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" s="85" t="s">
+      <c r="C26" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="E26" s="85" t="s">
-        <v>178</v>
-      </c>
-      <c r="F26" s="85" t="s">
+      <c r="E26" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="G26" s="85" t="s">
-        <v>179</v>
-      </c>
-      <c r="H26" s="85" t="s">
-        <v>180</v>
-      </c>
-      <c r="I26" s="85" t="s">
-        <v>137</v>
-      </c>
-      <c r="J26" s="85" t="s">
-        <v>181</v>
-      </c>
-      <c r="K26" s="85" t="s">
-        <v>137</v>
-      </c>
-      <c r="L26" s="85">
-        <v>2</v>
+      <c r="G26" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I26" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J26" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="K26" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="L26" s="37">
+        <v>5</v>
       </c>
       <c r="M26" s="37">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="N26" s="49">
         <v>10</v>
       </c>
-      <c r="O26" s="66" t="s">
-        <v>139</v>
-      </c>
-      <c r="P26" s="63">
-        <v>3.1E-2</v>
-      </c>
-      <c r="Q26" s="50">
-        <f t="shared" ref="Q26" si="8">P26*N26</f>
-        <v>0.31</v>
-      </c>
-      <c r="R26" s="49"/>
+      <c r="N26" s="37">
+        <v>100</v>
+      </c>
+      <c r="O26" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P26" s="38">
+        <v>1E-3</v>
+      </c>
+      <c r="Q26" s="38">
+        <f>P26*N26</f>
+        <v>0.1</v>
+      </c>
+      <c r="R26" s="37"/>
       <c r="S26" s="55"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="56"/>
       <c r="B27" s="46">
-        <f>ROW(B27) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="C27" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="37" t="s">
-        <v>182</v>
-      </c>
-      <c r="E27" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="F27" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G27" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="H27" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="I27" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J27" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="K27" s="37" t="s">
-        <v>125</v>
-      </c>
-      <c r="L27" s="37">
-        <v>5</v>
+      <c r="D27" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="H27" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="I27" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J27" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="K27" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="L27" s="49">
+        <v>1</v>
       </c>
       <c r="M27" s="37">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="N27" s="37">
+        <v>2</v>
+      </c>
+      <c r="N27" s="49">
         <v>100</v>
       </c>
-      <c r="O27" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P27" s="38">
-        <v>1E-3</v>
-      </c>
-      <c r="Q27" s="38">
-        <f>P27*N27</f>
-        <v>0.1</v>
-      </c>
-      <c r="R27" s="37"/>
+      <c r="O27" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P27" s="50">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q27" s="50">
+        <f t="shared" ref="Q27" si="9">P27*N27</f>
+        <v>0.12</v>
+      </c>
+      <c r="R27" s="49"/>
       <c r="S27" s="55"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="56"/>
       <c r="B28" s="46">
-        <f t="shared" si="1"/>
+        <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="68" t="s">
+      <c r="C28" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="F28" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="G28" s="49" t="s">
-        <v>81</v>
-      </c>
-      <c r="H28" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="I28" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="J28" s="49" t="s">
-        <v>113</v>
-      </c>
-      <c r="K28" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="L28" s="49">
-        <v>1</v>
+      <c r="D28" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="E28" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="F28" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="H28" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J28" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="K28" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="L28" s="37">
+        <v>3</v>
       </c>
       <c r="M28" s="37">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="N28" s="49">
+        <v>6</v>
+      </c>
+      <c r="N28" s="37">
         <v>100</v>
       </c>
-      <c r="O28" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P28" s="50">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q28" s="50">
-        <f t="shared" ref="Q28" si="9">P28*N28</f>
-        <v>0.12</v>
-      </c>
-      <c r="R28" s="49"/>
+      <c r="O28" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P28" s="38">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q28" s="38">
+        <f>P28*N28</f>
+        <v>0.11</v>
+      </c>
+      <c r="R28" s="37"/>
       <c r="S28" s="55"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="56"/>
       <c r="B29" s="46">
-        <f>ROW(B29) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="C29" s="67" t="s">
+      <c r="C29" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="37" t="s">
-        <v>184</v>
+      <c r="D29" s="70" t="s">
+        <v>178</v>
       </c>
       <c r="E29" s="37" t="s">
-        <v>185</v>
+        <v>50</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>186</v>
+        <v>80</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I29" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J29" s="37" t="s">
-        <v>187</v>
+        <v>111</v>
       </c>
       <c r="K29" s="37" t="s">
-        <v>188</v>
+        <v>121</v>
       </c>
       <c r="L29" s="37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M29" s="37">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N29" s="37">
         <v>100</v>
       </c>
       <c r="O29" s="59" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P29" s="38">
-        <v>1.1000000000000001E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="Q29" s="38">
         <f>P29*N29</f>
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="R29" s="37"/>
       <c r="S29" s="55"/>
@@ -3225,35 +3198,35 @@
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="56"/>
       <c r="B30" s="46">
-        <f t="shared" si="1"/>
+        <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
       <c r="C30" s="68" t="s">
         <v>18</v>
       </c>
       <c r="D30" s="70" t="s">
-        <v>183</v>
+        <v>32</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G30" s="37" t="s">
         <v>82</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -3262,167 +3235,168 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N30" s="37">
+      <c r="N30" s="49">
         <v>100</v>
       </c>
       <c r="O30" s="59" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P30" s="38">
-        <v>1E-3</v>
-      </c>
-      <c r="Q30" s="38">
-        <f>P30*N30</f>
-        <v>0.1</v>
-      </c>
-      <c r="R30" s="37"/>
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q30" s="50">
+        <f t="shared" ref="Q30" si="10">P30*N30</f>
+        <v>0.13</v>
+      </c>
+      <c r="R30" s="49"/>
       <c r="S30" s="55"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="56"/>
-      <c r="B31" s="46">
-        <f>ROW(B31) - ROW($B$9)</f>
+      <c r="B31" s="72">
+        <f t="shared" ref="B31" si="11">ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
       <c r="C31" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="70" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G31" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="H31" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="I31" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J31" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="K31" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="L31" s="37">
+      <c r="D31" s="49" t="s">
+        <v>183</v>
+      </c>
+      <c r="E31" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="H31" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="I31" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J31" s="49" t="s">
+        <v>112</v>
+      </c>
+      <c r="K31" s="49" t="s">
+        <v>184</v>
+      </c>
+      <c r="L31" s="49">
         <v>1</v>
       </c>
       <c r="M31" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N31" s="49">
+      <c r="N31" s="37">
         <v>100</v>
       </c>
       <c r="O31" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P31" s="38">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q31" s="50">
-        <f t="shared" ref="Q31" si="10">P31*N31</f>
-        <v>0.13</v>
-      </c>
-      <c r="R31" s="49"/>
+        <v>136</v>
+      </c>
+      <c r="P31" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q31" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="R31" s="76" t="s">
+        <v>184</v>
+      </c>
       <c r="S31" s="55"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="56"/>
-      <c r="B32" s="82">
-        <f t="shared" ref="B32" si="11">ROW(B32) - ROW($B$9)</f>
+      <c r="B32" s="72">
+        <f t="shared" ref="B32" si="12">ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
       <c r="C32" s="68" t="s">
         <v>18</v>
       </c>
       <c r="D32" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="E32" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="F32" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="G32" s="49" t="s">
         <v>189</v>
       </c>
-      <c r="E32" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="F32" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="G32" s="49" t="s">
-        <v>83</v>
-      </c>
       <c r="H32" s="49" t="s">
-        <v>88</v>
+        <v>190</v>
       </c>
       <c r="I32" s="49" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J32" s="49" t="s">
-        <v>115</v>
+        <v>191</v>
       </c>
       <c r="K32" s="49" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="L32" s="49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M32" s="37">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N32" s="37">
         <v>100</v>
       </c>
-      <c r="O32" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P32" s="38" t="s">
-        <v>137</v>
+      <c r="O32" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P32" s="50" t="s">
+        <v>134</v>
       </c>
       <c r="Q32" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="R32" s="86" t="s">
-        <v>190</v>
+        <v>134</v>
+      </c>
+      <c r="R32" s="76" t="s">
+        <v>184</v>
       </c>
       <c r="S32" s="55"/>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A33" s="56"/>
       <c r="B33" s="46">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="67" t="s">
-        <v>18</v>
+      <c r="C33" s="68" t="s">
+        <v>194</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>191</v>
+        <v>33</v>
       </c>
       <c r="E33" s="37" t="s">
         <v>192</v>
       </c>
       <c r="F33" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G33" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="G33" s="37" t="s">
-        <v>194</v>
-      </c>
       <c r="H33" s="37" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="K33" s="37" t="s">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="L33" s="37">
         <v>1</v>
@@ -3432,53 +3406,53 @@
         <v>2</v>
       </c>
       <c r="N33" s="49">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="O33" s="59" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P33" s="38">
-        <v>5.4999999999999997E-3</v>
+        <v>0.1336</v>
       </c>
       <c r="Q33" s="50">
-        <f t="shared" ref="Q33" si="12">P33*N33</f>
-        <v>0.54999999999999993</v>
-      </c>
-      <c r="R33" s="37"/>
+        <f t="shared" ref="Q33" si="13">P33*N33</f>
+        <v>0.66799999999999993</v>
+      </c>
+      <c r="R33" s="49"/>
       <c r="S33" s="55"/>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A34" s="56"/>
-      <c r="B34" s="82">
-        <f t="shared" ref="B34" si="13">ROW(B34) - ROW($B$9)</f>
+    <row r="34" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A34" s="61"/>
+      <c r="B34" s="72">
+        <f t="shared" ref="B34" si="14">ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
       <c r="C34" s="68" t="s">
-        <v>18</v>
+        <v>194</v>
       </c>
       <c r="D34" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="E34" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="F34" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="E34" s="49" t="s">
+      <c r="H34" s="49" t="s">
         <v>198</v>
       </c>
-      <c r="F34" s="49" t="s">
+      <c r="I34" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="49" t="s">
         <v>199</v>
       </c>
-      <c r="G34" s="49" t="s">
-        <v>200</v>
-      </c>
-      <c r="H34" s="49" t="s">
-        <v>201</v>
-      </c>
-      <c r="I34" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="J34" s="49" t="s">
-        <v>202</v>
-      </c>
       <c r="K34" s="49" t="s">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="L34" s="49">
         <v>2</v>
@@ -3487,55 +3461,54 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="N34" s="37">
-        <v>100</v>
+      <c r="N34" s="62">
+        <v>10</v>
       </c>
       <c r="O34" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P34" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q34" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="R34" s="86" t="s">
-        <v>190</v>
-      </c>
-      <c r="S34" s="55"/>
-    </row>
-    <row r="35" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="P34" s="50">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="Q34" s="63">
+        <f>P34*N34</f>
+        <v>0.48300000000000004</v>
+      </c>
+      <c r="R34" s="62"/>
+      <c r="S34" s="64"/>
+    </row>
+    <row r="35" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A35" s="56"/>
       <c r="B35" s="46">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="68" t="s">
-        <v>205</v>
+      <c r="C35" s="67" t="s">
+        <v>194</v>
       </c>
       <c r="D35" s="37" t="s">
-        <v>33</v>
+        <v>200</v>
       </c>
       <c r="E35" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="F35" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G35" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="H35" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I35" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="37" t="s">
         <v>203</v>
       </c>
-      <c r="F35" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="H35" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="I35" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J35" s="37" t="s">
-        <v>221</v>
-      </c>
       <c r="K35" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="L35" s="37">
         <v>1</v>
@@ -3545,111 +3518,111 @@
         <v>2</v>
       </c>
       <c r="N35" s="49">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O35" s="59" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P35" s="38">
-        <v>0.1336</v>
+        <v>6.4600000000000005E-2</v>
       </c>
       <c r="Q35" s="50">
-        <f t="shared" ref="Q35" si="14">P35*N35</f>
-        <v>0.66799999999999993</v>
+        <f t="shared" ref="Q35" si="15">P35*N35</f>
+        <v>0.64600000000000002</v>
       </c>
       <c r="R35" s="49"/>
       <c r="S35" s="55"/>
     </row>
-    <row r="36" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A36" s="61"/>
-      <c r="B36" s="82">
-        <f t="shared" ref="B36" si="15">ROW(B36) - ROW($B$9)</f>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36" s="56"/>
+      <c r="B36" s="46">
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="C36" s="68" t="s">
-        <v>205</v>
+        <v>17</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>206</v>
+        <v>34</v>
       </c>
       <c r="E36" s="49" t="s">
-        <v>207</v>
+        <v>53</v>
       </c>
       <c r="F36" s="49" t="s">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="G36" s="49" t="s">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="H36" s="49" t="s">
-        <v>209</v>
+        <v>96</v>
       </c>
       <c r="I36" s="49" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J36" s="49" t="s">
-        <v>210</v>
-      </c>
-      <c r="K36" s="49" t="s">
-        <v>137</v>
+        <v>114</v>
+      </c>
+      <c r="K36" s="37" t="s">
+        <v>134</v>
       </c>
       <c r="L36" s="49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M36" s="37">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="N36" s="62">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="N36" s="37">
+        <v>5</v>
       </c>
       <c r="O36" s="60" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P36" s="50">
-        <v>4.8300000000000003E-2</v>
-      </c>
-      <c r="Q36" s="63">
+        <v>0.2079</v>
+      </c>
+      <c r="Q36" s="38">
         <f>P36*N36</f>
-        <v>0.48300000000000004</v>
-      </c>
-      <c r="R36" s="62"/>
-      <c r="S36" s="64"/>
-    </row>
-    <row r="37" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+        <v>1.0395000000000001</v>
+      </c>
+      <c r="R36" s="37"/>
+      <c r="S36" s="55"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="56"/>
       <c r="B37" s="46">
-        <f>ROW(B37) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="C37" s="67" t="s">
-        <v>205</v>
-      </c>
-      <c r="D37" s="37" t="s">
-        <v>211</v>
-      </c>
-      <c r="E37" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="F37" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="G37" s="37" t="s">
-        <v>213</v>
-      </c>
-      <c r="H37" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="I37" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J37" s="37" t="s">
-        <v>214</v>
+      <c r="C37" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="G37" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="H37" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="I37" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J37" s="49" t="s">
+        <v>115</v>
       </c>
       <c r="K37" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L37" s="37">
+        <v>134</v>
+      </c>
+      <c r="L37" s="49">
         <v>1</v>
       </c>
       <c r="M37" s="37">
@@ -3657,17 +3630,17 @@
         <v>2</v>
       </c>
       <c r="N37" s="49">
-        <v>10</v>
-      </c>
-      <c r="O37" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P37" s="38">
-        <v>6.4600000000000005E-2</v>
+        <v>3</v>
+      </c>
+      <c r="O37" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P37" s="50">
+        <v>0.54569999999999996</v>
       </c>
       <c r="Q37" s="50">
         <f t="shared" ref="Q37" si="16">P37*N37</f>
-        <v>0.64600000000000002</v>
+        <v>1.6370999999999998</v>
       </c>
       <c r="R37" s="49"/>
       <c r="S37" s="55"/>
@@ -3678,34 +3651,34 @@
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="C38" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="D38" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="E38" s="49" t="s">
-        <v>54</v>
-      </c>
-      <c r="F38" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="G38" s="49" t="s">
-        <v>85</v>
-      </c>
-      <c r="H38" s="49" t="s">
+      <c r="C38" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="F38" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G38" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="H38" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="I38" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="J38" s="49" t="s">
-        <v>117</v>
+      <c r="I38" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J38" s="37" t="s">
+        <v>116</v>
       </c>
       <c r="K38" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L38" s="49">
+        <v>134</v>
+      </c>
+      <c r="L38" s="37">
         <v>1</v>
       </c>
       <c r="M38" s="37">
@@ -3713,17 +3686,17 @@
         <v>2</v>
       </c>
       <c r="N38" s="37">
-        <v>5</v>
-      </c>
-      <c r="O38" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P38" s="50">
-        <v>0.2079</v>
+        <v>3</v>
+      </c>
+      <c r="O38" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P38" s="38">
+        <v>2.8589000000000002</v>
       </c>
       <c r="Q38" s="38">
         <f>P38*N38</f>
-        <v>1.0395000000000001</v>
+        <v>8.5767000000000007</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="55"/>
@@ -3731,37 +3704,37 @@
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="56"/>
       <c r="B39" s="46">
-        <f t="shared" si="1"/>
+        <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="68" t="s">
+      <c r="C39" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="D39" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="E39" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="F39" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="G39" s="49" t="s">
-        <v>86</v>
-      </c>
-      <c r="H39" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="I39" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="J39" s="49" t="s">
-        <v>118</v>
+      <c r="D39" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="E39" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="F39" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="G39" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="H39" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="I39" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J39" s="37" t="s">
+        <v>209</v>
       </c>
       <c r="K39" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L39" s="49">
+        <v>134</v>
+      </c>
+      <c r="L39" s="37">
         <v>1</v>
       </c>
       <c r="M39" s="37">
@@ -3771,52 +3744,50 @@
       <c r="N39" s="49">
         <v>3</v>
       </c>
-      <c r="O39" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P39" s="50">
-        <v>0.54569999999999996</v>
+      <c r="O39" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P39" s="38">
+        <v>1.2776000000000001</v>
       </c>
       <c r="Q39" s="50">
         <f t="shared" ref="Q39" si="17">P39*N39</f>
-        <v>1.6370999999999998</v>
+        <v>3.8328000000000002</v>
       </c>
       <c r="R39" s="49"/>
       <c r="S39" s="55"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A40" s="56"/>
       <c r="B40" s="46">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="C40" s="67" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>56</v>
+        <v>146</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J40" s="37" t="s">
-        <v>119</v>
-      </c>
-      <c r="K40" s="37" t="s">
-        <v>137</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="K40" s="37"/>
       <c r="L40" s="37">
         <v>1</v>
       </c>
@@ -3825,54 +3796,52 @@
         <v>2</v>
       </c>
       <c r="N40" s="37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O40" s="59" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="P40" s="38">
-        <v>2.8589000000000002</v>
+        <v>3.28</v>
       </c>
       <c r="Q40" s="38">
         <f>P40*N40</f>
-        <v>8.5767000000000007</v>
+        <v>6.56</v>
       </c>
       <c r="R40" s="37"/>
       <c r="S40" s="55"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="56"/>
       <c r="B41" s="46">
-        <f>ROW(B41) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="C41" s="67" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="D41" s="37" t="s">
-        <v>215</v>
+        <v>143</v>
       </c>
       <c r="E41" s="37" t="s">
-        <v>216</v>
+        <v>148</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>217</v>
+        <v>134</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>218</v>
+        <v>134</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>219</v>
+        <v>134</v>
       </c>
       <c r="I41" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J41" s="37" t="s">
-        <v>220</v>
-      </c>
-      <c r="K41" s="37" t="s">
-        <v>137</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="K41" s="37"/>
       <c r="L41" s="37">
         <v>1</v>
       </c>
@@ -3881,234 +3850,124 @@
         <v>2</v>
       </c>
       <c r="N41" s="49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O41" s="59" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="P41" s="38">
-        <v>1.2776000000000001</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="Q41" s="50">
         <f t="shared" ref="Q41" si="18">P41*N41</f>
-        <v>3.8328000000000002</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="R41" s="49"/>
       <c r="S41" s="55"/>
     </row>
-    <row r="42" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="56"/>
-      <c r="B42" s="46">
-        <f t="shared" si="1"/>
-        <v>33</v>
-      </c>
-      <c r="C42" s="67" t="s">
-        <v>147</v>
-      </c>
-      <c r="D42" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="E42" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="F42" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="G42" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="H42" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="I42" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J42" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="K42" s="37"/>
-      <c r="L42" s="37">
-        <v>1</v>
-      </c>
-      <c r="M42" s="37">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="N42" s="37">
-        <v>2</v>
-      </c>
-      <c r="O42" s="59" t="s">
-        <v>150</v>
-      </c>
-      <c r="P42" s="38">
-        <v>3.28</v>
-      </c>
-      <c r="Q42" s="38">
-        <f>P42*N42</f>
-        <v>6.56</v>
-      </c>
-      <c r="R42" s="37"/>
-      <c r="S42" s="55"/>
-    </row>
-    <row r="43" spans="1:19" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="77" t="s">
+        <v>5</v>
+      </c>
+      <c r="O42" s="78"/>
+      <c r="P42" s="78"/>
+      <c r="Q42" s="47">
+        <f>SUM(Q10:Q41)</f>
+        <v>36.5366</v>
+      </c>
+      <c r="R42" s="79"/>
+      <c r="S42" s="80"/>
+    </row>
+    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="56"/>
-      <c r="B43" s="46">
-        <f t="shared" si="1"/>
-        <v>34</v>
-      </c>
-      <c r="C43" s="67" t="s">
-        <v>148</v>
-      </c>
-      <c r="D43" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="E43" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="F43" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="G43" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="H43" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="I43" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J43" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="K43" s="37"/>
-      <c r="L43" s="37">
-        <v>1</v>
-      </c>
-      <c r="M43" s="37">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="N43" s="49">
-        <v>1</v>
-      </c>
-      <c r="O43" s="59" t="s">
-        <v>150</v>
-      </c>
-      <c r="P43" s="38">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="Q43" s="50">
-        <f t="shared" ref="Q43" si="19">P43*N43</f>
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="R43" s="49"/>
-      <c r="S43" s="55"/>
-    </row>
-    <row r="44" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="56"/>
-      <c r="B44" s="40"/>
-      <c r="C44" s="41"/>
-      <c r="D44" s="42"/>
-      <c r="E44" s="43"/>
-      <c r="F44" s="44"/>
-      <c r="G44" s="45"/>
-      <c r="H44" s="44"/>
-      <c r="I44" s="45"/>
-      <c r="J44" s="44"/>
-      <c r="K44" s="45"/>
-      <c r="L44" s="45"/>
-      <c r="M44" s="45"/>
-      <c r="N44" s="80" t="s">
-        <v>5</v>
-      </c>
-      <c r="O44" s="81"/>
-      <c r="P44" s="81"/>
-      <c r="Q44" s="47">
-        <f>SUM(Q10:Q43)</f>
-        <v>37.456600000000002</v>
-      </c>
-      <c r="R44" s="76"/>
-      <c r="S44" s="77"/>
-    </row>
-    <row r="45" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="56"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="36"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="80" t="s">
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="O45" s="81"/>
-      <c r="P45" s="81"/>
-      <c r="Q45" s="48">
-        <f>Q44/2</f>
-        <v>18.728300000000001</v>
-      </c>
-      <c r="R45" s="78"/>
-      <c r="S45" s="79"/>
+      <c r="O43" s="78"/>
+      <c r="P43" s="78"/>
+      <c r="Q43" s="48">
+        <f>Q42/2</f>
+        <v>18.2683</v>
+      </c>
+      <c r="R43" s="81"/>
+      <c r="S43" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S45"/>
-    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S43"/>
+    <mergeCell ref="N43:P43"/>
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O11" r:id="rId1"/>
-    <hyperlink ref="O10" r:id="rId2"/>
-    <hyperlink ref="O12" r:id="rId3"/>
-    <hyperlink ref="O14" r:id="rId4"/>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O13" r:id="rId3"/>
+    <hyperlink ref="O15" r:id="rId4"/>
     <hyperlink ref="O16" r:id="rId5"/>
-    <hyperlink ref="O17" r:id="rId6"/>
+    <hyperlink ref="O18" r:id="rId6"/>
     <hyperlink ref="O19" r:id="rId7"/>
     <hyperlink ref="O20" r:id="rId8"/>
     <hyperlink ref="O21" r:id="rId9"/>
     <hyperlink ref="O22" r:id="rId10"/>
     <hyperlink ref="O23" r:id="rId11"/>
-    <hyperlink ref="O24" r:id="rId12"/>
-    <hyperlink ref="O28" r:id="rId13"/>
-    <hyperlink ref="O30" r:id="rId14"/>
-    <hyperlink ref="O27" r:id="rId15"/>
-    <hyperlink ref="O31" r:id="rId16"/>
-    <hyperlink ref="O38" r:id="rId17"/>
-    <hyperlink ref="O39" r:id="rId18"/>
+    <hyperlink ref="O27" r:id="rId12"/>
+    <hyperlink ref="O29" r:id="rId13"/>
+    <hyperlink ref="O26" r:id="rId14"/>
+    <hyperlink ref="O30" r:id="rId15"/>
+    <hyperlink ref="O36" r:id="rId16"/>
+    <hyperlink ref="O37" r:id="rId17"/>
+    <hyperlink ref="O38" r:id="rId18"/>
     <hyperlink ref="O40" r:id="rId19"/>
-    <hyperlink ref="O42" r:id="rId20"/>
-    <hyperlink ref="O43" r:id="rId21"/>
-    <hyperlink ref="O13" r:id="rId22"/>
-    <hyperlink ref="O15" r:id="rId23"/>
-    <hyperlink ref="O18" r:id="rId24"/>
+    <hyperlink ref="O41" r:id="rId20"/>
+    <hyperlink ref="O12" r:id="rId21"/>
+    <hyperlink ref="O14" r:id="rId22"/>
+    <hyperlink ref="O17" r:id="rId23"/>
+    <hyperlink ref="O24" r:id="rId24"/>
     <hyperlink ref="O25" r:id="rId25"/>
-    <hyperlink ref="O26" r:id="rId26"/>
-    <hyperlink ref="O29" r:id="rId27"/>
+    <hyperlink ref="O28" r:id="rId26"/>
+    <hyperlink ref="O31" r:id="rId27"/>
     <hyperlink ref="O32" r:id="rId28"/>
     <hyperlink ref="O33" r:id="rId29"/>
     <hyperlink ref="O34" r:id="rId30"/>
     <hyperlink ref="O35" r:id="rId31"/>
-    <hyperlink ref="O36" r:id="rId32"/>
-    <hyperlink ref="O37" r:id="rId33"/>
-    <hyperlink ref="O41" r:id="rId34"/>
+    <hyperlink ref="O39" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId35"/>
-  <drawing r:id="rId36"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId33"/>
+  <drawing r:id="rId34"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S45"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -4141,15 +4000,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="73"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="84"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -4160,7 +4019,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="51" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -4185,7 +4044,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="52" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -4199,7 +4058,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="74"/>
+      <c r="S3" s="85"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -4210,7 +4069,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="53" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -4224,7 +4083,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="75"/>
+      <c r="S4" s="86"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -4249,7 +4108,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="75"/>
+      <c r="S5" s="86"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -4270,7 +4129,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="75"/>
+      <c r="S6" s="86"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -4291,7 +4150,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="75"/>
+      <c r="S7" s="86"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -4312,7 +4171,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="75"/>
+      <c r="S8" s="86"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -4329,212 +4188,212 @@
         <v>37</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="N9" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="J9" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="K9" s="30" t="s">
+      <c r="O9" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="L9" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="M9" s="30" t="s">
+      <c r="P9" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="R9" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="N9" s="30" t="s">
+      <c r="S9" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="O9" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="56"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="68" t="s">
+      <c r="C10" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="E10" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="49" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="H10" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="I10" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="J10" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="K10" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="L10" s="49">
-        <v>11</v>
-      </c>
-      <c r="M10" s="49">
-        <f t="shared" ref="M10" si="0">L10*5</f>
-        <v>55</v>
-      </c>
-      <c r="N10" s="49">
+      <c r="D10" s="49" t="s">
+        <v>153</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J10" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="O10" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P10" s="50">
-        <v>3.7000000000000002E-3</v>
-      </c>
-      <c r="Q10" s="50">
-        <f t="shared" ref="Q10" si="1">P10*N10</f>
-        <v>0.37</v>
-      </c>
-      <c r="R10" s="49"/>
-      <c r="S10" s="55"/>
+      <c r="K10" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="L10" s="37">
+        <v>6</v>
+      </c>
+      <c r="M10" s="37">
+        <f>L10*5</f>
+        <v>30</v>
+      </c>
+      <c r="N10" s="37">
+        <v>100</v>
+      </c>
+      <c r="O10" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P10" s="38">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="Q10" s="38">
+        <f>P10*N10</f>
+        <v>0.52</v>
+      </c>
+      <c r="R10" s="37"/>
+      <c r="S10" s="57"/>
     </row>
     <row r="11" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="56"/>
       <c r="B11" s="46">
-        <f>ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="49" t="s">
-        <v>158</v>
+      <c r="D11" s="37" t="s">
+        <v>154</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G11" s="37" t="s">
         <v>71</v>
       </c>
       <c r="H11" s="37" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I11" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J11" s="37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K11" s="37" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L11" s="37">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M11" s="37">
         <f>L11*5</f>
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="N11" s="37">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="O11" s="59" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P11" s="38">
-        <v>5.1999999999999998E-3</v>
+        <v>0.15809999999999999</v>
       </c>
       <c r="Q11" s="38">
         <f>P11*N11</f>
-        <v>0.52</v>
+        <v>2.3714999999999997</v>
       </c>
       <c r="R11" s="37"/>
-      <c r="S11" s="57"/>
-    </row>
-    <row r="12" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="S11" s="55"/>
+    </row>
+    <row r="12" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A12" s="56"/>
       <c r="B12" s="46">
-        <f t="shared" ref="B12:B43" si="2">ROW(B12) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C12" s="67" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>159</v>
+        <v>211</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>40</v>
+        <v>149</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="L12" s="37">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M12" s="37">
         <f>L12*5</f>
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="N12" s="37">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="O12" s="59" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P12" s="38">
-        <v>0.15809999999999999</v>
+        <v>1.8E-3</v>
       </c>
       <c r="Q12" s="38">
         <f>P12*N12</f>
-        <v>2.3714999999999997</v>
+        <v>0.18</v>
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="55"/>
@@ -4542,945 +4401,945 @@
     <row r="13" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="56"/>
       <c r="B13" s="46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="67" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="70" t="s">
-        <v>152</v>
+        <v>22</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>153</v>
+        <v>40</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="G13" s="37" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="H13" s="37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I13" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J13" s="37" t="s">
-        <v>156</v>
+        <v>102</v>
       </c>
       <c r="K13" s="37" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="L13" s="37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M13" s="37">
         <f>L13*5</f>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N13" s="37">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="O13" s="59" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P13" s="38">
-        <v>1.8E-3</v>
+        <v>6.4299999999999996E-2</v>
       </c>
       <c r="Q13" s="38">
         <f>P13*N13</f>
-        <v>0.18</v>
+        <v>0.38579999999999998</v>
       </c>
       <c r="R13" s="37"/>
       <c r="S13" s="55"/>
     </row>
-    <row r="14" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="56"/>
-      <c r="B14" s="46">
-        <f t="shared" si="2"/>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="72">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="70" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="37" t="s">
+      <c r="D14" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="F14" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>159</v>
+      </c>
+      <c r="I14" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J14" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="K14" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L14" s="49">
+        <v>1</v>
+      </c>
+      <c r="M14" s="49">
+        <f t="shared" ref="M14" si="1">L14*5</f>
+        <v>5</v>
+      </c>
+      <c r="N14" s="49">
+        <v>6</v>
+      </c>
+      <c r="O14" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P14" s="50">
+        <v>0.22550000000000001</v>
+      </c>
+      <c r="Q14" s="50">
+        <f t="shared" ref="Q14" si="2">P14*N14</f>
+        <v>1.353</v>
+      </c>
+      <c r="R14" s="49"/>
+      <c r="S14" s="55"/>
+    </row>
+    <row r="15" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A15" s="56"/>
+      <c r="B15" s="46">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="67" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F15" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="K14" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L14" s="37">
+      <c r="G15" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="K15" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L15" s="37">
         <v>1</v>
       </c>
-      <c r="M14" s="37">
-        <f>L14*5</f>
+      <c r="M15" s="37">
+        <f>L15*5</f>
         <v>5</v>
       </c>
-      <c r="N14" s="37">
-        <v>6</v>
-      </c>
-      <c r="O14" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P14" s="38">
-        <v>6.4299999999999996E-2</v>
-      </c>
-      <c r="Q14" s="38">
-        <f>P14*N14</f>
-        <v>0.38579999999999998</v>
-      </c>
-      <c r="R14" s="37"/>
-      <c r="S14" s="55"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="82">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="C15" s="67" t="s">
+      <c r="N15" s="37">
         <v>10</v>
       </c>
-      <c r="D15" s="49" t="s">
-        <v>160</v>
-      </c>
-      <c r="E15" s="49" t="s">
-        <v>161</v>
-      </c>
-      <c r="F15" s="49" t="s">
-        <v>162</v>
-      </c>
-      <c r="G15" s="49" t="s">
-        <v>163</v>
-      </c>
-      <c r="H15" s="49" t="s">
-        <v>164</v>
-      </c>
-      <c r="I15" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="J15" s="49" t="s">
-        <v>165</v>
-      </c>
-      <c r="K15" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="L15" s="49">
-        <v>1</v>
-      </c>
-      <c r="M15" s="49">
-        <f t="shared" ref="M15" si="3">L15*5</f>
-        <v>5</v>
-      </c>
-      <c r="N15" s="49">
-        <v>6</v>
-      </c>
-      <c r="O15" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P15" s="50">
-        <v>0.22550000000000001</v>
-      </c>
-      <c r="Q15" s="50">
-        <f t="shared" ref="Q15" si="4">P15*N15</f>
-        <v>1.353</v>
-      </c>
-      <c r="R15" s="49"/>
+      <c r="O15" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P15" s="38">
+        <v>9.5100000000000004E-2</v>
+      </c>
+      <c r="Q15" s="38">
+        <f>P15*N15</f>
+        <v>0.95100000000000007</v>
+      </c>
+      <c r="R15" s="37"/>
       <c r="S15" s="55"/>
     </row>
-    <row r="16" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="56"/>
       <c r="B16" s="46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="67" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="70" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="37" t="s">
+      <c r="C16" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="69" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="37" t="s">
+      <c r="F16" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="G16" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="H16" s="37" t="s">
+      <c r="G16" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="49" t="s">
+        <v>89</v>
+      </c>
+      <c r="I16" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J16" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L16" s="49">
+        <v>1</v>
+      </c>
+      <c r="M16" s="49">
+        <f t="shared" ref="M16" si="3">L16*5</f>
+        <v>5</v>
+      </c>
+      <c r="N16" s="49">
+        <v>20</v>
+      </c>
+      <c r="O16" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P16" s="50">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="Q16" s="50">
+        <f t="shared" ref="Q16" si="4">P16*N16</f>
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="R16" s="49"/>
+      <c r="S16" s="55"/>
+    </row>
+    <row r="17" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="46">
+        <f>ROW(B17) - ROW($B$9)</f>
+        <v>8</v>
+      </c>
+      <c r="C17" s="67" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="F17" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G17" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="H17" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="I17" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J17" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37">
+        <v>1</v>
+      </c>
+      <c r="M17" s="37">
+        <f>L17*5</f>
+        <v>5</v>
+      </c>
+      <c r="N17" s="37">
+        <v>10</v>
+      </c>
+      <c r="O17" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P17" s="38">
+        <v>0.1636</v>
+      </c>
+      <c r="Q17" s="38">
+        <f>P17*N17</f>
+        <v>1.6359999999999999</v>
+      </c>
+      <c r="R17" s="37"/>
+      <c r="S17" s="55"/>
+    </row>
+    <row r="18" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A18" s="56"/>
+      <c r="B18" s="46">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C18" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="69" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G18" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="K16" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L16" s="37">
+      <c r="I18" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J18" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L18" s="49">
         <v>1</v>
       </c>
-      <c r="M16" s="37">
-        <f>L16*5</f>
+      <c r="M18" s="49">
+        <f t="shared" ref="M18" si="5">L18*5</f>
         <v>5</v>
       </c>
-      <c r="N16" s="37">
-        <v>10</v>
-      </c>
-      <c r="O16" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P16" s="38">
-        <v>9.5100000000000004E-2</v>
-      </c>
-      <c r="Q16" s="38">
-        <f>P16*N16</f>
-        <v>0.95100000000000007</v>
-      </c>
-      <c r="R16" s="37"/>
-      <c r="S16" s="55"/>
-    </row>
-    <row r="17" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="56"/>
-      <c r="B17" s="46">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="C17" s="68" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="49" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="H17" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="I17" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="J17" s="49" t="s">
-        <v>107</v>
-      </c>
-      <c r="K17" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L17" s="49">
-        <v>1</v>
-      </c>
-      <c r="M17" s="49">
-        <f t="shared" ref="M17" si="5">L17*5</f>
-        <v>5</v>
-      </c>
-      <c r="N17" s="49">
+      <c r="N18" s="49">
         <v>20</v>
       </c>
-      <c r="O17" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P17" s="50">
-        <v>3.2199999999999999E-2</v>
-      </c>
-      <c r="Q17" s="50">
-        <f t="shared" ref="Q17" si="6">P17*N17</f>
-        <v>0.64400000000000002</v>
-      </c>
-      <c r="R17" s="49"/>
-      <c r="S17" s="55"/>
-    </row>
-    <row r="18" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="46">
-        <f>ROW(B18) - ROW($B$9)</f>
-        <v>9</v>
-      </c>
-      <c r="C18" s="67" t="s">
-        <v>166</v>
-      </c>
-      <c r="D18" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="F18" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="G18" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="H18" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="I18" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J18" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="K18" s="37"/>
-      <c r="L18" s="37">
-        <v>1</v>
-      </c>
-      <c r="M18" s="37">
-        <f>L18*5</f>
-        <v>5</v>
-      </c>
-      <c r="N18" s="37">
-        <v>10</v>
-      </c>
-      <c r="O18" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P18" s="38">
-        <v>0.1636</v>
-      </c>
-      <c r="Q18" s="38">
-        <f>P18*N18</f>
-        <v>1.6359999999999999</v>
-      </c>
-      <c r="R18" s="37"/>
+      <c r="O18" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P18" s="50">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="Q18" s="50">
+        <f t="shared" ref="Q18" si="6">P18*N18</f>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="R18" s="49"/>
       <c r="S18" s="55"/>
     </row>
-    <row r="19" spans="1:19" s="58" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A19" s="56"/>
       <c r="B19" s="46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="68" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="69" t="s">
-        <v>170</v>
-      </c>
-      <c r="E19" s="49" t="s">
+      <c r="C19" s="67" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="37" t="s">
         <v>44</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="G19" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="H19" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="I19" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="J19" s="49" t="s">
-        <v>108</v>
+        <v>135</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="I19" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J19" s="37" t="s">
+        <v>75</v>
       </c>
       <c r="K19" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L19" s="49">
+        <v>134</v>
+      </c>
+      <c r="L19" s="37">
         <v>1</v>
       </c>
-      <c r="M19" s="49">
-        <f t="shared" ref="M19" si="7">L19*5</f>
+      <c r="M19" s="37">
+        <f>L19*5</f>
         <v>5</v>
       </c>
-      <c r="N19" s="49">
-        <v>20</v>
-      </c>
-      <c r="O19" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P19" s="50">
-        <v>2.2499999999999999E-2</v>
-      </c>
-      <c r="Q19" s="50">
-        <f t="shared" ref="Q19" si="8">P19*N19</f>
-        <v>0.44999999999999996</v>
-      </c>
-      <c r="R19" s="49"/>
+      <c r="N19" s="37">
+        <v>12</v>
+      </c>
+      <c r="O19" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P19" s="38">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="Q19" s="38">
+        <f>P19*N19</f>
+        <v>0.86399999999999988</v>
+      </c>
+      <c r="R19" s="37"/>
       <c r="S19" s="55"/>
     </row>
-    <row r="20" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="56"/>
       <c r="B20" s="46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="67" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="70" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="37" t="s">
+      <c r="C20" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="69" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="49" t="s">
         <v>45</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="G20" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="H20" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="I20" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J20" s="37" t="s">
-        <v>77</v>
+        <v>135</v>
+      </c>
+      <c r="G20" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49" t="s">
+        <v>106</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L20" s="37">
+        <v>134</v>
+      </c>
+      <c r="L20" s="49">
         <v>1</v>
       </c>
-      <c r="M20" s="37">
-        <f>L20*5</f>
+      <c r="M20" s="49">
+        <f t="shared" ref="M20" si="7">L20*5</f>
         <v>5</v>
       </c>
-      <c r="N20" s="37">
-        <v>12</v>
-      </c>
-      <c r="O20" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P20" s="38">
-        <v>7.1999999999999995E-2</v>
-      </c>
-      <c r="Q20" s="38">
-        <f>P20*N20</f>
-        <v>0.86399999999999988</v>
-      </c>
-      <c r="R20" s="37"/>
+      <c r="N20" s="49">
+        <v>10</v>
+      </c>
+      <c r="O20" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P20" s="50">
+        <v>0.20130000000000001</v>
+      </c>
+      <c r="Q20" s="50">
+        <f t="shared" ref="Q20" si="8">P20*N20</f>
+        <v>2.0129999999999999</v>
+      </c>
+      <c r="R20" s="49"/>
       <c r="S20" s="55"/>
     </row>
     <row r="21" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A21" s="56"/>
       <c r="B21" s="46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="68" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="49" t="s">
+      <c r="C21" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="37" t="s">
         <v>46</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="G21" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="H21" s="49" t="s">
-        <v>94</v>
-      </c>
-      <c r="I21" s="49"/>
-      <c r="J21" s="49" t="s">
-        <v>109</v>
+      <c r="G21" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J21" s="37" t="s">
+        <v>107</v>
       </c>
       <c r="K21" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L21" s="49">
+        <v>134</v>
+      </c>
+      <c r="L21" s="37">
         <v>1</v>
       </c>
-      <c r="M21" s="49">
-        <f t="shared" ref="M21" si="9">L21*5</f>
+      <c r="M21" s="37">
+        <f>L21*5</f>
         <v>5</v>
       </c>
-      <c r="N21" s="49">
-        <v>10</v>
-      </c>
-      <c r="O21" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P21" s="50">
-        <v>0.20130000000000001</v>
-      </c>
-      <c r="Q21" s="50">
-        <f t="shared" ref="Q21" si="10">P21*N21</f>
-        <v>2.0129999999999999</v>
-      </c>
-      <c r="R21" s="49"/>
+      <c r="N21" s="37">
+        <v>20</v>
+      </c>
+      <c r="O21" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P21" s="38">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="Q21" s="38">
+        <f>P21*N21</f>
+        <v>0.53</v>
+      </c>
+      <c r="R21" s="37"/>
       <c r="S21" s="55"/>
     </row>
     <row r="22" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A22" s="56"/>
       <c r="B22" s="46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="67" t="s">
+      <c r="C22" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="70" t="s">
-        <v>28</v>
-      </c>
-      <c r="E22" s="37" t="s">
+      <c r="D22" s="69" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="G22" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="H22" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="I22" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J22" s="37" t="s">
-        <v>110</v>
+      <c r="F22" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J22" s="49" t="s">
+        <v>108</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L22" s="37">
+        <v>134</v>
+      </c>
+      <c r="L22" s="49">
         <v>1</v>
       </c>
-      <c r="M22" s="37">
-        <f>L22*5</f>
+      <c r="M22" s="49">
+        <f t="shared" ref="M22" si="9">L22*5</f>
         <v>5</v>
       </c>
-      <c r="N22" s="37">
+      <c r="N22" s="49">
         <v>20</v>
       </c>
-      <c r="O22" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P22" s="38">
-        <v>2.6499999999999999E-2</v>
-      </c>
-      <c r="Q22" s="38">
-        <f>P22*N22</f>
-        <v>0.53</v>
-      </c>
-      <c r="R22" s="37"/>
+      <c r="O22" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P22" s="50">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="Q22" s="50">
+        <f t="shared" ref="Q22" si="10">P22*N22</f>
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="R22" s="49"/>
       <c r="S22" s="55"/>
     </row>
     <row r="23" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A23" s="56"/>
       <c r="B23" s="46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="68" t="s">
+      <c r="C23" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="69" t="s">
-        <v>29</v>
-      </c>
-      <c r="E23" s="49" t="s">
+      <c r="D23" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="G23" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="H23" s="49" t="s">
-        <v>95</v>
-      </c>
-      <c r="I23" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="J23" s="49" t="s">
-        <v>111</v>
+      <c r="F23" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I23" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J23" s="37" t="s">
+        <v>109</v>
       </c>
       <c r="K23" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L23" s="49">
+        <v>134</v>
+      </c>
+      <c r="L23" s="37">
         <v>1</v>
       </c>
-      <c r="M23" s="49">
-        <f t="shared" ref="M23" si="11">L23*5</f>
+      <c r="M23" s="37">
+        <f>L23*5</f>
         <v>5</v>
       </c>
-      <c r="N23" s="49">
+      <c r="N23" s="37">
         <v>20</v>
       </c>
-      <c r="O23" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P23" s="50">
-        <v>2.3300000000000001E-2</v>
-      </c>
-      <c r="Q23" s="50">
-        <f t="shared" ref="Q23" si="12">P23*N23</f>
-        <v>0.46600000000000003</v>
-      </c>
-      <c r="R23" s="49"/>
+      <c r="O23" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P23" s="38">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="Q23" s="38">
+        <f>P23*N23</f>
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="R23" s="37"/>
       <c r="S23" s="55"/>
     </row>
-    <row r="24" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="56"/>
+    <row r="24" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
       <c r="B24" s="46">
-        <f t="shared" si="2"/>
+        <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
       <c r="C24" s="67" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="70" t="s">
-        <v>30</v>
+        <v>166</v>
+      </c>
+      <c r="D24" s="37" t="s">
+        <v>167</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>49</v>
+        <v>168</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>64</v>
+        <v>135</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J24" s="37" t="s">
-        <v>112</v>
+        <v>171</v>
       </c>
       <c r="K24" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="L24" s="37">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M24" s="37">
         <f>L24*5</f>
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="N24" s="37">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="O24" s="59" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P24" s="38">
-        <v>3.2199999999999999E-2</v>
+        <v>7.1300000000000002E-2</v>
       </c>
       <c r="Q24" s="38">
         <f>P24*N24</f>
-        <v>0.64400000000000002</v>
+        <v>2.4955000000000003</v>
       </c>
       <c r="R24" s="37"/>
       <c r="S24" s="55"/>
     </row>
-    <row r="25" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="46">
-        <f>ROW(B25) - ROW($B$9)</f>
+    <row r="25" spans="1:19" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="61"/>
+      <c r="B25" s="73">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="67" t="s">
-        <v>171</v>
-      </c>
-      <c r="D25" s="37" t="s">
+      <c r="C25" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="75" t="s">
         <v>172</v>
       </c>
-      <c r="E25" s="37" t="s">
+      <c r="E25" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="F25" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="G25" s="37" t="s">
+      <c r="F25" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" s="75" t="s">
         <v>174</v>
       </c>
-      <c r="H25" s="37" t="s">
+      <c r="H25" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="I25" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J25" s="37" t="s">
+      <c r="I25" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="75" t="s">
         <v>176</v>
       </c>
-      <c r="K25" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L25" s="37">
-        <v>6</v>
+      <c r="K25" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="L25" s="75">
+        <v>2</v>
       </c>
       <c r="M25" s="37">
         <f>L25*5</f>
-        <v>30</v>
-      </c>
-      <c r="N25" s="37">
-        <v>35</v>
-      </c>
-      <c r="O25" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P25" s="38">
-        <v>7.1300000000000002E-2</v>
-      </c>
-      <c r="Q25" s="38">
+        <v>10</v>
+      </c>
+      <c r="N25" s="62">
+        <v>20</v>
+      </c>
+      <c r="O25" s="66" t="s">
+        <v>136</v>
+      </c>
+      <c r="P25" s="63">
+        <v>3.1E-2</v>
+      </c>
+      <c r="Q25" s="63">
         <f>P25*N25</f>
-        <v>2.4955000000000003</v>
-      </c>
-      <c r="R25" s="37"/>
-      <c r="S25" s="55"/>
-    </row>
-    <row r="26" spans="1:19" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="61"/>
-      <c r="B26" s="83">
-        <f t="shared" si="2"/>
+        <v>0.62</v>
+      </c>
+      <c r="R25" s="62"/>
+      <c r="S25" s="64"/>
+    </row>
+    <row r="26" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="56"/>
+      <c r="B26" s="46">
+        <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="84" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" s="85" t="s">
+      <c r="C26" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="E26" s="85" t="s">
-        <v>178</v>
-      </c>
-      <c r="F26" s="85" t="s">
+      <c r="E26" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="G26" s="85" t="s">
-        <v>179</v>
-      </c>
-      <c r="H26" s="85" t="s">
-        <v>180</v>
-      </c>
-      <c r="I26" s="85" t="s">
-        <v>137</v>
-      </c>
-      <c r="J26" s="85" t="s">
-        <v>181</v>
-      </c>
-      <c r="K26" s="85" t="s">
-        <v>137</v>
-      </c>
-      <c r="L26" s="85">
-        <v>2</v>
+      <c r="G26" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I26" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J26" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="K26" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="L26" s="37">
+        <v>5</v>
       </c>
       <c r="M26" s="37">
         <f>L26*5</f>
-        <v>10</v>
-      </c>
-      <c r="N26" s="62">
-        <v>20</v>
-      </c>
-      <c r="O26" s="66" t="s">
-        <v>139</v>
-      </c>
-      <c r="P26" s="63">
-        <v>3.1E-2</v>
-      </c>
-      <c r="Q26" s="63">
+        <v>25</v>
+      </c>
+      <c r="N26" s="37">
+        <v>100</v>
+      </c>
+      <c r="O26" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P26" s="38">
+        <v>1E-3</v>
+      </c>
+      <c r="Q26" s="38">
         <f>P26*N26</f>
-        <v>0.62</v>
-      </c>
-      <c r="R26" s="62"/>
-      <c r="S26" s="64"/>
+        <v>0.1</v>
+      </c>
+      <c r="R26" s="37"/>
+      <c r="S26" s="55"/>
     </row>
     <row r="27" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="56"/>
       <c r="B27" s="46">
-        <f>ROW(B27) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C27" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="37" t="s">
+      <c r="D27" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="H27" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="I27" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J27" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="K27" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="L27" s="49">
+        <v>1</v>
+      </c>
+      <c r="M27" s="49">
+        <f t="shared" ref="M27" si="11">L27*5</f>
+        <v>5</v>
+      </c>
+      <c r="N27" s="49">
+        <v>100</v>
+      </c>
+      <c r="O27" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P27" s="50">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q27" s="50">
+        <f t="shared" ref="Q27" si="12">P27*N27</f>
+        <v>0.12</v>
+      </c>
+      <c r="R27" s="49"/>
+      <c r="S27" s="55"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="46">
+        <f>ROW(B28) - ROW($B$9)</f>
+        <v>19</v>
+      </c>
+      <c r="C28" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="E28" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="F28" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="H28" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J28" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="K28" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="E27" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="F27" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G27" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="H27" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="I27" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J27" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="K27" s="37" t="s">
-        <v>125</v>
-      </c>
-      <c r="L27" s="37">
-        <v>5</v>
-      </c>
-      <c r="M27" s="37">
-        <f>L27*5</f>
-        <v>25</v>
-      </c>
-      <c r="N27" s="37">
+      <c r="L28" s="37">
+        <v>3</v>
+      </c>
+      <c r="M28" s="37">
+        <f>L28*5</f>
+        <v>15</v>
+      </c>
+      <c r="N28" s="37">
         <v>100</v>
       </c>
-      <c r="O27" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P27" s="38">
-        <v>1E-3</v>
-      </c>
-      <c r="Q27" s="38">
-        <f>P27*N27</f>
-        <v>0.1</v>
-      </c>
-      <c r="R27" s="37"/>
-      <c r="S27" s="55"/>
-    </row>
-    <row r="28" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="56"/>
-      <c r="B28" s="46">
-        <f t="shared" si="2"/>
-        <v>19</v>
-      </c>
-      <c r="C28" s="68" t="s">
+      <c r="O28" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P28" s="38">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q28" s="38">
+        <f>P28*N28</f>
+        <v>0.11</v>
+      </c>
+      <c r="R28" s="37"/>
+      <c r="S28" s="55"/>
+    </row>
+    <row r="29" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="56"/>
+      <c r="B29" s="46">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C29" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" s="49" t="s">
+      <c r="D29" s="70" t="s">
+        <v>178</v>
+      </c>
+      <c r="E29" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="F28" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="G28" s="49" t="s">
-        <v>81</v>
-      </c>
-      <c r="H28" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="I28" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="J28" s="49" t="s">
-        <v>113</v>
-      </c>
-      <c r="K28" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="L28" s="49">
+      <c r="F29" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G29" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="H29" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I29" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J29" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="K29" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="L29" s="37">
         <v>1</v>
-      </c>
-      <c r="M28" s="49">
-        <f t="shared" ref="M28" si="13">L28*5</f>
-        <v>5</v>
-      </c>
-      <c r="N28" s="49">
-        <v>100</v>
-      </c>
-      <c r="O28" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P28" s="50">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q28" s="50">
-        <f t="shared" ref="Q28" si="14">P28*N28</f>
-        <v>0.12</v>
-      </c>
-      <c r="R28" s="49"/>
-      <c r="S28" s="55"/>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="46">
-        <f>ROW(B29) - ROW($B$9)</f>
-        <v>20</v>
-      </c>
-      <c r="C29" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="E29" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="F29" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G29" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="H29" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="I29" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J29" s="37" t="s">
-        <v>187</v>
-      </c>
-      <c r="K29" s="37" t="s">
-        <v>188</v>
-      </c>
-      <c r="L29" s="37">
-        <v>2</v>
       </c>
       <c r="M29" s="37">
         <f>L29*5</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N29" s="37">
         <v>100</v>
       </c>
       <c r="O29" s="59" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P29" s="38">
-        <v>1.1000000000000001E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="Q29" s="38">
         <f>P29*N29</f>
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="R29" s="37"/>
       <c r="S29" s="55"/>
@@ -5488,35 +5347,35 @@
     <row r="30" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="56"/>
       <c r="B30" s="46">
-        <f t="shared" si="2"/>
+        <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
       <c r="C30" s="68" t="s">
         <v>18</v>
       </c>
       <c r="D30" s="70" t="s">
-        <v>183</v>
+        <v>32</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G30" s="37" t="s">
         <v>82</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -5529,77 +5388,78 @@
         <v>100</v>
       </c>
       <c r="O30" s="59" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P30" s="38">
-        <v>1E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q30" s="38">
         <f>P30*N30</f>
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="R30" s="37"/>
       <c r="S30" s="55"/>
     </row>
-    <row r="31" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="56"/>
-      <c r="B31" s="46">
-        <f>ROW(B31) - ROW($B$9)</f>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="72">
+        <f t="shared" ref="B31" si="13">ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
       <c r="C31" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="70" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G31" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="H31" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="I31" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J31" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="K31" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="L31" s="37">
+      <c r="D31" s="49" t="s">
+        <v>183</v>
+      </c>
+      <c r="E31" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="H31" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="I31" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J31" s="49" t="s">
+        <v>112</v>
+      </c>
+      <c r="K31" s="49" t="s">
+        <v>184</v>
+      </c>
+      <c r="L31" s="49">
         <v>1</v>
       </c>
-      <c r="M31" s="37">
-        <f>L31*5</f>
+      <c r="M31" s="49">
+        <f t="shared" ref="M31" si="14">L31*5</f>
         <v>5</v>
       </c>
-      <c r="N31" s="37">
-        <v>100</v>
+      <c r="N31" s="37" t="s">
+        <v>134</v>
       </c>
       <c r="O31" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P31" s="38">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q31" s="38">
-        <f>P31*N31</f>
-        <v>0.13</v>
-      </c>
-      <c r="R31" s="37"/>
+        <v>136</v>
+      </c>
+      <c r="P31" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q31" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="R31" s="76" t="s">
+        <v>184</v>
+      </c>
       <c r="S31" s="55"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="82">
+      <c r="B32" s="72">
         <f t="shared" ref="B32" si="15">ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
@@ -5607,85 +5467,85 @@
         <v>18</v>
       </c>
       <c r="D32" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="E32" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="F32" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="G32" s="49" t="s">
         <v>189</v>
       </c>
-      <c r="E32" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="F32" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="G32" s="49" t="s">
-        <v>83</v>
-      </c>
       <c r="H32" s="49" t="s">
-        <v>88</v>
+        <v>190</v>
       </c>
       <c r="I32" s="49" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J32" s="49" t="s">
-        <v>115</v>
+        <v>191</v>
       </c>
       <c r="K32" s="49" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="L32" s="49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M32" s="49">
         <f t="shared" ref="M32" si="16">L32*5</f>
-        <v>5</v>
-      </c>
-      <c r="N32" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="O32" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P32" s="38" t="s">
-        <v>137</v>
+        <v>10</v>
+      </c>
+      <c r="N32" s="49">
+        <v>20</v>
+      </c>
+      <c r="O32" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P32" s="50" t="s">
+        <v>134</v>
       </c>
       <c r="Q32" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="R32" s="86" t="s">
-        <v>190</v>
+        <v>134</v>
+      </c>
+      <c r="R32" s="76" t="s">
+        <v>184</v>
       </c>
       <c r="S32" s="55"/>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="46">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="67" t="s">
-        <v>18</v>
+      <c r="C33" s="68" t="s">
+        <v>194</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>191</v>
+        <v>33</v>
       </c>
       <c r="E33" s="37" t="s">
         <v>192</v>
       </c>
       <c r="F33" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G33" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="G33" s="37" t="s">
-        <v>194</v>
-      </c>
       <c r="H33" s="37" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="K33" s="37" t="s">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="L33" s="37">
         <v>1</v>
@@ -5695,53 +5555,53 @@
         <v>5</v>
       </c>
       <c r="N33" s="37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O33" s="59" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P33" s="38">
-        <v>5.4999999999999997E-3</v>
+        <v>0.1336</v>
       </c>
       <c r="Q33" s="38">
         <f>P33*N33</f>
-        <v>3.3000000000000002E-2</v>
+        <v>1.3359999999999999</v>
       </c>
       <c r="R33" s="37"/>
       <c r="S33" s="55"/>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="82">
+      <c r="B34" s="72">
         <f t="shared" ref="B34" si="17">ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
       <c r="C34" s="68" t="s">
-        <v>18</v>
+        <v>194</v>
       </c>
       <c r="D34" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="E34" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="F34" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="49" t="s">
         <v>197</v>
       </c>
-      <c r="E34" s="49" t="s">
+      <c r="H34" s="49" t="s">
         <v>198</v>
       </c>
-      <c r="F34" s="49" t="s">
+      <c r="I34" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="49" t="s">
         <v>199</v>
       </c>
-      <c r="G34" s="49" t="s">
-        <v>200</v>
-      </c>
-      <c r="H34" s="49" t="s">
-        <v>201</v>
-      </c>
-      <c r="I34" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="J34" s="49" t="s">
-        <v>202</v>
-      </c>
       <c r="K34" s="49" t="s">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="L34" s="49">
         <v>2</v>
@@ -5754,51 +5614,50 @@
         <v>20</v>
       </c>
       <c r="O34" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P34" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q34" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="R34" s="86" t="s">
-        <v>190</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="P34" s="50">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="Q34" s="50">
+        <f t="shared" ref="Q34" si="19">P34*N34</f>
+        <v>0.96600000000000008</v>
+      </c>
+      <c r="R34" s="49"/>
       <c r="S34" s="55"/>
     </row>
-    <row r="35" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="46">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="68" t="s">
-        <v>205</v>
+      <c r="C35" s="67" t="s">
+        <v>194</v>
       </c>
       <c r="D35" s="37" t="s">
-        <v>33</v>
+        <v>200</v>
       </c>
       <c r="E35" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="F35" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G35" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="H35" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I35" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="37" t="s">
         <v>203</v>
       </c>
-      <c r="F35" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="H35" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="I35" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J35" s="37" t="s">
-        <v>221</v>
-      </c>
       <c r="K35" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="L35" s="37">
         <v>1</v>
@@ -5811,275 +5670,273 @@
         <v>10</v>
       </c>
       <c r="O35" s="59" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P35" s="38">
-        <v>0.1336</v>
+        <v>6.4600000000000005E-2</v>
       </c>
       <c r="Q35" s="38">
         <f>P35*N35</f>
-        <v>1.3359999999999999</v>
+        <v>0.64600000000000002</v>
       </c>
       <c r="R35" s="37"/>
       <c r="S35" s="55"/>
     </row>
-    <row r="36" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="82">
-        <f t="shared" ref="B36" si="19">ROW(B36) - ROW($B$9)</f>
+    <row r="36" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="56"/>
+      <c r="B36" s="46">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C36" s="68" t="s">
-        <v>205</v>
+        <v>17</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>206</v>
+        <v>34</v>
       </c>
       <c r="E36" s="49" t="s">
-        <v>207</v>
+        <v>53</v>
       </c>
       <c r="F36" s="49" t="s">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="G36" s="49" t="s">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="H36" s="49" t="s">
-        <v>209</v>
+        <v>96</v>
       </c>
       <c r="I36" s="49" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J36" s="49" t="s">
-        <v>210</v>
-      </c>
-      <c r="K36" s="49" t="s">
-        <v>137</v>
+        <v>114</v>
+      </c>
+      <c r="K36" s="37" t="s">
+        <v>134</v>
       </c>
       <c r="L36" s="49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M36" s="49">
         <f t="shared" ref="M36" si="20">L36*5</f>
+        <v>5</v>
+      </c>
+      <c r="N36" s="49">
         <v>10</v>
       </c>
-      <c r="N36" s="49">
-        <v>20</v>
-      </c>
       <c r="O36" s="60" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P36" s="50">
-        <v>4.8300000000000003E-2</v>
+        <v>0.2079</v>
       </c>
       <c r="Q36" s="50">
         <f t="shared" ref="Q36" si="21">P36*N36</f>
-        <v>0.96600000000000008</v>
+        <v>2.0790000000000002</v>
       </c>
       <c r="R36" s="49"/>
       <c r="S36" s="55"/>
     </row>
-    <row r="37" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
+    <row r="37" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="56"/>
       <c r="B37" s="46">
-        <f>ROW(B37) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="67" t="s">
-        <v>205</v>
-      </c>
-      <c r="D37" s="37" t="s">
-        <v>211</v>
-      </c>
-      <c r="E37" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="F37" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="G37" s="37" t="s">
-        <v>213</v>
-      </c>
-      <c r="H37" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="I37" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J37" s="37" t="s">
-        <v>214</v>
+      <c r="C37" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="G37" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="H37" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="I37" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J37" s="49" t="s">
+        <v>115</v>
       </c>
       <c r="K37" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L37" s="37">
+        <v>134</v>
+      </c>
+      <c r="L37" s="49">
         <v>1</v>
       </c>
-      <c r="M37" s="37">
-        <f>L37*5</f>
+      <c r="M37" s="49">
+        <f t="shared" ref="M37" si="22">L37*5</f>
         <v>5</v>
       </c>
-      <c r="N37" s="37">
-        <v>10</v>
-      </c>
-      <c r="O37" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="P37" s="38">
-        <v>6.4600000000000005E-2</v>
-      </c>
-      <c r="Q37" s="38">
-        <f>P37*N37</f>
-        <v>0.64600000000000002</v>
-      </c>
-      <c r="R37" s="37"/>
+      <c r="N37" s="49">
+        <v>6</v>
+      </c>
+      <c r="O37" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P37" s="50">
+        <v>0.54569999999999996</v>
+      </c>
+      <c r="Q37" s="50">
+        <f t="shared" ref="Q37" si="23">P37*N37</f>
+        <v>3.2741999999999996</v>
+      </c>
+      <c r="R37" s="49"/>
       <c r="S37" s="55"/>
     </row>
-    <row r="38" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="56"/>
       <c r="B38" s="46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="D38" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="E38" s="49" t="s">
-        <v>54</v>
-      </c>
-      <c r="F38" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="G38" s="49" t="s">
-        <v>85</v>
-      </c>
-      <c r="H38" s="49" t="s">
+      <c r="C38" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="F38" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G38" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="H38" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="I38" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="J38" s="49" t="s">
-        <v>117</v>
+      <c r="I38" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J38" s="37" t="s">
+        <v>116</v>
       </c>
       <c r="K38" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L38" s="49">
+        <v>134</v>
+      </c>
+      <c r="L38" s="37">
         <v>1</v>
       </c>
-      <c r="M38" s="49">
-        <f t="shared" ref="M38" si="22">L38*5</f>
+      <c r="M38" s="37">
+        <f>L38*5</f>
         <v>5</v>
       </c>
-      <c r="N38" s="49">
-        <v>10</v>
-      </c>
-      <c r="O38" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P38" s="50">
-        <v>0.2079</v>
-      </c>
-      <c r="Q38" s="50">
-        <f t="shared" ref="Q38" si="23">P38*N38</f>
-        <v>2.0790000000000002</v>
-      </c>
-      <c r="R38" s="49"/>
-      <c r="S38" s="55"/>
-    </row>
-    <row r="39" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="56"/>
+      <c r="N38" s="37">
+        <v>6</v>
+      </c>
+      <c r="O38" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P38" s="38">
+        <v>2.8589000000000002</v>
+      </c>
+      <c r="Q38" s="38">
+        <f>P38*N38</f>
+        <v>17.153400000000001</v>
+      </c>
+      <c r="R38" s="37"/>
+      <c r="S38" s="39"/>
+    </row>
+    <row r="39" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1"/>
       <c r="B39" s="46">
-        <f t="shared" si="2"/>
+        <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="68" t="s">
+      <c r="C39" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="D39" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="E39" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="F39" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="G39" s="49" t="s">
-        <v>86</v>
-      </c>
-      <c r="H39" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="I39" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="J39" s="49" t="s">
-        <v>118</v>
+      <c r="D39" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="E39" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="F39" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="G39" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="H39" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="I39" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J39" s="37" t="s">
+        <v>209</v>
       </c>
       <c r="K39" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="L39" s="49">
+        <v>134</v>
+      </c>
+      <c r="L39" s="37">
         <v>1</v>
       </c>
-      <c r="M39" s="49">
-        <f t="shared" ref="M39" si="24">L39*5</f>
+      <c r="M39" s="37">
+        <f>L39*5</f>
         <v>5</v>
       </c>
-      <c r="N39" s="49">
+      <c r="N39" s="37">
         <v>6</v>
       </c>
-      <c r="O39" s="60" t="s">
-        <v>139</v>
-      </c>
-      <c r="P39" s="50">
-        <v>0.54569999999999996</v>
-      </c>
-      <c r="Q39" s="50">
-        <f t="shared" ref="Q39" si="25">P39*N39</f>
-        <v>3.2741999999999996</v>
-      </c>
-      <c r="R39" s="49"/>
-      <c r="S39" s="55"/>
-    </row>
-    <row r="40" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O39" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P39" s="38">
+        <v>1.2776000000000001</v>
+      </c>
+      <c r="Q39" s="38">
+        <f>P39*N39</f>
+        <v>7.6656000000000004</v>
+      </c>
+      <c r="R39" s="37"/>
+      <c r="S39" s="39"/>
+    </row>
+    <row r="40" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="56"/>
       <c r="B40" s="46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C40" s="67" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>56</v>
+        <v>146</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J40" s="37" t="s">
-        <v>119</v>
-      </c>
-      <c r="K40" s="37" t="s">
-        <v>137</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="K40" s="37"/>
       <c r="L40" s="37">
         <v>1</v>
       </c>
@@ -6088,54 +5945,52 @@
         <v>5</v>
       </c>
       <c r="N40" s="37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O40" s="59" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="P40" s="38">
-        <v>2.8589000000000002</v>
+        <v>3.28</v>
       </c>
       <c r="Q40" s="38">
         <f>P40*N40</f>
-        <v>17.153400000000001</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="R40" s="37"/>
       <c r="S40" s="39"/>
     </row>
-    <row r="41" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1"/>
+    <row r="41" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="56"/>
       <c r="B41" s="46">
-        <f>ROW(B41) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="C41" s="67" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="D41" s="37" t="s">
-        <v>215</v>
+        <v>143</v>
       </c>
       <c r="E41" s="37" t="s">
-        <v>216</v>
+        <v>148</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>217</v>
+        <v>134</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>218</v>
+        <v>134</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>219</v>
+        <v>134</v>
       </c>
       <c r="I41" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J41" s="37" t="s">
-        <v>220</v>
-      </c>
-      <c r="K41" s="37" t="s">
-        <v>137</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="K41" s="37"/>
       <c r="L41" s="37">
         <v>1</v>
       </c>
@@ -6144,227 +5999,117 @@
         <v>5</v>
       </c>
       <c r="N41" s="37">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O41" s="59" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="P41" s="38">
-        <v>1.2776000000000001</v>
-      </c>
-      <c r="Q41" s="38">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="Q41" s="71">
         <f>P41*N41</f>
-        <v>7.6656000000000004</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="R41" s="37"/>
       <c r="S41" s="39"/>
     </row>
-    <row r="42" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="56"/>
-      <c r="B42" s="46">
-        <f t="shared" si="2"/>
-        <v>33</v>
-      </c>
-      <c r="C42" s="67" t="s">
-        <v>147</v>
-      </c>
-      <c r="D42" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="E42" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="F42" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="G42" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="H42" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="I42" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J42" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="K42" s="37"/>
-      <c r="L42" s="37">
-        <v>1</v>
-      </c>
-      <c r="M42" s="37">
-        <f>L42*5</f>
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="N42" s="37">
-        <v>5</v>
-      </c>
-      <c r="O42" s="59" t="s">
-        <v>150</v>
-      </c>
-      <c r="P42" s="38">
-        <v>3.28</v>
-      </c>
-      <c r="Q42" s="38">
-        <f>P42*N42</f>
-        <v>16.399999999999999</v>
-      </c>
-      <c r="R42" s="37"/>
-      <c r="S42" s="39"/>
-    </row>
-    <row r="43" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="56"/>
-      <c r="B43" s="46">
-        <f t="shared" si="2"/>
-        <v>34</v>
-      </c>
-      <c r="C43" s="67" t="s">
-        <v>148</v>
-      </c>
-      <c r="D43" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="E43" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="F43" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="G43" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="H43" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="I43" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="J43" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="K43" s="37"/>
-      <c r="L43" s="37">
-        <v>1</v>
-      </c>
-      <c r="M43" s="37">
-        <f>L43*5</f>
-        <v>5</v>
-      </c>
-      <c r="N43" s="37">
-        <v>1</v>
-      </c>
-      <c r="O43" s="59" t="s">
-        <v>150</v>
-      </c>
-      <c r="P43" s="38">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="Q43" s="71">
-        <f>P43*N43</f>
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="R43" s="37"/>
-      <c r="S43" s="39"/>
-    </row>
-    <row r="44" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1"/>
-      <c r="B44" s="40"/>
-      <c r="C44" s="41"/>
-      <c r="D44" s="42"/>
-      <c r="E44" s="43"/>
-      <c r="F44" s="44"/>
-      <c r="G44" s="45"/>
-      <c r="H44" s="44"/>
-      <c r="I44" s="45"/>
-      <c r="J44" s="44"/>
-      <c r="K44" s="45"/>
-      <c r="L44" s="45"/>
-      <c r="M44" s="45"/>
-      <c r="N44" s="80" t="s">
-        <v>5</v>
-      </c>
-      <c r="O44" s="81"/>
-      <c r="P44" s="81"/>
-      <c r="Q44" s="47">
-        <f>SUM(Q10:Q43)</f>
-        <v>69.076999999999998</v>
-      </c>
-      <c r="R44" s="76"/>
-      <c r="S44" s="77"/>
-    </row>
-    <row r="45" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="1"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="36"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="80" t="s">
+      <c r="O42" s="78"/>
+      <c r="P42" s="78"/>
+      <c r="Q42" s="47">
+        <f>SUM(Q10:Q41)</f>
+        <v>68.674000000000007</v>
+      </c>
+      <c r="R42" s="79"/>
+      <c r="S42" s="80"/>
+    </row>
+    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="O45" s="81"/>
-      <c r="P45" s="81"/>
-      <c r="Q45" s="48">
-        <f>Q44/5</f>
-        <v>13.8154</v>
-      </c>
-      <c r="R45" s="78"/>
-      <c r="S45" s="79"/>
+      <c r="O43" s="78"/>
+      <c r="P43" s="78"/>
+      <c r="Q43" s="48">
+        <f>Q42/5</f>
+        <v>13.734800000000002</v>
+      </c>
+      <c r="R43" s="81"/>
+      <c r="S43" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S45"/>
-    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S43"/>
+    <mergeCell ref="N43:P43"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O11" r:id="rId1"/>
-    <hyperlink ref="O10" r:id="rId2"/>
-    <hyperlink ref="O12" r:id="rId3"/>
-    <hyperlink ref="O14" r:id="rId4"/>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O13" r:id="rId3"/>
+    <hyperlink ref="O15" r:id="rId4"/>
     <hyperlink ref="O16" r:id="rId5"/>
-    <hyperlink ref="O17" r:id="rId6"/>
+    <hyperlink ref="O18" r:id="rId6"/>
     <hyperlink ref="O19" r:id="rId7"/>
     <hyperlink ref="O20" r:id="rId8"/>
     <hyperlink ref="O21" r:id="rId9"/>
     <hyperlink ref="O22" r:id="rId10"/>
     <hyperlink ref="O23" r:id="rId11"/>
-    <hyperlink ref="O24" r:id="rId12"/>
-    <hyperlink ref="O28" r:id="rId13"/>
-    <hyperlink ref="O30" r:id="rId14"/>
-    <hyperlink ref="O27" r:id="rId15"/>
-    <hyperlink ref="O31" r:id="rId16"/>
-    <hyperlink ref="O38" r:id="rId17"/>
-    <hyperlink ref="O39" r:id="rId18"/>
+    <hyperlink ref="O27" r:id="rId12"/>
+    <hyperlink ref="O29" r:id="rId13"/>
+    <hyperlink ref="O26" r:id="rId14"/>
+    <hyperlink ref="O30" r:id="rId15"/>
+    <hyperlink ref="O36" r:id="rId16"/>
+    <hyperlink ref="O37" r:id="rId17"/>
+    <hyperlink ref="O38" r:id="rId18"/>
     <hyperlink ref="O40" r:id="rId19"/>
-    <hyperlink ref="O42" r:id="rId20"/>
-    <hyperlink ref="O43" r:id="rId21"/>
-    <hyperlink ref="O13" r:id="rId22"/>
-    <hyperlink ref="O15" r:id="rId23"/>
-    <hyperlink ref="O18" r:id="rId24"/>
+    <hyperlink ref="O41" r:id="rId20"/>
+    <hyperlink ref="O12" r:id="rId21"/>
+    <hyperlink ref="O14" r:id="rId22"/>
+    <hyperlink ref="O17" r:id="rId23"/>
+    <hyperlink ref="O24" r:id="rId24"/>
     <hyperlink ref="O25" r:id="rId25"/>
-    <hyperlink ref="O26" r:id="rId26"/>
-    <hyperlink ref="O29" r:id="rId27"/>
+    <hyperlink ref="O28" r:id="rId26"/>
+    <hyperlink ref="O31" r:id="rId27"/>
     <hyperlink ref="O32" r:id="rId28"/>
     <hyperlink ref="O33" r:id="rId29"/>
     <hyperlink ref="O34" r:id="rId30"/>
     <hyperlink ref="O35" r:id="rId31"/>
-    <hyperlink ref="O36" r:id="rId32"/>
-    <hyperlink ref="O37" r:id="rId33"/>
-    <hyperlink ref="O41" r:id="rId34"/>
+    <hyperlink ref="O39" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId35"/>
-  <drawing r:id="rId36"/>
+  <pageSetup orientation="portrait" r:id="rId33"/>
+  <drawing r:id="rId34"/>
 </worksheet>
 </file>
--- a/Design Files/IoT-Button-v1.2/BOM/eSpark-BOM-IoT-Button.xlsx
+++ b/Design Files/IoT-Button-v1.2/BOM/eSpark-BOM-IoT-Button.xlsx
@@ -9,18 +9,21 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="2 Boards" sheetId="1" r:id="rId1"/>
     <sheet name="5 Boards" sheetId="2" r:id="rId2"/>
+    <sheet name="50 Boards" sheetId="3" r:id="rId3"/>
+    <sheet name="500 Boards" sheetId="4" r:id="rId4"/>
+    <sheet name="3000 Boards" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="221">
   <si>
     <t>Component list</t>
   </si>
@@ -659,6 +662,30 @@
   </si>
   <si>
     <t>R3, R5, R12</t>
+  </si>
+  <si>
+    <t>MOQ (50 Boards)</t>
+  </si>
+  <si>
+    <t>Unit Cost (50 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (50 Boards)</t>
+  </si>
+  <si>
+    <t>Quantity (50 Boards)</t>
+  </si>
+  <si>
+    <t>Quantity (500 Boards)</t>
+  </si>
+  <si>
+    <t>MOQ (500 Boards)</t>
+  </si>
+  <si>
+    <t>Unit Cost (500 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (500 Boards)</t>
   </si>
 </sst>
 </file>
@@ -1551,6 +1578,168 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10417</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1724025</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21002625" y="620017"/>
+          <a:ext cx="1714500" cy="1104008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10417</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1724025</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21002625" y="620017"/>
+          <a:ext cx="1714500" cy="1104008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>10417</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21002625" y="620017"/>
+          <a:ext cx="1714500" cy="1104008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6112,4 +6301,6430 @@
   <pageSetup orientation="portrait" r:id="rId33"/>
   <drawing r:id="rId34"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" customWidth="1"/>
+    <col min="5" max="5" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="8" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="84"/>
+    </row>
+    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="85"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="86"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="86"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="86"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="86"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="86"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="56"/>
+      <c r="B10" s="46">
+        <f>ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>153</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="L10" s="37">
+        <v>6</v>
+      </c>
+      <c r="M10" s="37">
+        <f>L10*50</f>
+        <v>300</v>
+      </c>
+      <c r="N10" s="37">
+        <v>400</v>
+      </c>
+      <c r="O10" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P10" s="38">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="Q10" s="38">
+        <f>P10*N10</f>
+        <v>2.1999999999999997</v>
+      </c>
+      <c r="R10" s="37"/>
+      <c r="S10" s="57"/>
+    </row>
+    <row r="11" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="56"/>
+      <c r="B11" s="46">
+        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J11" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="K11" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="L11" s="37">
+        <v>2</v>
+      </c>
+      <c r="M11" s="37">
+        <f t="shared" ref="M11:M41" si="1">L11*50</f>
+        <v>100</v>
+      </c>
+      <c r="N11" s="37">
+        <v>110</v>
+      </c>
+      <c r="O11" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P11" s="38">
+        <v>0.13039999999999999</v>
+      </c>
+      <c r="Q11" s="38">
+        <f>P11*N11</f>
+        <v>14.343999999999999</v>
+      </c>
+      <c r="R11" s="37"/>
+      <c r="S11" s="55"/>
+    </row>
+    <row r="12" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A12" s="56"/>
+      <c r="B12" s="46">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C12" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="L12" s="37">
+        <v>15</v>
+      </c>
+      <c r="M12" s="37">
+        <f t="shared" si="1"/>
+        <v>750</v>
+      </c>
+      <c r="N12" s="37">
+        <v>800</v>
+      </c>
+      <c r="O12" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P12" s="38">
+        <v>1.8E-3</v>
+      </c>
+      <c r="Q12" s="38">
+        <f>P12*N12</f>
+        <v>1.44</v>
+      </c>
+      <c r="R12" s="37"/>
+      <c r="S12" s="55"/>
+    </row>
+    <row r="13" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="56"/>
+      <c r="B13" s="46">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="I13" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J13" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="K13" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L13" s="37">
+        <v>1</v>
+      </c>
+      <c r="M13" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N13" s="37">
+        <v>60</v>
+      </c>
+      <c r="O13" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P13" s="38">
+        <v>6.4299999999999996E-2</v>
+      </c>
+      <c r="Q13" s="38">
+        <f>P13*N13</f>
+        <v>3.8579999999999997</v>
+      </c>
+      <c r="R13" s="37"/>
+      <c r="S13" s="55"/>
+    </row>
+    <row r="14" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="56"/>
+      <c r="B14" s="72">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C14" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="F14" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>159</v>
+      </c>
+      <c r="I14" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J14" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="K14" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L14" s="49">
+        <v>1</v>
+      </c>
+      <c r="M14" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N14" s="49">
+        <v>52</v>
+      </c>
+      <c r="O14" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P14" s="50">
+        <v>0.16969999999999999</v>
+      </c>
+      <c r="Q14" s="50">
+        <f t="shared" ref="Q14" si="2">P14*N14</f>
+        <v>8.8243999999999989</v>
+      </c>
+      <c r="R14" s="49"/>
+      <c r="S14" s="55"/>
+    </row>
+    <row r="15" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A15" s="56"/>
+      <c r="B15" s="46">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="67" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="K15" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L15" s="37">
+        <v>1</v>
+      </c>
+      <c r="M15" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N15" s="37">
+        <v>55</v>
+      </c>
+      <c r="O15" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P15" s="38">
+        <v>7.7600000000000002E-2</v>
+      </c>
+      <c r="Q15" s="38">
+        <f>P15*N15</f>
+        <v>4.2679999999999998</v>
+      </c>
+      <c r="R15" s="37"/>
+      <c r="S15" s="55"/>
+    </row>
+    <row r="16" spans="1:19" s="58" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="56"/>
+      <c r="B16" s="46">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C16" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="69" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="49" t="s">
+        <v>89</v>
+      </c>
+      <c r="I16" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J16" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L16" s="49">
+        <v>1</v>
+      </c>
+      <c r="M16" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N16" s="49">
+        <v>60</v>
+      </c>
+      <c r="O16" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P16" s="50">
+        <v>3.1E-2</v>
+      </c>
+      <c r="Q16" s="50">
+        <f t="shared" ref="Q16" si="3">P16*N16</f>
+        <v>1.8599999999999999</v>
+      </c>
+      <c r="R16" s="49"/>
+      <c r="S16" s="55"/>
+    </row>
+    <row r="17" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A17" s="56"/>
+      <c r="B17" s="46">
+        <f>ROW(B17) - ROW($B$9)</f>
+        <v>8</v>
+      </c>
+      <c r="C17" s="67" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="F17" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G17" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="H17" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="I17" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J17" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37">
+        <v>1</v>
+      </c>
+      <c r="M17" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N17" s="37">
+        <v>55</v>
+      </c>
+      <c r="O17" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P17" s="38">
+        <v>0.13289999999999999</v>
+      </c>
+      <c r="Q17" s="38">
+        <f>P17*N17</f>
+        <v>7.3094999999999999</v>
+      </c>
+      <c r="R17" s="37"/>
+      <c r="S17" s="55"/>
+    </row>
+    <row r="18" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A18" s="56"/>
+      <c r="B18" s="46">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C18" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="69" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G18" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="I18" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J18" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L18" s="49">
+        <v>1</v>
+      </c>
+      <c r="M18" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N18" s="49">
+        <v>60</v>
+      </c>
+      <c r="O18" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P18" s="50">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="Q18" s="50">
+        <f t="shared" ref="Q18" si="4">P18*N18</f>
+        <v>1.3499999999999999</v>
+      </c>
+      <c r="R18" s="49"/>
+      <c r="S18" s="55"/>
+    </row>
+    <row r="19" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A19" s="56"/>
+      <c r="B19" s="46">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C19" s="67" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="I19" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J19" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="K19" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L19" s="37">
+        <v>1</v>
+      </c>
+      <c r="M19" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N19" s="37">
+        <v>60</v>
+      </c>
+      <c r="O19" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P19" s="38">
+        <v>7.0400000000000004E-2</v>
+      </c>
+      <c r="Q19" s="38">
+        <f>P19*N19</f>
+        <v>4.2240000000000002</v>
+      </c>
+      <c r="R19" s="37"/>
+      <c r="S19" s="55"/>
+    </row>
+    <row r="20" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="56"/>
+      <c r="B20" s="46">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C20" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="69" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G20" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L20" s="49">
+        <v>1</v>
+      </c>
+      <c r="M20" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N20" s="49">
+        <v>55</v>
+      </c>
+      <c r="O20" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P20" s="50">
+        <v>0.1646</v>
+      </c>
+      <c r="Q20" s="50">
+        <f t="shared" ref="Q20" si="5">P20*N20</f>
+        <v>9.052999999999999</v>
+      </c>
+      <c r="R20" s="49"/>
+      <c r="S20" s="55"/>
+    </row>
+    <row r="21" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A21" s="56"/>
+      <c r="B21" s="46">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C21" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J21" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="K21" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L21" s="37">
+        <v>1</v>
+      </c>
+      <c r="M21" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N21" s="37">
+        <v>60</v>
+      </c>
+      <c r="O21" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P21" s="38">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="Q21" s="38">
+        <f>P21*N21</f>
+        <v>1.5899999999999999</v>
+      </c>
+      <c r="R21" s="37"/>
+      <c r="S21" s="55"/>
+    </row>
+    <row r="22" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A22" s="56"/>
+      <c r="B22" s="46">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C22" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="69" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J22" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L22" s="49">
+        <v>1</v>
+      </c>
+      <c r="M22" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N22" s="49">
+        <v>60</v>
+      </c>
+      <c r="O22" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P22" s="50">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="Q22" s="50">
+        <f t="shared" ref="Q22" si="6">P22*N22</f>
+        <v>1.3980000000000001</v>
+      </c>
+      <c r="R22" s="49"/>
+      <c r="S22" s="55"/>
+    </row>
+    <row r="23" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A23" s="56"/>
+      <c r="B23" s="46">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C23" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I23" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J23" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="K23" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L23" s="37">
+        <v>1</v>
+      </c>
+      <c r="M23" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N23" s="37">
+        <v>60</v>
+      </c>
+      <c r="O23" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P23" s="38">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="Q23" s="38">
+        <f>P23*N23</f>
+        <v>1.9319999999999999</v>
+      </c>
+      <c r="R23" s="37"/>
+      <c r="S23" s="55"/>
+    </row>
+    <row r="24" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A24" s="56"/>
+      <c r="B24" s="46">
+        <f>ROW(B24) - ROW($B$9)</f>
+        <v>15</v>
+      </c>
+      <c r="C24" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="E24" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="F24" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G24" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="I24" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="K24" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L24" s="37">
+        <v>6</v>
+      </c>
+      <c r="M24" s="37">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="N24" s="37">
+        <v>310</v>
+      </c>
+      <c r="O24" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P24" s="38">
+        <v>5.0200000000000002E-2</v>
+      </c>
+      <c r="Q24" s="38">
+        <f>P24*N24</f>
+        <v>15.562000000000001</v>
+      </c>
+      <c r="R24" s="37"/>
+      <c r="S24" s="55"/>
+    </row>
+    <row r="25" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="56"/>
+      <c r="B25" s="46">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="49" t="s">
+        <v>172</v>
+      </c>
+      <c r="E25" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="F25" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="H25" s="49" t="s">
+        <v>175</v>
+      </c>
+      <c r="I25" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="K25" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L25" s="49">
+        <v>2</v>
+      </c>
+      <c r="M25" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N25" s="37">
+        <v>110</v>
+      </c>
+      <c r="O25" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P25" s="38">
+        <v>2.53E-2</v>
+      </c>
+      <c r="Q25" s="38">
+        <f>P25*N25</f>
+        <v>2.7829999999999999</v>
+      </c>
+      <c r="R25" s="37"/>
+      <c r="S25" s="55"/>
+    </row>
+    <row r="26" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="56"/>
+      <c r="B26" s="46">
+        <f>ROW(B26) - ROW($B$9)</f>
+        <v>17</v>
+      </c>
+      <c r="C26" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G26" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I26" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J26" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="K26" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="L26" s="37">
+        <v>5</v>
+      </c>
+      <c r="M26" s="37">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="N26" s="37">
+        <v>300</v>
+      </c>
+      <c r="O26" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P26" s="38">
+        <v>1E-3</v>
+      </c>
+      <c r="Q26" s="38">
+        <f>P26*N26</f>
+        <v>0.3</v>
+      </c>
+      <c r="R26" s="37"/>
+      <c r="S26" s="55"/>
+    </row>
+    <row r="27" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="56"/>
+      <c r="B27" s="46">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C27" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="H27" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="I27" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J27" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="K27" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="L27" s="49">
+        <v>1</v>
+      </c>
+      <c r="M27" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N27" s="49">
+        <v>100</v>
+      </c>
+      <c r="O27" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P27" s="50">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q27" s="50">
+        <f t="shared" ref="Q27" si="7">P27*N27</f>
+        <v>0.12</v>
+      </c>
+      <c r="R27" s="49"/>
+      <c r="S27" s="55"/>
+    </row>
+    <row r="28" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="56"/>
+      <c r="B28" s="46">
+        <f>ROW(B28) - ROW($B$9)</f>
+        <v>19</v>
+      </c>
+      <c r="C28" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="E28" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="F28" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="H28" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J28" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="K28" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="L28" s="37">
+        <v>3</v>
+      </c>
+      <c r="M28" s="37">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+      <c r="N28" s="37">
+        <v>200</v>
+      </c>
+      <c r="O28" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P28" s="38">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q28" s="38">
+        <f>P28*N28</f>
+        <v>0.22</v>
+      </c>
+      <c r="R28" s="37"/>
+      <c r="S28" s="55"/>
+    </row>
+    <row r="29" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="56"/>
+      <c r="B29" s="46">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C29" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="70" t="s">
+        <v>178</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="F29" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G29" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="H29" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I29" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J29" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="K29" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="L29" s="37">
+        <v>1</v>
+      </c>
+      <c r="M29" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N29" s="37">
+        <v>100</v>
+      </c>
+      <c r="O29" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P29" s="38">
+        <v>1E-3</v>
+      </c>
+      <c r="Q29" s="38">
+        <f>P29*N29</f>
+        <v>0.1</v>
+      </c>
+      <c r="R29" s="37"/>
+      <c r="S29" s="55"/>
+    </row>
+    <row r="30" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="56"/>
+      <c r="B30" s="46">
+        <f>ROW(B30) - ROW($B$9)</f>
+        <v>21</v>
+      </c>
+      <c r="C30" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G30" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="H30" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I30" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J30" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="K30" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="L30" s="37">
+        <v>1</v>
+      </c>
+      <c r="M30" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N30" s="37">
+        <v>100</v>
+      </c>
+      <c r="O30" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P30" s="38">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q30" s="38">
+        <f>P30*N30</f>
+        <v>0.13</v>
+      </c>
+      <c r="R30" s="37"/>
+      <c r="S30" s="55"/>
+    </row>
+    <row r="31" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="56"/>
+      <c r="B31" s="72">
+        <f t="shared" ref="B31:B32" si="8">ROW(B31) - ROW($B$9)</f>
+        <v>22</v>
+      </c>
+      <c r="C31" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="49" t="s">
+        <v>183</v>
+      </c>
+      <c r="E31" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="H31" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="I31" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J31" s="49" t="s">
+        <v>112</v>
+      </c>
+      <c r="K31" s="49" t="s">
+        <v>184</v>
+      </c>
+      <c r="L31" s="49">
+        <v>1</v>
+      </c>
+      <c r="M31" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N31" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="O31" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P31" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q31" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="R31" s="76" t="s">
+        <v>184</v>
+      </c>
+      <c r="S31" s="55"/>
+    </row>
+    <row r="32" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="56"/>
+      <c r="B32" s="72">
+        <f t="shared" si="8"/>
+        <v>23</v>
+      </c>
+      <c r="C32" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="E32" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="F32" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="G32" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="H32" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="I32" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="K32" s="49" t="s">
+        <v>184</v>
+      </c>
+      <c r="L32" s="49">
+        <v>2</v>
+      </c>
+      <c r="M32" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N32" s="49">
+        <v>20</v>
+      </c>
+      <c r="O32" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P32" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q32" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="R32" s="76" t="s">
+        <v>184</v>
+      </c>
+      <c r="S32" s="55"/>
+    </row>
+    <row r="33" spans="1:19" s="58" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="56"/>
+      <c r="B33" s="46">
+        <f>ROW(B33) - ROW($B$9)</f>
+        <v>24</v>
+      </c>
+      <c r="C33" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="D33" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="F33" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G33" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="H33" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J33" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="K33" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L33" s="37">
+        <v>1</v>
+      </c>
+      <c r="M33" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N33" s="37">
+        <v>55</v>
+      </c>
+      <c r="O33" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P33" s="38">
+        <v>0.1336</v>
+      </c>
+      <c r="Q33" s="38">
+        <f>P33*N33</f>
+        <v>7.3479999999999999</v>
+      </c>
+      <c r="R33" s="37"/>
+      <c r="S33" s="55"/>
+    </row>
+    <row r="34" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A34" s="56"/>
+      <c r="B34" s="72">
+        <f t="shared" ref="B34" si="9">ROW(B34) - ROW($B$9)</f>
+        <v>25</v>
+      </c>
+      <c r="C34" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="D34" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="E34" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="F34" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="49" t="s">
+        <v>197</v>
+      </c>
+      <c r="H34" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="I34" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="K34" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L34" s="49">
+        <v>2</v>
+      </c>
+      <c r="M34" s="37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="N34" s="49">
+        <v>110</v>
+      </c>
+      <c r="O34" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P34" s="50">
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="Q34" s="50">
+        <f t="shared" ref="Q34" si="10">P34*N34</f>
+        <v>4.5540000000000003</v>
+      </c>
+      <c r="R34" s="49"/>
+      <c r="S34" s="55"/>
+    </row>
+    <row r="35" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A35" s="56"/>
+      <c r="B35" s="46">
+        <f>ROW(B35) - ROW($B$9)</f>
+        <v>26</v>
+      </c>
+      <c r="C35" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="D35" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="E35" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="F35" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G35" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="H35" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I35" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="K35" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L35" s="37">
+        <v>1</v>
+      </c>
+      <c r="M35" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N35" s="37">
+        <v>60</v>
+      </c>
+      <c r="O35" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P35" s="38">
+        <v>6.4600000000000005E-2</v>
+      </c>
+      <c r="Q35" s="38">
+        <f>P35*N35</f>
+        <v>3.8760000000000003</v>
+      </c>
+      <c r="R35" s="37"/>
+      <c r="S35" s="55"/>
+    </row>
+    <row r="36" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="56"/>
+      <c r="B36" s="46">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C36" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="F36" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="G36" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="H36" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="I36" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J36" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="K36" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L36" s="49">
+        <v>1</v>
+      </c>
+      <c r="M36" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N36" s="49">
+        <v>55</v>
+      </c>
+      <c r="O36" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P36" s="50">
+        <v>0.14460000000000001</v>
+      </c>
+      <c r="Q36" s="50">
+        <f t="shared" ref="Q36:Q37" si="11">P36*N36</f>
+        <v>7.9530000000000003</v>
+      </c>
+      <c r="R36" s="49"/>
+      <c r="S36" s="55"/>
+    </row>
+    <row r="37" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A37" s="56"/>
+      <c r="B37" s="46">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C37" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="G37" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="H37" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="I37" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J37" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="K37" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L37" s="49">
+        <v>1</v>
+      </c>
+      <c r="M37" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N37" s="49">
+        <v>52</v>
+      </c>
+      <c r="O37" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P37" s="50">
+        <v>0.4073</v>
+      </c>
+      <c r="Q37" s="50">
+        <f t="shared" si="11"/>
+        <v>21.179600000000001</v>
+      </c>
+      <c r="R37" s="49"/>
+      <c r="S37" s="55"/>
+    </row>
+    <row r="38" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="56"/>
+      <c r="B38" s="46">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C38" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="F38" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G38" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="H38" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="I38" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J38" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="K38" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L38" s="37">
+        <v>1</v>
+      </c>
+      <c r="M38" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N38" s="37">
+        <v>52</v>
+      </c>
+      <c r="O38" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P38" s="38">
+        <v>2.7953000000000001</v>
+      </c>
+      <c r="Q38" s="38">
+        <f>P38*N38</f>
+        <v>145.35560000000001</v>
+      </c>
+      <c r="R38" s="37"/>
+      <c r="S38" s="39"/>
+    </row>
+    <row r="39" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="56"/>
+      <c r="B39" s="46">
+        <f>ROW(B39) - ROW($B$9)</f>
+        <v>30</v>
+      </c>
+      <c r="C39" s="67" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="E39" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="F39" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="G39" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="H39" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="I39" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J39" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="K39" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L39" s="37">
+        <v>1</v>
+      </c>
+      <c r="M39" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N39" s="37">
+        <v>52</v>
+      </c>
+      <c r="O39" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P39" s="38">
+        <v>0.98480000000000001</v>
+      </c>
+      <c r="Q39" s="38">
+        <f>P39*N39</f>
+        <v>51.209600000000002</v>
+      </c>
+      <c r="R39" s="37"/>
+      <c r="S39" s="39"/>
+    </row>
+    <row r="40" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="56"/>
+      <c r="B40" s="46">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="G40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="I40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="K40" s="37"/>
+      <c r="L40" s="37">
+        <v>1</v>
+      </c>
+      <c r="M40" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N40" s="37">
+        <v>52</v>
+      </c>
+      <c r="O40" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="P40" s="38">
+        <v>3.28</v>
+      </c>
+      <c r="Q40" s="38">
+        <f>P40*N40</f>
+        <v>170.56</v>
+      </c>
+      <c r="R40" s="37"/>
+      <c r="S40" s="39"/>
+    </row>
+    <row r="41" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="56"/>
+      <c r="B41" s="46">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C41" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="F41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="G41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="I41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="K41" s="37"/>
+      <c r="L41" s="37">
+        <v>1</v>
+      </c>
+      <c r="M41" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N41" s="37">
+        <v>1</v>
+      </c>
+      <c r="O41" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="P41" s="38">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="Q41" s="71">
+        <f>P41*N41</f>
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="R41" s="37"/>
+      <c r="S41" s="39"/>
+    </row>
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="77" t="s">
+        <v>5</v>
+      </c>
+      <c r="O42" s="78"/>
+      <c r="P42" s="78"/>
+      <c r="Q42" s="47">
+        <f>SUM(Q10:Q41)</f>
+        <v>497.37170000000009</v>
+      </c>
+      <c r="R42" s="79"/>
+      <c r="S42" s="80"/>
+    </row>
+    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="77" t="s">
+        <v>6</v>
+      </c>
+      <c r="O43" s="78"/>
+      <c r="P43" s="78"/>
+      <c r="Q43" s="48">
+        <f>Q42/50</f>
+        <v>9.9474340000000012</v>
+      </c>
+      <c r="R43" s="81"/>
+      <c r="S43" s="82"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S43"/>
+    <mergeCell ref="N43:P43"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O13" r:id="rId3"/>
+    <hyperlink ref="O15" r:id="rId4"/>
+    <hyperlink ref="O16" r:id="rId5"/>
+    <hyperlink ref="O18" r:id="rId6"/>
+    <hyperlink ref="O19" r:id="rId7"/>
+    <hyperlink ref="O20" r:id="rId8"/>
+    <hyperlink ref="O21" r:id="rId9"/>
+    <hyperlink ref="O22" r:id="rId10"/>
+    <hyperlink ref="O23" r:id="rId11"/>
+    <hyperlink ref="O27" r:id="rId12"/>
+    <hyperlink ref="O29" r:id="rId13"/>
+    <hyperlink ref="O26" r:id="rId14"/>
+    <hyperlink ref="O30" r:id="rId15"/>
+    <hyperlink ref="O36" r:id="rId16"/>
+    <hyperlink ref="O37" r:id="rId17"/>
+    <hyperlink ref="O38" r:id="rId18"/>
+    <hyperlink ref="O40" r:id="rId19"/>
+    <hyperlink ref="O41" r:id="rId20"/>
+    <hyperlink ref="O12" r:id="rId21"/>
+    <hyperlink ref="O14" r:id="rId22"/>
+    <hyperlink ref="O17" r:id="rId23"/>
+    <hyperlink ref="O24" r:id="rId24"/>
+    <hyperlink ref="O25" r:id="rId25"/>
+    <hyperlink ref="O28" r:id="rId26"/>
+    <hyperlink ref="O31" r:id="rId27"/>
+    <hyperlink ref="O32" r:id="rId28"/>
+    <hyperlink ref="O33" r:id="rId29"/>
+    <hyperlink ref="O34" r:id="rId30"/>
+    <hyperlink ref="O35" r:id="rId31"/>
+    <hyperlink ref="O39" r:id="rId32"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId33"/>
+  <drawing r:id="rId34"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" customWidth="1"/>
+    <col min="7" max="8" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="84"/>
+    </row>
+    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="85"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="86"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="86"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="86"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="86"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="86"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="56"/>
+      <c r="B10" s="46">
+        <f>ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>153</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="L10" s="37">
+        <v>6</v>
+      </c>
+      <c r="M10" s="37">
+        <f>L10*500</f>
+        <v>3000</v>
+      </c>
+      <c r="N10" s="37">
+        <v>3100</v>
+      </c>
+      <c r="O10" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P10" s="38">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="Q10" s="38">
+        <f>P10*N10</f>
+        <v>13.64</v>
+      </c>
+      <c r="R10" s="37"/>
+      <c r="S10" s="57"/>
+    </row>
+    <row r="11" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="56"/>
+      <c r="B11" s="46">
+        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J11" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="K11" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="L11" s="37">
+        <v>2</v>
+      </c>
+      <c r="M11" s="37">
+        <f t="shared" ref="M11:M41" si="1">L11*500</f>
+        <v>1000</v>
+      </c>
+      <c r="N11" s="37">
+        <v>1050</v>
+      </c>
+      <c r="O11" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P11" s="38">
+        <v>9.8500000000000004E-2</v>
+      </c>
+      <c r="Q11" s="38">
+        <f>P11*N11</f>
+        <v>103.42500000000001</v>
+      </c>
+      <c r="R11" s="37"/>
+      <c r="S11" s="55"/>
+    </row>
+    <row r="12" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A12" s="56"/>
+      <c r="B12" s="46">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C12" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="L12" s="37">
+        <v>15</v>
+      </c>
+      <c r="M12" s="37">
+        <f t="shared" si="1"/>
+        <v>7500</v>
+      </c>
+      <c r="N12" s="37">
+        <v>7600</v>
+      </c>
+      <c r="O12" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P12" s="38">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q12" s="38">
+        <f>P12*N12</f>
+        <v>9.879999999999999</v>
+      </c>
+      <c r="R12" s="37"/>
+      <c r="S12" s="55"/>
+    </row>
+    <row r="13" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="56"/>
+      <c r="B13" s="46">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="I13" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J13" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="K13" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L13" s="37">
+        <v>1</v>
+      </c>
+      <c r="M13" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N13" s="37">
+        <v>6</v>
+      </c>
+      <c r="O13" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P13" s="38">
+        <v>6.4299999999999996E-2</v>
+      </c>
+      <c r="Q13" s="38">
+        <f>P13*N13</f>
+        <v>0.38579999999999998</v>
+      </c>
+      <c r="R13" s="37"/>
+      <c r="S13" s="55"/>
+    </row>
+    <row r="14" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="56"/>
+      <c r="B14" s="72">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C14" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="F14" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>159</v>
+      </c>
+      <c r="I14" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J14" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="K14" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L14" s="49">
+        <v>1</v>
+      </c>
+      <c r="M14" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N14" s="49">
+        <v>6</v>
+      </c>
+      <c r="O14" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P14" s="50">
+        <v>0.22550000000000001</v>
+      </c>
+      <c r="Q14" s="50">
+        <f t="shared" ref="Q14" si="2">P14*N14</f>
+        <v>1.353</v>
+      </c>
+      <c r="R14" s="49"/>
+      <c r="S14" s="55"/>
+    </row>
+    <row r="15" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A15" s="56"/>
+      <c r="B15" s="46">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="67" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="K15" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L15" s="37">
+        <v>1</v>
+      </c>
+      <c r="M15" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N15" s="37">
+        <v>10</v>
+      </c>
+      <c r="O15" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P15" s="38">
+        <v>9.5100000000000004E-2</v>
+      </c>
+      <c r="Q15" s="38">
+        <f>P15*N15</f>
+        <v>0.95100000000000007</v>
+      </c>
+      <c r="R15" s="37"/>
+      <c r="S15" s="55"/>
+    </row>
+    <row r="16" spans="1:19" s="58" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="56"/>
+      <c r="B16" s="46">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C16" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="69" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="49" t="s">
+        <v>89</v>
+      </c>
+      <c r="I16" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J16" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L16" s="49">
+        <v>1</v>
+      </c>
+      <c r="M16" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N16" s="49">
+        <v>20</v>
+      </c>
+      <c r="O16" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P16" s="50">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="Q16" s="50">
+        <f t="shared" ref="Q16" si="3">P16*N16</f>
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="R16" s="49"/>
+      <c r="S16" s="55"/>
+    </row>
+    <row r="17" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A17" s="56"/>
+      <c r="B17" s="46">
+        <f>ROW(B17) - ROW($B$9)</f>
+        <v>8</v>
+      </c>
+      <c r="C17" s="67" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="F17" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G17" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="H17" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="I17" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J17" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37">
+        <v>1</v>
+      </c>
+      <c r="M17" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N17" s="37">
+        <v>10</v>
+      </c>
+      <c r="O17" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P17" s="38">
+        <v>0.1636</v>
+      </c>
+      <c r="Q17" s="38">
+        <f>P17*N17</f>
+        <v>1.6359999999999999</v>
+      </c>
+      <c r="R17" s="37"/>
+      <c r="S17" s="55"/>
+    </row>
+    <row r="18" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A18" s="56"/>
+      <c r="B18" s="46">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C18" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="69" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G18" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="I18" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J18" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L18" s="49">
+        <v>1</v>
+      </c>
+      <c r="M18" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N18" s="49">
+        <v>20</v>
+      </c>
+      <c r="O18" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P18" s="50">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="Q18" s="50">
+        <f t="shared" ref="Q18" si="4">P18*N18</f>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="R18" s="49"/>
+      <c r="S18" s="55"/>
+    </row>
+    <row r="19" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A19" s="56"/>
+      <c r="B19" s="46">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C19" s="67" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="I19" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J19" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="K19" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L19" s="37">
+        <v>1</v>
+      </c>
+      <c r="M19" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N19" s="37">
+        <v>12</v>
+      </c>
+      <c r="O19" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P19" s="38">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="Q19" s="38">
+        <f>P19*N19</f>
+        <v>0.86399999999999988</v>
+      </c>
+      <c r="R19" s="37"/>
+      <c r="S19" s="55"/>
+    </row>
+    <row r="20" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="56"/>
+      <c r="B20" s="46">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C20" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="69" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G20" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L20" s="49">
+        <v>1</v>
+      </c>
+      <c r="M20" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N20" s="49">
+        <v>10</v>
+      </c>
+      <c r="O20" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P20" s="50">
+        <v>0.20130000000000001</v>
+      </c>
+      <c r="Q20" s="50">
+        <f t="shared" ref="Q20" si="5">P20*N20</f>
+        <v>2.0129999999999999</v>
+      </c>
+      <c r="R20" s="49"/>
+      <c r="S20" s="55"/>
+    </row>
+    <row r="21" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A21" s="56"/>
+      <c r="B21" s="46">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C21" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J21" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="K21" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L21" s="37">
+        <v>1</v>
+      </c>
+      <c r="M21" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N21" s="37">
+        <v>20</v>
+      </c>
+      <c r="O21" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P21" s="38">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="Q21" s="38">
+        <f>P21*N21</f>
+        <v>0.53</v>
+      </c>
+      <c r="R21" s="37"/>
+      <c r="S21" s="55"/>
+    </row>
+    <row r="22" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A22" s="56"/>
+      <c r="B22" s="46">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C22" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="69" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J22" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L22" s="49">
+        <v>1</v>
+      </c>
+      <c r="M22" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N22" s="49">
+        <v>20</v>
+      </c>
+      <c r="O22" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P22" s="50">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="Q22" s="50">
+        <f t="shared" ref="Q22" si="6">P22*N22</f>
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="R22" s="49"/>
+      <c r="S22" s="55"/>
+    </row>
+    <row r="23" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A23" s="56"/>
+      <c r="B23" s="46">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C23" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I23" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J23" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="K23" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L23" s="37">
+        <v>1</v>
+      </c>
+      <c r="M23" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N23" s="37">
+        <v>20</v>
+      </c>
+      <c r="O23" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P23" s="38">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="Q23" s="38">
+        <f>P23*N23</f>
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="R23" s="37"/>
+      <c r="S23" s="55"/>
+    </row>
+    <row r="24" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A24" s="56"/>
+      <c r="B24" s="46">
+        <f>ROW(B24) - ROW($B$9)</f>
+        <v>15</v>
+      </c>
+      <c r="C24" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="E24" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="F24" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G24" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="I24" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="K24" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L24" s="37">
+        <v>6</v>
+      </c>
+      <c r="M24" s="37">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="N24" s="37">
+        <v>35</v>
+      </c>
+      <c r="O24" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P24" s="38">
+        <v>7.1300000000000002E-2</v>
+      </c>
+      <c r="Q24" s="38">
+        <f>P24*N24</f>
+        <v>2.4955000000000003</v>
+      </c>
+      <c r="R24" s="37"/>
+      <c r="S24" s="55"/>
+    </row>
+    <row r="25" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="56"/>
+      <c r="B25" s="46">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="49" t="s">
+        <v>172</v>
+      </c>
+      <c r="E25" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="F25" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="H25" s="49" t="s">
+        <v>175</v>
+      </c>
+      <c r="I25" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="K25" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L25" s="49">
+        <v>2</v>
+      </c>
+      <c r="M25" s="37">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N25" s="37">
+        <v>20</v>
+      </c>
+      <c r="O25" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P25" s="38">
+        <v>3.1E-2</v>
+      </c>
+      <c r="Q25" s="38">
+        <f>P25*N25</f>
+        <v>0.62</v>
+      </c>
+      <c r="R25" s="37"/>
+      <c r="S25" s="55"/>
+    </row>
+    <row r="26" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="56"/>
+      <c r="B26" s="46">
+        <f>ROW(B26) - ROW($B$9)</f>
+        <v>17</v>
+      </c>
+      <c r="C26" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G26" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I26" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J26" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="K26" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="L26" s="37">
+        <v>5</v>
+      </c>
+      <c r="M26" s="37">
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="N26" s="37">
+        <v>100</v>
+      </c>
+      <c r="O26" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P26" s="38">
+        <v>1E-3</v>
+      </c>
+      <c r="Q26" s="38">
+        <f>P26*N26</f>
+        <v>0.1</v>
+      </c>
+      <c r="R26" s="37"/>
+      <c r="S26" s="55"/>
+    </row>
+    <row r="27" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="56"/>
+      <c r="B27" s="46">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C27" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="H27" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="I27" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J27" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="K27" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="L27" s="49">
+        <v>1</v>
+      </c>
+      <c r="M27" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N27" s="49">
+        <v>100</v>
+      </c>
+      <c r="O27" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P27" s="50">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q27" s="50">
+        <f t="shared" ref="Q27" si="7">P27*N27</f>
+        <v>0.12</v>
+      </c>
+      <c r="R27" s="49"/>
+      <c r="S27" s="55"/>
+    </row>
+    <row r="28" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="56"/>
+      <c r="B28" s="46">
+        <f>ROW(B28) - ROW($B$9)</f>
+        <v>19</v>
+      </c>
+      <c r="C28" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="E28" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="F28" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="H28" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J28" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="K28" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="L28" s="37">
+        <v>3</v>
+      </c>
+      <c r="M28" s="37">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="N28" s="37">
+        <v>100</v>
+      </c>
+      <c r="O28" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P28" s="38">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q28" s="38">
+        <f>P28*N28</f>
+        <v>0.11</v>
+      </c>
+      <c r="R28" s="37"/>
+      <c r="S28" s="55"/>
+    </row>
+    <row r="29" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="56"/>
+      <c r="B29" s="46">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C29" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="70" t="s">
+        <v>178</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="F29" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G29" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="H29" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I29" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J29" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="K29" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="L29" s="37">
+        <v>1</v>
+      </c>
+      <c r="M29" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N29" s="37">
+        <v>100</v>
+      </c>
+      <c r="O29" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P29" s="38">
+        <v>1E-3</v>
+      </c>
+      <c r="Q29" s="38">
+        <f>P29*N29</f>
+        <v>0.1</v>
+      </c>
+      <c r="R29" s="37"/>
+      <c r="S29" s="55"/>
+    </row>
+    <row r="30" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="56"/>
+      <c r="B30" s="46">
+        <f>ROW(B30) - ROW($B$9)</f>
+        <v>21</v>
+      </c>
+      <c r="C30" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G30" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="H30" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I30" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J30" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="K30" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="L30" s="37">
+        <v>1</v>
+      </c>
+      <c r="M30" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N30" s="37">
+        <v>100</v>
+      </c>
+      <c r="O30" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P30" s="38">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q30" s="38">
+        <f>P30*N30</f>
+        <v>0.13</v>
+      </c>
+      <c r="R30" s="37"/>
+      <c r="S30" s="55"/>
+    </row>
+    <row r="31" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="56"/>
+      <c r="B31" s="72">
+        <f t="shared" ref="B31:B32" si="8">ROW(B31) - ROW($B$9)</f>
+        <v>22</v>
+      </c>
+      <c r="C31" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="49" t="s">
+        <v>183</v>
+      </c>
+      <c r="E31" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="H31" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="I31" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J31" s="49" t="s">
+        <v>112</v>
+      </c>
+      <c r="K31" s="49" t="s">
+        <v>184</v>
+      </c>
+      <c r="L31" s="49">
+        <v>1</v>
+      </c>
+      <c r="M31" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N31" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="O31" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P31" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q31" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="R31" s="76" t="s">
+        <v>184</v>
+      </c>
+      <c r="S31" s="55"/>
+    </row>
+    <row r="32" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="56"/>
+      <c r="B32" s="72">
+        <f t="shared" si="8"/>
+        <v>23</v>
+      </c>
+      <c r="C32" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="E32" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="F32" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="G32" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="H32" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="I32" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="K32" s="49" t="s">
+        <v>184</v>
+      </c>
+      <c r="L32" s="49">
+        <v>2</v>
+      </c>
+      <c r="M32" s="37">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N32" s="49">
+        <v>20</v>
+      </c>
+      <c r="O32" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P32" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q32" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="R32" s="76" t="s">
+        <v>184</v>
+      </c>
+      <c r="S32" s="55"/>
+    </row>
+    <row r="33" spans="1:19" s="58" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A33" s="56"/>
+      <c r="B33" s="46">
+        <f>ROW(B33) - ROW($B$9)</f>
+        <v>24</v>
+      </c>
+      <c r="C33" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="D33" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="F33" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G33" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="H33" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J33" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="K33" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L33" s="37">
+        <v>1</v>
+      </c>
+      <c r="M33" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N33" s="37">
+        <v>10</v>
+      </c>
+      <c r="O33" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P33" s="38">
+        <v>0.1336</v>
+      </c>
+      <c r="Q33" s="38">
+        <f>P33*N33</f>
+        <v>1.3359999999999999</v>
+      </c>
+      <c r="R33" s="37"/>
+      <c r="S33" s="55"/>
+    </row>
+    <row r="34" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A34" s="56"/>
+      <c r="B34" s="72">
+        <f t="shared" ref="B34" si="9">ROW(B34) - ROW($B$9)</f>
+        <v>25</v>
+      </c>
+      <c r="C34" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="D34" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="E34" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="F34" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="49" t="s">
+        <v>197</v>
+      </c>
+      <c r="H34" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="I34" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="K34" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L34" s="49">
+        <v>2</v>
+      </c>
+      <c r="M34" s="37">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N34" s="49">
+        <v>20</v>
+      </c>
+      <c r="O34" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P34" s="50">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="Q34" s="50">
+        <f t="shared" ref="Q34" si="10">P34*N34</f>
+        <v>0.96600000000000008</v>
+      </c>
+      <c r="R34" s="49"/>
+      <c r="S34" s="55"/>
+    </row>
+    <row r="35" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A35" s="56"/>
+      <c r="B35" s="46">
+        <f>ROW(B35) - ROW($B$9)</f>
+        <v>26</v>
+      </c>
+      <c r="C35" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="D35" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="E35" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="F35" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G35" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="H35" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I35" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="K35" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L35" s="37">
+        <v>1</v>
+      </c>
+      <c r="M35" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N35" s="37">
+        <v>10</v>
+      </c>
+      <c r="O35" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P35" s="38">
+        <v>6.4600000000000005E-2</v>
+      </c>
+      <c r="Q35" s="38">
+        <f>P35*N35</f>
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="R35" s="37"/>
+      <c r="S35" s="55"/>
+    </row>
+    <row r="36" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="56"/>
+      <c r="B36" s="46">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C36" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="F36" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="G36" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="H36" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="I36" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J36" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="K36" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L36" s="49">
+        <v>1</v>
+      </c>
+      <c r="M36" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N36" s="49">
+        <v>10</v>
+      </c>
+      <c r="O36" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P36" s="50">
+        <v>0.2079</v>
+      </c>
+      <c r="Q36" s="50">
+        <f t="shared" ref="Q36:Q37" si="11">P36*N36</f>
+        <v>2.0790000000000002</v>
+      </c>
+      <c r="R36" s="49"/>
+      <c r="S36" s="55"/>
+    </row>
+    <row r="37" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="56"/>
+      <c r="B37" s="46">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C37" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="G37" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="H37" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="I37" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J37" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="K37" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L37" s="49">
+        <v>1</v>
+      </c>
+      <c r="M37" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N37" s="49">
+        <v>6</v>
+      </c>
+      <c r="O37" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P37" s="50">
+        <v>0.54569999999999996</v>
+      </c>
+      <c r="Q37" s="50">
+        <f t="shared" si="11"/>
+        <v>3.2741999999999996</v>
+      </c>
+      <c r="R37" s="49"/>
+      <c r="S37" s="55"/>
+    </row>
+    <row r="38" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="56"/>
+      <c r="B38" s="46">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C38" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="F38" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G38" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="H38" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="I38" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J38" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="K38" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L38" s="37">
+        <v>1</v>
+      </c>
+      <c r="M38" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N38" s="37">
+        <v>6</v>
+      </c>
+      <c r="O38" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P38" s="38">
+        <v>2.8589000000000002</v>
+      </c>
+      <c r="Q38" s="38">
+        <f>P38*N38</f>
+        <v>17.153400000000001</v>
+      </c>
+      <c r="R38" s="37"/>
+      <c r="S38" s="39"/>
+    </row>
+    <row r="39" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="56"/>
+      <c r="B39" s="46">
+        <f>ROW(B39) - ROW($B$9)</f>
+        <v>30</v>
+      </c>
+      <c r="C39" s="67" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="E39" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="F39" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="G39" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="H39" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="I39" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J39" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="K39" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L39" s="37">
+        <v>1</v>
+      </c>
+      <c r="M39" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N39" s="37">
+        <v>6</v>
+      </c>
+      <c r="O39" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P39" s="38">
+        <v>1.2776000000000001</v>
+      </c>
+      <c r="Q39" s="38">
+        <f>P39*N39</f>
+        <v>7.6656000000000004</v>
+      </c>
+      <c r="R39" s="37"/>
+      <c r="S39" s="39"/>
+    </row>
+    <row r="40" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="56"/>
+      <c r="B40" s="46">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="G40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="I40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="K40" s="37"/>
+      <c r="L40" s="37">
+        <v>1</v>
+      </c>
+      <c r="M40" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N40" s="37">
+        <v>5</v>
+      </c>
+      <c r="O40" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="P40" s="38">
+        <v>3.28</v>
+      </c>
+      <c r="Q40" s="38">
+        <f>P40*N40</f>
+        <v>16.399999999999999</v>
+      </c>
+      <c r="R40" s="37"/>
+      <c r="S40" s="39"/>
+    </row>
+    <row r="41" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="56"/>
+      <c r="B41" s="46">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C41" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="F41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="G41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="I41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="K41" s="37"/>
+      <c r="L41" s="37">
+        <v>1</v>
+      </c>
+      <c r="M41" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N41" s="37">
+        <v>1</v>
+      </c>
+      <c r="O41" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="P41" s="38">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="Q41" s="71">
+        <f>P41*N41</f>
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="R41" s="37"/>
+      <c r="S41" s="39"/>
+    </row>
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="77" t="s">
+        <v>5</v>
+      </c>
+      <c r="O42" s="78"/>
+      <c r="P42" s="78"/>
+      <c r="Q42" s="47">
+        <f>SUM(Q10:Q41)</f>
+        <v>192.54750000000007</v>
+      </c>
+      <c r="R42" s="79"/>
+      <c r="S42" s="80"/>
+    </row>
+    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="77" t="s">
+        <v>6</v>
+      </c>
+      <c r="O43" s="78"/>
+      <c r="P43" s="78"/>
+      <c r="Q43" s="48">
+        <f>Q42/500</f>
+        <v>0.38509500000000013</v>
+      </c>
+      <c r="R43" s="81"/>
+      <c r="S43" s="82"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S43"/>
+    <mergeCell ref="N43:P43"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O13" r:id="rId3"/>
+    <hyperlink ref="O15" r:id="rId4"/>
+    <hyperlink ref="O16" r:id="rId5"/>
+    <hyperlink ref="O18" r:id="rId6"/>
+    <hyperlink ref="O19" r:id="rId7"/>
+    <hyperlink ref="O20" r:id="rId8"/>
+    <hyperlink ref="O21" r:id="rId9"/>
+    <hyperlink ref="O22" r:id="rId10"/>
+    <hyperlink ref="O23" r:id="rId11"/>
+    <hyperlink ref="O27" r:id="rId12"/>
+    <hyperlink ref="O29" r:id="rId13"/>
+    <hyperlink ref="O26" r:id="rId14"/>
+    <hyperlink ref="O30" r:id="rId15"/>
+    <hyperlink ref="O36" r:id="rId16"/>
+    <hyperlink ref="O37" r:id="rId17"/>
+    <hyperlink ref="O38" r:id="rId18"/>
+    <hyperlink ref="O40" r:id="rId19"/>
+    <hyperlink ref="O41" r:id="rId20"/>
+    <hyperlink ref="O12" r:id="rId21"/>
+    <hyperlink ref="O14" r:id="rId22"/>
+    <hyperlink ref="O17" r:id="rId23"/>
+    <hyperlink ref="O24" r:id="rId24"/>
+    <hyperlink ref="O25" r:id="rId25"/>
+    <hyperlink ref="O28" r:id="rId26"/>
+    <hyperlink ref="O31" r:id="rId27"/>
+    <hyperlink ref="O32" r:id="rId28"/>
+    <hyperlink ref="O33" r:id="rId29"/>
+    <hyperlink ref="O34" r:id="rId30"/>
+    <hyperlink ref="O35" r:id="rId31"/>
+    <hyperlink ref="O39" r:id="rId32"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId33"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="84"/>
+    </row>
+    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2" s="12"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="85"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="13"/>
+      <c r="F4" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="86"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="86"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="86"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="86"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="86"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A10" s="56"/>
+      <c r="B10" s="46">
+        <f>ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>153</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="L10" s="37">
+        <v>6</v>
+      </c>
+      <c r="M10" s="37">
+        <f>L10*5</f>
+        <v>30</v>
+      </c>
+      <c r="N10" s="37">
+        <v>100</v>
+      </c>
+      <c r="O10" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P10" s="38">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="Q10" s="38">
+        <f>P10*N10</f>
+        <v>0.52</v>
+      </c>
+      <c r="R10" s="37"/>
+      <c r="S10" s="57"/>
+    </row>
+    <row r="11" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A11" s="56"/>
+      <c r="B11" s="46">
+        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J11" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="K11" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="L11" s="37">
+        <v>2</v>
+      </c>
+      <c r="M11" s="37">
+        <f>L11*5</f>
+        <v>10</v>
+      </c>
+      <c r="N11" s="37">
+        <v>15</v>
+      </c>
+      <c r="O11" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P11" s="38">
+        <v>0.15809999999999999</v>
+      </c>
+      <c r="Q11" s="38">
+        <f>P11*N11</f>
+        <v>2.3714999999999997</v>
+      </c>
+      <c r="R11" s="37"/>
+      <c r="S11" s="55"/>
+    </row>
+    <row r="12" spans="1:19" ht="84" x14ac:dyDescent="0.25">
+      <c r="A12" s="56"/>
+      <c r="B12" s="46">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C12" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="E12" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="L12" s="37">
+        <v>15</v>
+      </c>
+      <c r="M12" s="37">
+        <f>L12*5</f>
+        <v>75</v>
+      </c>
+      <c r="N12" s="37">
+        <v>100</v>
+      </c>
+      <c r="O12" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P12" s="38">
+        <v>1.8E-3</v>
+      </c>
+      <c r="Q12" s="38">
+        <f>P12*N12</f>
+        <v>0.18</v>
+      </c>
+      <c r="R12" s="37"/>
+      <c r="S12" s="55"/>
+    </row>
+    <row r="13" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A13" s="56"/>
+      <c r="B13" s="46">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="I13" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J13" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="K13" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L13" s="37">
+        <v>1</v>
+      </c>
+      <c r="M13" s="37">
+        <f>L13*5</f>
+        <v>5</v>
+      </c>
+      <c r="N13" s="37">
+        <v>6</v>
+      </c>
+      <c r="O13" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P13" s="38">
+        <v>6.4299999999999996E-2</v>
+      </c>
+      <c r="Q13" s="38">
+        <f>P13*N13</f>
+        <v>0.38579999999999998</v>
+      </c>
+      <c r="R13" s="37"/>
+      <c r="S13" s="55"/>
+    </row>
+    <row r="14" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="72">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C14" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="F14" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>159</v>
+      </c>
+      <c r="I14" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J14" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="K14" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L14" s="49">
+        <v>1</v>
+      </c>
+      <c r="M14" s="49">
+        <f t="shared" ref="M14" si="1">L14*5</f>
+        <v>5</v>
+      </c>
+      <c r="N14" s="49">
+        <v>6</v>
+      </c>
+      <c r="O14" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P14" s="50">
+        <v>0.22550000000000001</v>
+      </c>
+      <c r="Q14" s="50">
+        <f t="shared" ref="Q14" si="2">P14*N14</f>
+        <v>1.353</v>
+      </c>
+      <c r="R14" s="49"/>
+      <c r="S14" s="55"/>
+    </row>
+    <row r="15" spans="1:19" ht="96" x14ac:dyDescent="0.25">
+      <c r="A15" s="56"/>
+      <c r="B15" s="46">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="67" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="K15" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L15" s="37">
+        <v>1</v>
+      </c>
+      <c r="M15" s="37">
+        <f>L15*5</f>
+        <v>5</v>
+      </c>
+      <c r="N15" s="37">
+        <v>10</v>
+      </c>
+      <c r="O15" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P15" s="38">
+        <v>9.5100000000000004E-2</v>
+      </c>
+      <c r="Q15" s="38">
+        <f>P15*N15</f>
+        <v>0.95100000000000007</v>
+      </c>
+      <c r="R15" s="37"/>
+      <c r="S15" s="55"/>
+    </row>
+    <row r="16" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A16" s="56"/>
+      <c r="B16" s="46">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C16" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="69" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="49" t="s">
+        <v>89</v>
+      </c>
+      <c r="I16" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J16" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L16" s="49">
+        <v>1</v>
+      </c>
+      <c r="M16" s="49">
+        <f t="shared" ref="M16" si="3">L16*5</f>
+        <v>5</v>
+      </c>
+      <c r="N16" s="49">
+        <v>20</v>
+      </c>
+      <c r="O16" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P16" s="50">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="Q16" s="50">
+        <f t="shared" ref="Q16" si="4">P16*N16</f>
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="R16" s="49"/>
+      <c r="S16" s="55"/>
+    </row>
+    <row r="17" spans="1:19" ht="168" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="46">
+        <f>ROW(B17) - ROW($B$9)</f>
+        <v>8</v>
+      </c>
+      <c r="C17" s="67" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="F17" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G17" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="H17" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="I17" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J17" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37">
+        <v>1</v>
+      </c>
+      <c r="M17" s="37">
+        <f>L17*5</f>
+        <v>5</v>
+      </c>
+      <c r="N17" s="37">
+        <v>10</v>
+      </c>
+      <c r="O17" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P17" s="38">
+        <v>0.1636</v>
+      </c>
+      <c r="Q17" s="38">
+        <f>P17*N17</f>
+        <v>1.6359999999999999</v>
+      </c>
+      <c r="R17" s="37"/>
+      <c r="S17" s="55"/>
+    </row>
+    <row r="18" spans="1:19" ht="168" x14ac:dyDescent="0.25">
+      <c r="A18" s="56"/>
+      <c r="B18" s="46">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C18" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="69" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G18" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="I18" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J18" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L18" s="49">
+        <v>1</v>
+      </c>
+      <c r="M18" s="49">
+        <f t="shared" ref="M18" si="5">L18*5</f>
+        <v>5</v>
+      </c>
+      <c r="N18" s="49">
+        <v>20</v>
+      </c>
+      <c r="O18" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P18" s="50">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="Q18" s="50">
+        <f t="shared" ref="Q18" si="6">P18*N18</f>
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="R18" s="49"/>
+      <c r="S18" s="55"/>
+    </row>
+    <row r="19" spans="1:19" ht="108" x14ac:dyDescent="0.25">
+      <c r="A19" s="56"/>
+      <c r="B19" s="46">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C19" s="67" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="I19" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J19" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="K19" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L19" s="37">
+        <v>1</v>
+      </c>
+      <c r="M19" s="37">
+        <f>L19*5</f>
+        <v>5</v>
+      </c>
+      <c r="N19" s="37">
+        <v>12</v>
+      </c>
+      <c r="O19" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P19" s="38">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="Q19" s="38">
+        <f>P19*N19</f>
+        <v>0.86399999999999988</v>
+      </c>
+      <c r="R19" s="37"/>
+      <c r="S19" s="55"/>
+    </row>
+    <row r="20" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="A20" s="56"/>
+      <c r="B20" s="46">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C20" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="69" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G20" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L20" s="49">
+        <v>1</v>
+      </c>
+      <c r="M20" s="49">
+        <f t="shared" ref="M20" si="7">L20*5</f>
+        <v>5</v>
+      </c>
+      <c r="N20" s="49">
+        <v>10</v>
+      </c>
+      <c r="O20" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P20" s="50">
+        <v>0.20130000000000001</v>
+      </c>
+      <c r="Q20" s="50">
+        <f t="shared" ref="Q20" si="8">P20*N20</f>
+        <v>2.0129999999999999</v>
+      </c>
+      <c r="R20" s="49"/>
+      <c r="S20" s="55"/>
+    </row>
+    <row r="21" spans="1:19" ht="72" x14ac:dyDescent="0.25">
+      <c r="A21" s="56"/>
+      <c r="B21" s="46">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C21" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J21" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="K21" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L21" s="37">
+        <v>1</v>
+      </c>
+      <c r="M21" s="37">
+        <f>L21*5</f>
+        <v>5</v>
+      </c>
+      <c r="N21" s="37">
+        <v>20</v>
+      </c>
+      <c r="O21" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P21" s="38">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="Q21" s="38">
+        <f>P21*N21</f>
+        <v>0.53</v>
+      </c>
+      <c r="R21" s="37"/>
+      <c r="S21" s="55"/>
+    </row>
+    <row r="22" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="56"/>
+      <c r="B22" s="46">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C22" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="69" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J22" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L22" s="49">
+        <v>1</v>
+      </c>
+      <c r="M22" s="49">
+        <f t="shared" ref="M22" si="9">L22*5</f>
+        <v>5</v>
+      </c>
+      <c r="N22" s="49">
+        <v>20</v>
+      </c>
+      <c r="O22" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P22" s="50">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="Q22" s="50">
+        <f t="shared" ref="Q22" si="10">P22*N22</f>
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="R22" s="49"/>
+      <c r="S22" s="55"/>
+    </row>
+    <row r="23" spans="1:19" ht="84" x14ac:dyDescent="0.25">
+      <c r="A23" s="56"/>
+      <c r="B23" s="46">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C23" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I23" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J23" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="K23" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L23" s="37">
+        <v>1</v>
+      </c>
+      <c r="M23" s="37">
+        <f>L23*5</f>
+        <v>5</v>
+      </c>
+      <c r="N23" s="37">
+        <v>20</v>
+      </c>
+      <c r="O23" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P23" s="38">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="Q23" s="38">
+        <f>P23*N23</f>
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="R23" s="37"/>
+      <c r="S23" s="55"/>
+    </row>
+    <row r="24" spans="1:19" ht="72" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="46">
+        <f>ROW(B24) - ROW($B$9)</f>
+        <v>15</v>
+      </c>
+      <c r="C24" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="E24" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="F24" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G24" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="I24" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="K24" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L24" s="37">
+        <v>6</v>
+      </c>
+      <c r="M24" s="37">
+        <f>L24*5</f>
+        <v>30</v>
+      </c>
+      <c r="N24" s="37">
+        <v>35</v>
+      </c>
+      <c r="O24" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P24" s="38">
+        <v>7.1300000000000002E-2</v>
+      </c>
+      <c r="Q24" s="38">
+        <f>P24*N24</f>
+        <v>2.4955000000000003</v>
+      </c>
+      <c r="R24" s="37"/>
+      <c r="S24" s="55"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="61"/>
+      <c r="B25" s="73">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="75" t="s">
+        <v>172</v>
+      </c>
+      <c r="E25" s="75" t="s">
+        <v>173</v>
+      </c>
+      <c r="F25" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" s="75" t="s">
+        <v>174</v>
+      </c>
+      <c r="H25" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="I25" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="75" t="s">
+        <v>176</v>
+      </c>
+      <c r="K25" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="L25" s="75">
+        <v>2</v>
+      </c>
+      <c r="M25" s="37">
+        <f>L25*5</f>
+        <v>10</v>
+      </c>
+      <c r="N25" s="62">
+        <v>20</v>
+      </c>
+      <c r="O25" s="66" t="s">
+        <v>136</v>
+      </c>
+      <c r="P25" s="63">
+        <v>3.1E-2</v>
+      </c>
+      <c r="Q25" s="63">
+        <f>P25*N25</f>
+        <v>0.62</v>
+      </c>
+      <c r="R25" s="62"/>
+      <c r="S25" s="64"/>
+    </row>
+    <row r="26" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A26" s="56"/>
+      <c r="B26" s="46">
+        <f>ROW(B26) - ROW($B$9)</f>
+        <v>17</v>
+      </c>
+      <c r="C26" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G26" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I26" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J26" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="K26" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="L26" s="37">
+        <v>5</v>
+      </c>
+      <c r="M26" s="37">
+        <f>L26*5</f>
+        <v>25</v>
+      </c>
+      <c r="N26" s="37">
+        <v>100</v>
+      </c>
+      <c r="O26" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P26" s="38">
+        <v>1E-3</v>
+      </c>
+      <c r="Q26" s="38">
+        <f>P26*N26</f>
+        <v>0.1</v>
+      </c>
+      <c r="R26" s="37"/>
+      <c r="S26" s="55"/>
+    </row>
+    <row r="27" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A27" s="56"/>
+      <c r="B27" s="46">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C27" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="H27" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="I27" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J27" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="K27" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="L27" s="49">
+        <v>1</v>
+      </c>
+      <c r="M27" s="49">
+        <f t="shared" ref="M27" si="11">L27*5</f>
+        <v>5</v>
+      </c>
+      <c r="N27" s="49">
+        <v>100</v>
+      </c>
+      <c r="O27" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P27" s="50">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q27" s="50">
+        <f t="shared" ref="Q27" si="12">P27*N27</f>
+        <v>0.12</v>
+      </c>
+      <c r="R27" s="49"/>
+      <c r="S27" s="55"/>
+    </row>
+    <row r="28" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="46">
+        <f>ROW(B28) - ROW($B$9)</f>
+        <v>19</v>
+      </c>
+      <c r="C28" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="E28" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="F28" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="H28" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J28" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="K28" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="L28" s="37">
+        <v>3</v>
+      </c>
+      <c r="M28" s="37">
+        <f>L28*5</f>
+        <v>15</v>
+      </c>
+      <c r="N28" s="37">
+        <v>100</v>
+      </c>
+      <c r="O28" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P28" s="38">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q28" s="38">
+        <f>P28*N28</f>
+        <v>0.11</v>
+      </c>
+      <c r="R28" s="37"/>
+      <c r="S28" s="55"/>
+    </row>
+    <row r="29" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A29" s="56"/>
+      <c r="B29" s="46">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C29" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="70" t="s">
+        <v>178</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="F29" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G29" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="H29" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I29" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J29" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="K29" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="L29" s="37">
+        <v>1</v>
+      </c>
+      <c r="M29" s="37">
+        <f>L29*5</f>
+        <v>5</v>
+      </c>
+      <c r="N29" s="37">
+        <v>100</v>
+      </c>
+      <c r="O29" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P29" s="38">
+        <v>1E-3</v>
+      </c>
+      <c r="Q29" s="38">
+        <f>P29*N29</f>
+        <v>0.1</v>
+      </c>
+      <c r="R29" s="37"/>
+      <c r="S29" s="55"/>
+    </row>
+    <row r="30" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A30" s="56"/>
+      <c r="B30" s="46">
+        <f>ROW(B30) - ROW($B$9)</f>
+        <v>21</v>
+      </c>
+      <c r="C30" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G30" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="H30" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I30" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J30" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="K30" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="L30" s="37">
+        <v>1</v>
+      </c>
+      <c r="M30" s="37">
+        <f>L30*5</f>
+        <v>5</v>
+      </c>
+      <c r="N30" s="37">
+        <v>100</v>
+      </c>
+      <c r="O30" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P30" s="38">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q30" s="38">
+        <f>P30*N30</f>
+        <v>0.13</v>
+      </c>
+      <c r="R30" s="37"/>
+      <c r="S30" s="55"/>
+    </row>
+    <row r="31" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="72">
+        <f t="shared" ref="B31:B32" si="13">ROW(B31) - ROW($B$9)</f>
+        <v>22</v>
+      </c>
+      <c r="C31" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="49" t="s">
+        <v>183</v>
+      </c>
+      <c r="E31" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="H31" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="I31" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J31" s="49" t="s">
+        <v>112</v>
+      </c>
+      <c r="K31" s="49" t="s">
+        <v>184</v>
+      </c>
+      <c r="L31" s="49">
+        <v>1</v>
+      </c>
+      <c r="M31" s="49">
+        <f t="shared" ref="M31:M32" si="14">L31*5</f>
+        <v>5</v>
+      </c>
+      <c r="N31" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="O31" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P31" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q31" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="R31" s="76" t="s">
+        <v>184</v>
+      </c>
+      <c r="S31" s="55"/>
+    </row>
+    <row r="32" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="72">
+        <f t="shared" si="13"/>
+        <v>23</v>
+      </c>
+      <c r="C32" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="E32" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="F32" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="G32" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="H32" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="I32" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="K32" s="49" t="s">
+        <v>184</v>
+      </c>
+      <c r="L32" s="49">
+        <v>2</v>
+      </c>
+      <c r="M32" s="49">
+        <f t="shared" si="14"/>
+        <v>10</v>
+      </c>
+      <c r="N32" s="49">
+        <v>20</v>
+      </c>
+      <c r="O32" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P32" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q32" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="R32" s="76" t="s">
+        <v>184</v>
+      </c>
+      <c r="S32" s="55"/>
+    </row>
+    <row r="33" spans="1:19" ht="72" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="46">
+        <f>ROW(B33) - ROW($B$9)</f>
+        <v>24</v>
+      </c>
+      <c r="C33" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="D33" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="F33" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G33" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="H33" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J33" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="K33" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L33" s="37">
+        <v>1</v>
+      </c>
+      <c r="M33" s="37">
+        <f>L33*5</f>
+        <v>5</v>
+      </c>
+      <c r="N33" s="37">
+        <v>10</v>
+      </c>
+      <c r="O33" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P33" s="38">
+        <v>0.1336</v>
+      </c>
+      <c r="Q33" s="38">
+        <f>P33*N33</f>
+        <v>1.3359999999999999</v>
+      </c>
+      <c r="R33" s="37"/>
+      <c r="S33" s="55"/>
+    </row>
+    <row r="34" spans="1:19" ht="156" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="72">
+        <f t="shared" ref="B34" si="15">ROW(B34) - ROW($B$9)</f>
+        <v>25</v>
+      </c>
+      <c r="C34" s="68" t="s">
+        <v>194</v>
+      </c>
+      <c r="D34" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="E34" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="F34" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="49" t="s">
+        <v>197</v>
+      </c>
+      <c r="H34" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="I34" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="K34" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L34" s="49">
+        <v>2</v>
+      </c>
+      <c r="M34" s="49">
+        <f t="shared" ref="M34" si="16">L34*5</f>
+        <v>10</v>
+      </c>
+      <c r="N34" s="49">
+        <v>20</v>
+      </c>
+      <c r="O34" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P34" s="50">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="Q34" s="50">
+        <f t="shared" ref="Q34" si="17">P34*N34</f>
+        <v>0.96600000000000008</v>
+      </c>
+      <c r="R34" s="49"/>
+      <c r="S34" s="55"/>
+    </row>
+    <row r="35" spans="1:19" ht="144" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="46">
+        <f>ROW(B35) - ROW($B$9)</f>
+        <v>26</v>
+      </c>
+      <c r="C35" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="D35" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="E35" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="F35" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G35" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="H35" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I35" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="K35" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L35" s="37">
+        <v>1</v>
+      </c>
+      <c r="M35" s="37">
+        <f>L35*5</f>
+        <v>5</v>
+      </c>
+      <c r="N35" s="37">
+        <v>10</v>
+      </c>
+      <c r="O35" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P35" s="38">
+        <v>6.4600000000000005E-2</v>
+      </c>
+      <c r="Q35" s="38">
+        <f>P35*N35</f>
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="R35" s="37"/>
+      <c r="S35" s="55"/>
+    </row>
+    <row r="36" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="A36" s="56"/>
+      <c r="B36" s="46">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C36" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="F36" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="G36" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="H36" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="I36" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J36" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="K36" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L36" s="49">
+        <v>1</v>
+      </c>
+      <c r="M36" s="49">
+        <f t="shared" ref="M36:M37" si="18">L36*5</f>
+        <v>5</v>
+      </c>
+      <c r="N36" s="49">
+        <v>10</v>
+      </c>
+      <c r="O36" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P36" s="50">
+        <v>0.2079</v>
+      </c>
+      <c r="Q36" s="50">
+        <f t="shared" ref="Q36:Q37" si="19">P36*N36</f>
+        <v>2.0790000000000002</v>
+      </c>
+      <c r="R36" s="49"/>
+      <c r="S36" s="55"/>
+    </row>
+    <row r="37" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="A37" s="56"/>
+      <c r="B37" s="46">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C37" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="G37" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="H37" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="I37" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J37" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="K37" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L37" s="49">
+        <v>1</v>
+      </c>
+      <c r="M37" s="49">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="N37" s="49">
+        <v>6</v>
+      </c>
+      <c r="O37" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P37" s="50">
+        <v>0.54569999999999996</v>
+      </c>
+      <c r="Q37" s="50">
+        <f t="shared" si="19"/>
+        <v>3.2741999999999996</v>
+      </c>
+      <c r="R37" s="49"/>
+      <c r="S37" s="55"/>
+    </row>
+    <row r="38" spans="1:19" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="56"/>
+      <c r="B38" s="46">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C38" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="F38" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G38" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="H38" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="I38" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J38" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="K38" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L38" s="37">
+        <v>1</v>
+      </c>
+      <c r="M38" s="37">
+        <f>L38*5</f>
+        <v>5</v>
+      </c>
+      <c r="N38" s="37">
+        <v>6</v>
+      </c>
+      <c r="O38" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P38" s="38">
+        <v>2.8589000000000002</v>
+      </c>
+      <c r="Q38" s="38">
+        <f>P38*N38</f>
+        <v>17.153400000000001</v>
+      </c>
+      <c r="R38" s="37"/>
+      <c r="S38" s="39"/>
+    </row>
+    <row r="39" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1"/>
+      <c r="B39" s="46">
+        <f>ROW(B39) - ROW($B$9)</f>
+        <v>30</v>
+      </c>
+      <c r="C39" s="67" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="E39" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="F39" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="G39" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="H39" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="I39" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J39" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="K39" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L39" s="37">
+        <v>1</v>
+      </c>
+      <c r="M39" s="37">
+        <f>L39*5</f>
+        <v>5</v>
+      </c>
+      <c r="N39" s="37">
+        <v>6</v>
+      </c>
+      <c r="O39" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P39" s="38">
+        <v>1.2776000000000001</v>
+      </c>
+      <c r="Q39" s="38">
+        <f>P39*N39</f>
+        <v>7.6656000000000004</v>
+      </c>
+      <c r="R39" s="37"/>
+      <c r="S39" s="39"/>
+    </row>
+    <row r="40" spans="1:19" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="56"/>
+      <c r="B40" s="46">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="G40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="I40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="K40" s="37"/>
+      <c r="L40" s="37">
+        <v>1</v>
+      </c>
+      <c r="M40" s="37">
+        <f>L40*5</f>
+        <v>5</v>
+      </c>
+      <c r="N40" s="37">
+        <v>5</v>
+      </c>
+      <c r="O40" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="P40" s="38">
+        <v>3.28</v>
+      </c>
+      <c r="Q40" s="38">
+        <f>P40*N40</f>
+        <v>16.399999999999999</v>
+      </c>
+      <c r="R40" s="37"/>
+      <c r="S40" s="39"/>
+    </row>
+    <row r="41" spans="1:19" ht="144.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="56"/>
+      <c r="B41" s="46">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C41" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="F41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="G41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="I41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="K41" s="37"/>
+      <c r="L41" s="37">
+        <v>1</v>
+      </c>
+      <c r="M41" s="37">
+        <f>L41*5</f>
+        <v>5</v>
+      </c>
+      <c r="N41" s="37">
+        <v>1</v>
+      </c>
+      <c r="O41" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="P41" s="38">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="Q41" s="71">
+        <f>P41*N41</f>
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="R41" s="37"/>
+      <c r="S41" s="39"/>
+    </row>
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="77" t="s">
+        <v>5</v>
+      </c>
+      <c r="O42" s="78"/>
+      <c r="P42" s="78"/>
+      <c r="Q42" s="47">
+        <f>SUM(Q10:Q41)</f>
+        <v>68.674000000000007</v>
+      </c>
+      <c r="R42" s="79"/>
+      <c r="S42" s="80"/>
+    </row>
+    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="77" t="s">
+        <v>6</v>
+      </c>
+      <c r="O43" s="78"/>
+      <c r="P43" s="78"/>
+      <c r="Q43" s="48">
+        <f>Q42/5</f>
+        <v>13.734800000000002</v>
+      </c>
+      <c r="R43" s="81"/>
+      <c r="S43" s="82"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S43"/>
+    <mergeCell ref="N43:P43"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O13" r:id="rId3"/>
+    <hyperlink ref="O15" r:id="rId4"/>
+    <hyperlink ref="O16" r:id="rId5"/>
+    <hyperlink ref="O18" r:id="rId6"/>
+    <hyperlink ref="O19" r:id="rId7"/>
+    <hyperlink ref="O20" r:id="rId8"/>
+    <hyperlink ref="O21" r:id="rId9"/>
+    <hyperlink ref="O22" r:id="rId10"/>
+    <hyperlink ref="O23" r:id="rId11"/>
+    <hyperlink ref="O27" r:id="rId12"/>
+    <hyperlink ref="O29" r:id="rId13"/>
+    <hyperlink ref="O26" r:id="rId14"/>
+    <hyperlink ref="O30" r:id="rId15"/>
+    <hyperlink ref="O36" r:id="rId16"/>
+    <hyperlink ref="O37" r:id="rId17"/>
+    <hyperlink ref="O38" r:id="rId18"/>
+    <hyperlink ref="O40" r:id="rId19"/>
+    <hyperlink ref="O41" r:id="rId20"/>
+    <hyperlink ref="O12" r:id="rId21"/>
+    <hyperlink ref="O14" r:id="rId22"/>
+    <hyperlink ref="O17" r:id="rId23"/>
+    <hyperlink ref="O24" r:id="rId24"/>
+    <hyperlink ref="O25" r:id="rId25"/>
+    <hyperlink ref="O28" r:id="rId26"/>
+    <hyperlink ref="O31" r:id="rId27"/>
+    <hyperlink ref="O32" r:id="rId28"/>
+    <hyperlink ref="O33" r:id="rId29"/>
+    <hyperlink ref="O34" r:id="rId30"/>
+    <hyperlink ref="O35" r:id="rId31"/>
+    <hyperlink ref="O39" r:id="rId32"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId33"/>
+</worksheet>
 </file>
--- a/Design Files/IoT-Button-v1.2/BOM/eSpark-BOM-IoT-Button.xlsx
+++ b/Design Files/IoT-Button-v1.2/BOM/eSpark-BOM-IoT-Button.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="2 Boards" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="209">
   <si>
     <t>Component list</t>
   </si>
@@ -541,9 +541,6 @@
     <t>C4154882</t>
   </si>
   <si>
-    <t>Q1, Q2</t>
-  </si>
-  <si>
     <t>Trans Mosfet P-ch 30V 4A 3-PIN SOT-23 T/r</t>
   </si>
   <si>
@@ -583,24 +580,6 @@
     <t>TE Connectivity</t>
   </si>
   <si>
-    <t>Rx1, Rx2</t>
-  </si>
-  <si>
-    <t>RES SMD 0 OHM JUMPER 1/5W 0402</t>
-  </si>
-  <si>
-    <t>Res-0402</t>
-  </si>
-  <si>
-    <t>RCS04020000Z0ED</t>
-  </si>
-  <si>
-    <t>Vishay Dale</t>
-  </si>
-  <si>
-    <t>C844673</t>
-  </si>
-  <si>
     <t>50mA Lying SPST 24V Plugin Tactile Switches ROHS</t>
   </si>
   <si>
@@ -637,24 +616,6 @@
     <t>C963229</t>
   </si>
   <si>
-    <t>U7</t>
-  </si>
-  <si>
-    <t>IC CNTRLR ON/OFF W/DEB TSOT23-6</t>
-  </si>
-  <si>
-    <t>TSOT-23-6</t>
-  </si>
-  <si>
-    <t>MAX16054AZT+T</t>
-  </si>
-  <si>
-    <t>Maxim</t>
-  </si>
-  <si>
-    <t>C79401</t>
-  </si>
-  <si>
     <t>C266196</t>
   </si>
   <si>
@@ -686,6 +647,9 @@
   </si>
   <si>
     <t>Total Cost (500 Boards)</t>
+  </si>
+  <si>
+    <t>Q2</t>
   </si>
 </sst>
 </file>
@@ -1157,7 +1121,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1396,6 +1360,30 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1696,14 +1684,14 @@
       <xdr:rowOff>10417</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1724025</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
@@ -1727,7 +1715,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21002625" y="620017"/>
+          <a:off x="20412075" y="620017"/>
           <a:ext cx="1714500" cy="1104008"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2004,7 +1992,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -2268,7 +2256,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="56"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -2277,17 +2265,17 @@
       <c r="C10" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="49" t="s">
-        <v>153</v>
+      <c r="D10" s="37" t="s">
+        <v>198</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>38</v>
+        <v>149</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="H10" s="37" t="s">
         <v>86</v>
@@ -2296,54 +2284,54 @@
         <v>134</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L10" s="37">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M10" s="37">
         <f>L10*2</f>
-        <v>12</v>
-      </c>
-      <c r="N10" s="49">
+        <v>30</v>
+      </c>
+      <c r="N10" s="37">
         <v>100</v>
       </c>
       <c r="O10" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P10" s="38">
-        <v>5.1999999999999998E-3</v>
-      </c>
-      <c r="Q10" s="50">
-        <f t="shared" ref="Q10" si="0">P10*N10</f>
-        <v>0.52</v>
-      </c>
-      <c r="R10" s="49"/>
+        <v>1.8E-3</v>
+      </c>
+      <c r="Q10" s="38">
+        <f>P10*N10</f>
+        <v>0.18</v>
+      </c>
+      <c r="R10" s="37"/>
       <c r="S10" s="55"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="56"/>
       <c r="B11" s="46">
-        <f t="shared" ref="B11:B41" si="1">ROW(B11) - ROW($B$9)</f>
+        <f>ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="37" t="s">
-        <v>154</v>
+      <c r="D11" s="49" t="s">
+        <v>153</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11" s="37" t="s">
         <v>57</v>
       </c>
       <c r="G11" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H11" s="37" t="s">
         <v>86</v>
@@ -2352,54 +2340,54 @@
         <v>134</v>
       </c>
       <c r="J11" s="37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K11" s="37" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L11" s="37">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M11" s="37">
         <f>L11*2</f>
-        <v>4</v>
-      </c>
-      <c r="N11" s="37">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="N11" s="49">
+        <v>100</v>
       </c>
       <c r="O11" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P11" s="38">
-        <v>0.15809999999999999</v>
-      </c>
-      <c r="Q11" s="38">
-        <f>P11*N11</f>
-        <v>0.79049999999999998</v>
-      </c>
-      <c r="R11" s="37"/>
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="Q11" s="50">
+        <f t="shared" ref="Q11" si="0">P11*N11</f>
+        <v>0.52</v>
+      </c>
+      <c r="R11" s="49"/>
       <c r="S11" s="55"/>
     </row>
-    <row r="12" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="56"/>
       <c r="B12" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="B12:B39" si="1">ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
       <c r="C12" s="67" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>149</v>
+        <v>39</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>150</v>
+        <v>57</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="H12" s="37" t="s">
         <v>86</v>
@@ -2408,30 +2396,30 @@
         <v>134</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L12" s="37">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M12" s="37">
         <f>L12*2</f>
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="N12" s="37">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="O12" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P12" s="38">
-        <v>1.8E-3</v>
+        <v>0.15809999999999999</v>
       </c>
       <c r="Q12" s="38">
         <f>P12*N12</f>
-        <v>0.18</v>
+        <v>0.79049999999999998</v>
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="55"/>
@@ -2473,7 +2461,7 @@
         <v>1</v>
       </c>
       <c r="M13" s="37">
-        <f t="shared" ref="M13:M41" si="2">L13*2</f>
+        <f t="shared" ref="M13:M39" si="2">L13*2</f>
         <v>2</v>
       </c>
       <c r="N13" s="49">
@@ -3114,35 +3102,35 @@
         <v>17</v>
       </c>
       <c r="D25" s="75" t="s">
+        <v>208</v>
+      </c>
+      <c r="E25" s="75" t="s">
         <v>172</v>
-      </c>
-      <c r="E25" s="75" t="s">
-        <v>173</v>
       </c>
       <c r="F25" s="75" t="s">
         <v>64</v>
       </c>
       <c r="G25" s="75" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25" s="75" t="s">
         <v>174</v>
       </c>
-      <c r="H25" s="75" t="s">
+      <c r="I25" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="I25" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="J25" s="75" t="s">
-        <v>176</v>
-      </c>
       <c r="K25" s="75" t="s">
         <v>134</v>
       </c>
       <c r="L25" s="75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M25" s="37">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N25" s="49">
         <v>10</v>
@@ -3170,7 +3158,7 @@
         <v>18</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>51</v>
@@ -3282,16 +3270,16 @@
         <v>18</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F28" s="37" t="s">
         <v>65</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H28" s="37" t="s">
         <v>86</v>
@@ -3300,10 +3288,10 @@
         <v>134</v>
       </c>
       <c r="J28" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="K28" s="37" t="s">
         <v>181</v>
-      </c>
-      <c r="K28" s="37" t="s">
-        <v>182</v>
       </c>
       <c r="L28" s="37">
         <v>3</v>
@@ -3338,7 +3326,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="70" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E29" s="37" t="s">
         <v>50</v>
@@ -3450,7 +3438,7 @@
         <v>18</v>
       </c>
       <c r="D31" s="49" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E31" s="49" t="s">
         <v>51</v>
@@ -3471,7 +3459,7 @@
         <v>112</v>
       </c>
       <c r="K31" s="49" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L31" s="49">
         <v>1</v>
@@ -3493,233 +3481,232 @@
         <v>134</v>
       </c>
       <c r="R31" s="76" t="s">
+        <v>183</v>
+      </c>
+      <c r="S31" s="55"/>
+    </row>
+    <row r="32" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A32" s="56"/>
+      <c r="B32" s="46">
+        <f>ROW(B32) - ROW($B$9)</f>
+        <v>23</v>
+      </c>
+      <c r="C32" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G32" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="H32" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="S31" s="55"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" s="56"/>
-      <c r="B32" s="72">
-        <f t="shared" ref="B32" si="12">ROW(B32) - ROW($B$9)</f>
-        <v>23</v>
-      </c>
-      <c r="C32" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="E32" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="F32" s="49" t="s">
-        <v>188</v>
-      </c>
-      <c r="G32" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="H32" s="49" t="s">
-        <v>190</v>
-      </c>
-      <c r="I32" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J32" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="K32" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="L32" s="49">
-        <v>2</v>
+      <c r="I32" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="K32" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L32" s="37">
+        <v>1</v>
       </c>
       <c r="M32" s="37">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="N32" s="37">
-        <v>100</v>
-      </c>
-      <c r="O32" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P32" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q32" s="38" t="s">
-        <v>134</v>
-      </c>
-      <c r="R32" s="76" t="s">
-        <v>184</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N32" s="49">
+        <v>5</v>
+      </c>
+      <c r="O32" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P32" s="38">
+        <v>0.1336</v>
+      </c>
+      <c r="Q32" s="50">
+        <f t="shared" ref="Q32" si="12">P32*N32</f>
+        <v>0.66799999999999993</v>
+      </c>
+      <c r="R32" s="49"/>
       <c r="S32" s="55"/>
     </row>
-    <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A33" s="56"/>
-      <c r="B33" s="46">
-        <f>ROW(B33) - ROW($B$9)</f>
+    <row r="33" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A33" s="61"/>
+      <c r="B33" s="72">
+        <f t="shared" ref="B33" si="13">ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
       <c r="C33" s="68" t="s">
-        <v>194</v>
-      </c>
-      <c r="D33" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="E33" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="F33" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="G33" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="H33" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="I33" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J33" s="49" t="s">
         <v>192</v>
       </c>
-      <c r="F33" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G33" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="H33" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="I33" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J33" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="K33" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L33" s="37">
-        <v>1</v>
+      <c r="K33" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L33" s="49">
+        <v>2</v>
       </c>
       <c r="M33" s="37">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="N33" s="49">
-        <v>5</v>
-      </c>
-      <c r="O33" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P33" s="38">
-        <v>0.1336</v>
-      </c>
-      <c r="Q33" s="50">
-        <f t="shared" ref="Q33" si="13">P33*N33</f>
-        <v>0.66799999999999993</v>
-      </c>
-      <c r="R33" s="49"/>
-      <c r="S33" s="55"/>
+        <v>4</v>
+      </c>
+      <c r="N33" s="62">
+        <v>10</v>
+      </c>
+      <c r="O33" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P33" s="50">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="Q33" s="63">
+        <f>P33*N33</f>
+        <v>0.48300000000000004</v>
+      </c>
+      <c r="R33" s="62"/>
+      <c r="S33" s="64"/>
     </row>
     <row r="34" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A34" s="61"/>
-      <c r="B34" s="72">
-        <f t="shared" ref="B34" si="14">ROW(B34) - ROW($B$9)</f>
+      <c r="A34" s="56"/>
+      <c r="B34" s="46">
+        <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="68" t="s">
+      <c r="C34" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="E34" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="D34" s="49" t="s">
+      <c r="F34" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="E34" s="49" t="s">
+      <c r="H34" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I34" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="F34" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="G34" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="H34" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="I34" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J34" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="K34" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="L34" s="49">
-        <v>2</v>
+      <c r="K34" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L34" s="37">
+        <v>1</v>
       </c>
       <c r="M34" s="37">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="N34" s="62">
+        <v>2</v>
+      </c>
+      <c r="N34" s="49">
         <v>10</v>
       </c>
-      <c r="O34" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P34" s="50">
-        <v>4.8300000000000003E-2</v>
-      </c>
-      <c r="Q34" s="63">
-        <f>P34*N34</f>
-        <v>0.48300000000000004</v>
-      </c>
-      <c r="R34" s="62"/>
-      <c r="S34" s="64"/>
-    </row>
-    <row r="35" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="O34" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P34" s="38">
+        <v>6.4600000000000005E-2</v>
+      </c>
+      <c r="Q34" s="50">
+        <f t="shared" ref="Q34" si="14">P34*N34</f>
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="R34" s="49"/>
+      <c r="S34" s="55"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="56"/>
       <c r="B35" s="46">
-        <f>ROW(B35) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="C35" s="67" t="s">
-        <v>194</v>
-      </c>
-      <c r="D35" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="E35" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="F35" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="H35" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="I35" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J35" s="37" t="s">
-        <v>203</v>
+      <c r="C35" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="G35" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="H35" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="I35" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="49" t="s">
+        <v>114</v>
       </c>
       <c r="K35" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L35" s="37">
+      <c r="L35" s="49">
         <v>1</v>
       </c>
       <c r="M35" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N35" s="49">
-        <v>10</v>
-      </c>
-      <c r="O35" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P35" s="38">
-        <v>6.4600000000000005E-2</v>
-      </c>
-      <c r="Q35" s="50">
-        <f t="shared" ref="Q35" si="15">P35*N35</f>
-        <v>0.64600000000000002</v>
-      </c>
-      <c r="R35" s="49"/>
+      <c r="N35" s="37">
+        <v>5</v>
+      </c>
+      <c r="O35" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P35" s="50">
+        <v>0.2079</v>
+      </c>
+      <c r="Q35" s="38">
+        <f>P35*N35</f>
+        <v>1.0395000000000001</v>
+      </c>
+      <c r="R35" s="37"/>
       <c r="S35" s="55"/>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
@@ -3729,28 +3716,28 @@
         <v>27</v>
       </c>
       <c r="C36" s="68" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E36" s="49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F36" s="49" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G36" s="49" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H36" s="49" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I36" s="49" t="s">
         <v>134</v>
       </c>
       <c r="J36" s="49" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K36" s="37" t="s">
         <v>134</v>
@@ -3762,20 +3749,20 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N36" s="37">
-        <v>5</v>
+      <c r="N36" s="49">
+        <v>3</v>
       </c>
       <c r="O36" s="60" t="s">
         <v>136</v>
       </c>
       <c r="P36" s="50">
-        <v>0.2079</v>
-      </c>
-      <c r="Q36" s="38">
-        <f>P36*N36</f>
-        <v>1.0395000000000001</v>
-      </c>
-      <c r="R36" s="37"/>
+        <v>0.54569999999999996</v>
+      </c>
+      <c r="Q36" s="50">
+        <f t="shared" ref="Q36" si="15">P36*N36</f>
+        <v>1.6370999999999998</v>
+      </c>
+      <c r="R36" s="49"/>
       <c r="S36" s="55"/>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
@@ -3784,89 +3771,87 @@
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="C37" s="68" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="E37" s="49" t="s">
-        <v>54</v>
-      </c>
-      <c r="F37" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="G37" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="H37" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="I37" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J37" s="49" t="s">
-        <v>115</v>
+      <c r="C37" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="F37" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G37" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="H37" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="I37" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J37" s="37" t="s">
+        <v>116</v>
       </c>
       <c r="K37" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L37" s="49">
+      <c r="L37" s="37">
         <v>1</v>
       </c>
       <c r="M37" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N37" s="49">
+      <c r="N37" s="37">
         <v>3</v>
       </c>
-      <c r="O37" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P37" s="50">
-        <v>0.54569999999999996</v>
-      </c>
-      <c r="Q37" s="50">
-        <f t="shared" ref="Q37" si="16">P37*N37</f>
-        <v>1.6370999999999998</v>
-      </c>
-      <c r="R37" s="49"/>
+      <c r="O37" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P37" s="38">
+        <v>2.8589000000000002</v>
+      </c>
+      <c r="Q37" s="38">
+        <f>P37*N37</f>
+        <v>8.5767000000000007</v>
+      </c>
+      <c r="R37" s="37"/>
       <c r="S37" s="55"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A38" s="56"/>
       <c r="B38" s="46">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="C38" s="67" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="I38" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="K38" s="37" t="s">
-        <v>134</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="K38" s="37"/>
       <c r="L38" s="37">
         <v>1</v>
       </c>
@@ -3875,54 +3860,52 @@
         <v>2</v>
       </c>
       <c r="N38" s="37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O38" s="59" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="P38" s="38">
-        <v>2.8589000000000002</v>
+        <v>3.28</v>
       </c>
       <c r="Q38" s="38">
         <f>P38*N38</f>
-        <v>8.5767000000000007</v>
+        <v>6.56</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="55"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="56"/>
       <c r="B39" s="46">
-        <f>ROW(B39) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="C39" s="67" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>205</v>
+        <v>148</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>206</v>
+        <v>134</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>207</v>
+        <v>134</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>208</v>
+        <v>134</v>
       </c>
       <c r="I39" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J39" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="K39" s="37" t="s">
-        <v>134</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="K39" s="37"/>
       <c r="L39" s="37">
         <v>1</v>
       </c>
@@ -3931,192 +3914,84 @@
         <v>2</v>
       </c>
       <c r="N39" s="49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O39" s="59" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="P39" s="38">
-        <v>1.2776000000000001</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="Q39" s="50">
-        <f t="shared" ref="Q39" si="17">P39*N39</f>
-        <v>3.8328000000000002</v>
+        <f t="shared" ref="Q39" si="16">P39*N39</f>
+        <v>2.4700000000000002</v>
       </c>
       <c r="R39" s="49"/>
       <c r="S39" s="55"/>
     </row>
-    <row r="40" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="56"/>
-      <c r="B40" s="46">
-        <f t="shared" si="1"/>
-        <v>31</v>
-      </c>
-      <c r="C40" s="67" t="s">
-        <v>144</v>
-      </c>
-      <c r="D40" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="E40" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="G40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="H40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="I40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="K40" s="37"/>
-      <c r="L40" s="37">
-        <v>1</v>
-      </c>
-      <c r="M40" s="37">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="N40" s="37">
-        <v>2</v>
-      </c>
-      <c r="O40" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="P40" s="38">
-        <v>3.28</v>
-      </c>
-      <c r="Q40" s="38">
-        <f>P40*N40</f>
-        <v>6.56</v>
-      </c>
-      <c r="R40" s="37"/>
-      <c r="S40" s="55"/>
-    </row>
-    <row r="41" spans="1:19" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="40"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="44"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="45"/>
+      <c r="J40" s="44"/>
+      <c r="K40" s="45"/>
+      <c r="L40" s="45"/>
+      <c r="M40" s="45"/>
+      <c r="N40" s="77" t="s">
+        <v>5</v>
+      </c>
+      <c r="O40" s="78"/>
+      <c r="P40" s="78"/>
+      <c r="Q40" s="47">
+        <f>SUM(Q11:Q39)</f>
+        <v>32.523800000000001</v>
+      </c>
+      <c r="R40" s="79"/>
+      <c r="S40" s="80"/>
+    </row>
+    <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="56"/>
-      <c r="B41" s="46">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-      <c r="C41" s="67" t="s">
-        <v>145</v>
-      </c>
-      <c r="D41" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="E41" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="G41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="H41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="I41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="K41" s="37"/>
-      <c r="L41" s="37">
-        <v>1</v>
-      </c>
-      <c r="M41" s="37">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="N41" s="49">
-        <v>1</v>
-      </c>
-      <c r="O41" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="P41" s="38">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="Q41" s="50">
-        <f t="shared" ref="Q41" si="18">P41*N41</f>
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="R41" s="49"/>
-      <c r="S41" s="55"/>
-    </row>
-    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="56"/>
-      <c r="B42" s="40"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="45"/>
-      <c r="M42" s="45"/>
-      <c r="N42" s="77" t="s">
-        <v>5</v>
-      </c>
-      <c r="O42" s="78"/>
-      <c r="P42" s="78"/>
-      <c r="Q42" s="47">
-        <f>SUM(Q10:Q41)</f>
-        <v>36.5366</v>
-      </c>
-      <c r="R42" s="79"/>
-      <c r="S42" s="80"/>
-    </row>
-    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="56"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="77" t="s">
+      <c r="B41" s="25"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="O43" s="78"/>
-      <c r="P43" s="78"/>
-      <c r="Q43" s="48">
-        <f>Q42/2</f>
-        <v>18.2683</v>
-      </c>
-      <c r="R43" s="81"/>
-      <c r="S43" s="82"/>
+      <c r="O41" s="78"/>
+      <c r="P41" s="78"/>
+      <c r="Q41" s="48">
+        <f>Q40/2</f>
+        <v>16.261900000000001</v>
+      </c>
+      <c r="R41" s="81"/>
+      <c r="S41" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S43"/>
-    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S41"/>
+    <mergeCell ref="N41:P41"/>
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1"/>
-    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O11" r:id="rId1"/>
+    <hyperlink ref="O12" r:id="rId2"/>
     <hyperlink ref="O13" r:id="rId3"/>
     <hyperlink ref="O15" r:id="rId4"/>
     <hyperlink ref="O16" r:id="rId5"/>
@@ -4130,12 +4005,12 @@
     <hyperlink ref="O29" r:id="rId13"/>
     <hyperlink ref="O26" r:id="rId14"/>
     <hyperlink ref="O30" r:id="rId15"/>
-    <hyperlink ref="O36" r:id="rId16"/>
-    <hyperlink ref="O37" r:id="rId17"/>
-    <hyperlink ref="O38" r:id="rId18"/>
-    <hyperlink ref="O40" r:id="rId19"/>
-    <hyperlink ref="O41" r:id="rId20"/>
-    <hyperlink ref="O12" r:id="rId21"/>
+    <hyperlink ref="O35" r:id="rId16"/>
+    <hyperlink ref="O36" r:id="rId17"/>
+    <hyperlink ref="O37" r:id="rId18"/>
+    <hyperlink ref="O38" r:id="rId19"/>
+    <hyperlink ref="O39" r:id="rId20"/>
+    <hyperlink ref="O10" r:id="rId21"/>
     <hyperlink ref="O14" r:id="rId22"/>
     <hyperlink ref="O17" r:id="rId23"/>
     <hyperlink ref="O24" r:id="rId24"/>
@@ -4145,18 +4020,16 @@
     <hyperlink ref="O32" r:id="rId28"/>
     <hyperlink ref="O33" r:id="rId29"/>
     <hyperlink ref="O34" r:id="rId30"/>
-    <hyperlink ref="O35" r:id="rId31"/>
-    <hyperlink ref="O39" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId33"/>
-  <drawing r:id="rId34"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>
+  <drawing r:id="rId32"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -4419,7 +4292,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="56"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -4428,17 +4301,17 @@
       <c r="C10" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="49" t="s">
-        <v>153</v>
+      <c r="D10" s="37" t="s">
+        <v>198</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>38</v>
+        <v>149</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="H10" s="37" t="s">
         <v>86</v>
@@ -4447,17 +4320,17 @@
         <v>134</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L10" s="37">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M10" s="37">
         <f>L10*5</f>
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="N10" s="37">
         <v>100</v>
@@ -4466,35 +4339,35 @@
         <v>136</v>
       </c>
       <c r="P10" s="38">
-        <v>5.1999999999999998E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="Q10" s="38">
         <f>P10*N10</f>
-        <v>0.52</v>
+        <v>0.18</v>
       </c>
       <c r="R10" s="37"/>
-      <c r="S10" s="57"/>
+      <c r="S10" s="55"/>
     </row>
     <row r="11" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="56"/>
       <c r="B11" s="46">
-        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
+        <f>ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="37" t="s">
-        <v>154</v>
+      <c r="D11" s="49" t="s">
+        <v>153</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11" s="37" t="s">
         <v>57</v>
       </c>
       <c r="G11" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H11" s="37" t="s">
         <v>86</v>
@@ -4503,54 +4376,54 @@
         <v>134</v>
       </c>
       <c r="J11" s="37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K11" s="37" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L11" s="37">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M11" s="37">
         <f>L11*5</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="N11" s="37">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="O11" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P11" s="38">
-        <v>0.15809999999999999</v>
+        <v>5.1999999999999998E-3</v>
       </c>
       <c r="Q11" s="38">
         <f>P11*N11</f>
-        <v>2.3714999999999997</v>
+        <v>0.52</v>
       </c>
       <c r="R11" s="37"/>
-      <c r="S11" s="55"/>
-    </row>
-    <row r="12" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="S11" s="57"/>
+    </row>
+    <row r="12" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="56"/>
       <c r="B12" s="46">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B12:B39" si="0">ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
       <c r="C12" s="67" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>149</v>
+        <v>39</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>150</v>
+        <v>57</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="H12" s="37" t="s">
         <v>86</v>
@@ -4559,30 +4432,30 @@
         <v>134</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L12" s="37">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M12" s="37">
         <f>L12*5</f>
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="N12" s="37">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="O12" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P12" s="38">
-        <v>1.8E-3</v>
+        <v>0.15809999999999999</v>
       </c>
       <c r="Q12" s="38">
         <f>P12*N12</f>
-        <v>0.18</v>
+        <v>2.3714999999999997</v>
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="55"/>
@@ -5263,38 +5136,38 @@
         <v>17</v>
       </c>
       <c r="D25" s="75" t="s">
+        <v>208</v>
+      </c>
+      <c r="E25" s="75" t="s">
         <v>172</v>
-      </c>
-      <c r="E25" s="75" t="s">
-        <v>173</v>
       </c>
       <c r="F25" s="75" t="s">
         <v>64</v>
       </c>
       <c r="G25" s="75" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25" s="75" t="s">
         <v>174</v>
       </c>
-      <c r="H25" s="75" t="s">
+      <c r="I25" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="I25" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="J25" s="75" t="s">
-        <v>176</v>
-      </c>
       <c r="K25" s="75" t="s">
         <v>134</v>
       </c>
       <c r="L25" s="75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M25" s="37">
         <f>L25*5</f>
+        <v>5</v>
+      </c>
+      <c r="N25" s="62">
         <v>10</v>
-      </c>
-      <c r="N25" s="62">
-        <v>20</v>
       </c>
       <c r="O25" s="66" t="s">
         <v>136</v>
@@ -5304,7 +5177,7 @@
       </c>
       <c r="Q25" s="63">
         <f>P25*N25</f>
-        <v>0.62</v>
+        <v>0.31</v>
       </c>
       <c r="R25" s="62"/>
       <c r="S25" s="64"/>
@@ -5319,7 +5192,7 @@
         <v>18</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>51</v>
@@ -5431,16 +5304,16 @@
         <v>18</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F28" s="37" t="s">
         <v>65</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H28" s="37" t="s">
         <v>86</v>
@@ -5449,10 +5322,10 @@
         <v>134</v>
       </c>
       <c r="J28" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="K28" s="37" t="s">
         <v>181</v>
-      </c>
-      <c r="K28" s="37" t="s">
-        <v>182</v>
       </c>
       <c r="L28" s="37">
         <v>3</v>
@@ -5487,7 +5360,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="70" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E29" s="37" t="s">
         <v>50</v>
@@ -5599,7 +5472,7 @@
         <v>18</v>
       </c>
       <c r="D31" s="49" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E31" s="49" t="s">
         <v>51</v>
@@ -5620,7 +5493,7 @@
         <v>112</v>
       </c>
       <c r="K31" s="49" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L31" s="49">
         <v>1</v>
@@ -5642,233 +5515,232 @@
         <v>134</v>
       </c>
       <c r="R31" s="76" t="s">
+        <v>183</v>
+      </c>
+      <c r="S31" s="55"/>
+    </row>
+    <row r="32" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="46">
+        <f>ROW(B32) - ROW($B$9)</f>
+        <v>23</v>
+      </c>
+      <c r="C32" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G32" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="H32" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="S31" s="55"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="72">
-        <f t="shared" ref="B32" si="15">ROW(B32) - ROW($B$9)</f>
-        <v>23</v>
-      </c>
-      <c r="C32" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="E32" s="49" t="s">
+      <c r="I32" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="K32" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L32" s="37">
+        <v>1</v>
+      </c>
+      <c r="M32" s="37">
+        <f>L32*5</f>
+        <v>5</v>
+      </c>
+      <c r="N32" s="37">
+        <v>10</v>
+      </c>
+      <c r="O32" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P32" s="38">
+        <v>0.1336</v>
+      </c>
+      <c r="Q32" s="38">
+        <f>P32*N32</f>
+        <v>1.3359999999999999</v>
+      </c>
+      <c r="R32" s="37"/>
+      <c r="S32" s="55"/>
+    </row>
+    <row r="33" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="72">
+        <f t="shared" ref="B33" si="15">ROW(B33) - ROW($B$9)</f>
+        <v>24</v>
+      </c>
+      <c r="C33" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="F32" s="49" t="s">
+      <c r="D33" s="49" t="s">
         <v>188</v>
       </c>
-      <c r="G32" s="49" t="s">
+      <c r="E33" s="49" t="s">
         <v>189</v>
       </c>
-      <c r="H32" s="49" t="s">
+      <c r="F33" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="G33" s="49" t="s">
         <v>190</v>
       </c>
-      <c r="I32" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J32" s="49" t="s">
+      <c r="H33" s="49" t="s">
         <v>191</v>
       </c>
-      <c r="K32" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="L32" s="49">
+      <c r="I33" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J33" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="K33" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L33" s="49">
         <v>2</v>
       </c>
-      <c r="M32" s="49">
-        <f t="shared" ref="M32" si="16">L32*5</f>
+      <c r="M33" s="49">
+        <f t="shared" ref="M33" si="16">L33*5</f>
         <v>10</v>
       </c>
-      <c r="N32" s="49">
+      <c r="N33" s="49">
         <v>20</v>
       </c>
-      <c r="O32" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P32" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q32" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="R32" s="76" t="s">
-        <v>184</v>
-      </c>
-      <c r="S32" s="55"/>
-    </row>
-    <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="46">
-        <f>ROW(B33) - ROW($B$9)</f>
-        <v>24</v>
-      </c>
-      <c r="C33" s="68" t="s">
-        <v>194</v>
-      </c>
-      <c r="D33" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="37" t="s">
-        <v>192</v>
-      </c>
-      <c r="F33" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G33" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="H33" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="I33" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J33" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="K33" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L33" s="37">
-        <v>1</v>
-      </c>
-      <c r="M33" s="37">
-        <f>L33*5</f>
-        <v>5</v>
-      </c>
-      <c r="N33" s="37">
-        <v>10</v>
-      </c>
-      <c r="O33" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P33" s="38">
-        <v>0.1336</v>
-      </c>
-      <c r="Q33" s="38">
-        <f>P33*N33</f>
-        <v>1.3359999999999999</v>
-      </c>
-      <c r="R33" s="37"/>
+      <c r="O33" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P33" s="50">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="Q33" s="50">
+        <f t="shared" ref="Q33" si="17">P33*N33</f>
+        <v>0.96600000000000008</v>
+      </c>
+      <c r="R33" s="49"/>
       <c r="S33" s="55"/>
     </row>
     <row r="34" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="72">
-        <f t="shared" ref="B34" si="17">ROW(B34) - ROW($B$9)</f>
+      <c r="B34" s="46">
+        <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="68" t="s">
+      <c r="C34" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="E34" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="D34" s="49" t="s">
+      <c r="F34" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="E34" s="49" t="s">
+      <c r="H34" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I34" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="F34" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="G34" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="H34" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="I34" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J34" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="K34" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="L34" s="49">
-        <v>2</v>
-      </c>
-      <c r="M34" s="49">
-        <f t="shared" ref="M34" si="18">L34*5</f>
+      <c r="K34" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L34" s="37">
+        <v>1</v>
+      </c>
+      <c r="M34" s="37">
+        <f>L34*5</f>
+        <v>5</v>
+      </c>
+      <c r="N34" s="37">
         <v>10</v>
       </c>
-      <c r="N34" s="49">
-        <v>20</v>
-      </c>
-      <c r="O34" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P34" s="50">
-        <v>4.8300000000000003E-2</v>
-      </c>
-      <c r="Q34" s="50">
-        <f t="shared" ref="Q34" si="19">P34*N34</f>
-        <v>0.96600000000000008</v>
-      </c>
-      <c r="R34" s="49"/>
+      <c r="O34" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P34" s="38">
+        <v>6.4600000000000005E-2</v>
+      </c>
+      <c r="Q34" s="38">
+        <f>P34*N34</f>
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="R34" s="37"/>
       <c r="S34" s="55"/>
     </row>
-    <row r="35" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
+    <row r="35" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="56"/>
       <c r="B35" s="46">
-        <f>ROW(B35) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="67" t="s">
-        <v>194</v>
-      </c>
-      <c r="D35" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="E35" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="F35" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="H35" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="I35" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J35" s="37" t="s">
-        <v>203</v>
+      <c r="C35" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="G35" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="H35" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="I35" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="49" t="s">
+        <v>114</v>
       </c>
       <c r="K35" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L35" s="37">
-        <v>1</v>
-      </c>
-      <c r="M35" s="37">
-        <f>L35*5</f>
+      <c r="L35" s="49">
+        <v>1</v>
+      </c>
+      <c r="M35" s="49">
+        <f t="shared" ref="M35" si="18">L35*5</f>
         <v>5</v>
       </c>
-      <c r="N35" s="37">
+      <c r="N35" s="49">
         <v>10</v>
       </c>
-      <c r="O35" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P35" s="38">
-        <v>6.4600000000000005E-2</v>
-      </c>
-      <c r="Q35" s="38">
-        <f>P35*N35</f>
-        <v>0.64600000000000002</v>
-      </c>
-      <c r="R35" s="37"/>
+      <c r="O35" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P35" s="50">
+        <v>0.2079</v>
+      </c>
+      <c r="Q35" s="50">
+        <f t="shared" ref="Q35" si="19">P35*N35</f>
+        <v>2.0790000000000002</v>
+      </c>
+      <c r="R35" s="49"/>
       <c r="S35" s="55"/>
     </row>
     <row r="36" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
@@ -5878,28 +5750,28 @@
         <v>27</v>
       </c>
       <c r="C36" s="68" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E36" s="49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F36" s="49" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G36" s="49" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H36" s="49" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I36" s="49" t="s">
         <v>134</v>
       </c>
       <c r="J36" s="49" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K36" s="37" t="s">
         <v>134</v>
@@ -5912,110 +5784,108 @@
         <v>5</v>
       </c>
       <c r="N36" s="49">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O36" s="60" t="s">
         <v>136</v>
       </c>
       <c r="P36" s="50">
-        <v>0.2079</v>
+        <v>0.54569999999999996</v>
       </c>
       <c r="Q36" s="50">
         <f t="shared" ref="Q36" si="21">P36*N36</f>
-        <v>2.0790000000000002</v>
+        <v>3.2741999999999996</v>
       </c>
       <c r="R36" s="49"/>
       <c r="S36" s="55"/>
     </row>
-    <row r="37" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="56"/>
       <c r="B37" s="46">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="68" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="E37" s="49" t="s">
-        <v>54</v>
-      </c>
-      <c r="F37" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="G37" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="H37" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="I37" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J37" s="49" t="s">
-        <v>115</v>
+      <c r="C37" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="F37" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G37" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="H37" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="I37" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J37" s="37" t="s">
+        <v>116</v>
       </c>
       <c r="K37" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L37" s="49">
-        <v>1</v>
-      </c>
-      <c r="M37" s="49">
-        <f t="shared" ref="M37" si="22">L37*5</f>
+      <c r="L37" s="37">
+        <v>1</v>
+      </c>
+      <c r="M37" s="37">
+        <f>L37*5</f>
         <v>5</v>
       </c>
-      <c r="N37" s="49">
+      <c r="N37" s="37">
         <v>6</v>
       </c>
-      <c r="O37" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P37" s="50">
-        <v>0.54569999999999996</v>
-      </c>
-      <c r="Q37" s="50">
-        <f t="shared" ref="Q37" si="23">P37*N37</f>
-        <v>3.2741999999999996</v>
-      </c>
-      <c r="R37" s="49"/>
-      <c r="S37" s="55"/>
-    </row>
-    <row r="38" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O37" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P37" s="38">
+        <v>2.8589000000000002</v>
+      </c>
+      <c r="Q37" s="38">
+        <f>P37*N37</f>
+        <v>17.153400000000001</v>
+      </c>
+      <c r="R37" s="37"/>
+      <c r="S37" s="39"/>
+    </row>
+    <row r="38" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="56"/>
       <c r="B38" s="46">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C38" s="67" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="I38" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="K38" s="37" t="s">
-        <v>134</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="K38" s="37"/>
       <c r="L38" s="37">
         <v>1</v>
       </c>
@@ -6024,54 +5894,52 @@
         <v>5</v>
       </c>
       <c r="N38" s="37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O38" s="59" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="P38" s="38">
-        <v>2.8589000000000002</v>
+        <v>3.28</v>
       </c>
       <c r="Q38" s="38">
         <f>P38*N38</f>
-        <v>17.153400000000001</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="39"/>
     </row>
-    <row r="39" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1"/>
+    <row r="39" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="56"/>
       <c r="B39" s="46">
-        <f>ROW(B39) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C39" s="67" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>205</v>
+        <v>148</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>206</v>
+        <v>134</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>207</v>
+        <v>134</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>208</v>
+        <v>134</v>
       </c>
       <c r="I39" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J39" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="K39" s="37" t="s">
-        <v>134</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="K39" s="37"/>
       <c r="L39" s="37">
         <v>1</v>
       </c>
@@ -6080,192 +5948,84 @@
         <v>5</v>
       </c>
       <c r="N39" s="37">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O39" s="59" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="P39" s="38">
-        <v>1.2776000000000001</v>
-      </c>
-      <c r="Q39" s="38">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="Q39" s="71">
         <f>P39*N39</f>
-        <v>7.6656000000000004</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="R39" s="37"/>
       <c r="S39" s="39"/>
     </row>
-    <row r="40" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="56"/>
-      <c r="B40" s="46">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="C40" s="67" t="s">
-        <v>144</v>
-      </c>
-      <c r="D40" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="E40" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="G40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="H40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="I40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="K40" s="37"/>
-      <c r="L40" s="37">
-        <v>1</v>
-      </c>
-      <c r="M40" s="37">
-        <f>L40*5</f>
+    <row r="40" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="44"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="45"/>
+      <c r="J40" s="44"/>
+      <c r="K40" s="45"/>
+      <c r="L40" s="45"/>
+      <c r="M40" s="45"/>
+      <c r="N40" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="N40" s="37">
-        <v>5</v>
-      </c>
-      <c r="O40" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="P40" s="38">
-        <v>3.28</v>
-      </c>
-      <c r="Q40" s="38">
-        <f>P40*N40</f>
-        <v>16.399999999999999</v>
-      </c>
-      <c r="R40" s="37"/>
-      <c r="S40" s="39"/>
-    </row>
-    <row r="41" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="56"/>
-      <c r="B41" s="46">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="C41" s="67" t="s">
-        <v>145</v>
-      </c>
-      <c r="D41" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="E41" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="G41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="H41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="I41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="K41" s="37"/>
-      <c r="L41" s="37">
-        <v>1</v>
-      </c>
-      <c r="M41" s="37">
-        <f>L41*5</f>
-        <v>5</v>
-      </c>
-      <c r="N41" s="37">
-        <v>1</v>
-      </c>
-      <c r="O41" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="P41" s="38">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="Q41" s="71">
-        <f>P41*N41</f>
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="R41" s="37"/>
-      <c r="S41" s="39"/>
-    </row>
-    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1"/>
-      <c r="B42" s="40"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="45"/>
-      <c r="M42" s="45"/>
-      <c r="N42" s="77" t="s">
-        <v>5</v>
-      </c>
-      <c r="O42" s="78"/>
-      <c r="P42" s="78"/>
-      <c r="Q42" s="47">
-        <f>SUM(Q10:Q41)</f>
-        <v>68.674000000000007</v>
-      </c>
-      <c r="R42" s="79"/>
-      <c r="S42" s="80"/>
-    </row>
-    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="77" t="s">
+      <c r="O40" s="78"/>
+      <c r="P40" s="78"/>
+      <c r="Q40" s="47">
+        <f>SUM(Q11:Q39)</f>
+        <v>60.518399999999993</v>
+      </c>
+      <c r="R40" s="79"/>
+      <c r="S40" s="80"/>
+    </row>
+    <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="O43" s="78"/>
-      <c r="P43" s="78"/>
-      <c r="Q43" s="48">
-        <f>Q42/5</f>
-        <v>13.734800000000002</v>
-      </c>
-      <c r="R43" s="81"/>
-      <c r="S43" s="82"/>
+      <c r="O41" s="78"/>
+      <c r="P41" s="78"/>
+      <c r="Q41" s="48">
+        <f>Q40/5</f>
+        <v>12.103679999999999</v>
+      </c>
+      <c r="R41" s="81"/>
+      <c r="S41" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S43"/>
-    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S41"/>
+    <mergeCell ref="N41:P41"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1"/>
-    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O11" r:id="rId1"/>
+    <hyperlink ref="O12" r:id="rId2"/>
     <hyperlink ref="O13" r:id="rId3"/>
     <hyperlink ref="O15" r:id="rId4"/>
     <hyperlink ref="O16" r:id="rId5"/>
@@ -6279,12 +6039,12 @@
     <hyperlink ref="O29" r:id="rId13"/>
     <hyperlink ref="O26" r:id="rId14"/>
     <hyperlink ref="O30" r:id="rId15"/>
-    <hyperlink ref="O36" r:id="rId16"/>
-    <hyperlink ref="O37" r:id="rId17"/>
-    <hyperlink ref="O38" r:id="rId18"/>
-    <hyperlink ref="O40" r:id="rId19"/>
-    <hyperlink ref="O41" r:id="rId20"/>
-    <hyperlink ref="O12" r:id="rId21"/>
+    <hyperlink ref="O35" r:id="rId16"/>
+    <hyperlink ref="O36" r:id="rId17"/>
+    <hyperlink ref="O37" r:id="rId18"/>
+    <hyperlink ref="O38" r:id="rId19"/>
+    <hyperlink ref="O39" r:id="rId20"/>
+    <hyperlink ref="O10" r:id="rId21"/>
     <hyperlink ref="O14" r:id="rId22"/>
     <hyperlink ref="O17" r:id="rId23"/>
     <hyperlink ref="O24" r:id="rId24"/>
@@ -6294,22 +6054,20 @@
     <hyperlink ref="O32" r:id="rId28"/>
     <hyperlink ref="O33" r:id="rId29"/>
     <hyperlink ref="O34" r:id="rId30"/>
-    <hyperlink ref="O35" r:id="rId31"/>
-    <hyperlink ref="O39" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId33"/>
-  <drawing r:id="rId34"/>
+  <pageSetup orientation="portrait" r:id="rId31"/>
+  <drawing r:id="rId32"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
     <col min="4" max="4" width="23.5703125" customWidth="1"/>
     <col min="5" max="5" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.140625" customWidth="1"/>
@@ -6320,7 +6078,7 @@
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.85546875" customWidth="1"/>
     <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -6547,19 +6305,19 @@
         <v>124</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="N9" s="30" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="O9" s="30" t="s">
         <v>129</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>130</v>
@@ -6568,7 +6326,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A10" s="56"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -6577,17 +6335,17 @@
       <c r="C10" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="49" t="s">
-        <v>153</v>
+      <c r="D10" s="37" t="s">
+        <v>198</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>38</v>
+        <v>149</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="H10" s="37" t="s">
         <v>86</v>
@@ -6596,54 +6354,54 @@
         <v>134</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L10" s="37">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M10" s="37">
         <f>L10*50</f>
-        <v>300</v>
+        <v>750</v>
       </c>
       <c r="N10" s="37">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="O10" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P10" s="38">
-        <v>5.4999999999999997E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="Q10" s="38">
         <f>P10*N10</f>
-        <v>2.1999999999999997</v>
+        <v>1.44</v>
       </c>
       <c r="R10" s="37"/>
-      <c r="S10" s="57"/>
+      <c r="S10" s="55"/>
     </row>
     <row r="11" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="56"/>
       <c r="B11" s="46">
-        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
+        <f>ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="37" t="s">
-        <v>154</v>
+      <c r="D11" s="49" t="s">
+        <v>153</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11" s="37" t="s">
         <v>57</v>
       </c>
       <c r="G11" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H11" s="37" t="s">
         <v>86</v>
@@ -6652,54 +6410,54 @@
         <v>134</v>
       </c>
       <c r="J11" s="37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K11" s="37" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L11" s="37">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M11" s="37">
-        <f t="shared" ref="M11:M41" si="1">L11*50</f>
-        <v>100</v>
+        <f>L11*50</f>
+        <v>300</v>
       </c>
       <c r="N11" s="37">
-        <v>110</v>
+        <v>400</v>
       </c>
       <c r="O11" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P11" s="38">
-        <v>0.13039999999999999</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="Q11" s="38">
         <f>P11*N11</f>
-        <v>14.343999999999999</v>
+        <v>2.1999999999999997</v>
       </c>
       <c r="R11" s="37"/>
-      <c r="S11" s="55"/>
-    </row>
-    <row r="12" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="S11" s="57"/>
+    </row>
+    <row r="12" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="56"/>
       <c r="B12" s="46">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B12:B39" si="0">ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
       <c r="C12" s="67" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>149</v>
+        <v>39</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>150</v>
+        <v>57</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="H12" s="37" t="s">
         <v>86</v>
@@ -6708,30 +6466,30 @@
         <v>134</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L12" s="37">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M12" s="37">
-        <f t="shared" si="1"/>
-        <v>750</v>
+        <f t="shared" ref="M12:M39" si="1">L12*50</f>
+        <v>100</v>
       </c>
       <c r="N12" s="37">
-        <v>800</v>
+        <v>110</v>
       </c>
       <c r="O12" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P12" s="38">
-        <v>1.8E-3</v>
+        <v>0.13039999999999999</v>
       </c>
       <c r="Q12" s="38">
         <f>P12*N12</f>
-        <v>1.44</v>
+        <v>14.343999999999999</v>
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="55"/>
@@ -7412,48 +7170,48 @@
         <v>17</v>
       </c>
       <c r="D25" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="E25" s="49" t="s">
         <v>172</v>
-      </c>
-      <c r="E25" s="49" t="s">
-        <v>173</v>
       </c>
       <c r="F25" s="49" t="s">
         <v>64</v>
       </c>
       <c r="G25" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25" s="49" t="s">
         <v>174</v>
       </c>
-      <c r="H25" s="49" t="s">
+      <c r="I25" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="49" t="s">
         <v>175</v>
       </c>
-      <c r="I25" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J25" s="49" t="s">
-        <v>176</v>
-      </c>
       <c r="K25" s="49" t="s">
         <v>134</v>
       </c>
       <c r="L25" s="49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M25" s="37">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N25" s="37">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="O25" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P25" s="38">
-        <v>2.53E-2</v>
+        <v>3.2599999999999997E-2</v>
       </c>
       <c r="Q25" s="38">
         <f>P25*N25</f>
-        <v>2.7829999999999999</v>
+        <v>1.9559999999999997</v>
       </c>
       <c r="R25" s="37"/>
       <c r="S25" s="55"/>
@@ -7468,7 +7226,7 @@
         <v>18</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>51</v>
@@ -7580,16 +7338,16 @@
         <v>18</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F28" s="37" t="s">
         <v>65</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H28" s="37" t="s">
         <v>86</v>
@@ -7598,10 +7356,10 @@
         <v>134</v>
       </c>
       <c r="J28" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="K28" s="37" t="s">
         <v>181</v>
-      </c>
-      <c r="K28" s="37" t="s">
-        <v>182</v>
       </c>
       <c r="L28" s="37">
         <v>3</v>
@@ -7636,7 +7394,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="70" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E29" s="37" t="s">
         <v>50</v>
@@ -7741,14 +7499,14 @@
     <row r="31" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="56"/>
       <c r="B31" s="72">
-        <f t="shared" ref="B31:B32" si="8">ROW(B31) - ROW($B$9)</f>
+        <f t="shared" ref="B31" si="8">ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
       <c r="C31" s="68" t="s">
         <v>18</v>
       </c>
       <c r="D31" s="49" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E31" s="49" t="s">
         <v>51</v>
@@ -7769,7 +7527,7 @@
         <v>112</v>
       </c>
       <c r="K31" s="49" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L31" s="49">
         <v>1</v>
@@ -7791,264 +7549,263 @@
         <v>134</v>
       </c>
       <c r="R31" s="76" t="s">
+        <v>183</v>
+      </c>
+      <c r="S31" s="55"/>
+    </row>
+    <row r="32" spans="1:19" s="58" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="56"/>
+      <c r="B32" s="46">
+        <f>ROW(B32) - ROW($B$9)</f>
+        <v>23</v>
+      </c>
+      <c r="C32" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G32" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="H32" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="S31" s="55"/>
-    </row>
-    <row r="32" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="56"/>
-      <c r="B32" s="72">
-        <f t="shared" si="8"/>
-        <v>23</v>
-      </c>
-      <c r="C32" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="E32" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="F32" s="49" t="s">
-        <v>188</v>
-      </c>
-      <c r="G32" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="H32" s="49" t="s">
-        <v>190</v>
-      </c>
-      <c r="I32" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J32" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="K32" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="L32" s="49">
-        <v>2</v>
+      <c r="I32" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="K32" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L32" s="37">
+        <v>1</v>
       </c>
       <c r="M32" s="37">
         <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="N32" s="49">
-        <v>20</v>
-      </c>
-      <c r="O32" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P32" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q32" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="R32" s="76" t="s">
-        <v>184</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="N32" s="37">
+        <v>55</v>
+      </c>
+      <c r="O32" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P32" s="38">
+        <v>0.1336</v>
+      </c>
+      <c r="Q32" s="38">
+        <f>P32*N32</f>
+        <v>7.3479999999999999</v>
+      </c>
+      <c r="R32" s="37"/>
       <c r="S32" s="55"/>
     </row>
-    <row r="33" spans="1:19" s="58" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A33" s="56"/>
-      <c r="B33" s="46">
-        <f>ROW(B33) - ROW($B$9)</f>
+      <c r="B33" s="72">
+        <f t="shared" ref="B33" si="9">ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
       <c r="C33" s="68" t="s">
-        <v>194</v>
-      </c>
-      <c r="D33" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="E33" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="F33" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="G33" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="H33" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="I33" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J33" s="49" t="s">
         <v>192</v>
       </c>
-      <c r="F33" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G33" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="H33" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="I33" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J33" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="K33" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L33" s="37">
-        <v>1</v>
+      <c r="K33" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L33" s="49">
+        <v>2</v>
       </c>
       <c r="M33" s="37">
         <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="N33" s="37">
-        <v>55</v>
-      </c>
-      <c r="O33" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P33" s="38">
-        <v>0.1336</v>
-      </c>
-      <c r="Q33" s="38">
-        <f>P33*N33</f>
-        <v>7.3479999999999999</v>
-      </c>
-      <c r="R33" s="37"/>
+        <v>100</v>
+      </c>
+      <c r="N33" s="49">
+        <v>110</v>
+      </c>
+      <c r="O33" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P33" s="50">
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="Q33" s="50">
+        <f t="shared" ref="Q33" si="10">P33*N33</f>
+        <v>4.5540000000000003</v>
+      </c>
+      <c r="R33" s="49"/>
       <c r="S33" s="55"/>
     </row>
     <row r="34" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A34" s="56"/>
-      <c r="B34" s="72">
-        <f t="shared" ref="B34" si="9">ROW(B34) - ROW($B$9)</f>
+      <c r="B34" s="46">
+        <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="68" t="s">
+      <c r="C34" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="E34" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="D34" s="49" t="s">
+      <c r="F34" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="E34" s="49" t="s">
+      <c r="H34" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I34" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="F34" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="G34" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="H34" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="I34" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J34" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="K34" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="L34" s="49">
-        <v>2</v>
+      <c r="K34" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L34" s="37">
+        <v>1</v>
       </c>
       <c r="M34" s="37">
         <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="N34" s="49">
-        <v>110</v>
-      </c>
-      <c r="O34" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P34" s="50">
-        <v>4.1399999999999999E-2</v>
-      </c>
-      <c r="Q34" s="50">
-        <f t="shared" ref="Q34" si="10">P34*N34</f>
-        <v>4.5540000000000003</v>
-      </c>
-      <c r="R34" s="49"/>
+        <v>50</v>
+      </c>
+      <c r="N34" s="37">
+        <v>60</v>
+      </c>
+      <c r="O34" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P34" s="38">
+        <v>6.4600000000000005E-2</v>
+      </c>
+      <c r="Q34" s="38">
+        <f>P34*N34</f>
+        <v>3.8760000000000003</v>
+      </c>
+      <c r="R34" s="37"/>
       <c r="S34" s="55"/>
     </row>
-    <row r="35" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="56"/>
       <c r="B35" s="46">
-        <f>ROW(B35) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="67" t="s">
-        <v>194</v>
-      </c>
-      <c r="D35" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="E35" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="F35" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="H35" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="I35" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J35" s="37" t="s">
-        <v>203</v>
+      <c r="C35" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="G35" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="H35" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="I35" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="49" t="s">
+        <v>114</v>
       </c>
       <c r="K35" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L35" s="37">
+      <c r="L35" s="49">
         <v>1</v>
       </c>
       <c r="M35" s="37">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N35" s="37">
-        <v>60</v>
-      </c>
-      <c r="O35" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P35" s="38">
-        <v>6.4600000000000005E-2</v>
-      </c>
-      <c r="Q35" s="38">
-        <f>P35*N35</f>
-        <v>3.8760000000000003</v>
-      </c>
-      <c r="R35" s="37"/>
+      <c r="N35" s="49">
+        <v>55</v>
+      </c>
+      <c r="O35" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P35" s="50">
+        <v>0.14460000000000001</v>
+      </c>
+      <c r="Q35" s="50">
+        <f t="shared" ref="Q35:Q36" si="11">P35*N35</f>
+        <v>7.9530000000000003</v>
+      </c>
+      <c r="R35" s="49"/>
       <c r="S35" s="55"/>
     </row>
-    <row r="36" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A36" s="56"/>
       <c r="B36" s="46">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C36" s="68" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E36" s="49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F36" s="49" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G36" s="49" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H36" s="49" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I36" s="49" t="s">
         <v>134</v>
       </c>
       <c r="J36" s="49" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K36" s="37" t="s">
         <v>134</v>
@@ -8061,110 +7818,108 @@
         <v>50</v>
       </c>
       <c r="N36" s="49">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O36" s="60" t="s">
         <v>136</v>
       </c>
       <c r="P36" s="50">
-        <v>0.14460000000000001</v>
+        <v>0.4073</v>
       </c>
       <c r="Q36" s="50">
-        <f t="shared" ref="Q36:Q37" si="11">P36*N36</f>
-        <v>7.9530000000000003</v>
+        <f t="shared" si="11"/>
+        <v>21.179600000000001</v>
       </c>
       <c r="R36" s="49"/>
       <c r="S36" s="55"/>
     </row>
-    <row r="37" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="56"/>
       <c r="B37" s="46">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="68" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="E37" s="49" t="s">
-        <v>54</v>
-      </c>
-      <c r="F37" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="G37" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="H37" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="I37" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J37" s="49" t="s">
-        <v>115</v>
+      <c r="C37" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="F37" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G37" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="H37" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="I37" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J37" s="37" t="s">
+        <v>116</v>
       </c>
       <c r="K37" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L37" s="49">
+      <c r="L37" s="37">
         <v>1</v>
       </c>
       <c r="M37" s="37">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N37" s="49">
+      <c r="N37" s="37">
         <v>52</v>
       </c>
-      <c r="O37" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P37" s="50">
-        <v>0.4073</v>
-      </c>
-      <c r="Q37" s="50">
-        <f t="shared" si="11"/>
-        <v>21.179600000000001</v>
-      </c>
-      <c r="R37" s="49"/>
-      <c r="S37" s="55"/>
-    </row>
-    <row r="38" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O37" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P37" s="38">
+        <v>2.7953000000000001</v>
+      </c>
+      <c r="Q37" s="38">
+        <f>P37*N37</f>
+        <v>145.35560000000001</v>
+      </c>
+      <c r="R37" s="37"/>
+      <c r="S37" s="39"/>
+    </row>
+    <row r="38" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="56"/>
       <c r="B38" s="46">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C38" s="67" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="I38" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="K38" s="37" t="s">
-        <v>134</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="K38" s="37"/>
       <c r="L38" s="37">
         <v>1</v>
       </c>
@@ -8176,51 +7931,49 @@
         <v>52</v>
       </c>
       <c r="O38" s="59" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="P38" s="38">
-        <v>2.7953000000000001</v>
+        <v>3.28</v>
       </c>
       <c r="Q38" s="38">
         <f>P38*N38</f>
-        <v>145.35560000000001</v>
+        <v>170.56</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="39"/>
     </row>
-    <row r="39" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="56"/>
       <c r="B39" s="46">
-        <f>ROW(B39) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C39" s="67" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>205</v>
+        <v>148</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>206</v>
+        <v>134</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>207</v>
+        <v>134</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>208</v>
+        <v>134</v>
       </c>
       <c r="I39" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J39" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="K39" s="37" t="s">
-        <v>134</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="K39" s="37"/>
       <c r="L39" s="37">
         <v>1</v>
       </c>
@@ -8229,192 +7982,84 @@
         <v>50</v>
       </c>
       <c r="N39" s="37">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="O39" s="59" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="P39" s="38">
-        <v>0.98480000000000001</v>
-      </c>
-      <c r="Q39" s="38">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="Q39" s="71">
         <f>P39*N39</f>
-        <v>51.209600000000002</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="R39" s="37"/>
       <c r="S39" s="39"/>
     </row>
-    <row r="40" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="56"/>
-      <c r="B40" s="46">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="C40" s="67" t="s">
-        <v>144</v>
-      </c>
-      <c r="D40" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="E40" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="G40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="H40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="I40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="K40" s="37"/>
-      <c r="L40" s="37">
-        <v>1</v>
-      </c>
-      <c r="M40" s="37">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="N40" s="37">
-        <v>52</v>
-      </c>
-      <c r="O40" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="P40" s="38">
-        <v>3.28</v>
-      </c>
-      <c r="Q40" s="38">
-        <f>P40*N40</f>
-        <v>170.56</v>
-      </c>
-      <c r="R40" s="37"/>
-      <c r="S40" s="39"/>
-    </row>
-    <row r="41" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="56"/>
-      <c r="B41" s="46">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="C41" s="67" t="s">
-        <v>145</v>
-      </c>
-      <c r="D41" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="E41" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="G41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="H41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="I41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="K41" s="37"/>
-      <c r="L41" s="37">
-        <v>1</v>
-      </c>
-      <c r="M41" s="37">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="N41" s="37">
-        <v>1</v>
-      </c>
-      <c r="O41" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="P41" s="38">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="Q41" s="71">
-        <f>P41*N41</f>
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="R41" s="37"/>
-      <c r="S41" s="39"/>
-    </row>
-    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1"/>
-      <c r="B42" s="40"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="45"/>
-      <c r="M42" s="45"/>
-      <c r="N42" s="77" t="s">
+    <row r="40" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="44"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="45"/>
+      <c r="J40" s="44"/>
+      <c r="K40" s="45"/>
+      <c r="L40" s="45"/>
+      <c r="M40" s="45"/>
+      <c r="N40" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="O42" s="78"/>
-      <c r="P42" s="78"/>
-      <c r="Q42" s="47">
-        <f>SUM(Q10:Q41)</f>
-        <v>497.37170000000009</v>
-      </c>
-      <c r="R42" s="79"/>
-      <c r="S42" s="80"/>
-    </row>
-    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="77" t="s">
+      <c r="O40" s="78"/>
+      <c r="P40" s="78"/>
+      <c r="Q40" s="47">
+        <f>SUM(Q11:Q39)</f>
+        <v>443.89510000000001</v>
+      </c>
+      <c r="R40" s="79"/>
+      <c r="S40" s="80"/>
+    </row>
+    <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="O43" s="78"/>
-      <c r="P43" s="78"/>
-      <c r="Q43" s="48">
-        <f>Q42/50</f>
-        <v>9.9474340000000012</v>
-      </c>
-      <c r="R43" s="81"/>
-      <c r="S43" s="82"/>
+      <c r="O41" s="78"/>
+      <c r="P41" s="78"/>
+      <c r="Q41" s="48">
+        <f>Q40/50</f>
+        <v>8.8779020000000006</v>
+      </c>
+      <c r="R41" s="81"/>
+      <c r="S41" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S43"/>
-    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S41"/>
+    <mergeCell ref="N41:P41"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1"/>
-    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O11" r:id="rId1"/>
+    <hyperlink ref="O12" r:id="rId2"/>
     <hyperlink ref="O13" r:id="rId3"/>
     <hyperlink ref="O15" r:id="rId4"/>
     <hyperlink ref="O16" r:id="rId5"/>
@@ -8428,12 +8073,12 @@
     <hyperlink ref="O29" r:id="rId13"/>
     <hyperlink ref="O26" r:id="rId14"/>
     <hyperlink ref="O30" r:id="rId15"/>
-    <hyperlink ref="O36" r:id="rId16"/>
-    <hyperlink ref="O37" r:id="rId17"/>
-    <hyperlink ref="O38" r:id="rId18"/>
-    <hyperlink ref="O40" r:id="rId19"/>
-    <hyperlink ref="O41" r:id="rId20"/>
-    <hyperlink ref="O12" r:id="rId21"/>
+    <hyperlink ref="O35" r:id="rId16"/>
+    <hyperlink ref="O36" r:id="rId17"/>
+    <hyperlink ref="O37" r:id="rId18"/>
+    <hyperlink ref="O38" r:id="rId19"/>
+    <hyperlink ref="O39" r:id="rId20"/>
+    <hyperlink ref="O10" r:id="rId21"/>
     <hyperlink ref="O14" r:id="rId22"/>
     <hyperlink ref="O17" r:id="rId23"/>
     <hyperlink ref="O24" r:id="rId24"/>
@@ -8443,18 +8088,16 @@
     <hyperlink ref="O32" r:id="rId28"/>
     <hyperlink ref="O33" r:id="rId29"/>
     <hyperlink ref="O34" r:id="rId30"/>
-    <hyperlink ref="O35" r:id="rId31"/>
-    <hyperlink ref="O39" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId33"/>
-  <drawing r:id="rId34"/>
+  <pageSetup orientation="portrait" r:id="rId31"/>
+  <drawing r:id="rId32"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -8696,19 +8339,19 @@
         <v>124</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="N9" s="30" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="O9" s="30" t="s">
         <v>129</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>130</v>
@@ -8717,7 +8360,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="56"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -8726,17 +8369,17 @@
       <c r="C10" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="49" t="s">
-        <v>153</v>
+      <c r="D10" s="70" t="s">
+        <v>198</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>38</v>
+        <v>149</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="H10" s="37" t="s">
         <v>86</v>
@@ -8745,54 +8388,54 @@
         <v>134</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L10" s="37">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M10" s="37">
         <f>L10*500</f>
-        <v>3000</v>
+        <v>7500</v>
       </c>
       <c r="N10" s="37">
-        <v>3100</v>
+        <v>7600</v>
       </c>
       <c r="O10" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P10" s="38">
-        <v>4.4000000000000003E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q10" s="38">
         <f>P10*N10</f>
-        <v>13.64</v>
+        <v>9.879999999999999</v>
       </c>
       <c r="R10" s="37"/>
-      <c r="S10" s="57"/>
+      <c r="S10" s="55"/>
     </row>
     <row r="11" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="56"/>
       <c r="B11" s="46">
-        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
+        <f>ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="37" t="s">
-        <v>154</v>
+      <c r="D11" s="69" t="s">
+        <v>153</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11" s="37" t="s">
         <v>57</v>
       </c>
       <c r="G11" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H11" s="37" t="s">
         <v>86</v>
@@ -8801,54 +8444,54 @@
         <v>134</v>
       </c>
       <c r="J11" s="37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K11" s="37" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L11" s="37">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M11" s="37">
-        <f t="shared" ref="M11:M41" si="1">L11*500</f>
-        <v>1000</v>
+        <f>L11*500</f>
+        <v>3000</v>
       </c>
       <c r="N11" s="37">
-        <v>1050</v>
+        <v>3100</v>
       </c>
       <c r="O11" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P11" s="38">
-        <v>9.8500000000000004E-2</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="Q11" s="38">
         <f>P11*N11</f>
-        <v>103.42500000000001</v>
+        <v>13.64</v>
       </c>
       <c r="R11" s="37"/>
-      <c r="S11" s="55"/>
-    </row>
-    <row r="12" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="S11" s="57"/>
+    </row>
+    <row r="12" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="56"/>
       <c r="B12" s="46">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B12:B39" si="0">ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
       <c r="C12" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="37" t="s">
-        <v>211</v>
+      <c r="D12" s="70" t="s">
+        <v>154</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>149</v>
+        <v>39</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>150</v>
+        <v>57</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="H12" s="37" t="s">
         <v>86</v>
@@ -8857,30 +8500,30 @@
         <v>134</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L12" s="37">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M12" s="37">
-        <f t="shared" si="1"/>
-        <v>7500</v>
+        <f t="shared" ref="M12:M39" si="1">L12*500</f>
+        <v>1000</v>
       </c>
       <c r="N12" s="37">
-        <v>7600</v>
+        <v>1050</v>
       </c>
       <c r="O12" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P12" s="38">
-        <v>1.2999999999999999E-3</v>
+        <v>9.8500000000000004E-2</v>
       </c>
       <c r="Q12" s="38">
         <f>P12*N12</f>
-        <v>9.879999999999999</v>
+        <v>103.42500000000001</v>
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="55"/>
@@ -8950,7 +8593,7 @@
       <c r="C14" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="69" t="s">
         <v>155</v>
       </c>
       <c r="E14" s="49" t="s">
@@ -9051,7 +8694,7 @@
       <c r="R15" s="37"/>
       <c r="S15" s="55"/>
     </row>
-    <row r="16" spans="1:19" s="58" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A16" s="56"/>
       <c r="B16" s="46">
         <f t="shared" si="0"/>
@@ -9116,7 +8759,7 @@
       <c r="C17" s="67" t="s">
         <v>161</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="D17" s="70" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="37" t="s">
@@ -9504,7 +9147,7 @@
       <c r="C24" s="67" t="s">
         <v>166</v>
       </c>
-      <c r="D24" s="37" t="s">
+      <c r="D24" s="70" t="s">
         <v>167</v>
       </c>
       <c r="E24" s="37" t="s">
@@ -9560,36 +9203,36 @@
       <c r="C25" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="49" t="s">
+      <c r="D25" s="69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E25" s="49" t="s">
         <v>172</v>
-      </c>
-      <c r="E25" s="49" t="s">
-        <v>173</v>
       </c>
       <c r="F25" s="49" t="s">
         <v>64</v>
       </c>
       <c r="G25" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25" s="49" t="s">
         <v>174</v>
       </c>
-      <c r="H25" s="49" t="s">
+      <c r="I25" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="49" t="s">
         <v>175</v>
       </c>
-      <c r="I25" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J25" s="49" t="s">
-        <v>176</v>
-      </c>
       <c r="K25" s="49" t="s">
         <v>134</v>
       </c>
       <c r="L25" s="49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M25" s="37">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="N25" s="37">
         <v>20</v>
@@ -9616,8 +9259,8 @@
       <c r="C26" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="37" t="s">
-        <v>177</v>
+      <c r="D26" s="70" t="s">
+        <v>176</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>51</v>
@@ -9728,17 +9371,17 @@
       <c r="C28" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="37" t="s">
-        <v>212</v>
+      <c r="D28" s="70" t="s">
+        <v>199</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F28" s="37" t="s">
         <v>65</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H28" s="37" t="s">
         <v>86</v>
@@ -9747,10 +9390,10 @@
         <v>134</v>
       </c>
       <c r="J28" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="K28" s="37" t="s">
         <v>181</v>
-      </c>
-      <c r="K28" s="37" t="s">
-        <v>182</v>
       </c>
       <c r="L28" s="37">
         <v>3</v>
@@ -9785,7 +9428,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="70" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E29" s="37" t="s">
         <v>50</v>
@@ -9890,14 +9533,14 @@
     <row r="31" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="56"/>
       <c r="B31" s="72">
-        <f t="shared" ref="B31:B32" si="8">ROW(B31) - ROW($B$9)</f>
+        <f t="shared" ref="B31" si="8">ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
       <c r="C31" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="49" t="s">
-        <v>183</v>
+      <c r="D31" s="69" t="s">
+        <v>182</v>
       </c>
       <c r="E31" s="49" t="s">
         <v>51</v>
@@ -9918,7 +9561,7 @@
         <v>112</v>
       </c>
       <c r="K31" s="49" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L31" s="49">
         <v>1</v>
@@ -9940,233 +9583,232 @@
         <v>134</v>
       </c>
       <c r="R31" s="76" t="s">
+        <v>183</v>
+      </c>
+      <c r="S31" s="55"/>
+    </row>
+    <row r="32" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A32" s="56"/>
+      <c r="B32" s="46">
+        <f>ROW(B32) - ROW($B$9)</f>
+        <v>23</v>
+      </c>
+      <c r="C32" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" s="70" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G32" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="H32" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="S31" s="55"/>
-    </row>
-    <row r="32" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="56"/>
-      <c r="B32" s="72">
-        <f t="shared" si="8"/>
-        <v>23</v>
-      </c>
-      <c r="C32" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="E32" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="F32" s="49" t="s">
-        <v>188</v>
-      </c>
-      <c r="G32" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="H32" s="49" t="s">
-        <v>190</v>
-      </c>
-      <c r="I32" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J32" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="K32" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="L32" s="49">
-        <v>2</v>
+      <c r="I32" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="K32" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L32" s="37">
+        <v>1</v>
       </c>
       <c r="M32" s="37">
         <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N32" s="49">
-        <v>20</v>
-      </c>
-      <c r="O32" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P32" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q32" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="R32" s="76" t="s">
-        <v>184</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="N32" s="37">
+        <v>10</v>
+      </c>
+      <c r="O32" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P32" s="38">
+        <v>0.1336</v>
+      </c>
+      <c r="Q32" s="38">
+        <f>P32*N32</f>
+        <v>1.3359999999999999</v>
+      </c>
+      <c r="R32" s="37"/>
       <c r="S32" s="55"/>
     </row>
-    <row r="33" spans="1:19" s="58" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A33" s="56"/>
-      <c r="B33" s="46">
-        <f>ROW(B33) - ROW($B$9)</f>
+      <c r="B33" s="72">
+        <f t="shared" ref="B33" si="9">ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
       <c r="C33" s="68" t="s">
-        <v>194</v>
-      </c>
-      <c r="D33" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" s="69" t="s">
+        <v>188</v>
+      </c>
+      <c r="E33" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="F33" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="G33" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="H33" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="I33" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J33" s="49" t="s">
         <v>192</v>
       </c>
-      <c r="F33" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G33" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="H33" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="I33" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J33" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="K33" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L33" s="37">
-        <v>1</v>
+      <c r="K33" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L33" s="49">
+        <v>2</v>
       </c>
       <c r="M33" s="37">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="N33" s="37">
-        <v>10</v>
-      </c>
-      <c r="O33" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P33" s="38">
-        <v>0.1336</v>
-      </c>
-      <c r="Q33" s="38">
-        <f>P33*N33</f>
-        <v>1.3359999999999999</v>
-      </c>
-      <c r="R33" s="37"/>
+        <v>1000</v>
+      </c>
+      <c r="N33" s="49">
+        <v>20</v>
+      </c>
+      <c r="O33" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P33" s="50">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="Q33" s="50">
+        <f t="shared" ref="Q33" si="10">P33*N33</f>
+        <v>0.96600000000000008</v>
+      </c>
+      <c r="R33" s="49"/>
       <c r="S33" s="55"/>
     </row>
     <row r="34" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A34" s="56"/>
-      <c r="B34" s="72">
-        <f t="shared" ref="B34" si="9">ROW(B34) - ROW($B$9)</f>
+      <c r="B34" s="46">
+        <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="68" t="s">
+      <c r="C34" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" s="70" t="s">
+        <v>193</v>
+      </c>
+      <c r="E34" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="D34" s="49" t="s">
+      <c r="F34" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="E34" s="49" t="s">
+      <c r="H34" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I34" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="F34" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="G34" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="H34" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="I34" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J34" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="K34" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="L34" s="49">
-        <v>2</v>
+      <c r="K34" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L34" s="37">
+        <v>1</v>
       </c>
       <c r="M34" s="37">
         <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N34" s="49">
-        <v>20</v>
-      </c>
-      <c r="O34" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P34" s="50">
-        <v>4.8300000000000003E-2</v>
-      </c>
-      <c r="Q34" s="50">
-        <f t="shared" ref="Q34" si="10">P34*N34</f>
-        <v>0.96600000000000008</v>
-      </c>
-      <c r="R34" s="49"/>
+        <v>500</v>
+      </c>
+      <c r="N34" s="37">
+        <v>10</v>
+      </c>
+      <c r="O34" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P34" s="38">
+        <v>6.4600000000000005E-2</v>
+      </c>
+      <c r="Q34" s="38">
+        <f>P34*N34</f>
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="R34" s="37"/>
       <c r="S34" s="55"/>
     </row>
-    <row r="35" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="56"/>
       <c r="B35" s="46">
-        <f>ROW(B35) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="67" t="s">
-        <v>194</v>
-      </c>
-      <c r="D35" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="E35" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="F35" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="H35" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="I35" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J35" s="37" t="s">
-        <v>203</v>
+      <c r="C35" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="G35" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="H35" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="I35" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="49" t="s">
+        <v>114</v>
       </c>
       <c r="K35" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L35" s="37">
+      <c r="L35" s="49">
         <v>1</v>
       </c>
       <c r="M35" s="37">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N35" s="37">
+      <c r="N35" s="49">
         <v>10</v>
       </c>
-      <c r="O35" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P35" s="38">
-        <v>6.4600000000000005E-2</v>
-      </c>
-      <c r="Q35" s="38">
-        <f>P35*N35</f>
-        <v>0.64600000000000002</v>
-      </c>
-      <c r="R35" s="37"/>
+      <c r="O35" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P35" s="50">
+        <v>0.2079</v>
+      </c>
+      <c r="Q35" s="50">
+        <f t="shared" ref="Q35:Q36" si="11">P35*N35</f>
+        <v>2.0790000000000002</v>
+      </c>
+      <c r="R35" s="49"/>
       <c r="S35" s="55"/>
     </row>
     <row r="36" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
@@ -10176,28 +9818,28 @@
         <v>27</v>
       </c>
       <c r="C36" s="68" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E36" s="49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F36" s="49" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G36" s="49" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H36" s="49" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I36" s="49" t="s">
         <v>134</v>
       </c>
       <c r="J36" s="49" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K36" s="37" t="s">
         <v>134</v>
@@ -10210,110 +9852,108 @@
         <v>500</v>
       </c>
       <c r="N36" s="49">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O36" s="60" t="s">
         <v>136</v>
       </c>
       <c r="P36" s="50">
-        <v>0.2079</v>
+        <v>0.54569999999999996</v>
       </c>
       <c r="Q36" s="50">
-        <f t="shared" ref="Q36:Q37" si="11">P36*N36</f>
-        <v>2.0790000000000002</v>
+        <f t="shared" si="11"/>
+        <v>3.2741999999999996</v>
       </c>
       <c r="R36" s="49"/>
       <c r="S36" s="55"/>
     </row>
-    <row r="37" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="56"/>
       <c r="B37" s="46">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="68" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="E37" s="49" t="s">
-        <v>54</v>
-      </c>
-      <c r="F37" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="G37" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="H37" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="I37" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J37" s="49" t="s">
-        <v>115</v>
+      <c r="C37" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="F37" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G37" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="H37" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="I37" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J37" s="37" t="s">
+        <v>116</v>
       </c>
       <c r="K37" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L37" s="49">
+      <c r="L37" s="37">
         <v>1</v>
       </c>
       <c r="M37" s="37">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N37" s="49">
+      <c r="N37" s="37">
         <v>6</v>
       </c>
-      <c r="O37" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P37" s="50">
-        <v>0.54569999999999996</v>
-      </c>
-      <c r="Q37" s="50">
-        <f t="shared" si="11"/>
-        <v>3.2741999999999996</v>
-      </c>
-      <c r="R37" s="49"/>
-      <c r="S37" s="55"/>
-    </row>
-    <row r="38" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O37" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P37" s="38">
+        <v>2.8589000000000002</v>
+      </c>
+      <c r="Q37" s="38">
+        <f>P37*N37</f>
+        <v>17.153400000000001</v>
+      </c>
+      <c r="R37" s="37"/>
+      <c r="S37" s="39"/>
+    </row>
+    <row r="38" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="56"/>
       <c r="B38" s="46">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C38" s="67" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="I38" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="K38" s="37" t="s">
-        <v>134</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="K38" s="37"/>
       <c r="L38" s="37">
         <v>1</v>
       </c>
@@ -10322,54 +9962,52 @@
         <v>500</v>
       </c>
       <c r="N38" s="37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O38" s="59" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="P38" s="38">
-        <v>2.8589000000000002</v>
+        <v>3.28</v>
       </c>
       <c r="Q38" s="38">
         <f>P38*N38</f>
-        <v>17.153400000000001</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="39"/>
     </row>
-    <row r="39" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="56"/>
       <c r="B39" s="46">
-        <f>ROW(B39) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C39" s="67" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>205</v>
+        <v>148</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>206</v>
+        <v>134</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>207</v>
+        <v>134</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>208</v>
+        <v>134</v>
       </c>
       <c r="I39" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J39" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="K39" s="37" t="s">
-        <v>134</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="K39" s="37"/>
       <c r="L39" s="37">
         <v>1</v>
       </c>
@@ -10378,192 +10016,84 @@
         <v>500</v>
       </c>
       <c r="N39" s="37">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O39" s="59" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="P39" s="38">
-        <v>1.2776000000000001</v>
-      </c>
-      <c r="Q39" s="38">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="Q39" s="71">
         <f>P39*N39</f>
-        <v>7.6656000000000004</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="R39" s="37"/>
       <c r="S39" s="39"/>
     </row>
-    <row r="40" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="56"/>
-      <c r="B40" s="46">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="C40" s="67" t="s">
-        <v>144</v>
-      </c>
-      <c r="D40" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="E40" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="G40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="H40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="I40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="K40" s="37"/>
-      <c r="L40" s="37">
-        <v>1</v>
-      </c>
-      <c r="M40" s="37">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="N40" s="37">
+    <row r="40" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="44"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="45"/>
+      <c r="J40" s="44"/>
+      <c r="K40" s="45"/>
+      <c r="L40" s="45"/>
+      <c r="M40" s="45"/>
+      <c r="N40" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="O40" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="P40" s="38">
-        <v>3.28</v>
-      </c>
-      <c r="Q40" s="38">
-        <f>P40*N40</f>
-        <v>16.399999999999999</v>
-      </c>
-      <c r="R40" s="37"/>
-      <c r="S40" s="39"/>
-    </row>
-    <row r="41" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="56"/>
-      <c r="B41" s="46">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="C41" s="67" t="s">
-        <v>145</v>
-      </c>
-      <c r="D41" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="E41" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="G41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="H41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="I41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="K41" s="37"/>
-      <c r="L41" s="37">
-        <v>1</v>
-      </c>
-      <c r="M41" s="37">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="N41" s="37">
-        <v>1</v>
-      </c>
-      <c r="O41" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="P41" s="38">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="Q41" s="71">
-        <f>P41*N41</f>
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="R41" s="37"/>
-      <c r="S41" s="39"/>
-    </row>
-    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1"/>
-      <c r="B42" s="40"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="45"/>
-      <c r="M42" s="45"/>
-      <c r="N42" s="77" t="s">
-        <v>5</v>
-      </c>
-      <c r="O42" s="78"/>
-      <c r="P42" s="78"/>
-      <c r="Q42" s="47">
-        <f>SUM(Q10:Q41)</f>
-        <v>192.54750000000007</v>
-      </c>
-      <c r="R42" s="79"/>
-      <c r="S42" s="80"/>
-    </row>
-    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="77" t="s">
+      <c r="O40" s="78"/>
+      <c r="P40" s="78"/>
+      <c r="Q40" s="47">
+        <f>SUM(Q11:Q39)</f>
+        <v>175.00190000000006</v>
+      </c>
+      <c r="R40" s="79"/>
+      <c r="S40" s="80"/>
+    </row>
+    <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="O43" s="78"/>
-      <c r="P43" s="78"/>
-      <c r="Q43" s="48">
-        <f>Q42/500</f>
-        <v>0.38509500000000013</v>
-      </c>
-      <c r="R43" s="81"/>
-      <c r="S43" s="82"/>
+      <c r="O41" s="78"/>
+      <c r="P41" s="78"/>
+      <c r="Q41" s="48">
+        <f>Q40/500</f>
+        <v>0.35000380000000014</v>
+      </c>
+      <c r="R41" s="81"/>
+      <c r="S41" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S43"/>
-    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S41"/>
+    <mergeCell ref="N41:P41"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1"/>
-    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O11" r:id="rId1"/>
+    <hyperlink ref="O12" r:id="rId2"/>
     <hyperlink ref="O13" r:id="rId3"/>
     <hyperlink ref="O15" r:id="rId4"/>
     <hyperlink ref="O16" r:id="rId5"/>
@@ -10577,12 +10107,12 @@
     <hyperlink ref="O29" r:id="rId13"/>
     <hyperlink ref="O26" r:id="rId14"/>
     <hyperlink ref="O30" r:id="rId15"/>
-    <hyperlink ref="O36" r:id="rId16"/>
-    <hyperlink ref="O37" r:id="rId17"/>
-    <hyperlink ref="O38" r:id="rId18"/>
-    <hyperlink ref="O40" r:id="rId19"/>
-    <hyperlink ref="O41" r:id="rId20"/>
-    <hyperlink ref="O12" r:id="rId21"/>
+    <hyperlink ref="O35" r:id="rId16"/>
+    <hyperlink ref="O36" r:id="rId17"/>
+    <hyperlink ref="O37" r:id="rId18"/>
+    <hyperlink ref="O38" r:id="rId19"/>
+    <hyperlink ref="O39" r:id="rId20"/>
+    <hyperlink ref="O10" r:id="rId21"/>
     <hyperlink ref="O14" r:id="rId22"/>
     <hyperlink ref="O17" r:id="rId23"/>
     <hyperlink ref="O24" r:id="rId24"/>
@@ -10592,18 +10122,36 @@
     <hyperlink ref="O32" r:id="rId28"/>
     <hyperlink ref="O33" r:id="rId29"/>
     <hyperlink ref="O34" r:id="rId30"/>
-    <hyperlink ref="O35" r:id="rId31"/>
-    <hyperlink ref="O39" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId33"/>
+  <drawing r:id="rId31"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
@@ -10825,19 +10373,19 @@
         <v>124</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>127</v>
+        <v>204</v>
       </c>
       <c r="N9" s="30" t="s">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="O9" s="30" t="s">
         <v>129</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>132</v>
+        <v>206</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>133</v>
+        <v>207</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>130</v>
@@ -10846,7 +10394,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="56"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -10855,17 +10403,17 @@
       <c r="C10" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="49" t="s">
-        <v>153</v>
+      <c r="D10" s="70" t="s">
+        <v>198</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>38</v>
+        <v>149</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="H10" s="37" t="s">
         <v>86</v>
@@ -10874,54 +10422,54 @@
         <v>134</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L10" s="37">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M10" s="37">
-        <f>L10*5</f>
-        <v>30</v>
+        <f>L10*500</f>
+        <v>7500</v>
       </c>
       <c r="N10" s="37">
-        <v>100</v>
+        <v>7600</v>
       </c>
       <c r="O10" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P10" s="38">
-        <v>5.1999999999999998E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q10" s="38">
         <f>P10*N10</f>
-        <v>0.52</v>
+        <v>9.879999999999999</v>
       </c>
       <c r="R10" s="37"/>
-      <c r="S10" s="57"/>
-    </row>
-    <row r="11" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="S10" s="55"/>
+    </row>
+    <row r="11" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="56"/>
       <c r="B11" s="46">
-        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
+        <f>ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="37" t="s">
-        <v>154</v>
+      <c r="D11" s="69" t="s">
+        <v>153</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11" s="37" t="s">
         <v>57</v>
       </c>
       <c r="G11" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H11" s="37" t="s">
         <v>86</v>
@@ -10930,54 +10478,54 @@
         <v>134</v>
       </c>
       <c r="J11" s="37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K11" s="37" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L11" s="37">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M11" s="37">
-        <f>L11*5</f>
-        <v>10</v>
+        <f>L11*500</f>
+        <v>3000</v>
       </c>
       <c r="N11" s="37">
-        <v>15</v>
+        <v>3100</v>
       </c>
       <c r="O11" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P11" s="38">
-        <v>0.15809999999999999</v>
+        <v>4.4000000000000003E-3</v>
       </c>
       <c r="Q11" s="38">
         <f>P11*N11</f>
-        <v>2.3714999999999997</v>
+        <v>13.64</v>
       </c>
       <c r="R11" s="37"/>
-      <c r="S11" s="55"/>
-    </row>
-    <row r="12" spans="1:19" ht="84" x14ac:dyDescent="0.25">
+      <c r="S11" s="57"/>
+    </row>
+    <row r="12" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="56"/>
       <c r="B12" s="46">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B12:B39" si="0">ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
       <c r="C12" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="37" t="s">
-        <v>211</v>
+      <c r="D12" s="70" t="s">
+        <v>154</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>149</v>
+        <v>39</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>150</v>
+        <v>57</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="H12" s="37" t="s">
         <v>86</v>
@@ -10986,147 +10534,147 @@
         <v>134</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L12" s="37">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M12" s="37">
-        <f>L12*5</f>
-        <v>75</v>
+        <f t="shared" ref="M12:M39" si="1">L12*500</f>
+        <v>1000</v>
       </c>
       <c r="N12" s="37">
-        <v>100</v>
+        <v>1050</v>
       </c>
       <c r="O12" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P12" s="38">
-        <v>1.8E-3</v>
+        <v>9.8500000000000004E-2</v>
       </c>
       <c r="Q12" s="38">
         <f>P12*N12</f>
-        <v>0.18</v>
+        <v>103.42500000000001</v>
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="55"/>
     </row>
-    <row r="13" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A13" s="56"/>
-      <c r="B13" s="46">
+    <row r="13" spans="1:19" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="61"/>
+      <c r="B13" s="73">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="67" t="s">
+      <c r="C13" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="70" t="s">
+      <c r="D13" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="E13" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="37" t="s">
+      <c r="F13" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="H13" s="37" t="s">
+      <c r="H13" s="62" t="s">
         <v>87</v>
       </c>
-      <c r="I13" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J13" s="37" t="s">
+      <c r="I13" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="J13" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="K13" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L13" s="37">
-        <v>1</v>
-      </c>
-      <c r="M13" s="37">
-        <f>L13*5</f>
-        <v>5</v>
-      </c>
-      <c r="N13" s="37">
+      <c r="K13" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="L13" s="62">
+        <v>1</v>
+      </c>
+      <c r="M13" s="62">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N13" s="62">
         <v>6</v>
       </c>
-      <c r="O13" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P13" s="38">
+      <c r="O13" s="66" t="s">
+        <v>136</v>
+      </c>
+      <c r="P13" s="63">
         <v>6.4299999999999996E-2</v>
       </c>
-      <c r="Q13" s="38">
+      <c r="Q13" s="63">
         <f>P13*N13</f>
         <v>0.38579999999999998</v>
       </c>
-      <c r="R13" s="37"/>
-      <c r="S13" s="55"/>
-    </row>
-    <row r="14" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="72">
+      <c r="R13" s="62"/>
+      <c r="S13" s="64"/>
+    </row>
+    <row r="14" spans="1:19" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="61"/>
+      <c r="B14" s="90">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="67" t="s">
+      <c r="C14" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="89" t="s">
         <v>155</v>
       </c>
-      <c r="E14" s="49" t="s">
+      <c r="E14" s="75" t="s">
         <v>156</v>
       </c>
-      <c r="F14" s="49" t="s">
+      <c r="F14" s="75" t="s">
         <v>157</v>
       </c>
-      <c r="G14" s="49" t="s">
+      <c r="G14" s="75" t="s">
         <v>158</v>
       </c>
-      <c r="H14" s="49" t="s">
+      <c r="H14" s="75" t="s">
         <v>159</v>
       </c>
-      <c r="I14" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J14" s="49" t="s">
+      <c r="I14" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="J14" s="75" t="s">
         <v>160</v>
       </c>
-      <c r="K14" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="L14" s="49">
-        <v>1</v>
-      </c>
-      <c r="M14" s="49">
-        <f t="shared" ref="M14" si="1">L14*5</f>
-        <v>5</v>
-      </c>
-      <c r="N14" s="49">
+      <c r="K14" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="L14" s="75">
+        <v>1</v>
+      </c>
+      <c r="M14" s="62">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N14" s="75">
         <v>6</v>
       </c>
-      <c r="O14" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P14" s="50">
+      <c r="O14" s="91" t="s">
+        <v>136</v>
+      </c>
+      <c r="P14" s="92">
         <v>0.22550000000000001</v>
       </c>
-      <c r="Q14" s="50">
+      <c r="Q14" s="92">
         <f t="shared" ref="Q14" si="2">P14*N14</f>
         <v>1.353</v>
       </c>
-      <c r="R14" s="49"/>
-      <c r="S14" s="55"/>
-    </row>
-    <row r="15" spans="1:19" ht="96" x14ac:dyDescent="0.25">
+      <c r="R14" s="75"/>
+      <c r="S14" s="64"/>
+    </row>
+    <row r="15" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="56"/>
       <c r="B15" s="46">
         <f t="shared" si="0"/>
@@ -11161,8 +10709,8 @@
         <v>1</v>
       </c>
       <c r="M15" s="37">
-        <f>L15*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="N15" s="37">
         <v>10</v>
@@ -11180,7 +10728,7 @@
       <c r="R15" s="37"/>
       <c r="S15" s="55"/>
     </row>
-    <row r="16" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A16" s="56"/>
       <c r="B16" s="46">
         <f t="shared" si="0"/>
@@ -11216,9 +10764,9 @@
       <c r="L16" s="49">
         <v>1</v>
       </c>
-      <c r="M16" s="49">
-        <f t="shared" ref="M16" si="3">L16*5</f>
-        <v>5</v>
+      <c r="M16" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="N16" s="49">
         <v>20</v>
@@ -11230,14 +10778,14 @@
         <v>3.2199999999999999E-2</v>
       </c>
       <c r="Q16" s="50">
-        <f t="shared" ref="Q16" si="4">P16*N16</f>
+        <f t="shared" ref="Q16" si="3">P16*N16</f>
         <v>0.64400000000000002</v>
       </c>
       <c r="R16" s="49"/>
       <c r="S16" s="55"/>
     </row>
-    <row r="17" spans="1:19" ht="168" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
+    <row r="17" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A17" s="56"/>
       <c r="B17" s="46">
         <f>ROW(B17) - ROW($B$9)</f>
         <v>8</v>
@@ -11245,7 +10793,7 @@
       <c r="C17" s="67" t="s">
         <v>161</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="D17" s="70" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="37" t="s">
@@ -11271,8 +10819,8 @@
         <v>1</v>
       </c>
       <c r="M17" s="37">
-        <f>L17*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="N17" s="37">
         <v>10</v>
@@ -11290,7 +10838,7 @@
       <c r="R17" s="37"/>
       <c r="S17" s="55"/>
     </row>
-    <row r="18" spans="1:19" ht="168" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A18" s="56"/>
       <c r="B18" s="46">
         <f t="shared" si="0"/>
@@ -11326,9 +10874,9 @@
       <c r="L18" s="49">
         <v>1</v>
       </c>
-      <c r="M18" s="49">
-        <f t="shared" ref="M18" si="5">L18*5</f>
-        <v>5</v>
+      <c r="M18" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="N18" s="49">
         <v>20</v>
@@ -11340,13 +10888,13 @@
         <v>2.2499999999999999E-2</v>
       </c>
       <c r="Q18" s="50">
-        <f t="shared" ref="Q18" si="6">P18*N18</f>
+        <f t="shared" ref="Q18" si="4">P18*N18</f>
         <v>0.44999999999999996</v>
       </c>
       <c r="R18" s="49"/>
       <c r="S18" s="55"/>
     </row>
-    <row r="19" spans="1:19" ht="108" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A19" s="56"/>
       <c r="B19" s="46">
         <f t="shared" si="0"/>
@@ -11383,8 +10931,8 @@
         <v>1</v>
       </c>
       <c r="M19" s="37">
-        <f>L19*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="N19" s="37">
         <v>12</v>
@@ -11402,7 +10950,7 @@
       <c r="R19" s="37"/>
       <c r="S19" s="55"/>
     </row>
-    <row r="20" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="56"/>
       <c r="B20" s="46">
         <f t="shared" si="0"/>
@@ -11436,9 +10984,9 @@
       <c r="L20" s="49">
         <v>1</v>
       </c>
-      <c r="M20" s="49">
-        <f t="shared" ref="M20" si="7">L20*5</f>
-        <v>5</v>
+      <c r="M20" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="N20" s="49">
         <v>10</v>
@@ -11450,13 +10998,13 @@
         <v>0.20130000000000001</v>
       </c>
       <c r="Q20" s="50">
-        <f t="shared" ref="Q20" si="8">P20*N20</f>
+        <f t="shared" ref="Q20" si="5">P20*N20</f>
         <v>2.0129999999999999</v>
       </c>
       <c r="R20" s="49"/>
       <c r="S20" s="55"/>
     </row>
-    <row r="21" spans="1:19" ht="72" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A21" s="56"/>
       <c r="B21" s="46">
         <f t="shared" si="0"/>
@@ -11493,8 +11041,8 @@
         <v>1</v>
       </c>
       <c r="M21" s="37">
-        <f>L21*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="N21" s="37">
         <v>20</v>
@@ -11512,7 +11060,7 @@
       <c r="R21" s="37"/>
       <c r="S21" s="55"/>
     </row>
-    <row r="22" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A22" s="56"/>
       <c r="B22" s="46">
         <f t="shared" si="0"/>
@@ -11548,9 +11096,9 @@
       <c r="L22" s="49">
         <v>1</v>
       </c>
-      <c r="M22" s="49">
-        <f t="shared" ref="M22" si="9">L22*5</f>
-        <v>5</v>
+      <c r="M22" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="N22" s="49">
         <v>20</v>
@@ -11562,13 +11110,13 @@
         <v>2.3300000000000001E-2</v>
       </c>
       <c r="Q22" s="50">
-        <f t="shared" ref="Q22" si="10">P22*N22</f>
+        <f t="shared" ref="Q22" si="6">P22*N22</f>
         <v>0.46600000000000003</v>
       </c>
       <c r="R22" s="49"/>
       <c r="S22" s="55"/>
     </row>
-    <row r="23" spans="1:19" ht="84" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A23" s="56"/>
       <c r="B23" s="46">
         <f t="shared" si="0"/>
@@ -11605,8 +11153,8 @@
         <v>1</v>
       </c>
       <c r="M23" s="37">
-        <f>L23*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="N23" s="37">
         <v>20</v>
@@ -11624,8 +11172,8 @@
       <c r="R23" s="37"/>
       <c r="S23" s="55"/>
     </row>
-    <row r="24" spans="1:19" ht="72" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
+    <row r="24" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="56"/>
       <c r="B24" s="46">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
@@ -11633,7 +11181,7 @@
       <c r="C24" s="67" t="s">
         <v>166</v>
       </c>
-      <c r="D24" s="37" t="s">
+      <c r="D24" s="70" t="s">
         <v>167</v>
       </c>
       <c r="E24" s="37" t="s">
@@ -11661,8 +11209,8 @@
         <v>6</v>
       </c>
       <c r="M24" s="37">
-        <f>L24*5</f>
-        <v>30</v>
+        <f t="shared" si="1"/>
+        <v>3000</v>
       </c>
       <c r="N24" s="37">
         <v>35</v>
@@ -11680,7 +11228,7 @@
       <c r="R24" s="37"/>
       <c r="S24" s="55"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="61"/>
       <c r="B25" s="73">
         <f t="shared" si="0"/>
@@ -11689,36 +11237,36 @@
       <c r="C25" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="75" t="s">
+      <c r="D25" s="89" t="s">
+        <v>208</v>
+      </c>
+      <c r="E25" s="75" t="s">
         <v>172</v>
-      </c>
-      <c r="E25" s="75" t="s">
-        <v>173</v>
       </c>
       <c r="F25" s="75" t="s">
         <v>64</v>
       </c>
       <c r="G25" s="75" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25" s="75" t="s">
         <v>174</v>
       </c>
-      <c r="H25" s="75" t="s">
+      <c r="I25" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="I25" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="J25" s="75" t="s">
-        <v>176</v>
-      </c>
       <c r="K25" s="75" t="s">
         <v>134</v>
       </c>
       <c r="L25" s="75">
-        <v>2</v>
-      </c>
-      <c r="M25" s="37">
-        <f>L25*5</f>
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="M25" s="62">
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="N25" s="62">
         <v>20</v>
@@ -11736,7 +11284,7 @@
       <c r="R25" s="62"/>
       <c r="S25" s="64"/>
     </row>
-    <row r="26" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="56"/>
       <c r="B26" s="46">
         <f>ROW(B26) - ROW($B$9)</f>
@@ -11745,8 +11293,8 @@
       <c r="C26" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="37" t="s">
-        <v>177</v>
+      <c r="D26" s="70" t="s">
+        <v>176</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>51</v>
@@ -11773,8 +11321,8 @@
         <v>5</v>
       </c>
       <c r="M26" s="37">
-        <f>L26*5</f>
-        <v>25</v>
+        <f t="shared" si="1"/>
+        <v>2500</v>
       </c>
       <c r="N26" s="37">
         <v>100</v>
@@ -11792,64 +11340,64 @@
       <c r="R26" s="37"/>
       <c r="S26" s="55"/>
     </row>
-    <row r="27" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A27" s="56"/>
-      <c r="B27" s="46">
+    <row r="27" spans="1:19" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="61"/>
+      <c r="B27" s="73">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="68" t="s">
+      <c r="C27" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="69" t="s">
+      <c r="D27" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="49" t="s">
+      <c r="E27" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="F27" s="49" t="s">
+      <c r="F27" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="G27" s="49" t="s">
+      <c r="G27" s="75" t="s">
         <v>79</v>
       </c>
-      <c r="H27" s="49" t="s">
+      <c r="H27" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="I27" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J27" s="49" t="s">
+      <c r="I27" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="J27" s="75" t="s">
         <v>110</v>
       </c>
-      <c r="K27" s="49" t="s">
+      <c r="K27" s="75" t="s">
         <v>120</v>
       </c>
-      <c r="L27" s="49">
-        <v>1</v>
-      </c>
-      <c r="M27" s="49">
-        <f t="shared" ref="M27" si="11">L27*5</f>
-        <v>5</v>
-      </c>
-      <c r="N27" s="49">
+      <c r="L27" s="75">
+        <v>1</v>
+      </c>
+      <c r="M27" s="62">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N27" s="75">
         <v>100</v>
       </c>
-      <c r="O27" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P27" s="50">
+      <c r="O27" s="91" t="s">
+        <v>136</v>
+      </c>
+      <c r="P27" s="92">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q27" s="50">
-        <f t="shared" ref="Q27" si="12">P27*N27</f>
+      <c r="Q27" s="92">
+        <f t="shared" ref="Q27" si="7">P27*N27</f>
         <v>0.12</v>
       </c>
-      <c r="R27" s="49"/>
-      <c r="S27" s="55"/>
-    </row>
-    <row r="28" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
+      <c r="R27" s="75"/>
+      <c r="S27" s="64"/>
+    </row>
+    <row r="28" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="56"/>
       <c r="B28" s="46">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
@@ -11857,17 +11405,17 @@
       <c r="C28" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="37" t="s">
-        <v>212</v>
+      <c r="D28" s="70" t="s">
+        <v>199</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F28" s="37" t="s">
         <v>65</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H28" s="37" t="s">
         <v>86</v>
@@ -11876,17 +11424,17 @@
         <v>134</v>
       </c>
       <c r="J28" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="K28" s="37" t="s">
         <v>181</v>
-      </c>
-      <c r="K28" s="37" t="s">
-        <v>182</v>
       </c>
       <c r="L28" s="37">
         <v>3</v>
       </c>
       <c r="M28" s="37">
-        <f>L28*5</f>
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>1500</v>
       </c>
       <c r="N28" s="37">
         <v>100</v>
@@ -11904,7 +11452,7 @@
       <c r="R28" s="37"/>
       <c r="S28" s="55"/>
     </row>
-    <row r="29" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="56"/>
       <c r="B29" s="46">
         <f t="shared" si="0"/>
@@ -11914,7 +11462,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="70" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E29" s="37" t="s">
         <v>50</v>
@@ -11941,8 +11489,8 @@
         <v>1</v>
       </c>
       <c r="M29" s="37">
-        <f>L29*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="N29" s="37">
         <v>100</v>
@@ -11960,7 +11508,7 @@
       <c r="R29" s="37"/>
       <c r="S29" s="55"/>
     </row>
-    <row r="30" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="56"/>
       <c r="B30" s="46">
         <f>ROW(B30) - ROW($B$9)</f>
@@ -11997,8 +11545,8 @@
         <v>1</v>
       </c>
       <c r="M30" s="37">
-        <f>L30*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="N30" s="37">
         <v>100</v>
@@ -12016,317 +11564,316 @@
       <c r="R30" s="37"/>
       <c r="S30" s="55"/>
     </row>
-    <row r="31" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="72">
-        <f t="shared" ref="B31:B32" si="13">ROW(B31) - ROW($B$9)</f>
+    <row r="31" spans="1:19" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="61"/>
+      <c r="B31" s="90">
+        <f t="shared" ref="B31" si="8">ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="68" t="s">
+      <c r="C31" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="49" t="s">
+      <c r="D31" s="89" t="s">
+        <v>182</v>
+      </c>
+      <c r="E31" s="75" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31" s="75" t="s">
+        <v>81</v>
+      </c>
+      <c r="H31" s="75" t="s">
+        <v>86</v>
+      </c>
+      <c r="I31" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="J31" s="75" t="s">
+        <v>112</v>
+      </c>
+      <c r="K31" s="75" t="s">
         <v>183</v>
       </c>
-      <c r="E31" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="F31" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="G31" s="49" t="s">
-        <v>81</v>
-      </c>
-      <c r="H31" s="49" t="s">
-        <v>86</v>
-      </c>
-      <c r="I31" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J31" s="49" t="s">
-        <v>112</v>
-      </c>
-      <c r="K31" s="49" t="s">
+      <c r="L31" s="75">
+        <v>1</v>
+      </c>
+      <c r="M31" s="62">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N31" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="O31" s="66" t="s">
+        <v>136</v>
+      </c>
+      <c r="P31" s="63" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q31" s="92" t="s">
+        <v>134</v>
+      </c>
+      <c r="R31" s="93" t="s">
+        <v>183</v>
+      </c>
+      <c r="S31" s="64"/>
+    </row>
+    <row r="32" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A32" s="56"/>
+      <c r="B32" s="46">
+        <f>ROW(B32) - ROW($B$9)</f>
+        <v>23</v>
+      </c>
+      <c r="C32" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" s="70" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G32" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="H32" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="L31" s="49">
-        <v>1</v>
-      </c>
-      <c r="M31" s="49">
-        <f t="shared" ref="M31:M32" si="14">L31*5</f>
-        <v>5</v>
-      </c>
-      <c r="N31" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="O31" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P31" s="38" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q31" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="R31" s="76" t="s">
-        <v>184</v>
-      </c>
-      <c r="S31" s="55"/>
-    </row>
-    <row r="32" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="72">
-        <f t="shared" si="13"/>
-        <v>23</v>
-      </c>
-      <c r="C32" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="E32" s="49" t="s">
+      <c r="I32" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="K32" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L32" s="37">
+        <v>1</v>
+      </c>
+      <c r="M32" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N32" s="37">
+        <v>10</v>
+      </c>
+      <c r="O32" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P32" s="38">
+        <v>0.1336</v>
+      </c>
+      <c r="Q32" s="38">
+        <f>P32*N32</f>
+        <v>1.3359999999999999</v>
+      </c>
+      <c r="R32" s="37"/>
+      <c r="S32" s="55"/>
+    </row>
+    <row r="33" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A33" s="56"/>
+      <c r="B33" s="72">
+        <f t="shared" ref="B33" si="9">ROW(B33) - ROW($B$9)</f>
+        <v>24</v>
+      </c>
+      <c r="C33" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="F32" s="49" t="s">
+      <c r="D33" s="69" t="s">
         <v>188</v>
       </c>
-      <c r="G32" s="49" t="s">
+      <c r="E33" s="49" t="s">
         <v>189</v>
       </c>
-      <c r="H32" s="49" t="s">
+      <c r="F33" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="G33" s="49" t="s">
         <v>190</v>
       </c>
-      <c r="I32" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J32" s="49" t="s">
+      <c r="H33" s="49" t="s">
         <v>191</v>
       </c>
-      <c r="K32" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="L32" s="49">
+      <c r="I33" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J33" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="K33" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L33" s="49">
         <v>2</v>
       </c>
-      <c r="M32" s="49">
-        <f t="shared" si="14"/>
+      <c r="M33" s="37">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="N33" s="49">
+        <v>20</v>
+      </c>
+      <c r="O33" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P33" s="50">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="Q33" s="50">
+        <f t="shared" ref="Q33" si="10">P33*N33</f>
+        <v>0.96600000000000008</v>
+      </c>
+      <c r="R33" s="49"/>
+      <c r="S33" s="55"/>
+    </row>
+    <row r="34" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A34" s="56"/>
+      <c r="B34" s="46">
+        <f>ROW(B34) - ROW($B$9)</f>
+        <v>25</v>
+      </c>
+      <c r="C34" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" s="70" t="s">
+        <v>193</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="F34" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="H34" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I34" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="K34" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L34" s="37">
+        <v>1</v>
+      </c>
+      <c r="M34" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N34" s="37">
         <v>10</v>
       </c>
-      <c r="N32" s="49">
-        <v>20</v>
-      </c>
-      <c r="O32" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P32" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q32" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="R32" s="76" t="s">
-        <v>184</v>
-      </c>
-      <c r="S32" s="55"/>
-    </row>
-    <row r="33" spans="1:19" ht="72" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="46">
-        <f>ROW(B33) - ROW($B$9)</f>
-        <v>24</v>
-      </c>
-      <c r="C33" s="68" t="s">
-        <v>194</v>
-      </c>
-      <c r="D33" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="37" t="s">
-        <v>192</v>
-      </c>
-      <c r="F33" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G33" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="H33" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="I33" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J33" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="K33" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L33" s="37">
-        <v>1</v>
-      </c>
-      <c r="M33" s="37">
-        <f>L33*5</f>
-        <v>5</v>
-      </c>
-      <c r="N33" s="37">
+      <c r="O34" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P34" s="38">
+        <v>6.4600000000000005E-2</v>
+      </c>
+      <c r="Q34" s="38">
+        <f>P34*N34</f>
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="R34" s="37"/>
+      <c r="S34" s="55"/>
+    </row>
+    <row r="35" spans="1:19" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="61"/>
+      <c r="B35" s="73">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C35" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="75" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="75" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35" s="75" t="s">
+        <v>66</v>
+      </c>
+      <c r="G35" s="75" t="s">
+        <v>83</v>
+      </c>
+      <c r="H35" s="75" t="s">
+        <v>96</v>
+      </c>
+      <c r="I35" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="75" t="s">
+        <v>114</v>
+      </c>
+      <c r="K35" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="L35" s="75">
+        <v>1</v>
+      </c>
+      <c r="M35" s="62">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N35" s="75">
         <v>10</v>
       </c>
-      <c r="O33" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P33" s="38">
-        <v>0.1336</v>
-      </c>
-      <c r="Q33" s="38">
-        <f>P33*N33</f>
-        <v>1.3359999999999999</v>
-      </c>
-      <c r="R33" s="37"/>
-      <c r="S33" s="55"/>
-    </row>
-    <row r="34" spans="1:19" ht="156" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="72">
-        <f t="shared" ref="B34" si="15">ROW(B34) - ROW($B$9)</f>
-        <v>25</v>
-      </c>
-      <c r="C34" s="68" t="s">
-        <v>194</v>
-      </c>
-      <c r="D34" s="49" t="s">
-        <v>195</v>
-      </c>
-      <c r="E34" s="49" t="s">
-        <v>196</v>
-      </c>
-      <c r="F34" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="G34" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="H34" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="I34" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J34" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="K34" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="L34" s="49">
-        <v>2</v>
-      </c>
-      <c r="M34" s="49">
-        <f t="shared" ref="M34" si="16">L34*5</f>
-        <v>10</v>
-      </c>
-      <c r="N34" s="49">
-        <v>20</v>
-      </c>
-      <c r="O34" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P34" s="50">
-        <v>4.8300000000000003E-2</v>
-      </c>
-      <c r="Q34" s="50">
-        <f t="shared" ref="Q34" si="17">P34*N34</f>
-        <v>0.96600000000000008</v>
-      </c>
-      <c r="R34" s="49"/>
-      <c r="S34" s="55"/>
-    </row>
-    <row r="35" spans="1:19" ht="144" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="B35" s="46">
-        <f>ROW(B35) - ROW($B$9)</f>
-        <v>26</v>
-      </c>
-      <c r="C35" s="67" t="s">
-        <v>194</v>
-      </c>
-      <c r="D35" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="E35" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="F35" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="H35" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="I35" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J35" s="37" t="s">
-        <v>203</v>
-      </c>
-      <c r="K35" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L35" s="37">
-        <v>1</v>
-      </c>
-      <c r="M35" s="37">
-        <f>L35*5</f>
-        <v>5</v>
-      </c>
-      <c r="N35" s="37">
-        <v>10</v>
-      </c>
-      <c r="O35" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P35" s="38">
-        <v>6.4600000000000005E-2</v>
-      </c>
-      <c r="Q35" s="38">
-        <f>P35*N35</f>
-        <v>0.64600000000000002</v>
-      </c>
-      <c r="R35" s="37"/>
-      <c r="S35" s="55"/>
-    </row>
-    <row r="36" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="O35" s="91" t="s">
+        <v>136</v>
+      </c>
+      <c r="P35" s="92">
+        <v>0.2079</v>
+      </c>
+      <c r="Q35" s="92">
+        <f t="shared" ref="Q35:Q36" si="11">P35*N35</f>
+        <v>2.0790000000000002</v>
+      </c>
+      <c r="R35" s="75"/>
+      <c r="S35" s="64"/>
+    </row>
+    <row r="36" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A36" s="56"/>
       <c r="B36" s="46">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C36" s="68" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E36" s="49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F36" s="49" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G36" s="49" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H36" s="49" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I36" s="49" t="s">
         <v>134</v>
       </c>
       <c r="J36" s="49" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K36" s="37" t="s">
         <v>134</v>
@@ -12334,365 +11881,253 @@
       <c r="L36" s="49">
         <v>1</v>
       </c>
-      <c r="M36" s="49">
-        <f t="shared" ref="M36:M37" si="18">L36*5</f>
-        <v>5</v>
+      <c r="M36" s="37">
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="N36" s="49">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O36" s="60" t="s">
         <v>136</v>
       </c>
       <c r="P36" s="50">
-        <v>0.2079</v>
+        <v>0.54569999999999996</v>
       </c>
       <c r="Q36" s="50">
-        <f t="shared" ref="Q36:Q37" si="19">P36*N36</f>
-        <v>2.0790000000000002</v>
+        <f t="shared" si="11"/>
+        <v>3.2741999999999996</v>
       </c>
       <c r="R36" s="49"/>
       <c r="S36" s="55"/>
     </row>
-    <row r="37" spans="1:19" ht="60" x14ac:dyDescent="0.25">
-      <c r="A37" s="56"/>
-      <c r="B37" s="46">
+    <row r="37" spans="1:19" s="65" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="61"/>
+      <c r="B37" s="73">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="68" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="49" t="s">
-        <v>35</v>
-      </c>
-      <c r="E37" s="49" t="s">
-        <v>54</v>
-      </c>
-      <c r="F37" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="G37" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="H37" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="I37" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J37" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="K37" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L37" s="49">
-        <v>1</v>
-      </c>
-      <c r="M37" s="49">
-        <f t="shared" si="18"/>
-        <v>5</v>
-      </c>
-      <c r="N37" s="49">
+      <c r="C37" s="87" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="62" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" s="62" t="s">
+        <v>55</v>
+      </c>
+      <c r="F37" s="62" t="s">
+        <v>135</v>
+      </c>
+      <c r="G37" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="H37" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="I37" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="J37" s="62" t="s">
+        <v>116</v>
+      </c>
+      <c r="K37" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="L37" s="62">
+        <v>1</v>
+      </c>
+      <c r="M37" s="62">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N37" s="62">
         <v>6</v>
       </c>
-      <c r="O37" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P37" s="50">
-        <v>0.54569999999999996</v>
-      </c>
-      <c r="Q37" s="50">
-        <f t="shared" si="19"/>
-        <v>3.2741999999999996</v>
-      </c>
-      <c r="R37" s="49"/>
-      <c r="S37" s="55"/>
-    </row>
-    <row r="38" spans="1:19" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O37" s="66" t="s">
+        <v>136</v>
+      </c>
+      <c r="P37" s="63">
+        <v>2.8589000000000002</v>
+      </c>
+      <c r="Q37" s="63">
+        <f>P37*N37</f>
+        <v>17.153400000000001</v>
+      </c>
+      <c r="R37" s="62"/>
+      <c r="S37" s="94"/>
+    </row>
+    <row r="38" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="56"/>
       <c r="B38" s="46">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C38" s="67" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="I38" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="K38" s="37" t="s">
-        <v>134</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="K38" s="37"/>
       <c r="L38" s="37">
         <v>1</v>
       </c>
       <c r="M38" s="37">
-        <f>L38*5</f>
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="N38" s="37">
         <v>5</v>
       </c>
-      <c r="N38" s="37">
-        <v>6</v>
-      </c>
       <c r="O38" s="59" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="P38" s="38">
-        <v>2.8589000000000002</v>
+        <v>3.28</v>
       </c>
       <c r="Q38" s="38">
         <f>P38*N38</f>
-        <v>17.153400000000001</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="39"/>
     </row>
-    <row r="39" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1"/>
+    <row r="39" spans="1:19" s="58" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="56"/>
       <c r="B39" s="46">
-        <f>ROW(B39) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C39" s="67" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>205</v>
+        <v>148</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>206</v>
+        <v>134</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>207</v>
+        <v>134</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>208</v>
+        <v>134</v>
       </c>
       <c r="I39" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J39" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="K39" s="37" t="s">
-        <v>134</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="K39" s="37"/>
       <c r="L39" s="37">
         <v>1</v>
       </c>
       <c r="M39" s="37">
-        <f>L39*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="N39" s="37">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O39" s="59" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="P39" s="38">
-        <v>1.2776000000000001</v>
-      </c>
-      <c r="Q39" s="38">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="Q39" s="71">
         <f>P39*N39</f>
-        <v>7.6656000000000004</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="R39" s="37"/>
       <c r="S39" s="39"/>
     </row>
-    <row r="40" spans="1:19" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="56"/>
-      <c r="B40" s="46">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="C40" s="67" t="s">
-        <v>144</v>
-      </c>
-      <c r="D40" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="E40" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="G40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="H40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="I40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J40" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="K40" s="37"/>
-      <c r="L40" s="37">
-        <v>1</v>
-      </c>
-      <c r="M40" s="37">
-        <f>L40*5</f>
+    <row r="40" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="44"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="45"/>
+      <c r="J40" s="44"/>
+      <c r="K40" s="45"/>
+      <c r="L40" s="45"/>
+      <c r="M40" s="45"/>
+      <c r="N40" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="N40" s="37">
-        <v>5</v>
-      </c>
-      <c r="O40" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="P40" s="38">
-        <v>3.28</v>
-      </c>
-      <c r="Q40" s="38">
-        <f>P40*N40</f>
-        <v>16.399999999999999</v>
-      </c>
-      <c r="R40" s="37"/>
-      <c r="S40" s="39"/>
-    </row>
-    <row r="41" spans="1:19" ht="144.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="56"/>
-      <c r="B41" s="46">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="C41" s="67" t="s">
-        <v>145</v>
-      </c>
-      <c r="D41" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="E41" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="G41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="H41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="I41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J41" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="K41" s="37"/>
-      <c r="L41" s="37">
-        <v>1</v>
-      </c>
-      <c r="M41" s="37">
-        <f>L41*5</f>
-        <v>5</v>
-      </c>
-      <c r="N41" s="37">
-        <v>1</v>
-      </c>
-      <c r="O41" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="P41" s="38">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="Q41" s="71">
-        <f>P41*N41</f>
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="R41" s="37"/>
-      <c r="S41" s="39"/>
-    </row>
-    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1"/>
-      <c r="B42" s="40"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="45"/>
-      <c r="M42" s="45"/>
-      <c r="N42" s="77" t="s">
-        <v>5</v>
-      </c>
-      <c r="O42" s="78"/>
-      <c r="P42" s="78"/>
-      <c r="Q42" s="47">
-        <f>SUM(Q10:Q41)</f>
-        <v>68.674000000000007</v>
-      </c>
-      <c r="R42" s="79"/>
-      <c r="S42" s="80"/>
-    </row>
-    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="77" t="s">
+      <c r="O40" s="78"/>
+      <c r="P40" s="78"/>
+      <c r="Q40" s="47">
+        <f>SUM(Q11:Q39)</f>
+        <v>175.00190000000006</v>
+      </c>
+      <c r="R40" s="79"/>
+      <c r="S40" s="80"/>
+    </row>
+    <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="O43" s="78"/>
-      <c r="P43" s="78"/>
-      <c r="Q43" s="48">
-        <f>Q42/5</f>
-        <v>13.734800000000002</v>
-      </c>
-      <c r="R43" s="81"/>
-      <c r="S43" s="82"/>
+      <c r="O41" s="78"/>
+      <c r="P41" s="78"/>
+      <c r="Q41" s="48">
+        <f>Q40/500</f>
+        <v>0.35000380000000014</v>
+      </c>
+      <c r="R41" s="81"/>
+      <c r="S41" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S43"/>
-    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S41"/>
+    <mergeCell ref="N41:P41"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1"/>
-    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O11" r:id="rId1"/>
+    <hyperlink ref="O12" r:id="rId2"/>
     <hyperlink ref="O13" r:id="rId3"/>
     <hyperlink ref="O15" r:id="rId4"/>
     <hyperlink ref="O16" r:id="rId5"/>
@@ -12706,12 +12141,12 @@
     <hyperlink ref="O29" r:id="rId13"/>
     <hyperlink ref="O26" r:id="rId14"/>
     <hyperlink ref="O30" r:id="rId15"/>
-    <hyperlink ref="O36" r:id="rId16"/>
-    <hyperlink ref="O37" r:id="rId17"/>
-    <hyperlink ref="O38" r:id="rId18"/>
-    <hyperlink ref="O40" r:id="rId19"/>
-    <hyperlink ref="O41" r:id="rId20"/>
-    <hyperlink ref="O12" r:id="rId21"/>
+    <hyperlink ref="O35" r:id="rId16"/>
+    <hyperlink ref="O36" r:id="rId17"/>
+    <hyperlink ref="O37" r:id="rId18"/>
+    <hyperlink ref="O38" r:id="rId19"/>
+    <hyperlink ref="O39" r:id="rId20"/>
+    <hyperlink ref="O10" r:id="rId21"/>
     <hyperlink ref="O14" r:id="rId22"/>
     <hyperlink ref="O17" r:id="rId23"/>
     <hyperlink ref="O24" r:id="rId24"/>
@@ -12721,10 +12156,8 @@
     <hyperlink ref="O32" r:id="rId28"/>
     <hyperlink ref="O33" r:id="rId29"/>
     <hyperlink ref="O34" r:id="rId30"/>
-    <hyperlink ref="O35" r:id="rId31"/>
-    <hyperlink ref="O39" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId33"/>
+  <drawing r:id="rId31"/>
 </worksheet>
 </file>
--- a/Design Files/IoT-Button-v1.2/BOM/eSpark-BOM-IoT-Button.xlsx
+++ b/Design Files/IoT-Button-v1.2/BOM/eSpark-BOM-IoT-Button.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="219">
   <si>
     <t>Component list</t>
   </si>
@@ -650,6 +650,36 @@
   </si>
   <si>
     <t>Q2</t>
+  </si>
+  <si>
+    <t>DC Power Receptacle 260℃ Brass -20℃~+70℃ 2.5mm 6mm 2.5A 24V Plugin AC/DC Power Connectors ROHS</t>
+  </si>
+  <si>
+    <t>DC-0360-2.5</t>
+  </si>
+  <si>
+    <t>C319122</t>
+  </si>
+  <si>
+    <t>R5, R12</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>RES 56K OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>Res-0402</t>
+  </si>
+  <si>
+    <t>RC0402FR-0756KL</t>
+  </si>
+  <si>
+    <t>C114756</t>
+  </si>
+  <si>
+    <t>56K</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1151,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1329,6 +1359,30 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
@@ -1361,29 +1415,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2026,15 +2059,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="84"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="92"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2084,7 +2117,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="85"/>
+      <c r="S3" s="93"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2109,7 +2142,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="86"/>
+      <c r="S4" s="94"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2134,7 +2167,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="86"/>
+      <c r="S5" s="94"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2155,7 +2188,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="86"/>
+      <c r="S6" s="94"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2176,7 +2209,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="86"/>
+      <c r="S7" s="94"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2197,7 +2230,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="86"/>
+      <c r="S8" s="94"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2646,7 +2679,7 @@
       <c r="R16" s="37"/>
       <c r="S16" s="55"/>
     </row>
-    <row r="17" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A17" s="56"/>
       <c r="B17" s="46">
         <f>ROW(B17) - ROW($B$9)</f>
@@ -2655,17 +2688,17 @@
       <c r="C17" s="67" t="s">
         <v>161</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="D17" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="37" t="s">
-        <v>162</v>
+      <c r="E17" s="95" t="s">
+        <v>209</v>
       </c>
       <c r="F17" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="G17" s="37" t="s">
-        <v>163</v>
+      <c r="G17" s="95" t="s">
+        <v>210</v>
       </c>
       <c r="H17" s="37" t="s">
         <v>95</v>
@@ -2674,7 +2707,7 @@
         <v>134</v>
       </c>
       <c r="J17" s="37" t="s">
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="K17" s="37" t="s">
         <v>134</v>
@@ -2693,11 +2726,11 @@
         <v>136</v>
       </c>
       <c r="P17" s="38">
-        <v>0.1636</v>
+        <v>0.1384</v>
       </c>
       <c r="Q17" s="50">
         <f t="shared" ref="Q17" si="4">P17*N17</f>
-        <v>0.81799999999999995</v>
+        <v>0.69199999999999995</v>
       </c>
       <c r="R17" s="49"/>
       <c r="S17" s="55"/>
@@ -2820,52 +2853,54 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="C20" s="68" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="49" t="s">
-        <v>45</v>
+      <c r="C20" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>46</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G20" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49" t="s">
-        <v>106</v>
+        <v>63</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J20" s="37" t="s">
+        <v>107</v>
       </c>
       <c r="K20" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L20" s="49">
+      <c r="L20" s="37">
         <v>1</v>
       </c>
       <c r="M20" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N20" s="37">
-        <v>5</v>
-      </c>
-      <c r="O20" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P20" s="50">
-        <v>0.20130000000000001</v>
-      </c>
-      <c r="Q20" s="38">
-        <f>P20*N20</f>
-        <v>1.0065</v>
-      </c>
-      <c r="R20" s="37"/>
+      <c r="N20" s="49">
+        <v>20</v>
+      </c>
+      <c r="O20" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P20" s="38">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="Q20" s="50">
+        <f t="shared" ref="Q20" si="6">P20*N20</f>
+        <v>0.53</v>
+      </c>
+      <c r="R20" s="49"/>
       <c r="S20" s="55"/>
     </row>
     <row r="21" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -2874,54 +2909,54 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="C21" s="67" t="s">
+      <c r="C21" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="70" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" s="37" t="s">
+      <c r="D21" s="69" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="G21" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="H21" s="37" t="s">
+      <c r="G21" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="49" t="s">
         <v>93</v>
       </c>
-      <c r="I21" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J21" s="37" t="s">
-        <v>107</v>
+      <c r="I21" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J21" s="49" t="s">
+        <v>108</v>
       </c>
       <c r="K21" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L21" s="37">
+      <c r="L21" s="49">
         <v>1</v>
       </c>
       <c r="M21" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N21" s="49">
+      <c r="N21" s="37">
         <v>20</v>
       </c>
-      <c r="O21" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P21" s="38">
-        <v>2.6499999999999999E-2</v>
-      </c>
-      <c r="Q21" s="50">
-        <f t="shared" ref="Q21" si="6">P21*N21</f>
-        <v>0.53</v>
-      </c>
-      <c r="R21" s="49"/>
+      <c r="O21" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P21" s="50">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="Q21" s="38">
+        <f>P21*N21</f>
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="R21" s="37"/>
       <c r="S21" s="55"/>
     </row>
     <row r="22" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -2930,278 +2965,278 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="69" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="49" t="s">
+      <c r="D22" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="H22" s="49" t="s">
+      <c r="G22" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="I22" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J22" s="49" t="s">
-        <v>108</v>
+      <c r="I22" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>109</v>
       </c>
       <c r="K22" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L22" s="49">
+      <c r="L22" s="37">
         <v>1</v>
       </c>
       <c r="M22" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N22" s="37">
+      <c r="N22" s="49">
         <v>20</v>
       </c>
-      <c r="O22" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P22" s="50">
-        <v>2.3300000000000001E-2</v>
-      </c>
-      <c r="Q22" s="38">
-        <f>P22*N22</f>
-        <v>0.46600000000000003</v>
-      </c>
-      <c r="R22" s="37"/>
+      <c r="O22" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P22" s="38">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="Q22" s="50">
+        <f t="shared" ref="Q22" si="7">P22*N22</f>
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="R22" s="49"/>
       <c r="S22" s="55"/>
     </row>
     <row r="23" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A23" s="56"/>
       <c r="B23" s="46">
-        <f t="shared" si="1"/>
+        <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
       <c r="C23" s="67" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="70" t="s">
-        <v>30</v>
+        <v>166</v>
+      </c>
+      <c r="D23" s="37" t="s">
+        <v>167</v>
       </c>
       <c r="E23" s="37" t="s">
-        <v>48</v>
+        <v>168</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>78</v>
+        <v>169</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>93</v>
+        <v>170</v>
       </c>
       <c r="I23" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J23" s="37" t="s">
-        <v>109</v>
+        <v>171</v>
       </c>
       <c r="K23" s="37" t="s">
         <v>134</v>
       </c>
       <c r="L23" s="37">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M23" s="37">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="N23" s="49">
-        <v>20</v>
+        <v>12</v>
+      </c>
+      <c r="N23" s="37">
+        <v>15</v>
       </c>
       <c r="O23" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P23" s="38">
-        <v>3.2199999999999999E-2</v>
-      </c>
-      <c r="Q23" s="50">
-        <f t="shared" ref="Q23" si="7">P23*N23</f>
-        <v>0.64400000000000002</v>
-      </c>
-      <c r="R23" s="49"/>
+        <v>7.1300000000000002E-2</v>
+      </c>
+      <c r="Q23" s="38">
+        <f>P23*N23</f>
+        <v>1.0695000000000001</v>
+      </c>
+      <c r="R23" s="37"/>
       <c r="S23" s="55"/>
     </row>
-    <row r="24" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="56"/>
-      <c r="B24" s="46">
-        <f>ROW(B24) - ROW($B$9)</f>
+      <c r="B24" s="73">
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="C24" s="67" t="s">
-        <v>166</v>
-      </c>
-      <c r="D24" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="E24" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="F24" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G24" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>170</v>
-      </c>
-      <c r="I24" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J24" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="K24" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L24" s="37">
-        <v>6</v>
+      <c r="C24" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="75" t="s">
+        <v>208</v>
+      </c>
+      <c r="E24" s="75" t="s">
+        <v>172</v>
+      </c>
+      <c r="F24" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="G24" s="75" t="s">
+        <v>173</v>
+      </c>
+      <c r="H24" s="75" t="s">
+        <v>174</v>
+      </c>
+      <c r="I24" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="J24" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="K24" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="L24" s="75">
+        <v>1</v>
       </c>
       <c r="M24" s="37">
         <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="N24" s="37">
-        <v>15</v>
-      </c>
-      <c r="O24" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P24" s="38">
-        <v>7.1300000000000002E-2</v>
-      </c>
-      <c r="Q24" s="38">
-        <f>P24*N24</f>
-        <v>1.0695000000000001</v>
-      </c>
-      <c r="R24" s="37"/>
+        <v>2</v>
+      </c>
+      <c r="N24" s="49">
+        <v>10</v>
+      </c>
+      <c r="O24" s="66" t="s">
+        <v>136</v>
+      </c>
+      <c r="P24" s="63">
+        <v>3.1E-2</v>
+      </c>
+      <c r="Q24" s="50">
+        <f t="shared" ref="Q24" si="8">P24*N24</f>
+        <v>0.31</v>
+      </c>
+      <c r="R24" s="49"/>
       <c r="S24" s="55"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="56"/>
-      <c r="B25" s="73">
-        <f t="shared" si="1"/>
+      <c r="B25" s="46">
+        <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
-      <c r="C25" s="74" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="75" t="s">
-        <v>208</v>
-      </c>
-      <c r="E25" s="75" t="s">
-        <v>172</v>
-      </c>
-      <c r="F25" s="75" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25" s="75" t="s">
-        <v>173</v>
-      </c>
-      <c r="H25" s="75" t="s">
-        <v>174</v>
-      </c>
-      <c r="I25" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="J25" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="K25" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="L25" s="75">
-        <v>1</v>
+      <c r="C25" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G25" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I25" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="K25" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="L25" s="37">
+        <v>5</v>
       </c>
       <c r="M25" s="37">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="N25" s="49">
         <v>10</v>
       </c>
-      <c r="O25" s="66" t="s">
-        <v>136</v>
-      </c>
-      <c r="P25" s="63">
-        <v>3.1E-2</v>
-      </c>
-      <c r="Q25" s="50">
-        <f t="shared" ref="Q25" si="8">P25*N25</f>
-        <v>0.31</v>
-      </c>
-      <c r="R25" s="49"/>
+      <c r="N25" s="37">
+        <v>100</v>
+      </c>
+      <c r="O25" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P25" s="38">
+        <v>1E-3</v>
+      </c>
+      <c r="Q25" s="38">
+        <f>P25*N25</f>
+        <v>0.1</v>
+      </c>
+      <c r="R25" s="37"/>
       <c r="S25" s="55"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="56"/>
       <c r="B26" s="46">
-        <f>ROW(B26) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="C26" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="E26" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26" s="37" t="s">
+      <c r="D26" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="G26" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="H26" s="37" t="s">
+      <c r="G26" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="H26" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="I26" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J26" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="K26" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="L26" s="37">
-        <v>5</v>
+      <c r="I26" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J26" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="K26" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="L26" s="49">
+        <v>1</v>
       </c>
       <c r="M26" s="37">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="N26" s="37">
+        <v>2</v>
+      </c>
+      <c r="N26" s="49">
         <v>100</v>
       </c>
-      <c r="O26" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P26" s="38">
-        <v>1E-3</v>
-      </c>
-      <c r="Q26" s="38">
-        <f>P26*N26</f>
-        <v>0.1</v>
-      </c>
-      <c r="R26" s="37"/>
+      <c r="O26" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P26" s="50">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q26" s="50">
+        <f t="shared" ref="Q26:Q27" si="9">P26*N26</f>
+        <v>0.12</v>
+      </c>
+      <c r="R26" s="49"/>
       <c r="S26" s="55"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -3210,54 +3245,54 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="C27" s="68" t="s">
+      <c r="C27" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" s="49" t="s">
-        <v>49</v>
+      <c r="D27" s="49" t="s">
+        <v>213</v>
+      </c>
+      <c r="E27" s="95" t="s">
+        <v>214</v>
       </c>
       <c r="F27" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27" s="49" t="s">
-        <v>79</v>
+        <v>215</v>
+      </c>
+      <c r="G27" s="95" t="s">
+        <v>216</v>
       </c>
       <c r="H27" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="I27" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J27" s="49" t="s">
-        <v>110</v>
-      </c>
-      <c r="K27" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="L27" s="49">
+      <c r="I27" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J27" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="K27" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="L27" s="37">
         <v>1</v>
       </c>
       <c r="M27" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N27" s="49">
+      <c r="N27" s="37">
         <v>100</v>
       </c>
-      <c r="O27" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P27" s="50">
-        <v>1.1999999999999999E-3</v>
+      <c r="O27" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P27" s="38">
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="Q27" s="50">
-        <f t="shared" ref="Q27" si="9">P27*N27</f>
-        <v>0.12</v>
-      </c>
-      <c r="R27" s="49"/>
+        <f t="shared" si="9"/>
+        <v>0.06</v>
+      </c>
+      <c r="R27" s="37"/>
       <c r="S27" s="55"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
@@ -3270,7 +3305,7 @@
         <v>18</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="E28" s="37" t="s">
         <v>178</v>
@@ -3943,17 +3978,17 @@
       <c r="K40" s="45"/>
       <c r="L40" s="45"/>
       <c r="M40" s="45"/>
-      <c r="N40" s="77" t="s">
+      <c r="N40" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="O40" s="78"/>
-      <c r="P40" s="78"/>
+      <c r="O40" s="86"/>
+      <c r="P40" s="86"/>
       <c r="Q40" s="47">
         <f>SUM(Q11:Q39)</f>
-        <v>32.523800000000001</v>
-      </c>
-      <c r="R40" s="79"/>
-      <c r="S40" s="80"/>
+        <v>31.4513</v>
+      </c>
+      <c r="R40" s="87"/>
+      <c r="S40" s="88"/>
     </row>
     <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="56"/>
@@ -3969,17 +4004,17 @@
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
-      <c r="N41" s="77" t="s">
+      <c r="N41" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="O41" s="78"/>
-      <c r="P41" s="78"/>
+      <c r="O41" s="86"/>
+      <c r="P41" s="86"/>
       <c r="Q41" s="48">
         <f>Q40/2</f>
-        <v>16.261900000000001</v>
-      </c>
-      <c r="R41" s="81"/>
-      <c r="S41" s="82"/>
+        <v>15.72565</v>
+      </c>
+      <c r="R41" s="89"/>
+      <c r="S41" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4000,26 +4035,26 @@
     <hyperlink ref="O20" r:id="rId8"/>
     <hyperlink ref="O21" r:id="rId9"/>
     <hyperlink ref="O22" r:id="rId10"/>
-    <hyperlink ref="O23" r:id="rId11"/>
-    <hyperlink ref="O27" r:id="rId12"/>
-    <hyperlink ref="O29" r:id="rId13"/>
-    <hyperlink ref="O26" r:id="rId14"/>
-    <hyperlink ref="O30" r:id="rId15"/>
-    <hyperlink ref="O35" r:id="rId16"/>
-    <hyperlink ref="O36" r:id="rId17"/>
-    <hyperlink ref="O37" r:id="rId18"/>
-    <hyperlink ref="O38" r:id="rId19"/>
-    <hyperlink ref="O39" r:id="rId20"/>
-    <hyperlink ref="O10" r:id="rId21"/>
-    <hyperlink ref="O14" r:id="rId22"/>
-    <hyperlink ref="O17" r:id="rId23"/>
-    <hyperlink ref="O24" r:id="rId24"/>
-    <hyperlink ref="O25" r:id="rId25"/>
-    <hyperlink ref="O28" r:id="rId26"/>
-    <hyperlink ref="O31" r:id="rId27"/>
-    <hyperlink ref="O32" r:id="rId28"/>
-    <hyperlink ref="O33" r:id="rId29"/>
-    <hyperlink ref="O34" r:id="rId30"/>
+    <hyperlink ref="O26" r:id="rId11"/>
+    <hyperlink ref="O29" r:id="rId12"/>
+    <hyperlink ref="O25" r:id="rId13"/>
+    <hyperlink ref="O30" r:id="rId14"/>
+    <hyperlink ref="O35" r:id="rId15"/>
+    <hyperlink ref="O36" r:id="rId16"/>
+    <hyperlink ref="O37" r:id="rId17"/>
+    <hyperlink ref="O38" r:id="rId18"/>
+    <hyperlink ref="O39" r:id="rId19"/>
+    <hyperlink ref="O10" r:id="rId20"/>
+    <hyperlink ref="O14" r:id="rId21"/>
+    <hyperlink ref="O23" r:id="rId22"/>
+    <hyperlink ref="O24" r:id="rId23"/>
+    <hyperlink ref="O28" r:id="rId24"/>
+    <hyperlink ref="O31" r:id="rId25"/>
+    <hyperlink ref="O32" r:id="rId26"/>
+    <hyperlink ref="O33" r:id="rId27"/>
+    <hyperlink ref="O34" r:id="rId28"/>
+    <hyperlink ref="O17" r:id="rId29"/>
+    <hyperlink ref="O27" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>
@@ -4062,15 +4097,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="84"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="92"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -4120,7 +4155,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="85"/>
+      <c r="S3" s="93"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -4145,7 +4180,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="86"/>
+      <c r="S4" s="94"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -4170,7 +4205,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="86"/>
+      <c r="S5" s="94"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -4191,7 +4226,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="86"/>
+      <c r="S6" s="94"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -4212,7 +4247,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="86"/>
+      <c r="S7" s="94"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -4233,7 +4268,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="86"/>
+      <c r="S8" s="94"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -4663,7 +4698,7 @@
         <v>1</v>
       </c>
       <c r="M16" s="49">
-        <f t="shared" ref="M16" si="3">L16*5</f>
+        <f t="shared" ref="M16:M17" si="3">L16*5</f>
         <v>5</v>
       </c>
       <c r="N16" s="49">
@@ -4691,17 +4726,17 @@
       <c r="C17" s="67" t="s">
         <v>161</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="D17" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="37" t="s">
-        <v>162</v>
+      <c r="E17" s="95" t="s">
+        <v>209</v>
       </c>
       <c r="F17" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="G17" s="37" t="s">
-        <v>163</v>
+      <c r="G17" s="95" t="s">
+        <v>210</v>
       </c>
       <c r="H17" s="37" t="s">
         <v>95</v>
@@ -4710,28 +4745,30 @@
         <v>134</v>
       </c>
       <c r="J17" s="37" t="s">
-        <v>164</v>
-      </c>
-      <c r="K17" s="37"/>
+        <v>211</v>
+      </c>
+      <c r="K17" s="37" t="s">
+        <v>134</v>
+      </c>
       <c r="L17" s="37">
         <v>1</v>
       </c>
-      <c r="M17" s="37">
-        <f>L17*5</f>
+      <c r="M17" s="49">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="N17" s="37">
+      <c r="N17" s="49">
         <v>10</v>
       </c>
       <c r="O17" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P17" s="38">
-        <v>0.1636</v>
+        <v>0.1384</v>
       </c>
       <c r="Q17" s="38">
         <f>P17*N17</f>
-        <v>1.6359999999999999</v>
+        <v>1.3839999999999999</v>
       </c>
       <c r="R17" s="37"/>
       <c r="S17" s="55"/>
@@ -4848,58 +4885,60 @@
       <c r="R19" s="37"/>
       <c r="S19" s="55"/>
     </row>
-    <row r="20" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="56"/>
       <c r="B20" s="46">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="68" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="49" t="s">
-        <v>45</v>
+      <c r="C20" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>46</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G20" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49" t="s">
-        <v>106</v>
+        <v>63</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J20" s="37" t="s">
+        <v>107</v>
       </c>
       <c r="K20" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L20" s="49">
-        <v>1</v>
-      </c>
-      <c r="M20" s="49">
-        <f t="shared" ref="M20" si="7">L20*5</f>
+      <c r="L20" s="37">
+        <v>1</v>
+      </c>
+      <c r="M20" s="37">
+        <f>L20*5</f>
         <v>5</v>
       </c>
-      <c r="N20" s="49">
-        <v>10</v>
-      </c>
-      <c r="O20" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P20" s="50">
-        <v>0.20130000000000001</v>
-      </c>
-      <c r="Q20" s="50">
-        <f t="shared" ref="Q20" si="8">P20*N20</f>
-        <v>2.0129999999999999</v>
-      </c>
-      <c r="R20" s="49"/>
+      <c r="N20" s="37">
+        <v>20</v>
+      </c>
+      <c r="O20" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P20" s="38">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="Q20" s="38">
+        <f>P20*N20</f>
+        <v>0.53</v>
+      </c>
+      <c r="R20" s="37"/>
       <c r="S20" s="55"/>
     </row>
     <row r="21" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4908,54 +4947,54 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="67" t="s">
+      <c r="C21" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="70" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" s="37" t="s">
+      <c r="D21" s="69" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="G21" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="H21" s="37" t="s">
+      <c r="G21" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="49" t="s">
         <v>93</v>
       </c>
-      <c r="I21" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J21" s="37" t="s">
-        <v>107</v>
+      <c r="I21" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J21" s="49" t="s">
+        <v>108</v>
       </c>
       <c r="K21" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L21" s="37">
-        <v>1</v>
-      </c>
-      <c r="M21" s="37">
-        <f>L21*5</f>
+      <c r="L21" s="49">
+        <v>1</v>
+      </c>
+      <c r="M21" s="49">
+        <f t="shared" ref="M21" si="7">L21*5</f>
         <v>5</v>
       </c>
-      <c r="N21" s="37">
+      <c r="N21" s="49">
         <v>20</v>
       </c>
-      <c r="O21" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P21" s="38">
-        <v>2.6499999999999999E-2</v>
-      </c>
-      <c r="Q21" s="38">
-        <f>P21*N21</f>
-        <v>0.53</v>
-      </c>
-      <c r="R21" s="37"/>
+      <c r="O21" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P21" s="50">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="Q21" s="50">
+        <f t="shared" ref="Q21" si="8">P21*N21</f>
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="R21" s="49"/>
       <c r="S21" s="55"/>
     </row>
     <row r="22" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -4964,278 +5003,278 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="69" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="49" t="s">
+      <c r="D22" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="H22" s="49" t="s">
+      <c r="G22" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="I22" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J22" s="49" t="s">
-        <v>108</v>
+      <c r="I22" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>109</v>
       </c>
       <c r="K22" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L22" s="49">
-        <v>1</v>
-      </c>
-      <c r="M22" s="49">
-        <f t="shared" ref="M22" si="9">L22*5</f>
+      <c r="L22" s="37">
+        <v>1</v>
+      </c>
+      <c r="M22" s="37">
+        <f>L22*5</f>
         <v>5</v>
       </c>
-      <c r="N22" s="49">
+      <c r="N22" s="37">
         <v>20</v>
       </c>
-      <c r="O22" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P22" s="50">
-        <v>2.3300000000000001E-2</v>
-      </c>
-      <c r="Q22" s="50">
-        <f t="shared" ref="Q22" si="10">P22*N22</f>
-        <v>0.46600000000000003</v>
-      </c>
-      <c r="R22" s="49"/>
+      <c r="O22" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P22" s="38">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="Q22" s="38">
+        <f>P22*N22</f>
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="R22" s="37"/>
       <c r="S22" s="55"/>
     </row>
-    <row r="23" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
-      <c r="A23" s="56"/>
+    <row r="23" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
       <c r="B23" s="46">
-        <f t="shared" si="0"/>
+        <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
       <c r="C23" s="67" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="70" t="s">
-        <v>30</v>
+        <v>166</v>
+      </c>
+      <c r="D23" s="37" t="s">
+        <v>167</v>
       </c>
       <c r="E23" s="37" t="s">
-        <v>48</v>
+        <v>168</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>78</v>
+        <v>169</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>93</v>
+        <v>170</v>
       </c>
       <c r="I23" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J23" s="37" t="s">
-        <v>109</v>
+        <v>171</v>
       </c>
       <c r="K23" s="37" t="s">
         <v>134</v>
       </c>
       <c r="L23" s="37">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M23" s="37">
         <f>L23*5</f>
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="N23" s="37">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="O23" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P23" s="38">
-        <v>3.2199999999999999E-2</v>
+        <v>7.1300000000000002E-2</v>
       </c>
       <c r="Q23" s="38">
         <f>P23*N23</f>
-        <v>0.64400000000000002</v>
+        <v>2.4955000000000003</v>
       </c>
       <c r="R23" s="37"/>
       <c r="S23" s="55"/>
     </row>
-    <row r="24" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="46">
-        <f>ROW(B24) - ROW($B$9)</f>
+    <row r="24" spans="1:19" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="61"/>
+      <c r="B24" s="73">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="67" t="s">
-        <v>166</v>
-      </c>
-      <c r="D24" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="E24" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="F24" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G24" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>170</v>
-      </c>
-      <c r="I24" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J24" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="K24" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L24" s="37">
-        <v>6</v>
+      <c r="C24" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="75" t="s">
+        <v>208</v>
+      </c>
+      <c r="E24" s="75" t="s">
+        <v>172</v>
+      </c>
+      <c r="F24" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="G24" s="75" t="s">
+        <v>173</v>
+      </c>
+      <c r="H24" s="75" t="s">
+        <v>174</v>
+      </c>
+      <c r="I24" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="J24" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="K24" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="L24" s="75">
+        <v>1</v>
       </c>
       <c r="M24" s="37">
         <f>L24*5</f>
-        <v>30</v>
-      </c>
-      <c r="N24" s="37">
-        <v>35</v>
-      </c>
-      <c r="O24" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P24" s="38">
-        <v>7.1300000000000002E-2</v>
-      </c>
-      <c r="Q24" s="38">
+        <v>5</v>
+      </c>
+      <c r="N24" s="62">
+        <v>10</v>
+      </c>
+      <c r="O24" s="66" t="s">
+        <v>136</v>
+      </c>
+      <c r="P24" s="63">
+        <v>3.1E-2</v>
+      </c>
+      <c r="Q24" s="63">
         <f>P24*N24</f>
-        <v>2.4955000000000003</v>
-      </c>
-      <c r="R24" s="37"/>
-      <c r="S24" s="55"/>
-    </row>
-    <row r="25" spans="1:19" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="61"/>
-      <c r="B25" s="73">
-        <f t="shared" si="0"/>
+        <v>0.31</v>
+      </c>
+      <c r="R24" s="62"/>
+      <c r="S24" s="64"/>
+    </row>
+    <row r="25" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="56"/>
+      <c r="B25" s="46">
+        <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
-      <c r="C25" s="74" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="75" t="s">
-        <v>208</v>
-      </c>
-      <c r="E25" s="75" t="s">
-        <v>172</v>
-      </c>
-      <c r="F25" s="75" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25" s="75" t="s">
-        <v>173</v>
-      </c>
-      <c r="H25" s="75" t="s">
-        <v>174</v>
-      </c>
-      <c r="I25" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="J25" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="K25" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="L25" s="75">
-        <v>1</v>
+      <c r="C25" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G25" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I25" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="K25" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="L25" s="37">
+        <v>5</v>
       </c>
       <c r="M25" s="37">
         <f>L25*5</f>
-        <v>5</v>
-      </c>
-      <c r="N25" s="62">
-        <v>10</v>
-      </c>
-      <c r="O25" s="66" t="s">
-        <v>136</v>
-      </c>
-      <c r="P25" s="63">
-        <v>3.1E-2</v>
-      </c>
-      <c r="Q25" s="63">
+        <v>25</v>
+      </c>
+      <c r="N25" s="37">
+        <v>100</v>
+      </c>
+      <c r="O25" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P25" s="38">
+        <v>1E-3</v>
+      </c>
+      <c r="Q25" s="38">
         <f>P25*N25</f>
-        <v>0.31</v>
-      </c>
-      <c r="R25" s="62"/>
-      <c r="S25" s="64"/>
+        <v>0.1</v>
+      </c>
+      <c r="R25" s="37"/>
+      <c r="S25" s="55"/>
     </row>
     <row r="26" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="56"/>
       <c r="B26" s="46">
-        <f>ROW(B26) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C26" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="E26" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26" s="37" t="s">
+      <c r="D26" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="G26" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="H26" s="37" t="s">
+      <c r="G26" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="H26" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="I26" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J26" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="K26" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="L26" s="37">
+      <c r="I26" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J26" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="K26" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="L26" s="49">
+        <v>1</v>
+      </c>
+      <c r="M26" s="49">
+        <f t="shared" ref="M26:M27" si="9">L26*5</f>
         <v>5</v>
       </c>
-      <c r="M26" s="37">
-        <f>L26*5</f>
-        <v>25</v>
-      </c>
-      <c r="N26" s="37">
+      <c r="N26" s="49">
         <v>100</v>
       </c>
-      <c r="O26" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P26" s="38">
-        <v>1E-3</v>
-      </c>
-      <c r="Q26" s="38">
-        <f>P26*N26</f>
-        <v>0.1</v>
-      </c>
-      <c r="R26" s="37"/>
+      <c r="O26" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P26" s="50">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q26" s="50">
+        <f t="shared" ref="Q26:Q27" si="10">P26*N26</f>
+        <v>0.12</v>
+      </c>
+      <c r="R26" s="49"/>
       <c r="S26" s="55"/>
     </row>
     <row r="27" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
@@ -5244,54 +5283,54 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="68" t="s">
+      <c r="C27" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" s="49" t="s">
-        <v>49</v>
+      <c r="D27" s="49" t="s">
+        <v>213</v>
+      </c>
+      <c r="E27" s="95" t="s">
+        <v>214</v>
       </c>
       <c r="F27" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27" s="49" t="s">
-        <v>79</v>
+        <v>215</v>
+      </c>
+      <c r="G27" s="95" t="s">
+        <v>216</v>
       </c>
       <c r="H27" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="I27" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J27" s="49" t="s">
-        <v>110</v>
-      </c>
-      <c r="K27" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="L27" s="49">
+      <c r="I27" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J27" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="K27" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="L27" s="37">
         <v>1</v>
       </c>
       <c r="M27" s="49">
-        <f t="shared" ref="M27" si="11">L27*5</f>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="N27" s="49">
+      <c r="N27" s="37">
         <v>100</v>
       </c>
-      <c r="O27" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P27" s="50">
-        <v>1.1999999999999999E-3</v>
+      <c r="O27" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P27" s="38">
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="Q27" s="50">
-        <f t="shared" ref="Q27" si="12">P27*N27</f>
-        <v>0.12</v>
-      </c>
-      <c r="R27" s="49"/>
+        <f t="shared" si="10"/>
+        <v>0.06</v>
+      </c>
+      <c r="R27" s="37"/>
       <c r="S27" s="55"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
@@ -5304,7 +5343,7 @@
         <v>18</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="E28" s="37" t="s">
         <v>178</v>
@@ -5328,11 +5367,11 @@
         <v>181</v>
       </c>
       <c r="L28" s="37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M28" s="37">
         <f>L28*5</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N28" s="37">
         <v>100</v>
@@ -5465,7 +5504,7 @@
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="72">
-        <f t="shared" ref="B31" si="13">ROW(B31) - ROW($B$9)</f>
+        <f t="shared" ref="B31" si="11">ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
       <c r="C31" s="68" t="s">
@@ -5499,7 +5538,7 @@
         <v>1</v>
       </c>
       <c r="M31" s="49">
-        <f t="shared" ref="M31" si="14">L31*5</f>
+        <f t="shared" ref="M31" si="12">L31*5</f>
         <v>5</v>
       </c>
       <c r="N31" s="37" t="s">
@@ -5578,7 +5617,7 @@
     <row r="33" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="72">
-        <f t="shared" ref="B33" si="15">ROW(B33) - ROW($B$9)</f>
+        <f t="shared" ref="B33" si="13">ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
       <c r="C33" s="68" t="s">
@@ -5612,7 +5651,7 @@
         <v>2</v>
       </c>
       <c r="M33" s="49">
-        <f t="shared" ref="M33" si="16">L33*5</f>
+        <f t="shared" ref="M33" si="14">L33*5</f>
         <v>10</v>
       </c>
       <c r="N33" s="49">
@@ -5625,7 +5664,7 @@
         <v>4.8300000000000003E-2</v>
       </c>
       <c r="Q33" s="50">
-        <f t="shared" ref="Q33" si="17">P33*N33</f>
+        <f t="shared" ref="Q33" si="15">P33*N33</f>
         <v>0.96600000000000008</v>
       </c>
       <c r="R33" s="49"/>
@@ -5724,7 +5763,7 @@
         <v>1</v>
       </c>
       <c r="M35" s="49">
-        <f t="shared" ref="M35" si="18">L35*5</f>
+        <f t="shared" ref="M35" si="16">L35*5</f>
         <v>5</v>
       </c>
       <c r="N35" s="49">
@@ -5737,7 +5776,7 @@
         <v>0.2079</v>
       </c>
       <c r="Q35" s="50">
-        <f t="shared" ref="Q35" si="19">P35*N35</f>
+        <f t="shared" ref="Q35" si="17">P35*N35</f>
         <v>2.0790000000000002</v>
       </c>
       <c r="R35" s="49"/>
@@ -5780,7 +5819,7 @@
         <v>1</v>
       </c>
       <c r="M36" s="49">
-        <f t="shared" ref="M36" si="20">L36*5</f>
+        <f t="shared" ref="M36" si="18">L36*5</f>
         <v>5</v>
       </c>
       <c r="N36" s="49">
@@ -5793,7 +5832,7 @@
         <v>0.54569999999999996</v>
       </c>
       <c r="Q36" s="50">
-        <f t="shared" ref="Q36" si="21">P36*N36</f>
+        <f t="shared" ref="Q36" si="19">P36*N36</f>
         <v>3.2741999999999996</v>
       </c>
       <c r="R36" s="49"/>
@@ -5977,17 +6016,17 @@
       <c r="K40" s="45"/>
       <c r="L40" s="45"/>
       <c r="M40" s="45"/>
-      <c r="N40" s="77" t="s">
+      <c r="N40" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="O40" s="78"/>
-      <c r="P40" s="78"/>
+      <c r="O40" s="86"/>
+      <c r="P40" s="86"/>
       <c r="Q40" s="47">
         <f>SUM(Q11:Q39)</f>
-        <v>60.518399999999993</v>
-      </c>
-      <c r="R40" s="79"/>
-      <c r="S40" s="80"/>
+        <v>58.313400000000001</v>
+      </c>
+      <c r="R40" s="87"/>
+      <c r="S40" s="88"/>
     </row>
     <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -6003,17 +6042,17 @@
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
-      <c r="N41" s="77" t="s">
+      <c r="N41" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="O41" s="78"/>
-      <c r="P41" s="78"/>
+      <c r="O41" s="86"/>
+      <c r="P41" s="86"/>
       <c r="Q41" s="48">
         <f>Q40/5</f>
-        <v>12.103679999999999</v>
-      </c>
-      <c r="R41" s="81"/>
-      <c r="S41" s="82"/>
+        <v>11.66268</v>
+      </c>
+      <c r="R41" s="89"/>
+      <c r="S41" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6034,26 +6073,26 @@
     <hyperlink ref="O20" r:id="rId8"/>
     <hyperlink ref="O21" r:id="rId9"/>
     <hyperlink ref="O22" r:id="rId10"/>
-    <hyperlink ref="O23" r:id="rId11"/>
-    <hyperlink ref="O27" r:id="rId12"/>
-    <hyperlink ref="O29" r:id="rId13"/>
-    <hyperlink ref="O26" r:id="rId14"/>
-    <hyperlink ref="O30" r:id="rId15"/>
-    <hyperlink ref="O35" r:id="rId16"/>
-    <hyperlink ref="O36" r:id="rId17"/>
-    <hyperlink ref="O37" r:id="rId18"/>
-    <hyperlink ref="O38" r:id="rId19"/>
-    <hyperlink ref="O39" r:id="rId20"/>
-    <hyperlink ref="O10" r:id="rId21"/>
-    <hyperlink ref="O14" r:id="rId22"/>
-    <hyperlink ref="O17" r:id="rId23"/>
-    <hyperlink ref="O24" r:id="rId24"/>
-    <hyperlink ref="O25" r:id="rId25"/>
-    <hyperlink ref="O28" r:id="rId26"/>
-    <hyperlink ref="O31" r:id="rId27"/>
-    <hyperlink ref="O32" r:id="rId28"/>
-    <hyperlink ref="O33" r:id="rId29"/>
-    <hyperlink ref="O34" r:id="rId30"/>
+    <hyperlink ref="O26" r:id="rId11"/>
+    <hyperlink ref="O29" r:id="rId12"/>
+    <hyperlink ref="O25" r:id="rId13"/>
+    <hyperlink ref="O30" r:id="rId14"/>
+    <hyperlink ref="O35" r:id="rId15"/>
+    <hyperlink ref="O36" r:id="rId16"/>
+    <hyperlink ref="O37" r:id="rId17"/>
+    <hyperlink ref="O38" r:id="rId18"/>
+    <hyperlink ref="O39" r:id="rId19"/>
+    <hyperlink ref="O10" r:id="rId20"/>
+    <hyperlink ref="O14" r:id="rId21"/>
+    <hyperlink ref="O23" r:id="rId22"/>
+    <hyperlink ref="O24" r:id="rId23"/>
+    <hyperlink ref="O28" r:id="rId24"/>
+    <hyperlink ref="O31" r:id="rId25"/>
+    <hyperlink ref="O32" r:id="rId26"/>
+    <hyperlink ref="O33" r:id="rId27"/>
+    <hyperlink ref="O34" r:id="rId28"/>
+    <hyperlink ref="O17" r:id="rId29"/>
+    <hyperlink ref="O27" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId31"/>
@@ -6096,15 +6135,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="84"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="92"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -6154,7 +6193,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="85"/>
+      <c r="S3" s="93"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -6179,7 +6218,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="86"/>
+      <c r="S4" s="94"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -6204,7 +6243,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="86"/>
+      <c r="S5" s="94"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -6225,7 +6264,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="86"/>
+      <c r="S6" s="94"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -6246,7 +6285,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="86"/>
+      <c r="S7" s="94"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -6267,7 +6306,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="86"/>
+      <c r="S8" s="94"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -6725,17 +6764,17 @@
       <c r="C17" s="67" t="s">
         <v>161</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="D17" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="37" t="s">
-        <v>162</v>
+      <c r="E17" s="95" t="s">
+        <v>209</v>
       </c>
       <c r="F17" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="G17" s="37" t="s">
-        <v>163</v>
+      <c r="G17" s="95" t="s">
+        <v>210</v>
       </c>
       <c r="H17" s="37" t="s">
         <v>95</v>
@@ -6744,9 +6783,11 @@
         <v>134</v>
       </c>
       <c r="J17" s="37" t="s">
-        <v>164</v>
-      </c>
-      <c r="K17" s="37"/>
+        <v>211</v>
+      </c>
+      <c r="K17" s="37" t="s">
+        <v>134</v>
+      </c>
       <c r="L17" s="37">
         <v>1</v>
       </c>
@@ -6754,18 +6795,18 @@
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N17" s="37">
+      <c r="N17" s="49">
         <v>55</v>
       </c>
       <c r="O17" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P17" s="38">
-        <v>0.13289999999999999</v>
+        <v>0.11169999999999999</v>
       </c>
       <c r="Q17" s="38">
         <f>P17*N17</f>
-        <v>7.3094999999999999</v>
+        <v>6.1434999999999995</v>
       </c>
       <c r="R17" s="37"/>
       <c r="S17" s="55"/>
@@ -6882,58 +6923,60 @@
       <c r="R19" s="37"/>
       <c r="S19" s="55"/>
     </row>
-    <row r="20" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="56"/>
       <c r="B20" s="46">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="68" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="49" t="s">
-        <v>45</v>
+      <c r="C20" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>46</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G20" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49" t="s">
-        <v>106</v>
+        <v>63</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J20" s="37" t="s">
+        <v>107</v>
       </c>
       <c r="K20" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L20" s="49">
+      <c r="L20" s="37">
         <v>1</v>
       </c>
       <c r="M20" s="37">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N20" s="49">
-        <v>55</v>
-      </c>
-      <c r="O20" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P20" s="50">
-        <v>0.1646</v>
-      </c>
-      <c r="Q20" s="50">
-        <f t="shared" ref="Q20" si="5">P20*N20</f>
-        <v>9.052999999999999</v>
-      </c>
-      <c r="R20" s="49"/>
+      <c r="N20" s="37">
+        <v>60</v>
+      </c>
+      <c r="O20" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P20" s="38">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="Q20" s="38">
+        <f>P20*N20</f>
+        <v>1.5899999999999999</v>
+      </c>
+      <c r="R20" s="37"/>
       <c r="S20" s="55"/>
     </row>
     <row r="21" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -6942,54 +6985,54 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="67" t="s">
+      <c r="C21" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="70" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" s="37" t="s">
+      <c r="D21" s="69" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="G21" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="H21" s="37" t="s">
+      <c r="G21" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="49" t="s">
         <v>93</v>
       </c>
-      <c r="I21" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J21" s="37" t="s">
-        <v>107</v>
+      <c r="I21" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J21" s="49" t="s">
+        <v>108</v>
       </c>
       <c r="K21" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L21" s="37">
+      <c r="L21" s="49">
         <v>1</v>
       </c>
       <c r="M21" s="37">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N21" s="37">
+      <c r="N21" s="49">
         <v>60</v>
       </c>
-      <c r="O21" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P21" s="38">
-        <v>2.6499999999999999E-2</v>
-      </c>
-      <c r="Q21" s="38">
-        <f>P21*N21</f>
-        <v>1.5899999999999999</v>
-      </c>
-      <c r="R21" s="37"/>
+      <c r="O21" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P21" s="50">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="Q21" s="50">
+        <f t="shared" ref="Q21" si="5">P21*N21</f>
+        <v>1.3980000000000001</v>
+      </c>
+      <c r="R21" s="49"/>
       <c r="S21" s="55"/>
     </row>
     <row r="22" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
@@ -6998,164 +7041,164 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="69" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="49" t="s">
+      <c r="D22" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="H22" s="49" t="s">
+      <c r="G22" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="I22" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J22" s="49" t="s">
-        <v>108</v>
+      <c r="I22" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>109</v>
       </c>
       <c r="K22" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L22" s="49">
+      <c r="L22" s="37">
         <v>1</v>
       </c>
       <c r="M22" s="37">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N22" s="49">
+      <c r="N22" s="37">
         <v>60</v>
       </c>
-      <c r="O22" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P22" s="50">
-        <v>2.3300000000000001E-2</v>
-      </c>
-      <c r="Q22" s="50">
-        <f t="shared" ref="Q22" si="6">P22*N22</f>
-        <v>1.3980000000000001</v>
-      </c>
-      <c r="R22" s="49"/>
+      <c r="O22" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P22" s="38">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="Q22" s="38">
+        <f>P22*N22</f>
+        <v>1.9319999999999999</v>
+      </c>
+      <c r="R22" s="37"/>
       <c r="S22" s="55"/>
     </row>
     <row r="23" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A23" s="56"/>
       <c r="B23" s="46">
-        <f t="shared" si="0"/>
+        <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
       <c r="C23" s="67" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="70" t="s">
-        <v>30</v>
+        <v>166</v>
+      </c>
+      <c r="D23" s="37" t="s">
+        <v>167</v>
       </c>
       <c r="E23" s="37" t="s">
-        <v>48</v>
+        <v>168</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>78</v>
+        <v>169</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>93</v>
+        <v>170</v>
       </c>
       <c r="I23" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J23" s="37" t="s">
-        <v>109</v>
+        <v>171</v>
       </c>
       <c r="K23" s="37" t="s">
         <v>134</v>
       </c>
       <c r="L23" s="37">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M23" s="37">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="N23" s="37">
-        <v>60</v>
+        <v>310</v>
       </c>
       <c r="O23" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P23" s="38">
-        <v>3.2199999999999999E-2</v>
+        <v>5.0200000000000002E-2</v>
       </c>
       <c r="Q23" s="38">
         <f>P23*N23</f>
-        <v>1.9319999999999999</v>
+        <v>15.562000000000001</v>
       </c>
       <c r="R23" s="37"/>
       <c r="S23" s="55"/>
     </row>
-    <row r="24" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="56"/>
       <c r="B24" s="46">
-        <f>ROW(B24) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="67" t="s">
-        <v>166</v>
-      </c>
-      <c r="D24" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="E24" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="F24" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G24" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>170</v>
-      </c>
-      <c r="I24" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J24" s="37" t="s">
-        <v>171</v>
-      </c>
-      <c r="K24" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L24" s="37">
-        <v>6</v>
+      <c r="C24" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="E24" s="49" t="s">
+        <v>172</v>
+      </c>
+      <c r="F24" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="G24" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="H24" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="I24" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J24" s="49" t="s">
+        <v>175</v>
+      </c>
+      <c r="K24" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L24" s="49">
+        <v>1</v>
       </c>
       <c r="M24" s="37">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="N24" s="37">
-        <v>310</v>
+        <v>60</v>
       </c>
       <c r="O24" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P24" s="38">
-        <v>5.0200000000000002E-2</v>
+        <v>3.2599999999999997E-2</v>
       </c>
       <c r="Q24" s="38">
         <f>P24*N24</f>
-        <v>15.562000000000001</v>
+        <v>1.9559999999999997</v>
       </c>
       <c r="R24" s="37"/>
       <c r="S24" s="55"/>
@@ -7163,55 +7206,55 @@
     <row r="25" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="56"/>
       <c r="B25" s="46">
-        <f t="shared" si="0"/>
+        <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
       <c r="C25" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="49" t="s">
-        <v>208</v>
-      </c>
-      <c r="E25" s="49" t="s">
-        <v>172</v>
-      </c>
-      <c r="F25" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="H25" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="I25" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J25" s="49" t="s">
-        <v>175</v>
-      </c>
-      <c r="K25" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="L25" s="49">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="D25" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G25" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I25" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="K25" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="L25" s="37">
+        <v>5</v>
       </c>
       <c r="M25" s="37">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="N25" s="37">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="O25" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P25" s="38">
-        <v>3.2599999999999997E-2</v>
+        <v>1E-3</v>
       </c>
       <c r="Q25" s="38">
         <f>P25*N25</f>
-        <v>1.9559999999999997</v>
+        <v>0.3</v>
       </c>
       <c r="R25" s="37"/>
       <c r="S25" s="55"/>
@@ -7219,57 +7262,57 @@
     <row r="26" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="56"/>
       <c r="B26" s="46">
-        <f>ROW(B26) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C26" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="E26" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26" s="37" t="s">
+      <c r="D26" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="G26" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="H26" s="37" t="s">
+      <c r="G26" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="H26" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="I26" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J26" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="K26" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="L26" s="37">
-        <v>5</v>
+      <c r="I26" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J26" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="K26" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="L26" s="49">
+        <v>1</v>
       </c>
       <c r="M26" s="37">
         <f t="shared" si="1"/>
-        <v>250</v>
-      </c>
-      <c r="N26" s="37">
-        <v>300</v>
-      </c>
-      <c r="O26" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P26" s="38">
-        <v>1E-3</v>
-      </c>
-      <c r="Q26" s="38">
-        <f>P26*N26</f>
-        <v>0.3</v>
-      </c>
-      <c r="R26" s="37"/>
+        <v>50</v>
+      </c>
+      <c r="N26" s="49">
+        <v>100</v>
+      </c>
+      <c r="O26" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P26" s="50">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q26" s="50">
+        <f t="shared" ref="Q26" si="6">P26*N26</f>
+        <v>0.12</v>
+      </c>
+      <c r="R26" s="49"/>
       <c r="S26" s="55"/>
     </row>
     <row r="27" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
@@ -7278,54 +7321,51 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="68" t="s">
+      <c r="C27" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" s="49" t="s">
-        <v>49</v>
+      <c r="D27" s="49" t="s">
+        <v>213</v>
+      </c>
+      <c r="E27" s="95" t="s">
+        <v>214</v>
       </c>
       <c r="F27" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27" s="49" t="s">
-        <v>79</v>
+        <v>215</v>
+      </c>
+      <c r="G27" s="95" t="s">
+        <v>216</v>
       </c>
       <c r="H27" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="I27" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J27" s="49" t="s">
-        <v>110</v>
-      </c>
-      <c r="K27" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="L27" s="49">
-        <v>1</v>
-      </c>
-      <c r="M27" s="37">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="N27" s="49">
+      <c r="I27" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J27" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="K27" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="L27" s="37">
+        <v>1</v>
+      </c>
+      <c r="M27" s="49">
+        <f t="shared" ref="M27" si="7">L27*5</f>
+        <v>5</v>
+      </c>
+      <c r="N27" s="37">
         <v>100</v>
       </c>
-      <c r="O27" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P27" s="50">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q27" s="50">
-        <f t="shared" ref="Q27" si="7">P27*N27</f>
-        <v>0.12</v>
-      </c>
-      <c r="R27" s="49"/>
+      <c r="O27" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P27" s="38">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="Q27" s="38"/>
+      <c r="R27" s="37"/>
       <c r="S27" s="55"/>
     </row>
     <row r="28" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
@@ -7338,7 +7378,7 @@
         <v>18</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="E28" s="37" t="s">
         <v>178</v>
@@ -7362,11 +7402,11 @@
         <v>181</v>
       </c>
       <c r="L28" s="37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M28" s="37">
         <f t="shared" si="1"/>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="N28" s="37">
         <v>200</v>
@@ -8011,17 +8051,17 @@
       <c r="K40" s="45"/>
       <c r="L40" s="45"/>
       <c r="M40" s="45"/>
-      <c r="N40" s="77" t="s">
+      <c r="N40" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="O40" s="78"/>
-      <c r="P40" s="78"/>
+      <c r="O40" s="86"/>
+      <c r="P40" s="86"/>
       <c r="Q40" s="47">
         <f>SUM(Q11:Q39)</f>
-        <v>443.89510000000001</v>
-      </c>
-      <c r="R40" s="79"/>
-      <c r="S40" s="80"/>
+        <v>433.67610000000008</v>
+      </c>
+      <c r="R40" s="87"/>
+      <c r="S40" s="88"/>
     </row>
     <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -8037,17 +8077,17 @@
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
-      <c r="N41" s="77" t="s">
+      <c r="N41" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="O41" s="78"/>
-      <c r="P41" s="78"/>
+      <c r="O41" s="86"/>
+      <c r="P41" s="86"/>
       <c r="Q41" s="48">
         <f>Q40/50</f>
-        <v>8.8779020000000006</v>
-      </c>
-      <c r="R41" s="81"/>
-      <c r="S41" s="82"/>
+        <v>8.673522000000002</v>
+      </c>
+      <c r="R41" s="89"/>
+      <c r="S41" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -8068,26 +8108,26 @@
     <hyperlink ref="O20" r:id="rId8"/>
     <hyperlink ref="O21" r:id="rId9"/>
     <hyperlink ref="O22" r:id="rId10"/>
-    <hyperlink ref="O23" r:id="rId11"/>
-    <hyperlink ref="O27" r:id="rId12"/>
-    <hyperlink ref="O29" r:id="rId13"/>
-    <hyperlink ref="O26" r:id="rId14"/>
-    <hyperlink ref="O30" r:id="rId15"/>
-    <hyperlink ref="O35" r:id="rId16"/>
-    <hyperlink ref="O36" r:id="rId17"/>
-    <hyperlink ref="O37" r:id="rId18"/>
-    <hyperlink ref="O38" r:id="rId19"/>
-    <hyperlink ref="O39" r:id="rId20"/>
-    <hyperlink ref="O10" r:id="rId21"/>
-    <hyperlink ref="O14" r:id="rId22"/>
-    <hyperlink ref="O17" r:id="rId23"/>
-    <hyperlink ref="O24" r:id="rId24"/>
-    <hyperlink ref="O25" r:id="rId25"/>
-    <hyperlink ref="O28" r:id="rId26"/>
-    <hyperlink ref="O31" r:id="rId27"/>
-    <hyperlink ref="O32" r:id="rId28"/>
-    <hyperlink ref="O33" r:id="rId29"/>
-    <hyperlink ref="O34" r:id="rId30"/>
+    <hyperlink ref="O26" r:id="rId11"/>
+    <hyperlink ref="O29" r:id="rId12"/>
+    <hyperlink ref="O25" r:id="rId13"/>
+    <hyperlink ref="O30" r:id="rId14"/>
+    <hyperlink ref="O35" r:id="rId15"/>
+    <hyperlink ref="O36" r:id="rId16"/>
+    <hyperlink ref="O37" r:id="rId17"/>
+    <hyperlink ref="O38" r:id="rId18"/>
+    <hyperlink ref="O39" r:id="rId19"/>
+    <hyperlink ref="O10" r:id="rId20"/>
+    <hyperlink ref="O14" r:id="rId21"/>
+    <hyperlink ref="O23" r:id="rId22"/>
+    <hyperlink ref="O24" r:id="rId23"/>
+    <hyperlink ref="O28" r:id="rId24"/>
+    <hyperlink ref="O31" r:id="rId25"/>
+    <hyperlink ref="O32" r:id="rId26"/>
+    <hyperlink ref="O33" r:id="rId27"/>
+    <hyperlink ref="O34" r:id="rId28"/>
+    <hyperlink ref="O27" r:id="rId29"/>
+    <hyperlink ref="O17" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId31"/>
@@ -8130,15 +8170,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="84"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="92"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -8188,7 +8228,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="85"/>
+      <c r="S3" s="93"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -8213,7 +8253,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="86"/>
+      <c r="S4" s="94"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -8238,7 +8278,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="86"/>
+      <c r="S5" s="94"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -8259,7 +8299,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="86"/>
+      <c r="S6" s="94"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -8280,7 +8320,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="86"/>
+      <c r="S7" s="94"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -8301,7 +8341,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="86"/>
+      <c r="S8" s="94"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -10045,17 +10085,17 @@
       <c r="K40" s="45"/>
       <c r="L40" s="45"/>
       <c r="M40" s="45"/>
-      <c r="N40" s="77" t="s">
+      <c r="N40" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="O40" s="78"/>
-      <c r="P40" s="78"/>
+      <c r="O40" s="86"/>
+      <c r="P40" s="86"/>
       <c r="Q40" s="47">
         <f>SUM(Q11:Q39)</f>
         <v>175.00190000000006</v>
       </c>
-      <c r="R40" s="79"/>
-      <c r="S40" s="80"/>
+      <c r="R40" s="87"/>
+      <c r="S40" s="88"/>
     </row>
     <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -10071,17 +10111,17 @@
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
-      <c r="N41" s="77" t="s">
+      <c r="N41" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="O41" s="78"/>
-      <c r="P41" s="78"/>
+      <c r="O41" s="86"/>
+      <c r="P41" s="86"/>
       <c r="Q41" s="48">
         <f>Q40/500</f>
         <v>0.35000380000000014</v>
       </c>
-      <c r="R41" s="81"/>
-      <c r="S41" s="82"/>
+      <c r="R41" s="89"/>
+      <c r="S41" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -10164,15 +10204,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="84"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="92"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -10222,7 +10262,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="85"/>
+      <c r="S3" s="93"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -10247,7 +10287,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="86"/>
+      <c r="S4" s="94"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -10272,7 +10312,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="86"/>
+      <c r="S5" s="94"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -10293,7 +10333,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="86"/>
+      <c r="S6" s="94"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -10314,7 +10354,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="86"/>
+      <c r="S7" s="94"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -10335,7 +10375,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="86"/>
+      <c r="S8" s="94"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -10568,10 +10608,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="87" t="s">
+      <c r="C13" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="88" t="s">
+      <c r="D13" s="78" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="62" t="s">
@@ -10620,14 +10660,14 @@
     </row>
     <row r="14" spans="1:19" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="61"/>
-      <c r="B14" s="90">
+      <c r="B14" s="80">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="87" t="s">
+      <c r="C14" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="89" t="s">
+      <c r="D14" s="79" t="s">
         <v>155</v>
       </c>
       <c r="E14" s="75" t="s">
@@ -10661,13 +10701,13 @@
       <c r="N14" s="75">
         <v>6</v>
       </c>
-      <c r="O14" s="91" t="s">
-        <v>136</v>
-      </c>
-      <c r="P14" s="92">
+      <c r="O14" s="81" t="s">
+        <v>136</v>
+      </c>
+      <c r="P14" s="82">
         <v>0.22550000000000001</v>
       </c>
-      <c r="Q14" s="92">
+      <c r="Q14" s="82">
         <f t="shared" ref="Q14" si="2">P14*N14</f>
         <v>1.353</v>
       </c>
@@ -11237,7 +11277,7 @@
       <c r="C25" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="89" t="s">
+      <c r="D25" s="79" t="s">
         <v>208</v>
       </c>
       <c r="E25" s="75" t="s">
@@ -11349,7 +11389,7 @@
       <c r="C27" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="89" t="s">
+      <c r="D27" s="79" t="s">
         <v>31</v>
       </c>
       <c r="E27" s="75" t="s">
@@ -11383,13 +11423,13 @@
       <c r="N27" s="75">
         <v>100</v>
       </c>
-      <c r="O27" s="91" t="s">
-        <v>136</v>
-      </c>
-      <c r="P27" s="92">
+      <c r="O27" s="81" t="s">
+        <v>136</v>
+      </c>
+      <c r="P27" s="82">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q27" s="92">
+      <c r="Q27" s="82">
         <f t="shared" ref="Q27" si="7">P27*N27</f>
         <v>0.12</v>
       </c>
@@ -11566,14 +11606,14 @@
     </row>
     <row r="31" spans="1:19" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="61"/>
-      <c r="B31" s="90">
+      <c r="B31" s="80">
         <f t="shared" ref="B31" si="8">ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
       <c r="C31" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="89" t="s">
+      <c r="D31" s="79" t="s">
         <v>182</v>
       </c>
       <c r="E31" s="75" t="s">
@@ -11613,10 +11653,10 @@
       <c r="P31" s="63" t="s">
         <v>134</v>
       </c>
-      <c r="Q31" s="92" t="s">
-        <v>134</v>
-      </c>
-      <c r="R31" s="93" t="s">
+      <c r="Q31" s="82" t="s">
+        <v>134</v>
+      </c>
+      <c r="R31" s="83" t="s">
         <v>183</v>
       </c>
       <c r="S31" s="64"/>
@@ -11832,13 +11872,13 @@
       <c r="N35" s="75">
         <v>10</v>
       </c>
-      <c r="O35" s="91" t="s">
-        <v>136</v>
-      </c>
-      <c r="P35" s="92">
+      <c r="O35" s="81" t="s">
+        <v>136</v>
+      </c>
+      <c r="P35" s="82">
         <v>0.2079</v>
       </c>
-      <c r="Q35" s="92">
+      <c r="Q35" s="82">
         <f t="shared" ref="Q35:Q36" si="11">P35*N35</f>
         <v>2.0790000000000002</v>
       </c>
@@ -11907,7 +11947,7 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="87" t="s">
+      <c r="C37" s="77" t="s">
         <v>20</v>
       </c>
       <c r="D37" s="62" t="s">
@@ -11955,7 +11995,7 @@
         <v>17.153400000000001</v>
       </c>
       <c r="R37" s="62"/>
-      <c r="S37" s="94"/>
+      <c r="S37" s="84"/>
     </row>
     <row r="38" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="56"/>
@@ -12011,7 +12051,7 @@
       <c r="R38" s="37"/>
       <c r="S38" s="39"/>
     </row>
-    <row r="39" spans="1:19" s="58" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="56"/>
       <c r="B39" s="46">
         <f t="shared" si="0"/>
@@ -12079,17 +12119,17 @@
       <c r="K40" s="45"/>
       <c r="L40" s="45"/>
       <c r="M40" s="45"/>
-      <c r="N40" s="77" t="s">
+      <c r="N40" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="O40" s="78"/>
-      <c r="P40" s="78"/>
+      <c r="O40" s="86"/>
+      <c r="P40" s="86"/>
       <c r="Q40" s="47">
         <f>SUM(Q11:Q39)</f>
         <v>175.00190000000006</v>
       </c>
-      <c r="R40" s="79"/>
-      <c r="S40" s="80"/>
+      <c r="R40" s="87"/>
+      <c r="S40" s="88"/>
     </row>
     <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -12105,17 +12145,17 @@
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
-      <c r="N41" s="77" t="s">
+      <c r="N41" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="O41" s="78"/>
-      <c r="P41" s="78"/>
+      <c r="O41" s="86"/>
+      <c r="P41" s="86"/>
       <c r="Q41" s="48">
         <f>Q40/500</f>
         <v>0.35000380000000014</v>
       </c>
-      <c r="R41" s="81"/>
-      <c r="S41" s="82"/>
+      <c r="R41" s="89"/>
+      <c r="S41" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/Design Files/IoT-Button-v1.2/BOM/eSpark-BOM-IoT-Button.xlsx
+++ b/Design Files/IoT-Button-v1.2/BOM/eSpark-BOM-IoT-Button.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="2 Boards" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="228">
   <si>
     <t>Component list</t>
   </si>
@@ -680,6 +680,33 @@
   </si>
   <si>
     <t>56K</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>N-CHANNEL 20-V (D-S) MOSFET</t>
+  </si>
+  <si>
+    <t>Sot-23</t>
+  </si>
+  <si>
+    <t>SI2302CDS</t>
+  </si>
+  <si>
+    <t>TECH PUBLIC</t>
+  </si>
+  <si>
+    <t>R1, R4, R6, R8, R10, R13, R14</t>
+  </si>
+  <si>
+    <t>3.7V 250mAh 402035 JST 1.25mm lithium polymer li ion rechargeable battery Lipo cells for MP3 MP4 GPS bluetooth headset video pen</t>
+  </si>
+  <si>
+    <t>Black universal American Canada Japan power charger 100-240V US AC to DC 5.5*2.5mm power adapter 1A 3V/5V/6V/7V/9V/12V optional</t>
+  </si>
+  <si>
+    <t>C5310968</t>
   </si>
 </sst>
 </file>
@@ -691,7 +718,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -853,6 +880,39 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -1151,7 +1211,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1383,6 +1443,9 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
@@ -1415,7 +1478,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2025,7 +2112,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S41"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -2059,15 +2146,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="92"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92"/>
+      <c r="P1" s="92"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="92"/>
+      <c r="S1" s="93"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2117,7 +2204,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="93"/>
+      <c r="S3" s="94"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2142,7 +2229,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="94"/>
+      <c r="S4" s="95"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2167,7 +2254,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="94"/>
+      <c r="S5" s="95"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2188,7 +2275,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="94"/>
+      <c r="S6" s="95"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2209,7 +2296,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="94"/>
+      <c r="S7" s="95"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2230,7 +2317,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="94"/>
+      <c r="S8" s="95"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2404,7 +2491,7 @@
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="56"/>
       <c r="B12" s="46">
-        <f t="shared" ref="B12:B39" si="1">ROW(B12) - ROW($B$9)</f>
+        <f t="shared" ref="B12:B40" si="1">ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
       <c r="C12" s="67" t="s">
@@ -2494,7 +2581,7 @@
         <v>1</v>
       </c>
       <c r="M13" s="37">
-        <f t="shared" ref="M13:M39" si="2">L13*2</f>
+        <f t="shared" ref="M13:M40" si="2">L13*2</f>
         <v>2</v>
       </c>
       <c r="N13" s="49">
@@ -2691,13 +2778,13 @@
       <c r="D17" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="95" t="s">
+      <c r="E17" s="85" t="s">
         <v>209</v>
       </c>
       <c r="F17" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="G17" s="95" t="s">
+      <c r="G17" s="85" t="s">
         <v>210</v>
       </c>
       <c r="H17" s="37" t="s">
@@ -3073,170 +3160,170 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="56"/>
-      <c r="B24" s="73">
-        <f t="shared" si="1"/>
+      <c r="B24" s="46">
+        <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="74" t="s">
+      <c r="C24" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="75" t="s">
-        <v>208</v>
-      </c>
-      <c r="E24" s="75" t="s">
-        <v>172</v>
-      </c>
-      <c r="F24" s="75" t="s">
-        <v>64</v>
-      </c>
-      <c r="G24" s="75" t="s">
-        <v>173</v>
-      </c>
-      <c r="H24" s="75" t="s">
-        <v>174</v>
-      </c>
-      <c r="I24" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="J24" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="K24" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="L24" s="75">
+      <c r="D24" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="E24" s="96" t="s">
+        <v>220</v>
+      </c>
+      <c r="F24" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="G24" s="96" t="s">
+        <v>222</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="I24" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="K24" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L24" s="37">
         <v>1</v>
       </c>
       <c r="M24" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N24" s="49">
-        <v>10</v>
-      </c>
-      <c r="O24" s="66" t="s">
-        <v>136</v>
-      </c>
-      <c r="P24" s="63">
-        <v>3.1E-2</v>
-      </c>
-      <c r="Q24" s="50">
-        <f t="shared" ref="Q24" si="8">P24*N24</f>
-        <v>0.31</v>
-      </c>
-      <c r="R24" s="49"/>
+      <c r="N24" s="37">
+        <v>20</v>
+      </c>
+      <c r="O24" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P24" s="38">
+        <v>3.4099999999999998E-2</v>
+      </c>
+      <c r="Q24" s="38">
+        <f>P24*N24</f>
+        <v>0.68199999999999994</v>
+      </c>
+      <c r="R24" s="37"/>
       <c r="S24" s="55"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="56"/>
-      <c r="B25" s="46">
-        <f>ROW(B25) - ROW($B$9)</f>
+      <c r="B25" s="73">
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C25" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="E25" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="G25" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="H25" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="I25" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J25" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="K25" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="L25" s="37">
-        <v>5</v>
+      <c r="C25" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="75" t="s">
+        <v>208</v>
+      </c>
+      <c r="E25" s="75" t="s">
+        <v>172</v>
+      </c>
+      <c r="F25" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" s="75" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25" s="75" t="s">
+        <v>174</v>
+      </c>
+      <c r="I25" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="K25" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="L25" s="75">
+        <v>1</v>
       </c>
       <c r="M25" s="37">
         <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="N25" s="49">
         <v>10</v>
       </c>
-      <c r="N25" s="37">
-        <v>100</v>
-      </c>
-      <c r="O25" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P25" s="38">
-        <v>1E-3</v>
-      </c>
-      <c r="Q25" s="38">
-        <f>P25*N25</f>
-        <v>0.1</v>
-      </c>
-      <c r="R25" s="37"/>
+      <c r="O25" s="66" t="s">
+        <v>136</v>
+      </c>
+      <c r="P25" s="63">
+        <v>3.1E-2</v>
+      </c>
+      <c r="Q25" s="50">
+        <f t="shared" ref="Q25" si="8">P25*N25</f>
+        <v>0.31</v>
+      </c>
+      <c r="R25" s="49"/>
       <c r="S25" s="55"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="56"/>
       <c r="B26" s="46">
-        <f t="shared" si="1"/>
+        <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
       <c r="C26" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="F26" s="49" t="s">
+      <c r="D26" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="G26" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="H26" s="49" t="s">
+      <c r="G26" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="I26" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J26" s="49" t="s">
-        <v>110</v>
-      </c>
-      <c r="K26" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="L26" s="49">
-        <v>1</v>
+      <c r="I26" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J26" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="K26" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="L26" s="37">
+        <v>7</v>
       </c>
       <c r="M26" s="37">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="N26" s="49">
+        <v>14</v>
+      </c>
+      <c r="N26" s="37">
         <v>100</v>
       </c>
-      <c r="O26" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P26" s="50">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q26" s="50">
-        <f t="shared" ref="Q26:Q27" si="9">P26*N26</f>
-        <v>0.12</v>
-      </c>
-      <c r="R26" s="49"/>
+      <c r="O26" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P26" s="38">
+        <v>1E-3</v>
+      </c>
+      <c r="Q26" s="38">
+        <f>P26*N26</f>
+        <v>0.1</v>
+      </c>
+      <c r="R26" s="37"/>
       <c r="S26" s="55"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
@@ -3245,95 +3332,95 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="C27" s="67" t="s">
+      <c r="C27" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="49" t="s">
-        <v>213</v>
-      </c>
-      <c r="E27" s="95" t="s">
-        <v>214</v>
+      <c r="D27" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="49" t="s">
+        <v>49</v>
       </c>
       <c r="F27" s="49" t="s">
-        <v>215</v>
-      </c>
-      <c r="G27" s="95" t="s">
-        <v>216</v>
+        <v>65</v>
+      </c>
+      <c r="G27" s="49" t="s">
+        <v>79</v>
       </c>
       <c r="H27" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="I27" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J27" s="37" t="s">
-        <v>217</v>
-      </c>
-      <c r="K27" s="37" t="s">
-        <v>218</v>
-      </c>
-      <c r="L27" s="37">
+      <c r="I27" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J27" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="K27" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="L27" s="49">
         <v>1</v>
       </c>
       <c r="M27" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N27" s="37">
+      <c r="N27" s="49">
         <v>100</v>
       </c>
-      <c r="O27" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P27" s="38">
-        <v>5.9999999999999995E-4</v>
+      <c r="O27" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P27" s="50">
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q27" s="50">
-        <f t="shared" si="9"/>
-        <v>0.06</v>
-      </c>
-      <c r="R27" s="37"/>
+        <f t="shared" ref="Q27:Q28" si="9">P27*N27</f>
+        <v>0.12</v>
+      </c>
+      <c r="R27" s="49"/>
       <c r="S27" s="55"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="56"/>
       <c r="B28" s="46">
-        <f>ROW(B28) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="C28" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="E28" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="H28" s="37" t="s">
+      <c r="D28" s="49" t="s">
+        <v>213</v>
+      </c>
+      <c r="E28" s="85" t="s">
+        <v>214</v>
+      </c>
+      <c r="F28" s="49" t="s">
+        <v>215</v>
+      </c>
+      <c r="G28" s="85" t="s">
+        <v>216</v>
+      </c>
+      <c r="H28" s="49" t="s">
         <v>86</v>
       </c>
       <c r="I28" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>180</v>
+        <v>217</v>
       </c>
       <c r="K28" s="37" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="L28" s="37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M28" s="37">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N28" s="37">
         <v>100</v>
@@ -3342,11 +3429,11 @@
         <v>136</v>
       </c>
       <c r="P28" s="38">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="Q28" s="38">
-        <f>P28*N28</f>
-        <v>0.11</v>
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="Q28" s="50">
+        <f t="shared" si="9"/>
+        <v>0.06</v>
       </c>
       <c r="R28" s="37"/>
       <c r="S28" s="55"/>
@@ -3354,23 +3441,23 @@
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="56"/>
       <c r="B29" s="46">
-        <f t="shared" si="1"/>
+        <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="68" t="s">
+      <c r="C29" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="70" t="s">
-        <v>177</v>
+      <c r="D29" s="37" t="s">
+        <v>212</v>
       </c>
       <c r="E29" s="37" t="s">
-        <v>50</v>
+        <v>178</v>
       </c>
       <c r="F29" s="37" t="s">
         <v>65</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="H29" s="37" t="s">
         <v>86</v>
@@ -3379,17 +3466,17 @@
         <v>134</v>
       </c>
       <c r="J29" s="37" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
       <c r="K29" s="37" t="s">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="L29" s="37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M29" s="37">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N29" s="37">
         <v>100</v>
@@ -3398,11 +3485,11 @@
         <v>136</v>
       </c>
       <c r="P29" s="38">
-        <v>1E-3</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q29" s="38">
         <f>P29*N29</f>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="R29" s="37"/>
       <c r="S29" s="55"/>
@@ -3410,23 +3497,23 @@
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="56"/>
       <c r="B30" s="46">
-        <f>ROW(B30) - ROW($B$9)</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="C30" s="68" t="s">
         <v>18</v>
       </c>
       <c r="D30" s="70" t="s">
-        <v>32</v>
+        <v>177</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F30" s="37" t="s">
         <v>65</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H30" s="37" t="s">
         <v>86</v>
@@ -3435,10 +3522,10 @@
         <v>134</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -3447,301 +3534,301 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N30" s="49">
+      <c r="N30" s="37">
         <v>100</v>
       </c>
       <c r="O30" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P30" s="38">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q30" s="50">
-        <f t="shared" ref="Q30" si="10">P30*N30</f>
-        <v>0.13</v>
-      </c>
-      <c r="R30" s="49"/>
+        <v>1E-3</v>
+      </c>
+      <c r="Q30" s="38">
+        <f>P30*N30</f>
+        <v>0.1</v>
+      </c>
+      <c r="R30" s="37"/>
       <c r="S30" s="55"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="56"/>
-      <c r="B31" s="72">
-        <f t="shared" ref="B31" si="11">ROW(B31) - ROW($B$9)</f>
+      <c r="B31" s="46">
+        <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
       <c r="C31" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="E31" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="F31" s="49" t="s">
+      <c r="D31" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="G31" s="49" t="s">
-        <v>81</v>
-      </c>
-      <c r="H31" s="49" t="s">
+      <c r="G31" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="H31" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="I31" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J31" s="49" t="s">
-        <v>112</v>
-      </c>
-      <c r="K31" s="49" t="s">
-        <v>183</v>
-      </c>
-      <c r="L31" s="49">
+      <c r="I31" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J31" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="K31" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="L31" s="37">
         <v>1</v>
       </c>
       <c r="M31" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N31" s="37">
+      <c r="N31" s="49">
         <v>100</v>
       </c>
       <c r="O31" s="59" t="s">
         <v>136</v>
       </c>
-      <c r="P31" s="38" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q31" s="38" t="s">
-        <v>134</v>
-      </c>
-      <c r="R31" s="76" t="s">
+      <c r="P31" s="38">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q31" s="50">
+        <f t="shared" ref="Q31" si="10">P31*N31</f>
+        <v>0.13</v>
+      </c>
+      <c r="R31" s="49"/>
+      <c r="S31" s="55"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" s="56"/>
+      <c r="B32" s="72">
+        <f t="shared" ref="B32" si="11">ROW(B32) - ROW($B$9)</f>
+        <v>23</v>
+      </c>
+      <c r="C32" s="97" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="98" t="s">
+        <v>182</v>
+      </c>
+      <c r="E32" s="98" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" s="98" t="s">
+        <v>65</v>
+      </c>
+      <c r="G32" s="98" t="s">
+        <v>81</v>
+      </c>
+      <c r="H32" s="98" t="s">
+        <v>86</v>
+      </c>
+      <c r="I32" s="98" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="98" t="s">
+        <v>112</v>
+      </c>
+      <c r="K32" s="98" t="s">
         <v>183</v>
       </c>
-      <c r="S31" s="55"/>
-    </row>
-    <row r="32" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A32" s="56"/>
-      <c r="B32" s="46">
-        <f>ROW(B32) - ROW($B$9)</f>
-        <v>23</v>
-      </c>
-      <c r="C32" s="68" t="s">
-        <v>187</v>
-      </c>
-      <c r="D32" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="E32" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G32" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="K32" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L32" s="37">
-        <v>1</v>
-      </c>
-      <c r="M32" s="37">
+      <c r="L32" s="98">
+        <v>1</v>
+      </c>
+      <c r="M32" s="99">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N32" s="49">
-        <v>5</v>
-      </c>
-      <c r="O32" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P32" s="38">
-        <v>0.1336</v>
-      </c>
-      <c r="Q32" s="50">
-        <f t="shared" ref="Q32" si="12">P32*N32</f>
-        <v>0.66799999999999993</v>
-      </c>
-      <c r="R32" s="49"/>
+      <c r="N32" s="99">
+        <v>100</v>
+      </c>
+      <c r="O32" s="100" t="s">
+        <v>136</v>
+      </c>
+      <c r="P32" s="101" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q32" s="101" t="s">
+        <v>134</v>
+      </c>
+      <c r="R32" s="102" t="s">
+        <v>183</v>
+      </c>
       <c r="S32" s="55"/>
     </row>
-    <row r="33" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A33" s="61"/>
-      <c r="B33" s="72">
-        <f t="shared" ref="B33" si="13">ROW(B33) - ROW($B$9)</f>
+    <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A33" s="56"/>
+      <c r="B33" s="46">
+        <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
       <c r="C33" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="D33" s="49" t="s">
-        <v>188</v>
-      </c>
-      <c r="E33" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="F33" s="49" t="s">
+      <c r="D33" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="F33" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="G33" s="49" t="s">
-        <v>190</v>
-      </c>
-      <c r="H33" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="I33" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J33" s="49" t="s">
-        <v>192</v>
-      </c>
-      <c r="K33" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="L33" s="49">
-        <v>2</v>
+      <c r="G33" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="H33" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J33" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="K33" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L33" s="37">
+        <v>1</v>
       </c>
       <c r="M33" s="37">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="N33" s="62">
-        <v>10</v>
-      </c>
-      <c r="O33" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P33" s="50">
-        <v>4.8300000000000003E-2</v>
-      </c>
-      <c r="Q33" s="63">
-        <f>P33*N33</f>
-        <v>0.48300000000000004</v>
-      </c>
-      <c r="R33" s="62"/>
-      <c r="S33" s="64"/>
+        <v>2</v>
+      </c>
+      <c r="N33" s="49">
+        <v>5</v>
+      </c>
+      <c r="O33" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P33" s="38">
+        <v>0.1336</v>
+      </c>
+      <c r="Q33" s="50">
+        <f t="shared" ref="Q33" si="12">P33*N33</f>
+        <v>0.66799999999999993</v>
+      </c>
+      <c r="R33" s="49"/>
+      <c r="S33" s="55"/>
     </row>
     <row r="34" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A34" s="56"/>
-      <c r="B34" s="46">
-        <f>ROW(B34) - ROW($B$9)</f>
+      <c r="A34" s="61"/>
+      <c r="B34" s="72">
+        <f t="shared" ref="B34" si="13">ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="67" t="s">
+      <c r="C34" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="D34" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="E34" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="F34" s="37" t="s">
+      <c r="D34" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="E34" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="F34" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="G34" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="I34" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J34" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="K34" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L34" s="37">
-        <v>1</v>
+      <c r="G34" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="H34" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="I34" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="K34" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L34" s="49">
+        <v>2</v>
       </c>
       <c r="M34" s="37">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="N34" s="49">
+        <v>4</v>
+      </c>
+      <c r="N34" s="62">
         <v>10</v>
       </c>
-      <c r="O34" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P34" s="38">
-        <v>6.4600000000000005E-2</v>
-      </c>
-      <c r="Q34" s="50">
-        <f t="shared" ref="Q34" si="14">P34*N34</f>
-        <v>0.64600000000000002</v>
-      </c>
-      <c r="R34" s="49"/>
-      <c r="S34" s="55"/>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="O34" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P34" s="50">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="Q34" s="63">
+        <f>P34*N34</f>
+        <v>0.48300000000000004</v>
+      </c>
+      <c r="R34" s="62"/>
+      <c r="S34" s="64"/>
+    </row>
+    <row r="35" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A35" s="56"/>
       <c r="B35" s="46">
-        <f t="shared" si="1"/>
+        <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="E35" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="G35" s="49" t="s">
-        <v>83</v>
-      </c>
-      <c r="H35" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="I35" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J35" s="49" t="s">
-        <v>114</v>
+      <c r="C35" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="D35" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="E35" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="F35" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G35" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="H35" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I35" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="37" t="s">
+        <v>196</v>
       </c>
       <c r="K35" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L35" s="49">
+      <c r="L35" s="37">
         <v>1</v>
       </c>
       <c r="M35" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N35" s="37">
-        <v>5</v>
-      </c>
-      <c r="O35" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P35" s="50">
-        <v>0.2079</v>
-      </c>
-      <c r="Q35" s="38">
-        <f>P35*N35</f>
-        <v>1.0395000000000001</v>
-      </c>
-      <c r="R35" s="37"/>
+      <c r="N35" s="49">
+        <v>10</v>
+      </c>
+      <c r="O35" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P35" s="38">
+        <v>6.4600000000000005E-2</v>
+      </c>
+      <c r="Q35" s="50">
+        <f t="shared" ref="Q35" si="14">P35*N35</f>
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="R35" s="49"/>
       <c r="S35" s="55"/>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
@@ -3751,28 +3838,28 @@
         <v>27</v>
       </c>
       <c r="C36" s="68" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E36" s="49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F36" s="49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G36" s="49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H36" s="49" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I36" s="49" t="s">
         <v>134</v>
       </c>
       <c r="J36" s="49" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K36" s="37" t="s">
         <v>134</v>
@@ -3784,20 +3871,20 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N36" s="49">
-        <v>3</v>
+      <c r="N36" s="37">
+        <v>5</v>
       </c>
       <c r="O36" s="60" t="s">
         <v>136</v>
       </c>
       <c r="P36" s="50">
-        <v>0.54569999999999996</v>
-      </c>
-      <c r="Q36" s="50">
-        <f t="shared" ref="Q36" si="15">P36*N36</f>
-        <v>1.6370999999999998</v>
-      </c>
-      <c r="R36" s="49"/>
+        <v>0.2079</v>
+      </c>
+      <c r="Q36" s="38">
+        <f>P36*N36</f>
+        <v>1.0395000000000001</v>
+      </c>
+      <c r="R36" s="37"/>
       <c r="S36" s="55"/>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
@@ -3806,87 +3893,89 @@
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="C37" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="E37" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="F37" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G37" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="H37" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="I37" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J37" s="37" t="s">
-        <v>116</v>
+      <c r="C37" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="G37" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="H37" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="I37" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J37" s="49" t="s">
+        <v>115</v>
       </c>
       <c r="K37" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L37" s="37">
+      <c r="L37" s="49">
         <v>1</v>
       </c>
       <c r="M37" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N37" s="37">
+      <c r="N37" s="49">
         <v>3</v>
       </c>
-      <c r="O37" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P37" s="38">
-        <v>2.8589000000000002</v>
-      </c>
-      <c r="Q37" s="38">
-        <f>P37*N37</f>
-        <v>8.5767000000000007</v>
-      </c>
-      <c r="R37" s="37"/>
+      <c r="O37" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P37" s="50">
+        <v>0.54569999999999996</v>
+      </c>
+      <c r="Q37" s="50">
+        <f t="shared" ref="Q37" si="15">P37*N37</f>
+        <v>1.6370999999999998</v>
+      </c>
+      <c r="R37" s="49"/>
       <c r="S37" s="55"/>
     </row>
-    <row r="38" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="56"/>
       <c r="B38" s="46">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="C38" s="67" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>143</v>
+        <v>36</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="I38" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="K38" s="37"/>
+        <v>116</v>
+      </c>
+      <c r="K38" s="37" t="s">
+        <v>134</v>
+      </c>
       <c r="L38" s="37">
         <v>1</v>
       </c>
@@ -3895,35 +3984,35 @@
         <v>2</v>
       </c>
       <c r="N38" s="37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O38" s="59" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="P38" s="38">
-        <v>3.28</v>
+        <v>2.8589000000000002</v>
       </c>
       <c r="Q38" s="38">
         <f>P38*N38</f>
-        <v>6.56</v>
+        <v>8.5767000000000007</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="55"/>
     </row>
-    <row r="39" spans="1:19" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A39" s="56"/>
       <c r="B39" s="46">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="C39" s="67" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D39" s="37" t="s">
         <v>143</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>148</v>
+        <v>225</v>
       </c>
       <c r="F39" s="37" t="s">
         <v>134</v>
@@ -3948,79 +4037,133 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N39" s="49">
-        <v>1</v>
+      <c r="N39" s="37">
+        <v>2</v>
       </c>
       <c r="O39" s="59" t="s">
         <v>147</v>
       </c>
       <c r="P39" s="38">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="Q39" s="50">
-        <f t="shared" ref="Q39" si="16">P39*N39</f>
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="R39" s="49"/>
+        <v>4.67</v>
+      </c>
+      <c r="Q39" s="38">
+        <f>P39*N39</f>
+        <v>9.34</v>
+      </c>
+      <c r="R39" s="37"/>
       <c r="S39" s="55"/>
     </row>
-    <row r="40" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="56"/>
-      <c r="B40" s="40"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="44"/>
-      <c r="G40" s="45"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="44"/>
-      <c r="K40" s="45"/>
-      <c r="L40" s="45"/>
-      <c r="M40" s="45"/>
-      <c r="N40" s="85" t="s">
-        <v>5</v>
-      </c>
-      <c r="O40" s="86"/>
-      <c r="P40" s="86"/>
-      <c r="Q40" s="47">
-        <f>SUM(Q11:Q39)</f>
-        <v>31.4513</v>
-      </c>
-      <c r="R40" s="87"/>
-      <c r="S40" s="88"/>
+      <c r="B40" s="46">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="G40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="I40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="K40" s="37"/>
+      <c r="L40" s="37">
+        <v>1</v>
+      </c>
+      <c r="M40" s="37">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="N40" s="49">
+        <v>1</v>
+      </c>
+      <c r="O40" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="P40" s="38">
+        <v>0.35</v>
+      </c>
+      <c r="Q40" s="50">
+        <f t="shared" ref="Q40" si="16">P40*N40</f>
+        <v>0.35</v>
+      </c>
+      <c r="R40" s="49"/>
+      <c r="S40" s="55"/>
     </row>
     <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="56"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
-      <c r="N41" s="85" t="s">
+      <c r="B41" s="40"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="44"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="45"/>
+      <c r="J41" s="44"/>
+      <c r="K41" s="45"/>
+      <c r="L41" s="45"/>
+      <c r="M41" s="45"/>
+      <c r="N41" s="86" t="s">
+        <v>5</v>
+      </c>
+      <c r="O41" s="87"/>
+      <c r="P41" s="87"/>
+      <c r="Q41" s="47">
+        <f>SUM(Q11:Q40)</f>
+        <v>32.793300000000009</v>
+      </c>
+      <c r="R41" s="88"/>
+      <c r="S41" s="89"/>
+    </row>
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="56"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="O41" s="86"/>
-      <c r="P41" s="86"/>
-      <c r="Q41" s="48">
-        <f>Q40/2</f>
-        <v>15.72565</v>
-      </c>
-      <c r="R41" s="89"/>
-      <c r="S41" s="90"/>
+      <c r="O42" s="87"/>
+      <c r="P42" s="87"/>
+      <c r="Q42" s="48">
+        <f>Q41/2</f>
+        <v>16.396650000000005</v>
+      </c>
+      <c r="R42" s="90"/>
+      <c r="S42" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S41"/>
     <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S42"/>
+    <mergeCell ref="N42:P42"/>
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
   </mergeCells>
@@ -4035,36 +4178,37 @@
     <hyperlink ref="O20" r:id="rId8"/>
     <hyperlink ref="O21" r:id="rId9"/>
     <hyperlink ref="O22" r:id="rId10"/>
-    <hyperlink ref="O26" r:id="rId11"/>
-    <hyperlink ref="O29" r:id="rId12"/>
-    <hyperlink ref="O25" r:id="rId13"/>
-    <hyperlink ref="O30" r:id="rId14"/>
-    <hyperlink ref="O35" r:id="rId15"/>
-    <hyperlink ref="O36" r:id="rId16"/>
-    <hyperlink ref="O37" r:id="rId17"/>
-    <hyperlink ref="O38" r:id="rId18"/>
-    <hyperlink ref="O39" r:id="rId19"/>
-    <hyperlink ref="O10" r:id="rId20"/>
-    <hyperlink ref="O14" r:id="rId21"/>
-    <hyperlink ref="O23" r:id="rId22"/>
-    <hyperlink ref="O24" r:id="rId23"/>
-    <hyperlink ref="O28" r:id="rId24"/>
-    <hyperlink ref="O31" r:id="rId25"/>
-    <hyperlink ref="O32" r:id="rId26"/>
-    <hyperlink ref="O33" r:id="rId27"/>
-    <hyperlink ref="O34" r:id="rId28"/>
-    <hyperlink ref="O17" r:id="rId29"/>
-    <hyperlink ref="O27" r:id="rId30"/>
+    <hyperlink ref="O27" r:id="rId11"/>
+    <hyperlink ref="O30" r:id="rId12"/>
+    <hyperlink ref="O26" r:id="rId13"/>
+    <hyperlink ref="O31" r:id="rId14"/>
+    <hyperlink ref="O36" r:id="rId15"/>
+    <hyperlink ref="O37" r:id="rId16"/>
+    <hyperlink ref="O38" r:id="rId17"/>
+    <hyperlink ref="O10" r:id="rId18"/>
+    <hyperlink ref="O14" r:id="rId19"/>
+    <hyperlink ref="O23" r:id="rId20"/>
+    <hyperlink ref="O25" r:id="rId21"/>
+    <hyperlink ref="O29" r:id="rId22"/>
+    <hyperlink ref="O32" r:id="rId23"/>
+    <hyperlink ref="O33" r:id="rId24"/>
+    <hyperlink ref="O34" r:id="rId25"/>
+    <hyperlink ref="O35" r:id="rId26"/>
+    <hyperlink ref="O17" r:id="rId27"/>
+    <hyperlink ref="O28" r:id="rId28"/>
+    <hyperlink ref="O39" r:id="rId29"/>
+    <hyperlink ref="O40" r:id="rId30"/>
+    <hyperlink ref="O24" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>
-  <drawing r:id="rId32"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId32"/>
+  <drawing r:id="rId33"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S41"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -4097,15 +4241,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="92"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92"/>
+      <c r="P1" s="92"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="92"/>
+      <c r="S1" s="93"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -4155,7 +4299,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="93"/>
+      <c r="S3" s="94"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -4180,7 +4324,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="94"/>
+      <c r="S4" s="95"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -4205,7 +4349,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="94"/>
+      <c r="S5" s="95"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -4226,7 +4370,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="94"/>
+      <c r="S6" s="95"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -4247,7 +4391,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="94"/>
+      <c r="S7" s="95"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -4268,7 +4412,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="94"/>
+      <c r="S8" s="95"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -4442,7 +4586,7 @@
     <row r="12" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="56"/>
       <c r="B12" s="46">
-        <f t="shared" ref="B12:B39" si="0">ROW(B12) - ROW($B$9)</f>
+        <f t="shared" ref="B12:B40" si="0">ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
       <c r="C12" s="67" t="s">
@@ -4729,13 +4873,13 @@
       <c r="D17" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="95" t="s">
+      <c r="E17" s="85" t="s">
         <v>209</v>
       </c>
       <c r="F17" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="G17" s="95" t="s">
+      <c r="G17" s="85" t="s">
         <v>210</v>
       </c>
       <c r="H17" s="37" t="s">
@@ -5109,172 +5253,172 @@
       <c r="R23" s="37"/>
       <c r="S23" s="55"/>
     </row>
-    <row r="24" spans="1:19" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="61"/>
-      <c r="B24" s="73">
-        <f t="shared" si="0"/>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="56"/>
+      <c r="B24" s="46">
+        <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="74" t="s">
+      <c r="C24" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="75" t="s">
-        <v>208</v>
-      </c>
-      <c r="E24" s="75" t="s">
-        <v>172</v>
-      </c>
-      <c r="F24" s="75" t="s">
-        <v>64</v>
-      </c>
-      <c r="G24" s="75" t="s">
-        <v>173</v>
-      </c>
-      <c r="H24" s="75" t="s">
-        <v>174</v>
-      </c>
-      <c r="I24" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="J24" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="K24" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="L24" s="75">
+      <c r="D24" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="E24" s="96" t="s">
+        <v>220</v>
+      </c>
+      <c r="F24" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="G24" s="96" t="s">
+        <v>222</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="I24" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="K24" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L24" s="37">
         <v>1</v>
       </c>
       <c r="M24" s="37">
         <f>L24*5</f>
         <v>5</v>
       </c>
-      <c r="N24" s="62">
-        <v>10</v>
-      </c>
-      <c r="O24" s="66" t="s">
-        <v>136</v>
-      </c>
-      <c r="P24" s="63">
-        <v>3.1E-2</v>
-      </c>
-      <c r="Q24" s="63">
+      <c r="N24" s="37">
+        <v>20</v>
+      </c>
+      <c r="O24" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P24" s="38">
+        <v>3.4099999999999998E-2</v>
+      </c>
+      <c r="Q24" s="38">
         <f>P24*N24</f>
-        <v>0.31</v>
-      </c>
-      <c r="R24" s="62"/>
-      <c r="S24" s="64"/>
-    </row>
-    <row r="25" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="56"/>
-      <c r="B25" s="46">
-        <f>ROW(B25) - ROW($B$9)</f>
+        <v>0.68199999999999994</v>
+      </c>
+      <c r="R24" s="37"/>
+      <c r="S24" s="55"/>
+    </row>
+    <row r="25" spans="1:19" s="65" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="61"/>
+      <c r="B25" s="73">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="E25" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="G25" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="H25" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="I25" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J25" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="K25" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="L25" s="37">
-        <v>5</v>
+      <c r="C25" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="75" t="s">
+        <v>208</v>
+      </c>
+      <c r="E25" s="75" t="s">
+        <v>172</v>
+      </c>
+      <c r="F25" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" s="75" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25" s="75" t="s">
+        <v>174</v>
+      </c>
+      <c r="I25" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="K25" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="L25" s="75">
+        <v>1</v>
       </c>
       <c r="M25" s="37">
         <f>L25*5</f>
-        <v>25</v>
-      </c>
-      <c r="N25" s="37">
-        <v>100</v>
-      </c>
-      <c r="O25" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P25" s="38">
-        <v>1E-3</v>
-      </c>
-      <c r="Q25" s="38">
+        <v>5</v>
+      </c>
+      <c r="N25" s="62">
+        <v>10</v>
+      </c>
+      <c r="O25" s="66" t="s">
+        <v>136</v>
+      </c>
+      <c r="P25" s="63">
+        <v>3.1E-2</v>
+      </c>
+      <c r="Q25" s="63">
         <f>P25*N25</f>
-        <v>0.1</v>
-      </c>
-      <c r="R25" s="37"/>
-      <c r="S25" s="55"/>
+        <v>0.31</v>
+      </c>
+      <c r="R25" s="62"/>
+      <c r="S25" s="64"/>
     </row>
     <row r="26" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="56"/>
       <c r="B26" s="46">
-        <f t="shared" si="0"/>
+        <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
       <c r="C26" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="F26" s="49" t="s">
+      <c r="D26" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="G26" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="H26" s="49" t="s">
+      <c r="G26" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="I26" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J26" s="49" t="s">
-        <v>110</v>
-      </c>
-      <c r="K26" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="L26" s="49">
-        <v>1</v>
-      </c>
-      <c r="M26" s="49">
-        <f t="shared" ref="M26:M27" si="9">L26*5</f>
-        <v>5</v>
-      </c>
-      <c r="N26" s="49">
+      <c r="I26" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J26" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="K26" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="L26" s="37">
+        <v>7</v>
+      </c>
+      <c r="M26" s="37">
+        <f>L26*5</f>
+        <v>35</v>
+      </c>
+      <c r="N26" s="37">
         <v>100</v>
       </c>
-      <c r="O26" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P26" s="50">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q26" s="50">
-        <f t="shared" ref="Q26:Q27" si="10">P26*N26</f>
-        <v>0.12</v>
-      </c>
-      <c r="R26" s="49"/>
+      <c r="O26" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P26" s="38">
+        <v>1E-3</v>
+      </c>
+      <c r="Q26" s="38">
+        <f>P26*N26</f>
+        <v>0.1</v>
+      </c>
+      <c r="R26" s="37"/>
       <c r="S26" s="55"/>
     </row>
     <row r="27" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
@@ -5283,132 +5427,132 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="67" t="s">
+      <c r="C27" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="49" t="s">
-        <v>213</v>
-      </c>
-      <c r="E27" s="95" t="s">
-        <v>214</v>
+      <c r="D27" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="49" t="s">
+        <v>49</v>
       </c>
       <c r="F27" s="49" t="s">
-        <v>215</v>
-      </c>
-      <c r="G27" s="95" t="s">
-        <v>216</v>
+        <v>65</v>
+      </c>
+      <c r="G27" s="49" t="s">
+        <v>79</v>
       </c>
       <c r="H27" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="I27" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J27" s="37" t="s">
+      <c r="I27" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J27" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="K27" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="L27" s="49">
+        <v>1</v>
+      </c>
+      <c r="M27" s="49">
+        <f t="shared" ref="M27:M28" si="9">L27*5</f>
+        <v>5</v>
+      </c>
+      <c r="N27" s="49">
+        <v>100</v>
+      </c>
+      <c r="O27" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P27" s="50">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q27" s="50">
+        <f t="shared" ref="Q27:Q28" si="10">P27*N27</f>
+        <v>0.12</v>
+      </c>
+      <c r="R27" s="49"/>
+      <c r="S27" s="55"/>
+    </row>
+    <row r="28" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="56"/>
+      <c r="B28" s="46">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C28" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="49" t="s">
+        <v>213</v>
+      </c>
+      <c r="E28" s="85" t="s">
+        <v>214</v>
+      </c>
+      <c r="F28" s="49" t="s">
+        <v>215</v>
+      </c>
+      <c r="G28" s="85" t="s">
+        <v>216</v>
+      </c>
+      <c r="H28" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J28" s="37" t="s">
         <v>217</v>
       </c>
-      <c r="K27" s="37" t="s">
+      <c r="K28" s="37" t="s">
         <v>218</v>
       </c>
-      <c r="L27" s="37">
-        <v>1</v>
-      </c>
-      <c r="M27" s="49">
+      <c r="L28" s="37">
+        <v>1</v>
+      </c>
+      <c r="M28" s="49">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="N27" s="37">
+      <c r="N28" s="37">
         <v>100</v>
       </c>
-      <c r="O27" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P27" s="38">
+      <c r="O28" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P28" s="38">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="Q27" s="50">
+      <c r="Q28" s="50">
         <f t="shared" si="10"/>
         <v>0.06</v>
       </c>
-      <c r="R27" s="37"/>
-      <c r="S27" s="55"/>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="46">
-        <f>ROW(B28) - ROW($B$9)</f>
-        <v>19</v>
-      </c>
-      <c r="C28" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="E28" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="H28" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="I28" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J28" s="37" t="s">
-        <v>180</v>
-      </c>
-      <c r="K28" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="L28" s="37">
-        <v>2</v>
-      </c>
-      <c r="M28" s="37">
-        <f>L28*5</f>
-        <v>10</v>
-      </c>
-      <c r="N28" s="37">
-        <v>100</v>
-      </c>
-      <c r="O28" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P28" s="38">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="Q28" s="38">
-        <f>P28*N28</f>
-        <v>0.11</v>
-      </c>
       <c r="R28" s="37"/>
       <c r="S28" s="55"/>
     </row>
-    <row r="29" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="56"/>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
       <c r="B29" s="46">
-        <f t="shared" si="0"/>
+        <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="68" t="s">
+      <c r="C29" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="70" t="s">
-        <v>177</v>
+      <c r="D29" s="37" t="s">
+        <v>212</v>
       </c>
       <c r="E29" s="37" t="s">
-        <v>50</v>
+        <v>178</v>
       </c>
       <c r="F29" s="37" t="s">
         <v>65</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="H29" s="37" t="s">
         <v>86</v>
@@ -5417,17 +5561,17 @@
         <v>134</v>
       </c>
       <c r="J29" s="37" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
       <c r="K29" s="37" t="s">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="L29" s="37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M29" s="37">
         <f>L29*5</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N29" s="37">
         <v>100</v>
@@ -5436,11 +5580,11 @@
         <v>136</v>
       </c>
       <c r="P29" s="38">
-        <v>1E-3</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q29" s="38">
         <f>P29*N29</f>
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="R29" s="37"/>
       <c r="S29" s="55"/>
@@ -5448,23 +5592,23 @@
     <row r="30" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="56"/>
       <c r="B30" s="46">
-        <f>ROW(B30) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C30" s="68" t="s">
         <v>18</v>
       </c>
       <c r="D30" s="70" t="s">
-        <v>32</v>
+        <v>177</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F30" s="37" t="s">
         <v>65</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H30" s="37" t="s">
         <v>86</v>
@@ -5473,10 +5617,10 @@
         <v>134</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -5492,294 +5636,294 @@
         <v>136</v>
       </c>
       <c r="P30" s="38">
-        <v>1.2999999999999999E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="Q30" s="38">
         <f>P30*N30</f>
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="R30" s="37"/>
       <c r="S30" s="55"/>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="72">
-        <f t="shared" ref="B31" si="11">ROW(B31) - ROW($B$9)</f>
+    <row r="31" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="56"/>
+      <c r="B31" s="46">
+        <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
       <c r="C31" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="49" t="s">
+      <c r="D31" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="H31" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="I31" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J31" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="K31" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="L31" s="37">
+        <v>1</v>
+      </c>
+      <c r="M31" s="37">
+        <f>L31*5</f>
+        <v>5</v>
+      </c>
+      <c r="N31" s="37">
+        <v>100</v>
+      </c>
+      <c r="O31" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P31" s="38">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q31" s="38">
+        <f>P31*N31</f>
+        <v>0.13</v>
+      </c>
+      <c r="R31" s="37"/>
+      <c r="S31" s="55"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="72">
+        <f t="shared" ref="B32" si="11">ROW(B32) - ROW($B$9)</f>
+        <v>23</v>
+      </c>
+      <c r="C32" s="97" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="98" t="s">
         <v>182</v>
       </c>
-      <c r="E31" s="49" t="s">
+      <c r="E32" s="98" t="s">
         <v>51</v>
       </c>
-      <c r="F31" s="49" t="s">
+      <c r="F32" s="98" t="s">
         <v>65</v>
       </c>
-      <c r="G31" s="49" t="s">
+      <c r="G32" s="98" t="s">
         <v>81</v>
       </c>
-      <c r="H31" s="49" t="s">
+      <c r="H32" s="98" t="s">
         <v>86</v>
       </c>
-      <c r="I31" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J31" s="49" t="s">
+      <c r="I32" s="98" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="98" t="s">
         <v>112</v>
       </c>
-      <c r="K31" s="49" t="s">
+      <c r="K32" s="98" t="s">
         <v>183</v>
       </c>
-      <c r="L31" s="49">
-        <v>1</v>
-      </c>
-      <c r="M31" s="49">
-        <f t="shared" ref="M31" si="12">L31*5</f>
+      <c r="L32" s="98">
+        <v>1</v>
+      </c>
+      <c r="M32" s="98">
+        <f t="shared" ref="M32" si="12">L32*5</f>
         <v>5</v>
       </c>
-      <c r="N31" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="O31" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P31" s="38" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q31" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="R31" s="76" t="s">
+      <c r="N32" s="99" t="s">
+        <v>134</v>
+      </c>
+      <c r="O32" s="100" t="s">
+        <v>136</v>
+      </c>
+      <c r="P32" s="101" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q32" s="103" t="s">
+        <v>134</v>
+      </c>
+      <c r="R32" s="102" t="s">
         <v>183</v>
       </c>
-      <c r="S31" s="55"/>
-    </row>
-    <row r="32" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="46">
-        <f>ROW(B32) - ROW($B$9)</f>
-        <v>23</v>
-      </c>
-      <c r="C32" s="68" t="s">
-        <v>187</v>
-      </c>
-      <c r="D32" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="E32" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G32" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="K32" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L32" s="37">
-        <v>1</v>
-      </c>
-      <c r="M32" s="37">
-        <f>L32*5</f>
-        <v>5</v>
-      </c>
-      <c r="N32" s="37">
-        <v>10</v>
-      </c>
-      <c r="O32" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P32" s="38">
-        <v>0.1336</v>
-      </c>
-      <c r="Q32" s="38">
-        <f>P32*N32</f>
-        <v>1.3359999999999999</v>
-      </c>
-      <c r="R32" s="37"/>
-      <c r="S32" s="55"/>
-    </row>
-    <row r="33" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="S32" s="104"/>
+    </row>
+    <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="72">
-        <f t="shared" ref="B33" si="13">ROW(B33) - ROW($B$9)</f>
+      <c r="B33" s="46">
+        <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
       <c r="C33" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="D33" s="49" t="s">
-        <v>188</v>
-      </c>
-      <c r="E33" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="F33" s="49" t="s">
+      <c r="D33" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="F33" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="G33" s="49" t="s">
-        <v>190</v>
-      </c>
-      <c r="H33" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="I33" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J33" s="49" t="s">
-        <v>192</v>
-      </c>
-      <c r="K33" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="L33" s="49">
-        <v>2</v>
-      </c>
-      <c r="M33" s="49">
-        <f t="shared" ref="M33" si="14">L33*5</f>
+      <c r="G33" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="H33" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J33" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="K33" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L33" s="37">
+        <v>1</v>
+      </c>
+      <c r="M33" s="37">
+        <f>L33*5</f>
+        <v>5</v>
+      </c>
+      <c r="N33" s="37">
         <v>10</v>
       </c>
-      <c r="N33" s="49">
-        <v>20</v>
-      </c>
-      <c r="O33" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P33" s="50">
-        <v>4.8300000000000003E-2</v>
-      </c>
-      <c r="Q33" s="50">
-        <f t="shared" ref="Q33" si="15">P33*N33</f>
-        <v>0.96600000000000008</v>
-      </c>
-      <c r="R33" s="49"/>
+      <c r="O33" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P33" s="38">
+        <v>0.1336</v>
+      </c>
+      <c r="Q33" s="38">
+        <f>P33*N33</f>
+        <v>1.3359999999999999</v>
+      </c>
+      <c r="R33" s="37"/>
       <c r="S33" s="55"/>
     </row>
     <row r="34" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="46">
-        <f>ROW(B34) - ROW($B$9)</f>
+      <c r="B34" s="72">
+        <f t="shared" ref="B34" si="13">ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="67" t="s">
+      <c r="C34" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="D34" s="37" t="s">
+      <c r="D34" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="E34" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="F34" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="G34" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="H34" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="I34" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="K34" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L34" s="49">
+        <v>2</v>
+      </c>
+      <c r="M34" s="49">
+        <f t="shared" ref="M34" si="14">L34*5</f>
+        <v>10</v>
+      </c>
+      <c r="N34" s="49">
+        <v>20</v>
+      </c>
+      <c r="O34" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P34" s="50">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="Q34" s="50">
+        <f t="shared" ref="Q34" si="15">P34*N34</f>
+        <v>0.96600000000000008</v>
+      </c>
+      <c r="R34" s="49"/>
+      <c r="S34" s="55"/>
+    </row>
+    <row r="35" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="46">
+        <f>ROW(B35) - ROW($B$9)</f>
+        <v>26</v>
+      </c>
+      <c r="C35" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="D35" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="E34" s="37" t="s">
+      <c r="E35" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="F34" s="37" t="s">
+      <c r="F35" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="G34" s="37" t="s">
+      <c r="G35" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="H34" s="37" t="s">
+      <c r="H35" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="I34" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J34" s="37" t="s">
+      <c r="I35" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="K34" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L34" s="37">
-        <v>1</v>
-      </c>
-      <c r="M34" s="37">
-        <f>L34*5</f>
+      <c r="K35" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L35" s="37">
+        <v>1</v>
+      </c>
+      <c r="M35" s="37">
+        <f>L35*5</f>
         <v>5</v>
       </c>
-      <c r="N34" s="37">
+      <c r="N35" s="37">
         <v>10</v>
       </c>
-      <c r="O34" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P34" s="38">
+      <c r="O35" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P35" s="38">
         <v>6.4600000000000005E-2</v>
       </c>
-      <c r="Q34" s="38">
-        <f>P34*N34</f>
+      <c r="Q35" s="38">
+        <f>P35*N35</f>
         <v>0.64600000000000002</v>
       </c>
-      <c r="R34" s="37"/>
-      <c r="S34" s="55"/>
-    </row>
-    <row r="35" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="56"/>
-      <c r="B35" s="46">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="C35" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="E35" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="G35" s="49" t="s">
-        <v>83</v>
-      </c>
-      <c r="H35" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="I35" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J35" s="49" t="s">
-        <v>114</v>
-      </c>
-      <c r="K35" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L35" s="49">
-        <v>1</v>
-      </c>
-      <c r="M35" s="49">
-        <f t="shared" ref="M35" si="16">L35*5</f>
-        <v>5</v>
-      </c>
-      <c r="N35" s="49">
-        <v>10</v>
-      </c>
-      <c r="O35" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P35" s="50">
-        <v>0.2079</v>
-      </c>
-      <c r="Q35" s="50">
-        <f t="shared" ref="Q35" si="17">P35*N35</f>
-        <v>2.0790000000000002</v>
-      </c>
-      <c r="R35" s="49"/>
+      <c r="R35" s="37"/>
       <c r="S35" s="55"/>
     </row>
     <row r="36" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
@@ -5789,28 +5933,28 @@
         <v>27</v>
       </c>
       <c r="C36" s="68" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E36" s="49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F36" s="49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G36" s="49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H36" s="49" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I36" s="49" t="s">
         <v>134</v>
       </c>
       <c r="J36" s="49" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K36" s="37" t="s">
         <v>134</v>
@@ -5819,112 +5963,114 @@
         <v>1</v>
       </c>
       <c r="M36" s="49">
-        <f t="shared" ref="M36" si="18">L36*5</f>
+        <f t="shared" ref="M36" si="16">L36*5</f>
         <v>5</v>
       </c>
       <c r="N36" s="49">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O36" s="60" t="s">
         <v>136</v>
       </c>
       <c r="P36" s="50">
-        <v>0.54569999999999996</v>
+        <v>0.2079</v>
       </c>
       <c r="Q36" s="50">
-        <f t="shared" ref="Q36" si="19">P36*N36</f>
-        <v>3.2741999999999996</v>
+        <f t="shared" ref="Q36" si="17">P36*N36</f>
+        <v>2.0790000000000002</v>
       </c>
       <c r="R36" s="49"/>
       <c r="S36" s="55"/>
     </row>
-    <row r="37" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="56"/>
       <c r="B37" s="46">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="E37" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="F37" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G37" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="H37" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="I37" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J37" s="37" t="s">
-        <v>116</v>
+      <c r="C37" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="G37" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="H37" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="I37" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J37" s="49" t="s">
+        <v>115</v>
       </c>
       <c r="K37" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L37" s="37">
-        <v>1</v>
-      </c>
-      <c r="M37" s="37">
-        <f>L37*5</f>
+      <c r="L37" s="49">
+        <v>1</v>
+      </c>
+      <c r="M37" s="49">
+        <f t="shared" ref="M37" si="18">L37*5</f>
         <v>5</v>
       </c>
-      <c r="N37" s="37">
+      <c r="N37" s="49">
         <v>6</v>
       </c>
-      <c r="O37" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P37" s="38">
-        <v>2.8589000000000002</v>
-      </c>
-      <c r="Q37" s="38">
-        <f>P37*N37</f>
-        <v>17.153400000000001</v>
-      </c>
-      <c r="R37" s="37"/>
-      <c r="S37" s="39"/>
-    </row>
-    <row r="38" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O37" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P37" s="50">
+        <v>0.54569999999999996</v>
+      </c>
+      <c r="Q37" s="50">
+        <f t="shared" ref="Q37" si="19">P37*N37</f>
+        <v>3.2741999999999996</v>
+      </c>
+      <c r="R37" s="49"/>
+      <c r="S37" s="55"/>
+    </row>
+    <row r="38" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="56"/>
       <c r="B38" s="46">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C38" s="67" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>143</v>
+        <v>36</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="I38" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="K38" s="37"/>
+        <v>116</v>
+      </c>
+      <c r="K38" s="37" t="s">
+        <v>134</v>
+      </c>
       <c r="L38" s="37">
         <v>1</v>
       </c>
@@ -5933,35 +6079,35 @@
         <v>5</v>
       </c>
       <c r="N38" s="37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O38" s="59" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="P38" s="38">
-        <v>3.28</v>
+        <v>2.8589000000000002</v>
       </c>
       <c r="Q38" s="38">
         <f>P38*N38</f>
-        <v>16.399999999999999</v>
+        <v>17.153400000000001</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="39"/>
     </row>
-    <row r="39" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="56"/>
       <c r="B39" s="46">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C39" s="67" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D39" s="37" t="s">
         <v>143</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>148</v>
+        <v>225</v>
       </c>
       <c r="F39" s="37" t="s">
         <v>134</v>
@@ -5987,80 +6133,134 @@
         <v>5</v>
       </c>
       <c r="N39" s="37">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O39" s="59" t="s">
         <v>147</v>
       </c>
       <c r="P39" s="38">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="Q39" s="71">
+        <v>4.67</v>
+      </c>
+      <c r="Q39" s="38">
         <f>P39*N39</f>
-        <v>2.4700000000000002</v>
+        <v>23.35</v>
       </c>
       <c r="R39" s="37"/>
       <c r="S39" s="39"/>
     </row>
-    <row r="40" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1"/>
-      <c r="B40" s="40"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="44"/>
-      <c r="G40" s="45"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="44"/>
-      <c r="K40" s="45"/>
-      <c r="L40" s="45"/>
-      <c r="M40" s="45"/>
-      <c r="N40" s="85" t="s">
+    <row r="40" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="56"/>
+      <c r="B40" s="46">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="G40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="I40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="K40" s="37"/>
+      <c r="L40" s="37">
+        <v>1</v>
+      </c>
+      <c r="M40" s="37">
+        <f>L40*5</f>
         <v>5</v>
       </c>
-      <c r="O40" s="86"/>
-      <c r="P40" s="86"/>
-      <c r="Q40" s="47">
-        <f>SUM(Q11:Q39)</f>
-        <v>58.313400000000001</v>
-      </c>
-      <c r="R40" s="87"/>
-      <c r="S40" s="88"/>
+      <c r="N40" s="37">
+        <v>1</v>
+      </c>
+      <c r="O40" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="P40" s="38">
+        <v>0.35</v>
+      </c>
+      <c r="Q40" s="71">
+        <f>P40*N40</f>
+        <v>0.35</v>
+      </c>
+      <c r="R40" s="37"/>
+      <c r="S40" s="39"/>
     </row>
     <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
-      <c r="N41" s="85" t="s">
+      <c r="B41" s="40"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="44"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="45"/>
+      <c r="J41" s="44"/>
+      <c r="K41" s="45"/>
+      <c r="L41" s="45"/>
+      <c r="M41" s="45"/>
+      <c r="N41" s="86" t="s">
+        <v>5</v>
+      </c>
+      <c r="O41" s="87"/>
+      <c r="P41" s="87"/>
+      <c r="Q41" s="47">
+        <f>SUM(Q11:Q40)</f>
+        <v>63.825400000000002</v>
+      </c>
+      <c r="R41" s="88"/>
+      <c r="S41" s="89"/>
+    </row>
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="O41" s="86"/>
-      <c r="P41" s="86"/>
-      <c r="Q41" s="48">
-        <f>Q40/5</f>
-        <v>11.66268</v>
-      </c>
-      <c r="R41" s="89"/>
-      <c r="S41" s="90"/>
+      <c r="O42" s="87"/>
+      <c r="P42" s="87"/>
+      <c r="Q42" s="48">
+        <f>Q41/5</f>
+        <v>12.765080000000001</v>
+      </c>
+      <c r="R42" s="90"/>
+      <c r="S42" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S41"/>
     <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S42"/>
+    <mergeCell ref="N42:P42"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O11" r:id="rId1"/>
@@ -6073,36 +6273,37 @@
     <hyperlink ref="O20" r:id="rId8"/>
     <hyperlink ref="O21" r:id="rId9"/>
     <hyperlink ref="O22" r:id="rId10"/>
-    <hyperlink ref="O26" r:id="rId11"/>
-    <hyperlink ref="O29" r:id="rId12"/>
-    <hyperlink ref="O25" r:id="rId13"/>
-    <hyperlink ref="O30" r:id="rId14"/>
-    <hyperlink ref="O35" r:id="rId15"/>
-    <hyperlink ref="O36" r:id="rId16"/>
-    <hyperlink ref="O37" r:id="rId17"/>
-    <hyperlink ref="O38" r:id="rId18"/>
-    <hyperlink ref="O39" r:id="rId19"/>
-    <hyperlink ref="O10" r:id="rId20"/>
-    <hyperlink ref="O14" r:id="rId21"/>
-    <hyperlink ref="O23" r:id="rId22"/>
-    <hyperlink ref="O24" r:id="rId23"/>
-    <hyperlink ref="O28" r:id="rId24"/>
-    <hyperlink ref="O31" r:id="rId25"/>
-    <hyperlink ref="O32" r:id="rId26"/>
-    <hyperlink ref="O33" r:id="rId27"/>
-    <hyperlink ref="O34" r:id="rId28"/>
-    <hyperlink ref="O17" r:id="rId29"/>
-    <hyperlink ref="O27" r:id="rId30"/>
+    <hyperlink ref="O27" r:id="rId11"/>
+    <hyperlink ref="O30" r:id="rId12"/>
+    <hyperlink ref="O26" r:id="rId13"/>
+    <hyperlink ref="O31" r:id="rId14"/>
+    <hyperlink ref="O36" r:id="rId15"/>
+    <hyperlink ref="O37" r:id="rId16"/>
+    <hyperlink ref="O38" r:id="rId17"/>
+    <hyperlink ref="O10" r:id="rId18"/>
+    <hyperlink ref="O14" r:id="rId19"/>
+    <hyperlink ref="O23" r:id="rId20"/>
+    <hyperlink ref="O25" r:id="rId21"/>
+    <hyperlink ref="O29" r:id="rId22"/>
+    <hyperlink ref="O32" r:id="rId23"/>
+    <hyperlink ref="O33" r:id="rId24"/>
+    <hyperlink ref="O34" r:id="rId25"/>
+    <hyperlink ref="O35" r:id="rId26"/>
+    <hyperlink ref="O17" r:id="rId27"/>
+    <hyperlink ref="O28" r:id="rId28"/>
+    <hyperlink ref="O24" r:id="rId29"/>
+    <hyperlink ref="O39" r:id="rId30"/>
+    <hyperlink ref="O40" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId31"/>
-  <drawing r:id="rId32"/>
+  <pageSetup orientation="portrait" r:id="rId32"/>
+  <drawing r:id="rId33"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S41"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -6135,15 +6336,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="92"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92"/>
+      <c r="P1" s="92"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="92"/>
+      <c r="S1" s="93"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -6193,7 +6394,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="93"/>
+      <c r="S3" s="94"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -6218,7 +6419,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="94"/>
+      <c r="S4" s="95"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -6243,7 +6444,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="94"/>
+      <c r="S5" s="95"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -6264,7 +6465,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="94"/>
+      <c r="S6" s="95"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -6285,7 +6486,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="94"/>
+      <c r="S7" s="95"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -6306,7 +6507,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="94"/>
+      <c r="S8" s="95"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -6480,7 +6681,7 @@
     <row r="12" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="56"/>
       <c r="B12" s="46">
-        <f t="shared" ref="B12:B39" si="0">ROW(B12) - ROW($B$9)</f>
+        <f t="shared" ref="B12:B40" si="0">ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
       <c r="C12" s="67" t="s">
@@ -6514,7 +6715,7 @@
         <v>2</v>
       </c>
       <c r="M12" s="37">
-        <f t="shared" ref="M12:M39" si="1">L12*50</f>
+        <f t="shared" ref="M12:M40" si="1">L12*50</f>
         <v>100</v>
       </c>
       <c r="N12" s="37">
@@ -6767,13 +6968,13 @@
       <c r="D17" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="95" t="s">
+      <c r="E17" s="85" t="s">
         <v>209</v>
       </c>
       <c r="F17" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="G17" s="95" t="s">
+      <c r="G17" s="85" t="s">
         <v>210</v>
       </c>
       <c r="H17" s="37" t="s">
@@ -7147,40 +7348,40 @@
       <c r="R23" s="37"/>
       <c r="S23" s="55"/>
     </row>
-    <row r="24" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="56"/>
       <c r="B24" s="46">
-        <f t="shared" si="0"/>
+        <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="68" t="s">
+      <c r="C24" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="49" t="s">
-        <v>208</v>
-      </c>
-      <c r="E24" s="49" t="s">
-        <v>172</v>
-      </c>
-      <c r="F24" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="G24" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="H24" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="I24" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J24" s="49" t="s">
-        <v>175</v>
-      </c>
-      <c r="K24" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="L24" s="49">
+      <c r="D24" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="E24" s="96" t="s">
+        <v>220</v>
+      </c>
+      <c r="F24" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="G24" s="96" t="s">
+        <v>222</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="I24" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="K24" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L24" s="37">
         <v>1</v>
       </c>
       <c r="M24" s="37">
@@ -7194,11 +7395,11 @@
         <v>136</v>
       </c>
       <c r="P24" s="38">
-        <v>3.2599999999999997E-2</v>
+        <v>3.4099999999999998E-2</v>
       </c>
       <c r="Q24" s="38">
         <f>P24*N24</f>
-        <v>1.9559999999999997</v>
+        <v>2.0459999999999998</v>
       </c>
       <c r="R24" s="37"/>
       <c r="S24" s="55"/>
@@ -7206,55 +7407,55 @@
     <row r="25" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="56"/>
       <c r="B25" s="46">
-        <f>ROW(B25) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C25" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="E25" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="G25" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="H25" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="I25" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J25" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="K25" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="L25" s="37">
-        <v>5</v>
+        <v>17</v>
+      </c>
+      <c r="D25" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="E25" s="49" t="s">
+        <v>172</v>
+      </c>
+      <c r="F25" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="I25" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="49" t="s">
+        <v>175</v>
+      </c>
+      <c r="K25" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L25" s="49">
+        <v>1</v>
       </c>
       <c r="M25" s="37">
         <f t="shared" si="1"/>
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="N25" s="37">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="O25" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P25" s="38">
-        <v>1E-3</v>
+        <v>3.2599999999999997E-2</v>
       </c>
       <c r="Q25" s="38">
         <f>P25*N25</f>
-        <v>0.3</v>
+        <v>1.9559999999999997</v>
       </c>
       <c r="R25" s="37"/>
       <c r="S25" s="55"/>
@@ -7262,57 +7463,57 @@
     <row r="26" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="56"/>
       <c r="B26" s="46">
-        <f t="shared" si="0"/>
+        <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
       <c r="C26" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="F26" s="49" t="s">
+      <c r="D26" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="G26" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="H26" s="49" t="s">
+      <c r="G26" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="I26" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J26" s="49" t="s">
-        <v>110</v>
-      </c>
-      <c r="K26" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="L26" s="49">
-        <v>1</v>
+      <c r="I26" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J26" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="K26" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="L26" s="37">
+        <v>7</v>
       </c>
       <c r="M26" s="37">
         <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="N26" s="49">
-        <v>100</v>
-      </c>
-      <c r="O26" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P26" s="50">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q26" s="50">
-        <f t="shared" ref="Q26" si="6">P26*N26</f>
-        <v>0.12</v>
-      </c>
-      <c r="R26" s="49"/>
+        <v>350</v>
+      </c>
+      <c r="N26" s="37">
+        <v>400</v>
+      </c>
+      <c r="O26" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P26" s="38">
+        <v>1E-3</v>
+      </c>
+      <c r="Q26" s="38">
+        <f>P26*N26</f>
+        <v>0.4</v>
+      </c>
+      <c r="R26" s="37"/>
       <c r="S26" s="55"/>
     </row>
     <row r="27" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
@@ -7321,129 +7522,129 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="67" t="s">
+      <c r="C27" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="49" t="s">
-        <v>213</v>
-      </c>
-      <c r="E27" s="95" t="s">
-        <v>214</v>
+      <c r="D27" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="49" t="s">
+        <v>49</v>
       </c>
       <c r="F27" s="49" t="s">
-        <v>215</v>
-      </c>
-      <c r="G27" s="95" t="s">
-        <v>216</v>
+        <v>65</v>
+      </c>
+      <c r="G27" s="49" t="s">
+        <v>79</v>
       </c>
       <c r="H27" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="I27" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J27" s="37" t="s">
-        <v>217</v>
-      </c>
-      <c r="K27" s="37" t="s">
-        <v>218</v>
-      </c>
-      <c r="L27" s="37">
-        <v>1</v>
-      </c>
-      <c r="M27" s="49">
-        <f t="shared" ref="M27" si="7">L27*5</f>
-        <v>5</v>
-      </c>
-      <c r="N27" s="37">
+      <c r="I27" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J27" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="K27" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="L27" s="49">
+        <v>1</v>
+      </c>
+      <c r="M27" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N27" s="49">
         <v>100</v>
       </c>
-      <c r="O27" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P27" s="38">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="Q27" s="38"/>
-      <c r="R27" s="37"/>
+      <c r="O27" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P27" s="50">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q27" s="50">
+        <f t="shared" ref="Q27" si="6">P27*N27</f>
+        <v>0.12</v>
+      </c>
+      <c r="R27" s="49"/>
       <c r="S27" s="55"/>
     </row>
     <row r="28" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="56"/>
       <c r="B28" s="46">
-        <f>ROW(B28) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C28" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="E28" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="H28" s="37" t="s">
+      <c r="D28" s="49" t="s">
+        <v>213</v>
+      </c>
+      <c r="E28" s="85" t="s">
+        <v>214</v>
+      </c>
+      <c r="F28" s="49" t="s">
+        <v>215</v>
+      </c>
+      <c r="G28" s="85" t="s">
+        <v>216</v>
+      </c>
+      <c r="H28" s="49" t="s">
         <v>86</v>
       </c>
       <c r="I28" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>180</v>
+        <v>217</v>
       </c>
       <c r="K28" s="37" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="L28" s="37">
-        <v>2</v>
-      </c>
-      <c r="M28" s="37">
-        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M28" s="49">
+        <f t="shared" ref="M28" si="7">L28*5</f>
+        <v>5</v>
+      </c>
+      <c r="N28" s="37">
         <v>100</v>
       </c>
-      <c r="N28" s="37">
-        <v>200</v>
-      </c>
       <c r="O28" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P28" s="38">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="Q28" s="38">
-        <f>P28*N28</f>
-        <v>0.22</v>
-      </c>
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="Q28" s="38"/>
       <c r="R28" s="37"/>
       <c r="S28" s="55"/>
     </row>
     <row r="29" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="56"/>
       <c r="B29" s="46">
-        <f t="shared" si="0"/>
+        <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="68" t="s">
+      <c r="C29" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="70" t="s">
-        <v>177</v>
+      <c r="D29" s="37" t="s">
+        <v>212</v>
       </c>
       <c r="E29" s="37" t="s">
-        <v>50</v>
+        <v>178</v>
       </c>
       <c r="F29" s="37" t="s">
         <v>65</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="H29" s="37" t="s">
         <v>86</v>
@@ -7452,30 +7653,30 @@
         <v>134</v>
       </c>
       <c r="J29" s="37" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
       <c r="K29" s="37" t="s">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="L29" s="37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M29" s="37">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N29" s="37">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O29" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P29" s="38">
-        <v>1E-3</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q29" s="38">
         <f>P29*N29</f>
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="R29" s="37"/>
       <c r="S29" s="55"/>
@@ -7483,23 +7684,23 @@
     <row r="30" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="56"/>
       <c r="B30" s="46">
-        <f>ROW(B30) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C30" s="68" t="s">
         <v>18</v>
       </c>
       <c r="D30" s="70" t="s">
-        <v>32</v>
+        <v>177</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F30" s="37" t="s">
         <v>65</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H30" s="37" t="s">
         <v>86</v>
@@ -7508,10 +7709,10 @@
         <v>134</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -7527,325 +7728,325 @@
         <v>136</v>
       </c>
       <c r="P30" s="38">
-        <v>1.2999999999999999E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="Q30" s="38">
         <f>P30*N30</f>
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="R30" s="37"/>
       <c r="S30" s="55"/>
     </row>
     <row r="31" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="56"/>
-      <c r="B31" s="72">
-        <f t="shared" ref="B31" si="8">ROW(B31) - ROW($B$9)</f>
+      <c r="B31" s="46">
+        <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
       <c r="C31" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="E31" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="F31" s="49" t="s">
+      <c r="D31" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="G31" s="49" t="s">
-        <v>81</v>
-      </c>
-      <c r="H31" s="49" t="s">
+      <c r="G31" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="H31" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="I31" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J31" s="49" t="s">
-        <v>112</v>
-      </c>
-      <c r="K31" s="49" t="s">
-        <v>183</v>
-      </c>
-      <c r="L31" s="49">
+      <c r="I31" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J31" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="K31" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="L31" s="37">
         <v>1</v>
       </c>
       <c r="M31" s="37">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N31" s="37" t="s">
-        <v>134</v>
+      <c r="N31" s="37">
+        <v>100</v>
       </c>
       <c r="O31" s="59" t="s">
         <v>136</v>
       </c>
-      <c r="P31" s="38" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q31" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="R31" s="76" t="s">
+      <c r="P31" s="38">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q31" s="38">
+        <f>P31*N31</f>
+        <v>0.13</v>
+      </c>
+      <c r="R31" s="37"/>
+      <c r="S31" s="55"/>
+    </row>
+    <row r="32" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="56"/>
+      <c r="B32" s="72">
+        <f t="shared" ref="B32" si="8">ROW(B32) - ROW($B$9)</f>
+        <v>23</v>
+      </c>
+      <c r="C32" s="97" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="98" t="s">
+        <v>182</v>
+      </c>
+      <c r="E32" s="98" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" s="98" t="s">
+        <v>65</v>
+      </c>
+      <c r="G32" s="98" t="s">
+        <v>81</v>
+      </c>
+      <c r="H32" s="98" t="s">
+        <v>86</v>
+      </c>
+      <c r="I32" s="98" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="98" t="s">
+        <v>112</v>
+      </c>
+      <c r="K32" s="98" t="s">
         <v>183</v>
       </c>
-      <c r="S31" s="55"/>
-    </row>
-    <row r="32" spans="1:19" s="58" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="56"/>
-      <c r="B32" s="46">
-        <f>ROW(B32) - ROW($B$9)</f>
-        <v>23</v>
-      </c>
-      <c r="C32" s="68" t="s">
-        <v>187</v>
-      </c>
-      <c r="D32" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="E32" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G32" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="K32" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L32" s="37">
-        <v>1</v>
-      </c>
-      <c r="M32" s="37">
+      <c r="L32" s="98">
+        <v>1</v>
+      </c>
+      <c r="M32" s="99">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N32" s="37">
-        <v>55</v>
-      </c>
-      <c r="O32" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P32" s="38">
-        <v>0.1336</v>
-      </c>
-      <c r="Q32" s="38">
-        <f>P32*N32</f>
-        <v>7.3479999999999999</v>
-      </c>
-      <c r="R32" s="37"/>
-      <c r="S32" s="55"/>
-    </row>
-    <row r="33" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="N32" s="99" t="s">
+        <v>134</v>
+      </c>
+      <c r="O32" s="100" t="s">
+        <v>136</v>
+      </c>
+      <c r="P32" s="101" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q32" s="103" t="s">
+        <v>134</v>
+      </c>
+      <c r="R32" s="102" t="s">
+        <v>183</v>
+      </c>
+      <c r="S32" s="104"/>
+    </row>
+    <row r="33" spans="1:19" s="58" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A33" s="56"/>
-      <c r="B33" s="72">
-        <f t="shared" ref="B33" si="9">ROW(B33) - ROW($B$9)</f>
+      <c r="B33" s="46">
+        <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
       <c r="C33" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="D33" s="49" t="s">
-        <v>188</v>
-      </c>
-      <c r="E33" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="F33" s="49" t="s">
+      <c r="D33" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="F33" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="G33" s="49" t="s">
-        <v>190</v>
-      </c>
-      <c r="H33" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="I33" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J33" s="49" t="s">
-        <v>192</v>
-      </c>
-      <c r="K33" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="L33" s="49">
-        <v>2</v>
+      <c r="G33" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="H33" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J33" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="K33" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L33" s="37">
+        <v>1</v>
       </c>
       <c r="M33" s="37">
         <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="N33" s="49">
-        <v>110</v>
-      </c>
-      <c r="O33" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P33" s="50">
-        <v>4.1399999999999999E-2</v>
-      </c>
-      <c r="Q33" s="50">
-        <f t="shared" ref="Q33" si="10">P33*N33</f>
-        <v>4.5540000000000003</v>
-      </c>
-      <c r="R33" s="49"/>
+        <v>50</v>
+      </c>
+      <c r="N33" s="37">
+        <v>55</v>
+      </c>
+      <c r="O33" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P33" s="38">
+        <v>0.1336</v>
+      </c>
+      <c r="Q33" s="38">
+        <f>P33*N33</f>
+        <v>7.3479999999999999</v>
+      </c>
+      <c r="R33" s="37"/>
       <c r="S33" s="55"/>
     </row>
     <row r="34" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A34" s="56"/>
-      <c r="B34" s="46">
-        <f>ROW(B34) - ROW($B$9)</f>
+      <c r="B34" s="72">
+        <f t="shared" ref="B34" si="9">ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="67" t="s">
+      <c r="C34" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="D34" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="E34" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="F34" s="37" t="s">
+      <c r="D34" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="E34" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="F34" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="G34" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="I34" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J34" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="K34" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L34" s="37">
-        <v>1</v>
+      <c r="G34" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="H34" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="I34" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="K34" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L34" s="49">
+        <v>2</v>
       </c>
       <c r="M34" s="37">
         <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="N34" s="37">
-        <v>60</v>
-      </c>
-      <c r="O34" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P34" s="38">
-        <v>6.4600000000000005E-2</v>
-      </c>
-      <c r="Q34" s="38">
-        <f>P34*N34</f>
-        <v>3.8760000000000003</v>
-      </c>
-      <c r="R34" s="37"/>
+        <v>100</v>
+      </c>
+      <c r="N34" s="49">
+        <v>110</v>
+      </c>
+      <c r="O34" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P34" s="50">
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="Q34" s="50">
+        <f t="shared" ref="Q34" si="10">P34*N34</f>
+        <v>4.5540000000000003</v>
+      </c>
+      <c r="R34" s="49"/>
       <c r="S34" s="55"/>
     </row>
-    <row r="35" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A35" s="56"/>
       <c r="B35" s="46">
-        <f t="shared" si="0"/>
+        <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="E35" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="G35" s="49" t="s">
-        <v>83</v>
-      </c>
-      <c r="H35" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="I35" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J35" s="49" t="s">
-        <v>114</v>
+      <c r="C35" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="D35" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="E35" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="F35" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G35" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="H35" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I35" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="37" t="s">
+        <v>196</v>
       </c>
       <c r="K35" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L35" s="49">
+      <c r="L35" s="37">
         <v>1</v>
       </c>
       <c r="M35" s="37">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N35" s="49">
-        <v>55</v>
-      </c>
-      <c r="O35" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P35" s="50">
-        <v>0.14460000000000001</v>
-      </c>
-      <c r="Q35" s="50">
-        <f t="shared" ref="Q35:Q36" si="11">P35*N35</f>
-        <v>7.9530000000000003</v>
-      </c>
-      <c r="R35" s="49"/>
+      <c r="N35" s="37">
+        <v>60</v>
+      </c>
+      <c r="O35" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P35" s="38">
+        <v>6.4600000000000005E-2</v>
+      </c>
+      <c r="Q35" s="38">
+        <f>P35*N35</f>
+        <v>3.8760000000000003</v>
+      </c>
+      <c r="R35" s="37"/>
       <c r="S35" s="55"/>
     </row>
-    <row r="36" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="56"/>
       <c r="B36" s="46">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C36" s="68" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E36" s="49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F36" s="49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G36" s="49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H36" s="49" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I36" s="49" t="s">
         <v>134</v>
       </c>
       <c r="J36" s="49" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K36" s="37" t="s">
         <v>134</v>
@@ -7858,108 +8059,110 @@
         <v>50</v>
       </c>
       <c r="N36" s="49">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="O36" s="60" t="s">
         <v>136</v>
       </c>
       <c r="P36" s="50">
-        <v>0.4073</v>
+        <v>0.14460000000000001</v>
       </c>
       <c r="Q36" s="50">
-        <f t="shared" si="11"/>
-        <v>21.179600000000001</v>
+        <f t="shared" ref="Q36:Q37" si="11">P36*N36</f>
+        <v>7.9530000000000003</v>
       </c>
       <c r="R36" s="49"/>
       <c r="S36" s="55"/>
     </row>
-    <row r="37" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A37" s="56"/>
       <c r="B37" s="46">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="E37" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="F37" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G37" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="H37" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="I37" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J37" s="37" t="s">
-        <v>116</v>
+      <c r="C37" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="G37" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="H37" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="I37" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J37" s="49" t="s">
+        <v>115</v>
       </c>
       <c r="K37" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L37" s="37">
+      <c r="L37" s="49">
         <v>1</v>
       </c>
       <c r="M37" s="37">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N37" s="37">
+      <c r="N37" s="49">
         <v>52</v>
       </c>
-      <c r="O37" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P37" s="38">
-        <v>2.7953000000000001</v>
-      </c>
-      <c r="Q37" s="38">
-        <f>P37*N37</f>
-        <v>145.35560000000001</v>
-      </c>
-      <c r="R37" s="37"/>
-      <c r="S37" s="39"/>
-    </row>
-    <row r="38" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O37" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P37" s="50">
+        <v>0.4073</v>
+      </c>
+      <c r="Q37" s="50">
+        <f t="shared" si="11"/>
+        <v>21.179600000000001</v>
+      </c>
+      <c r="R37" s="49"/>
+      <c r="S37" s="55"/>
+    </row>
+    <row r="38" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="56"/>
       <c r="B38" s="46">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="C38" s="67" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>143</v>
+        <v>36</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="I38" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="K38" s="37"/>
+        <v>116</v>
+      </c>
+      <c r="K38" s="37" t="s">
+        <v>134</v>
+      </c>
       <c r="L38" s="37">
         <v>1</v>
       </c>
@@ -7971,32 +8174,32 @@
         <v>52</v>
       </c>
       <c r="O38" s="59" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="P38" s="38">
-        <v>3.28</v>
+        <v>2.7953000000000001</v>
       </c>
       <c r="Q38" s="38">
         <f>P38*N38</f>
-        <v>170.56</v>
+        <v>145.35560000000001</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="39"/>
     </row>
-    <row r="39" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" s="58" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="56"/>
       <c r="B39" s="46">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C39" s="67" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D39" s="37" t="s">
         <v>143</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>148</v>
+        <v>225</v>
       </c>
       <c r="F39" s="37" t="s">
         <v>134</v>
@@ -8022,80 +8225,134 @@
         <v>50</v>
       </c>
       <c r="N39" s="37">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="O39" s="59" t="s">
         <v>147</v>
       </c>
       <c r="P39" s="38">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="Q39" s="71">
+        <v>4.67</v>
+      </c>
+      <c r="Q39" s="38">
         <f>P39*N39</f>
-        <v>2.4700000000000002</v>
+        <v>233.5</v>
       </c>
       <c r="R39" s="37"/>
       <c r="S39" s="39"/>
     </row>
-    <row r="40" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1"/>
-      <c r="B40" s="40"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="44"/>
-      <c r="G40" s="45"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="44"/>
-      <c r="K40" s="45"/>
-      <c r="L40" s="45"/>
-      <c r="M40" s="45"/>
-      <c r="N40" s="85" t="s">
-        <v>5</v>
-      </c>
-      <c r="O40" s="86"/>
-      <c r="P40" s="86"/>
-      <c r="Q40" s="47">
-        <f>SUM(Q11:Q39)</f>
-        <v>433.67610000000008</v>
-      </c>
-      <c r="R40" s="87"/>
-      <c r="S40" s="88"/>
+    <row r="40" spans="1:19" s="58" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="56"/>
+      <c r="B40" s="46">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="G40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="I40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J40" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="K40" s="37"/>
+      <c r="L40" s="37">
+        <v>1</v>
+      </c>
+      <c r="M40" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N40" s="37">
+        <v>50</v>
+      </c>
+      <c r="O40" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="P40" s="38">
+        <v>0.35</v>
+      </c>
+      <c r="Q40" s="71">
+        <f>P40*N40</f>
+        <v>17.5</v>
+      </c>
+      <c r="R40" s="37"/>
+      <c r="S40" s="39"/>
     </row>
     <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
-      <c r="N41" s="85" t="s">
+      <c r="B41" s="40"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="44"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="45"/>
+      <c r="J41" s="44"/>
+      <c r="K41" s="45"/>
+      <c r="L41" s="45"/>
+      <c r="M41" s="45"/>
+      <c r="N41" s="86" t="s">
+        <v>5</v>
+      </c>
+      <c r="O41" s="87"/>
+      <c r="P41" s="87"/>
+      <c r="Q41" s="47">
+        <f>SUM(Q11:Q40)</f>
+        <v>513.7921</v>
+      </c>
+      <c r="R41" s="88"/>
+      <c r="S41" s="89"/>
+    </row>
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="O41" s="86"/>
-      <c r="P41" s="86"/>
-      <c r="Q41" s="48">
-        <f>Q40/50</f>
-        <v>8.673522000000002</v>
-      </c>
-      <c r="R41" s="89"/>
-      <c r="S41" s="90"/>
+      <c r="O42" s="87"/>
+      <c r="P42" s="87"/>
+      <c r="Q42" s="48">
+        <f>Q41/50</f>
+        <v>10.275842000000001</v>
+      </c>
+      <c r="R42" s="90"/>
+      <c r="S42" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S41"/>
     <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S42"/>
+    <mergeCell ref="N42:P42"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O11" r:id="rId1"/>
@@ -8108,30 +8365,31 @@
     <hyperlink ref="O20" r:id="rId8"/>
     <hyperlink ref="O21" r:id="rId9"/>
     <hyperlink ref="O22" r:id="rId10"/>
-    <hyperlink ref="O26" r:id="rId11"/>
-    <hyperlink ref="O29" r:id="rId12"/>
-    <hyperlink ref="O25" r:id="rId13"/>
-    <hyperlink ref="O30" r:id="rId14"/>
-    <hyperlink ref="O35" r:id="rId15"/>
-    <hyperlink ref="O36" r:id="rId16"/>
-    <hyperlink ref="O37" r:id="rId17"/>
-    <hyperlink ref="O38" r:id="rId18"/>
-    <hyperlink ref="O39" r:id="rId19"/>
-    <hyperlink ref="O10" r:id="rId20"/>
-    <hyperlink ref="O14" r:id="rId21"/>
-    <hyperlink ref="O23" r:id="rId22"/>
-    <hyperlink ref="O24" r:id="rId23"/>
-    <hyperlink ref="O28" r:id="rId24"/>
-    <hyperlink ref="O31" r:id="rId25"/>
-    <hyperlink ref="O32" r:id="rId26"/>
-    <hyperlink ref="O33" r:id="rId27"/>
-    <hyperlink ref="O34" r:id="rId28"/>
-    <hyperlink ref="O27" r:id="rId29"/>
-    <hyperlink ref="O17" r:id="rId30"/>
+    <hyperlink ref="O27" r:id="rId11"/>
+    <hyperlink ref="O30" r:id="rId12"/>
+    <hyperlink ref="O26" r:id="rId13"/>
+    <hyperlink ref="O31" r:id="rId14"/>
+    <hyperlink ref="O36" r:id="rId15"/>
+    <hyperlink ref="O37" r:id="rId16"/>
+    <hyperlink ref="O38" r:id="rId17"/>
+    <hyperlink ref="O10" r:id="rId18"/>
+    <hyperlink ref="O14" r:id="rId19"/>
+    <hyperlink ref="O23" r:id="rId20"/>
+    <hyperlink ref="O25" r:id="rId21"/>
+    <hyperlink ref="O29" r:id="rId22"/>
+    <hyperlink ref="O32" r:id="rId23"/>
+    <hyperlink ref="O33" r:id="rId24"/>
+    <hyperlink ref="O34" r:id="rId25"/>
+    <hyperlink ref="O35" r:id="rId26"/>
+    <hyperlink ref="O28" r:id="rId27"/>
+    <hyperlink ref="O17" r:id="rId28"/>
+    <hyperlink ref="O39" r:id="rId29"/>
+    <hyperlink ref="O40" r:id="rId30"/>
+    <hyperlink ref="O24" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId31"/>
-  <drawing r:id="rId32"/>
+  <pageSetup orientation="portrait" r:id="rId32"/>
+  <drawing r:id="rId33"/>
 </worksheet>
 </file>
 
@@ -8170,15 +8428,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="92"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92"/>
+      <c r="P1" s="92"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="92"/>
+      <c r="S1" s="93"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -8228,7 +8486,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="93"/>
+      <c r="S3" s="94"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -8253,7 +8511,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="94"/>
+      <c r="S4" s="95"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -8278,7 +8536,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="94"/>
+      <c r="S5" s="95"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -8299,7 +8557,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="94"/>
+      <c r="S6" s="95"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -8320,7 +8578,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="94"/>
+      <c r="S7" s="95"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -8341,7 +8599,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="94"/>
+      <c r="S8" s="95"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -9963,7 +10221,7 @@
       <c r="R37" s="37"/>
       <c r="S37" s="39"/>
     </row>
-    <row r="38" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" s="58" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="56"/>
       <c r="B38" s="46">
         <f t="shared" si="0"/>
@@ -9976,7 +10234,7 @@
         <v>143</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>146</v>
+        <v>225</v>
       </c>
       <c r="F38" s="37" t="s">
         <v>134</v>
@@ -10008,16 +10266,16 @@
         <v>147</v>
       </c>
       <c r="P38" s="38">
-        <v>3.28</v>
+        <v>4.67</v>
       </c>
       <c r="Q38" s="38">
         <f>P38*N38</f>
-        <v>16.399999999999999</v>
+        <v>23.35</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="39"/>
     </row>
-    <row r="39" spans="1:19" s="58" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" s="58" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="56"/>
       <c r="B39" s="46">
         <f t="shared" si="0"/>
@@ -10030,7 +10288,7 @@
         <v>143</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>148</v>
+        <v>226</v>
       </c>
       <c r="F39" s="37" t="s">
         <v>134</v>
@@ -10062,11 +10320,11 @@
         <v>147</v>
       </c>
       <c r="P39" s="38">
-        <v>2.4700000000000002</v>
+        <v>0.35</v>
       </c>
       <c r="Q39" s="71">
         <f>P39*N39</f>
-        <v>2.4700000000000002</v>
+        <v>0.35</v>
       </c>
       <c r="R39" s="37"/>
       <c r="S39" s="39"/>
@@ -10085,17 +10343,17 @@
       <c r="K40" s="45"/>
       <c r="L40" s="45"/>
       <c r="M40" s="45"/>
-      <c r="N40" s="85" t="s">
+      <c r="N40" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="O40" s="86"/>
-      <c r="P40" s="86"/>
+      <c r="O40" s="87"/>
+      <c r="P40" s="87"/>
       <c r="Q40" s="47">
         <f>SUM(Q11:Q39)</f>
-        <v>175.00190000000006</v>
-      </c>
-      <c r="R40" s="87"/>
-      <c r="S40" s="88"/>
+        <v>179.83190000000005</v>
+      </c>
+      <c r="R40" s="88"/>
+      <c r="S40" s="89"/>
     </row>
     <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -10111,17 +10369,17 @@
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
-      <c r="N41" s="85" t="s">
+      <c r="N41" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="O41" s="86"/>
-      <c r="P41" s="86"/>
+      <c r="O41" s="87"/>
+      <c r="P41" s="87"/>
       <c r="Q41" s="48">
         <f>Q40/500</f>
-        <v>0.35000380000000014</v>
-      </c>
-      <c r="R41" s="89"/>
-      <c r="S41" s="90"/>
+        <v>0.35966380000000009</v>
+      </c>
+      <c r="R41" s="90"/>
+      <c r="S41" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -10150,18 +10408,18 @@
     <hyperlink ref="O35" r:id="rId16"/>
     <hyperlink ref="O36" r:id="rId17"/>
     <hyperlink ref="O37" r:id="rId18"/>
-    <hyperlink ref="O38" r:id="rId19"/>
-    <hyperlink ref="O39" r:id="rId20"/>
-    <hyperlink ref="O10" r:id="rId21"/>
-    <hyperlink ref="O14" r:id="rId22"/>
-    <hyperlink ref="O17" r:id="rId23"/>
-    <hyperlink ref="O24" r:id="rId24"/>
-    <hyperlink ref="O25" r:id="rId25"/>
-    <hyperlink ref="O28" r:id="rId26"/>
-    <hyperlink ref="O31" r:id="rId27"/>
-    <hyperlink ref="O32" r:id="rId28"/>
-    <hyperlink ref="O33" r:id="rId29"/>
-    <hyperlink ref="O34" r:id="rId30"/>
+    <hyperlink ref="O10" r:id="rId19"/>
+    <hyperlink ref="O14" r:id="rId20"/>
+    <hyperlink ref="O17" r:id="rId21"/>
+    <hyperlink ref="O24" r:id="rId22"/>
+    <hyperlink ref="O25" r:id="rId23"/>
+    <hyperlink ref="O28" r:id="rId24"/>
+    <hyperlink ref="O31" r:id="rId25"/>
+    <hyperlink ref="O32" r:id="rId26"/>
+    <hyperlink ref="O33" r:id="rId27"/>
+    <hyperlink ref="O34" r:id="rId28"/>
+    <hyperlink ref="O38" r:id="rId29"/>
+    <hyperlink ref="O39" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId31"/>
@@ -10204,15 +10462,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="92"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92"/>
+      <c r="P1" s="92"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="92"/>
+      <c r="S1" s="93"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -10262,7 +10520,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="93"/>
+      <c r="S3" s="94"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -10287,7 +10545,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="94"/>
+      <c r="S4" s="95"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -10312,7 +10570,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="94"/>
+      <c r="S5" s="95"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -10333,7 +10591,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="94"/>
+      <c r="S6" s="95"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -10354,7 +10612,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="94"/>
+      <c r="S7" s="95"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -10375,7 +10633,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="94"/>
+      <c r="S8" s="95"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -12119,17 +12377,17 @@
       <c r="K40" s="45"/>
       <c r="L40" s="45"/>
       <c r="M40" s="45"/>
-      <c r="N40" s="85" t="s">
+      <c r="N40" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="O40" s="86"/>
-      <c r="P40" s="86"/>
+      <c r="O40" s="87"/>
+      <c r="P40" s="87"/>
       <c r="Q40" s="47">
         <f>SUM(Q11:Q39)</f>
         <v>175.00190000000006</v>
       </c>
-      <c r="R40" s="87"/>
-      <c r="S40" s="88"/>
+      <c r="R40" s="88"/>
+      <c r="S40" s="89"/>
     </row>
     <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -12145,17 +12403,17 @@
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
-      <c r="N41" s="85" t="s">
+      <c r="N41" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="O41" s="86"/>
-      <c r="P41" s="86"/>
+      <c r="O41" s="87"/>
+      <c r="P41" s="87"/>
       <c r="Q41" s="48">
         <f>Q40/500</f>
         <v>0.35000380000000014</v>
       </c>
-      <c r="R41" s="89"/>
-      <c r="S41" s="90"/>
+      <c r="R41" s="90"/>
+      <c r="S41" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/Design Files/IoT-Button-v1.2/BOM/eSpark-BOM-IoT-Button.xlsx
+++ b/Design Files/IoT-Button-v1.2/BOM/eSpark-BOM-IoT-Button.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\smartmasjid-hardware\Design Files\IoT-Button-v1.2\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Faizan\GitHub\smartmasjid-hardware\Design Files\IoT-Button-v1.2\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="2 Boards" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="500 Boards" sheetId="4" r:id="rId4"/>
     <sheet name="3000 Boards" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -712,7 +712,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -1446,6 +1446,33 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
@@ -1477,33 +1504,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1549,7 +1549,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1598,7 +1598,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1652,7 +1652,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1706,7 +1706,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1760,7 +1760,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1814,7 +1814,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2146,15 +2146,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="92"/>
-      <c r="S1" s="93"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="102"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2204,7 +2204,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="94"/>
+      <c r="S3" s="103"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2229,7 +2229,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="95"/>
+      <c r="S4" s="104"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2254,7 +2254,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="95"/>
+      <c r="S5" s="104"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2275,7 +2275,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="95"/>
+      <c r="S6" s="104"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2296,7 +2296,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="95"/>
+      <c r="S7" s="104"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2317,7 +2317,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="95"/>
+      <c r="S8" s="104"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -3170,13 +3170,13 @@
       <c r="D24" s="37" t="s">
         <v>219</v>
       </c>
-      <c r="E24" s="96" t="s">
+      <c r="E24" s="86" t="s">
         <v>220</v>
       </c>
       <c r="F24" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="G24" s="96" t="s">
+      <c r="G24" s="86" t="s">
         <v>222</v>
       </c>
       <c r="H24" s="37" t="s">
@@ -3612,53 +3612,53 @@
         <f t="shared" ref="B32" si="11">ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="97" t="s">
+      <c r="C32" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="D32" s="98" t="s">
+      <c r="D32" s="88" t="s">
         <v>182</v>
       </c>
-      <c r="E32" s="98" t="s">
+      <c r="E32" s="88" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="98" t="s">
+      <c r="F32" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="G32" s="98" t="s">
+      <c r="G32" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="H32" s="98" t="s">
+      <c r="H32" s="88" t="s">
         <v>86</v>
       </c>
-      <c r="I32" s="98" t="s">
-        <v>134</v>
-      </c>
-      <c r="J32" s="98" t="s">
+      <c r="I32" s="88" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="88" t="s">
         <v>112</v>
       </c>
-      <c r="K32" s="98" t="s">
+      <c r="K32" s="88" t="s">
         <v>183</v>
       </c>
-      <c r="L32" s="98">
-        <v>1</v>
-      </c>
-      <c r="M32" s="99">
+      <c r="L32" s="88">
+        <v>1</v>
+      </c>
+      <c r="M32" s="89">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N32" s="99">
+      <c r="N32" s="89">
         <v>100</v>
       </c>
-      <c r="O32" s="100" t="s">
-        <v>136</v>
-      </c>
-      <c r="P32" s="101" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q32" s="101" t="s">
-        <v>134</v>
-      </c>
-      <c r="R32" s="102" t="s">
+      <c r="O32" s="90" t="s">
+        <v>136</v>
+      </c>
+      <c r="P32" s="91" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q32" s="91" t="s">
+        <v>134</v>
+      </c>
+      <c r="R32" s="92" t="s">
         <v>183</v>
       </c>
       <c r="S32" s="55"/>
@@ -4121,17 +4121,17 @@
       <c r="K41" s="45"/>
       <c r="L41" s="45"/>
       <c r="M41" s="45"/>
-      <c r="N41" s="86" t="s">
+      <c r="N41" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="O41" s="87"/>
-      <c r="P41" s="87"/>
+      <c r="O41" s="96"/>
+      <c r="P41" s="96"/>
       <c r="Q41" s="47">
-        <f>SUM(Q11:Q40)</f>
-        <v>32.793300000000009</v>
-      </c>
-      <c r="R41" s="88"/>
-      <c r="S41" s="89"/>
+        <f>SUM(Q10:Q40)</f>
+        <v>32.973300000000002</v>
+      </c>
+      <c r="R41" s="97"/>
+      <c r="S41" s="98"/>
     </row>
     <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="56"/>
@@ -4147,17 +4147,17 @@
       <c r="K42" s="10"/>
       <c r="L42" s="10"/>
       <c r="M42" s="10"/>
-      <c r="N42" s="86" t="s">
+      <c r="N42" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="O42" s="87"/>
-      <c r="P42" s="87"/>
+      <c r="O42" s="96"/>
+      <c r="P42" s="96"/>
       <c r="Q42" s="48">
         <f>Q41/2</f>
-        <v>16.396650000000005</v>
-      </c>
-      <c r="R42" s="90"/>
-      <c r="S42" s="91"/>
+        <v>16.486650000000001</v>
+      </c>
+      <c r="R42" s="99"/>
+      <c r="S42" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4241,15 +4241,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="92"/>
-      <c r="S1" s="93"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="102"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -4299,7 +4299,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="94"/>
+      <c r="S3" s="103"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -4324,7 +4324,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="95"/>
+      <c r="S4" s="104"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -4349,7 +4349,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="95"/>
+      <c r="S5" s="104"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -4370,7 +4370,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="95"/>
+      <c r="S6" s="104"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -4391,7 +4391,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="95"/>
+      <c r="S7" s="104"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -4412,7 +4412,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="95"/>
+      <c r="S8" s="104"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -5265,13 +5265,13 @@
       <c r="D24" s="37" t="s">
         <v>219</v>
       </c>
-      <c r="E24" s="96" t="s">
+      <c r="E24" s="86" t="s">
         <v>220</v>
       </c>
       <c r="F24" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="G24" s="96" t="s">
+      <c r="G24" s="86" t="s">
         <v>222</v>
       </c>
       <c r="H24" s="37" t="s">
@@ -5707,56 +5707,56 @@
         <f t="shared" ref="B32" si="11">ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="97" t="s">
+      <c r="C32" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="D32" s="98" t="s">
+      <c r="D32" s="88" t="s">
         <v>182</v>
       </c>
-      <c r="E32" s="98" t="s">
+      <c r="E32" s="88" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="98" t="s">
+      <c r="F32" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="G32" s="98" t="s">
+      <c r="G32" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="H32" s="98" t="s">
+      <c r="H32" s="88" t="s">
         <v>86</v>
       </c>
-      <c r="I32" s="98" t="s">
-        <v>134</v>
-      </c>
-      <c r="J32" s="98" t="s">
+      <c r="I32" s="88" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="88" t="s">
         <v>112</v>
       </c>
-      <c r="K32" s="98" t="s">
+      <c r="K32" s="88" t="s">
         <v>183</v>
       </c>
-      <c r="L32" s="98">
-        <v>1</v>
-      </c>
-      <c r="M32" s="98">
+      <c r="L32" s="88">
+        <v>1</v>
+      </c>
+      <c r="M32" s="88">
         <f t="shared" ref="M32" si="12">L32*5</f>
         <v>5</v>
       </c>
-      <c r="N32" s="99" t="s">
-        <v>134</v>
-      </c>
-      <c r="O32" s="100" t="s">
-        <v>136</v>
-      </c>
-      <c r="P32" s="101" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q32" s="103" t="s">
-        <v>134</v>
-      </c>
-      <c r="R32" s="102" t="s">
+      <c r="N32" s="89" t="s">
+        <v>134</v>
+      </c>
+      <c r="O32" s="90" t="s">
+        <v>136</v>
+      </c>
+      <c r="P32" s="91" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q32" s="93" t="s">
+        <v>134</v>
+      </c>
+      <c r="R32" s="92" t="s">
         <v>183</v>
       </c>
-      <c r="S32" s="104"/>
+      <c r="S32" s="94"/>
     </row>
     <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
@@ -6216,17 +6216,17 @@
       <c r="K41" s="45"/>
       <c r="L41" s="45"/>
       <c r="M41" s="45"/>
-      <c r="N41" s="86" t="s">
+      <c r="N41" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="O41" s="87"/>
-      <c r="P41" s="87"/>
+      <c r="O41" s="96"/>
+      <c r="P41" s="96"/>
       <c r="Q41" s="47">
-        <f>SUM(Q11:Q40)</f>
-        <v>63.825400000000002</v>
-      </c>
-      <c r="R41" s="88"/>
-      <c r="S41" s="89"/>
+        <f>SUM(Q10:Q40)</f>
+        <v>64.005400000000009</v>
+      </c>
+      <c r="R41" s="97"/>
+      <c r="S41" s="98"/>
     </row>
     <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
@@ -6242,17 +6242,17 @@
       <c r="K42" s="10"/>
       <c r="L42" s="10"/>
       <c r="M42" s="10"/>
-      <c r="N42" s="86" t="s">
+      <c r="N42" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="O42" s="87"/>
-      <c r="P42" s="87"/>
+      <c r="O42" s="96"/>
+      <c r="P42" s="96"/>
       <c r="Q42" s="48">
         <f>Q41/5</f>
-        <v>12.765080000000001</v>
-      </c>
-      <c r="R42" s="90"/>
-      <c r="S42" s="91"/>
+        <v>12.801080000000002</v>
+      </c>
+      <c r="R42" s="99"/>
+      <c r="S42" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6336,15 +6336,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="92"/>
-      <c r="S1" s="93"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="102"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -6394,7 +6394,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="94"/>
+      <c r="S3" s="103"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -6419,7 +6419,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="95"/>
+      <c r="S4" s="104"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -6444,7 +6444,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="95"/>
+      <c r="S5" s="104"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -6465,7 +6465,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="95"/>
+      <c r="S6" s="104"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -6486,7 +6486,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="95"/>
+      <c r="S7" s="104"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -6507,7 +6507,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="95"/>
+      <c r="S8" s="104"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -7360,13 +7360,13 @@
       <c r="D24" s="37" t="s">
         <v>219</v>
       </c>
-      <c r="E24" s="96" t="s">
+      <c r="E24" s="86" t="s">
         <v>220</v>
       </c>
       <c r="F24" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="G24" s="96" t="s">
+      <c r="G24" s="86" t="s">
         <v>222</v>
       </c>
       <c r="H24" s="37" t="s">
@@ -7799,58 +7799,58 @@
         <f t="shared" ref="B32" si="8">ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="97" t="s">
+      <c r="C32" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="D32" s="98" t="s">
+      <c r="D32" s="88" t="s">
         <v>182</v>
       </c>
-      <c r="E32" s="98" t="s">
+      <c r="E32" s="88" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="98" t="s">
+      <c r="F32" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="G32" s="98" t="s">
+      <c r="G32" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="H32" s="98" t="s">
+      <c r="H32" s="88" t="s">
         <v>86</v>
       </c>
-      <c r="I32" s="98" t="s">
-        <v>134</v>
-      </c>
-      <c r="J32" s="98" t="s">
+      <c r="I32" s="88" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="88" t="s">
         <v>112</v>
       </c>
-      <c r="K32" s="98" t="s">
+      <c r="K32" s="88" t="s">
         <v>183</v>
       </c>
-      <c r="L32" s="98">
-        <v>1</v>
-      </c>
-      <c r="M32" s="99">
+      <c r="L32" s="88">
+        <v>1</v>
+      </c>
+      <c r="M32" s="89">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N32" s="99" t="s">
-        <v>134</v>
-      </c>
-      <c r="O32" s="100" t="s">
-        <v>136</v>
-      </c>
-      <c r="P32" s="101" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q32" s="103" t="s">
-        <v>134</v>
-      </c>
-      <c r="R32" s="102" t="s">
+      <c r="N32" s="89" t="s">
+        <v>134</v>
+      </c>
+      <c r="O32" s="90" t="s">
+        <v>136</v>
+      </c>
+      <c r="P32" s="91" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q32" s="93" t="s">
+        <v>134</v>
+      </c>
+      <c r="R32" s="92" t="s">
         <v>183</v>
       </c>
-      <c r="S32" s="104"/>
-    </row>
-    <row r="33" spans="1:19" s="58" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="S32" s="94"/>
+    </row>
+    <row r="33" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A33" s="56"/>
       <c r="B33" s="46">
         <f>ROW(B33) - ROW($B$9)</f>
@@ -8308,17 +8308,17 @@
       <c r="K41" s="45"/>
       <c r="L41" s="45"/>
       <c r="M41" s="45"/>
-      <c r="N41" s="86" t="s">
+      <c r="N41" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="O41" s="87"/>
-      <c r="P41" s="87"/>
+      <c r="O41" s="96"/>
+      <c r="P41" s="96"/>
       <c r="Q41" s="47">
-        <f>SUM(Q11:Q40)</f>
-        <v>513.7921</v>
-      </c>
-      <c r="R41" s="88"/>
-      <c r="S41" s="89"/>
+        <f>SUM(Q10:Q40)</f>
+        <v>515.23210000000006</v>
+      </c>
+      <c r="R41" s="97"/>
+      <c r="S41" s="98"/>
     </row>
     <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
@@ -8334,17 +8334,17 @@
       <c r="K42" s="10"/>
       <c r="L42" s="10"/>
       <c r="M42" s="10"/>
-      <c r="N42" s="86" t="s">
+      <c r="N42" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="O42" s="87"/>
-      <c r="P42" s="87"/>
+      <c r="O42" s="96"/>
+      <c r="P42" s="96"/>
       <c r="Q42" s="48">
         <f>Q41/50</f>
-        <v>10.275842000000001</v>
-      </c>
-      <c r="R42" s="90"/>
-      <c r="S42" s="91"/>
+        <v>10.304642000000001</v>
+      </c>
+      <c r="R42" s="99"/>
+      <c r="S42" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -8428,15 +8428,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="92"/>
-      <c r="S1" s="93"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="102"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -8486,7 +8486,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="94"/>
+      <c r="S3" s="103"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -8511,7 +8511,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="95"/>
+      <c r="S4" s="104"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -8536,7 +8536,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="95"/>
+      <c r="S5" s="104"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -8557,7 +8557,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="95"/>
+      <c r="S6" s="104"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -8578,7 +8578,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="95"/>
+      <c r="S7" s="104"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -8599,7 +8599,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="95"/>
+      <c r="S8" s="104"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -10343,17 +10343,17 @@
       <c r="K40" s="45"/>
       <c r="L40" s="45"/>
       <c r="M40" s="45"/>
-      <c r="N40" s="86" t="s">
+      <c r="N40" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="O40" s="87"/>
-      <c r="P40" s="87"/>
+      <c r="O40" s="96"/>
+      <c r="P40" s="96"/>
       <c r="Q40" s="47">
-        <f>SUM(Q11:Q39)</f>
-        <v>179.83190000000005</v>
-      </c>
-      <c r="R40" s="88"/>
-      <c r="S40" s="89"/>
+        <f>SUM(Q10:Q39)</f>
+        <v>189.71190000000004</v>
+      </c>
+      <c r="R40" s="97"/>
+      <c r="S40" s="98"/>
     </row>
     <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -10369,17 +10369,17 @@
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
-      <c r="N41" s="86" t="s">
+      <c r="N41" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="O41" s="87"/>
-      <c r="P41" s="87"/>
+      <c r="O41" s="96"/>
+      <c r="P41" s="96"/>
       <c r="Q41" s="48">
         <f>Q40/500</f>
-        <v>0.35966380000000009</v>
-      </c>
-      <c r="R41" s="90"/>
-      <c r="S41" s="91"/>
+        <v>0.37942380000000009</v>
+      </c>
+      <c r="R41" s="99"/>
+      <c r="S41" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -10462,15 +10462,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="92"/>
-      <c r="S1" s="93"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="102"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -10520,7 +10520,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="94"/>
+      <c r="S3" s="103"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -10545,7 +10545,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="95"/>
+      <c r="S4" s="104"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -10570,7 +10570,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="95"/>
+      <c r="S5" s="104"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -10591,7 +10591,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="95"/>
+      <c r="S6" s="104"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -10612,7 +10612,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="95"/>
+      <c r="S7" s="104"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -10633,7 +10633,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="95"/>
+      <c r="S8" s="104"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -12377,17 +12377,17 @@
       <c r="K40" s="45"/>
       <c r="L40" s="45"/>
       <c r="M40" s="45"/>
-      <c r="N40" s="86" t="s">
+      <c r="N40" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="O40" s="87"/>
-      <c r="P40" s="87"/>
+      <c r="O40" s="96"/>
+      <c r="P40" s="96"/>
       <c r="Q40" s="47">
-        <f>SUM(Q11:Q39)</f>
-        <v>175.00190000000006</v>
-      </c>
-      <c r="R40" s="88"/>
-      <c r="S40" s="89"/>
+        <f>SUM(Q10:Q39)</f>
+        <v>184.88190000000006</v>
+      </c>
+      <c r="R40" s="97"/>
+      <c r="S40" s="98"/>
     </row>
     <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -12403,17 +12403,17 @@
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10"/>
-      <c r="N41" s="86" t="s">
+      <c r="N41" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="O41" s="87"/>
-      <c r="P41" s="87"/>
+      <c r="O41" s="96"/>
+      <c r="P41" s="96"/>
       <c r="Q41" s="48">
         <f>Q40/500</f>
-        <v>0.35000380000000014</v>
-      </c>
-      <c r="R41" s="90"/>
-      <c r="S41" s="91"/>
+        <v>0.36976380000000014</v>
+      </c>
+      <c r="R41" s="99"/>
+      <c r="S41" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/Design Files/IoT-Button-v1.2/BOM/eSpark-BOM-IoT-Button.xlsx
+++ b/Design Files/IoT-Button-v1.2/BOM/eSpark-BOM-IoT-Button.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Faizan\GitHub\smartmasjid-hardware\Design Files\IoT-Button-v1.2\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\smartmasjid-hardware\Design Files\IoT-Button-v1.2\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="2 Boards" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,12 @@
     <sheet name="500 Boards" sheetId="4" r:id="rId4"/>
     <sheet name="3000 Boards" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="233">
   <si>
     <t>Component list</t>
   </si>
@@ -707,12 +707,27 @@
   </si>
   <si>
     <t>C5310968</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>RES SMD 1K OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RC0603FR-071KL</t>
+  </si>
+  <si>
+    <t>C22548</t>
+  </si>
+  <si>
+    <t>1K</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -1549,7 +1564,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1598,7 +1613,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1652,7 +1667,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1706,7 +1721,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1760,7 +1775,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1814,7 +1829,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2112,7 +2127,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -2435,7 +2450,7 @@
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="56"/>
       <c r="B11" s="46">
-        <f>ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="67" t="s">
@@ -2482,7 +2497,7 @@
         <v>5.1999999999999998E-3</v>
       </c>
       <c r="Q11" s="50">
-        <f t="shared" ref="Q11" si="0">P11*N11</f>
+        <f t="shared" ref="Q11" si="1">P11*N11</f>
         <v>0.52</v>
       </c>
       <c r="R11" s="49"/>
@@ -2491,7 +2506,7 @@
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="56"/>
       <c r="B12" s="46">
-        <f t="shared" ref="B12:B40" si="1">ROW(B12) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C12" s="67" t="s">
@@ -2547,7 +2562,7 @@
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="56"/>
       <c r="B13" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="67" t="s">
@@ -2581,7 +2596,7 @@
         <v>1</v>
       </c>
       <c r="M13" s="37">
-        <f t="shared" ref="M13:M40" si="2">L13*2</f>
+        <f t="shared" ref="M13:M41" si="2">L13*2</f>
         <v>2</v>
       </c>
       <c r="N13" s="49">
@@ -2602,8 +2617,8 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="56"/>
-      <c r="B14" s="72">
-        <f t="shared" si="1"/>
+      <c r="B14" s="46">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="67" t="s">
@@ -2659,7 +2674,7 @@
     <row r="15" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="56"/>
       <c r="B15" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C15" s="67" t="s">
@@ -2713,7 +2728,7 @@
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="56"/>
       <c r="B16" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C16" s="68" t="s">
@@ -2769,7 +2784,7 @@
     <row r="17" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A17" s="56"/>
       <c r="B17" s="46">
-        <f>ROW(B17) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C17" s="67" t="s">
@@ -2825,7 +2840,7 @@
     <row r="18" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A18" s="56"/>
       <c r="B18" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C18" s="68" t="s">
@@ -2881,7 +2896,7 @@
     <row r="19" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A19" s="56"/>
       <c r="B19" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C19" s="67" t="s">
@@ -2937,7 +2952,7 @@
     <row r="20" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="56"/>
       <c r="B20" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C20" s="67" t="s">
@@ -2993,7 +3008,7 @@
     <row r="21" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A21" s="56"/>
       <c r="B21" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C21" s="68" t="s">
@@ -3049,7 +3064,7 @@
     <row r="22" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A22" s="56"/>
       <c r="B22" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C22" s="67" t="s">
@@ -3105,7 +3120,7 @@
     <row r="23" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A23" s="56"/>
       <c r="B23" s="46">
-        <f>ROW(B23) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C23" s="67" t="s">
@@ -3161,7 +3176,7 @@
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="56"/>
       <c r="B24" s="46">
-        <f>ROW(B24) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C24" s="67" t="s">
@@ -3214,10 +3229,10 @@
       <c r="R24" s="37"/>
       <c r="S24" s="55"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A25" s="56"/>
-      <c r="B25" s="73">
-        <f t="shared" si="1"/>
+      <c r="B25" s="46">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C25" s="74" t="s">
@@ -3226,7 +3241,7 @@
       <c r="D25" s="75" t="s">
         <v>208</v>
       </c>
-      <c r="E25" s="75" t="s">
+      <c r="E25" s="49" t="s">
         <v>172</v>
       </c>
       <c r="F25" s="75" t="s">
@@ -3273,7 +3288,7 @@
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="56"/>
       <c r="B26" s="46">
-        <f>ROW(B26) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C26" s="68" t="s">
@@ -3329,7 +3344,7 @@
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="56"/>
       <c r="B27" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C27" s="68" t="s">
@@ -3385,7 +3400,7 @@
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="56"/>
       <c r="B28" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C28" s="67" t="s">
@@ -3441,7 +3456,7 @@
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="56"/>
       <c r="B29" s="46">
-        <f>ROW(B29) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C29" s="67" t="s">
@@ -3497,7 +3512,7 @@
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="56"/>
       <c r="B30" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C30" s="68" t="s">
@@ -3553,7 +3568,7 @@
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="56"/>
       <c r="B31" s="46">
-        <f>ROW(B31) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C31" s="68" t="s">
@@ -3608,8 +3623,8 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="56"/>
-      <c r="B32" s="72">
-        <f t="shared" ref="B32" si="11">ROW(B32) - ROW($B$9)</f>
+      <c r="B32" s="46">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="C32" s="87" t="s">
@@ -3663,38 +3678,38 @@
       </c>
       <c r="S32" s="55"/>
     </row>
-    <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="56"/>
       <c r="B33" s="46">
-        <f>ROW(B33) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="68" t="s">
-        <v>187</v>
-      </c>
-      <c r="D33" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="F33" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G33" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="H33" s="37" t="s">
-        <v>184</v>
+      <c r="C33" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="49" t="s">
+        <v>228</v>
+      </c>
+      <c r="E33" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="F33" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="G33" s="85" t="s">
+        <v>230</v>
+      </c>
+      <c r="H33" s="49" t="s">
+        <v>86</v>
       </c>
       <c r="I33" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="K33" s="37" t="s">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="L33" s="37">
         <v>1</v>
@@ -3703,219 +3718,219 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N33" s="49">
-        <v>5</v>
+      <c r="N33" s="37">
+        <v>100</v>
       </c>
       <c r="O33" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P33" s="38">
-        <v>0.1336</v>
+        <v>1E-3</v>
       </c>
       <c r="Q33" s="50">
-        <f t="shared" ref="Q33" si="12">P33*N33</f>
-        <v>0.66799999999999993</v>
-      </c>
-      <c r="R33" s="49"/>
+        <f>P33*N33</f>
+        <v>0.1</v>
+      </c>
+      <c r="R33" s="76"/>
       <c r="S33" s="55"/>
     </row>
-    <row r="34" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A34" s="61"/>
-      <c r="B34" s="72">
-        <f t="shared" ref="B34" si="13">ROW(B34) - ROW($B$9)</f>
+    <row r="34" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A34" s="56"/>
+      <c r="B34" s="46">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="C34" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="D34" s="49" t="s">
-        <v>188</v>
-      </c>
-      <c r="E34" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="F34" s="49" t="s">
+      <c r="D34" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="F34" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="G34" s="49" t="s">
-        <v>190</v>
-      </c>
-      <c r="H34" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="I34" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J34" s="49" t="s">
-        <v>192</v>
-      </c>
-      <c r="K34" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="L34" s="49">
-        <v>2</v>
+      <c r="G34" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="H34" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="I34" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="K34" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L34" s="37">
+        <v>1</v>
       </c>
       <c r="M34" s="37">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="N34" s="62">
-        <v>10</v>
-      </c>
-      <c r="O34" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P34" s="50">
-        <v>4.8300000000000003E-2</v>
-      </c>
-      <c r="Q34" s="63">
-        <f>P34*N34</f>
-        <v>0.48300000000000004</v>
-      </c>
-      <c r="R34" s="62"/>
-      <c r="S34" s="64"/>
+        <v>2</v>
+      </c>
+      <c r="N34" s="49">
+        <v>5</v>
+      </c>
+      <c r="O34" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P34" s="38">
+        <v>0.1336</v>
+      </c>
+      <c r="Q34" s="50">
+        <f t="shared" ref="Q34" si="11">P34*N34</f>
+        <v>0.66799999999999993</v>
+      </c>
+      <c r="R34" s="49"/>
+      <c r="S34" s="55"/>
     </row>
     <row r="35" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A35" s="56"/>
+      <c r="A35" s="61"/>
       <c r="B35" s="46">
-        <f>ROW(B35) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="67" t="s">
+      <c r="C35" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="D35" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="E35" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="F35" s="37" t="s">
+      <c r="D35" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="E35" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="F35" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="G35" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="H35" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="I35" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J35" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="K35" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L35" s="37">
-        <v>1</v>
+      <c r="G35" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="H35" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="I35" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="K35" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L35" s="49">
+        <v>2</v>
       </c>
       <c r="M35" s="37">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="N35" s="49">
+        <v>4</v>
+      </c>
+      <c r="N35" s="62">
         <v>10</v>
       </c>
-      <c r="O35" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P35" s="38">
-        <v>6.4600000000000005E-2</v>
-      </c>
-      <c r="Q35" s="50">
-        <f t="shared" ref="Q35" si="14">P35*N35</f>
-        <v>0.64600000000000002</v>
-      </c>
-      <c r="R35" s="49"/>
-      <c r="S35" s="55"/>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="O35" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P35" s="50">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="Q35" s="63">
+        <f>P35*N35</f>
+        <v>0.48300000000000004</v>
+      </c>
+      <c r="R35" s="62"/>
+      <c r="S35" s="64"/>
+    </row>
+    <row r="36" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A36" s="56"/>
       <c r="B36" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="E36" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="F36" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="G36" s="49" t="s">
-        <v>83</v>
-      </c>
-      <c r="H36" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="I36" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J36" s="49" t="s">
-        <v>114</v>
+      <c r="C36" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="D36" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="E36" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="F36" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G36" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="H36" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I36" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J36" s="37" t="s">
+        <v>196</v>
       </c>
       <c r="K36" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L36" s="49">
+      <c r="L36" s="37">
         <v>1</v>
       </c>
       <c r="M36" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N36" s="37">
-        <v>5</v>
-      </c>
-      <c r="O36" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P36" s="50">
-        <v>0.2079</v>
-      </c>
-      <c r="Q36" s="38">
-        <f>P36*N36</f>
-        <v>1.0395000000000001</v>
-      </c>
-      <c r="R36" s="37"/>
+      <c r="N36" s="49">
+        <v>10</v>
+      </c>
+      <c r="O36" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P36" s="38">
+        <v>6.4600000000000005E-2</v>
+      </c>
+      <c r="Q36" s="50">
+        <f t="shared" ref="Q36" si="12">P36*N36</f>
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="R36" s="49"/>
       <c r="S36" s="55"/>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="56"/>
       <c r="B37" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C37" s="68" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D37" s="49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E37" s="49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F37" s="49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G37" s="49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H37" s="49" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I37" s="49" t="s">
         <v>134</v>
       </c>
       <c r="J37" s="49" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K37" s="37" t="s">
         <v>134</v>
@@ -3927,109 +3942,111 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N37" s="49">
-        <v>3</v>
+      <c r="N37" s="37">
+        <v>5</v>
       </c>
       <c r="O37" s="60" t="s">
         <v>136</v>
       </c>
       <c r="P37" s="50">
-        <v>0.54569999999999996</v>
-      </c>
-      <c r="Q37" s="50">
-        <f t="shared" ref="Q37" si="15">P37*N37</f>
-        <v>1.6370999999999998</v>
-      </c>
-      <c r="R37" s="49"/>
+        <v>0.2079</v>
+      </c>
+      <c r="Q37" s="38">
+        <f>P37*N37</f>
+        <v>1.0395000000000001</v>
+      </c>
+      <c r="R37" s="37"/>
       <c r="S37" s="55"/>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="56"/>
       <c r="B38" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="E38" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="F38" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G38" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="H38" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="I38" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J38" s="37" t="s">
-        <v>116</v>
+      <c r="C38" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="F38" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="G38" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="H38" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="I38" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J38" s="49" t="s">
+        <v>115</v>
       </c>
       <c r="K38" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L38" s="37">
+      <c r="L38" s="49">
         <v>1</v>
       </c>
       <c r="M38" s="37">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N38" s="37">
+      <c r="N38" s="49">
         <v>3</v>
       </c>
-      <c r="O38" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P38" s="38">
-        <v>2.8589000000000002</v>
-      </c>
-      <c r="Q38" s="38">
-        <f>P38*N38</f>
-        <v>8.5767000000000007</v>
-      </c>
-      <c r="R38" s="37"/>
+      <c r="O38" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P38" s="50">
+        <v>0.54569999999999996</v>
+      </c>
+      <c r="Q38" s="50">
+        <f t="shared" ref="Q38" si="13">P38*N38</f>
+        <v>1.6370999999999998</v>
+      </c>
+      <c r="R38" s="49"/>
       <c r="S38" s="55"/>
     </row>
-    <row r="39" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="56"/>
       <c r="B39" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C39" s="67" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>143</v>
+        <v>36</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>225</v>
+        <v>55</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="I39" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J39" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="K39" s="37"/>
+        <v>116</v>
+      </c>
+      <c r="K39" s="37" t="s">
+        <v>134</v>
+      </c>
       <c r="L39" s="37">
         <v>1</v>
       </c>
@@ -4038,35 +4055,35 @@
         <v>2</v>
       </c>
       <c r="N39" s="37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O39" s="59" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="P39" s="38">
-        <v>4.67</v>
+        <v>2.8589000000000002</v>
       </c>
       <c r="Q39" s="38">
         <f>P39*N39</f>
-        <v>9.34</v>
+        <v>8.5767000000000007</v>
       </c>
       <c r="R39" s="37"/>
       <c r="S39" s="55"/>
     </row>
-    <row r="40" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="48" x14ac:dyDescent="0.25">
       <c r="A40" s="56"/>
       <c r="B40" s="46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="C40" s="67" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D40" s="37" t="s">
         <v>143</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F40" s="37" t="s">
         <v>134</v>
@@ -4091,79 +4108,133 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="N40" s="49">
-        <v>1</v>
+      <c r="N40" s="37">
+        <v>2</v>
       </c>
       <c r="O40" s="59" t="s">
         <v>147</v>
       </c>
       <c r="P40" s="38">
+        <v>4.67</v>
+      </c>
+      <c r="Q40" s="38">
+        <f>P40*N40</f>
+        <v>9.34</v>
+      </c>
+      <c r="R40" s="37"/>
+      <c r="S40" s="55"/>
+    </row>
+    <row r="41" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="56"/>
+      <c r="B41" s="46">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C41" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="F41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="G41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="I41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="K41" s="37"/>
+      <c r="L41" s="37">
+        <v>1</v>
+      </c>
+      <c r="M41" s="37">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="N41" s="49">
+        <v>1</v>
+      </c>
+      <c r="O41" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="P41" s="38">
         <v>0.35</v>
       </c>
-      <c r="Q40" s="50">
-        <f t="shared" ref="Q40" si="16">P40*N40</f>
+      <c r="Q41" s="50">
+        <f t="shared" ref="Q41" si="14">P41*N41</f>
         <v>0.35</v>
       </c>
-      <c r="R40" s="49"/>
-      <c r="S40" s="55"/>
-    </row>
-    <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="56"/>
-      <c r="B41" s="40"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="44"/>
-      <c r="G41" s="45"/>
-      <c r="H41" s="44"/>
-      <c r="I41" s="45"/>
-      <c r="J41" s="44"/>
-      <c r="K41" s="45"/>
-      <c r="L41" s="45"/>
-      <c r="M41" s="45"/>
-      <c r="N41" s="95" t="s">
-        <v>5</v>
-      </c>
-      <c r="O41" s="96"/>
-      <c r="P41" s="96"/>
-      <c r="Q41" s="47">
-        <f>SUM(Q10:Q40)</f>
-        <v>32.973300000000002</v>
-      </c>
-      <c r="R41" s="97"/>
-      <c r="S41" s="98"/>
+      <c r="R41" s="49"/>
+      <c r="S41" s="55"/>
     </row>
     <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="56"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
       <c r="N42" s="95" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O42" s="96"/>
       <c r="P42" s="96"/>
-      <c r="Q42" s="48">
-        <f>Q41/2</f>
-        <v>16.486650000000001</v>
-      </c>
-      <c r="R42" s="99"/>
-      <c r="S42" s="100"/>
+      <c r="Q42" s="47">
+        <f>SUM(Q10:Q41)</f>
+        <v>33.073300000000003</v>
+      </c>
+      <c r="R42" s="97"/>
+      <c r="S42" s="98"/>
+    </row>
+    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="56"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="95" t="s">
+        <v>6</v>
+      </c>
+      <c r="O43" s="96"/>
+      <c r="P43" s="96"/>
+      <c r="Q43" s="48">
+        <f>Q42/2</f>
+        <v>16.536650000000002</v>
+      </c>
+      <c r="R43" s="99"/>
+      <c r="S43" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S42"/>
     <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S43"/>
+    <mergeCell ref="N43:P43"/>
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
   </mergeCells>
@@ -4182,33 +4253,34 @@
     <hyperlink ref="O30" r:id="rId12"/>
     <hyperlink ref="O26" r:id="rId13"/>
     <hyperlink ref="O31" r:id="rId14"/>
-    <hyperlink ref="O36" r:id="rId15"/>
-    <hyperlink ref="O37" r:id="rId16"/>
-    <hyperlink ref="O38" r:id="rId17"/>
+    <hyperlink ref="O37" r:id="rId15"/>
+    <hyperlink ref="O38" r:id="rId16"/>
+    <hyperlink ref="O39" r:id="rId17"/>
     <hyperlink ref="O10" r:id="rId18"/>
     <hyperlink ref="O14" r:id="rId19"/>
     <hyperlink ref="O23" r:id="rId20"/>
     <hyperlink ref="O25" r:id="rId21"/>
     <hyperlink ref="O29" r:id="rId22"/>
     <hyperlink ref="O32" r:id="rId23"/>
-    <hyperlink ref="O33" r:id="rId24"/>
-    <hyperlink ref="O34" r:id="rId25"/>
-    <hyperlink ref="O35" r:id="rId26"/>
+    <hyperlink ref="O34" r:id="rId24"/>
+    <hyperlink ref="O35" r:id="rId25"/>
+    <hyperlink ref="O36" r:id="rId26"/>
     <hyperlink ref="O17" r:id="rId27"/>
     <hyperlink ref="O28" r:id="rId28"/>
-    <hyperlink ref="O39" r:id="rId29"/>
-    <hyperlink ref="O40" r:id="rId30"/>
+    <hyperlink ref="O40" r:id="rId29"/>
+    <hyperlink ref="O41" r:id="rId30"/>
     <hyperlink ref="O24" r:id="rId31"/>
+    <hyperlink ref="O33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId32"/>
-  <drawing r:id="rId33"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId33"/>
+  <drawing r:id="rId34"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -4586,7 +4658,7 @@
     <row r="12" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="56"/>
       <c r="B12" s="46">
-        <f t="shared" ref="B12:B40" si="0">ROW(B12) - ROW($B$9)</f>
+        <f t="shared" ref="B12:B41" si="0">ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
       <c r="C12" s="67" t="s">
@@ -5704,7 +5776,7 @@
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="72">
-        <f t="shared" ref="B32" si="11">ROW(B32) - ROW($B$9)</f>
+        <f t="shared" ref="B32:B33" si="11">ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
       <c r="C32" s="87" t="s">
@@ -5758,38 +5830,38 @@
       </c>
       <c r="S32" s="94"/>
     </row>
-    <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" s="56"/>
       <c r="B33" s="46">
-        <f>ROW(B33) - ROW($B$9)</f>
+        <f t="shared" si="11"/>
         <v>24</v>
       </c>
-      <c r="C33" s="68" t="s">
-        <v>187</v>
-      </c>
-      <c r="D33" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="F33" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G33" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="H33" s="37" t="s">
-        <v>184</v>
+      <c r="C33" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="49" t="s">
+        <v>228</v>
+      </c>
+      <c r="E33" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="F33" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="G33" s="85" t="s">
+        <v>230</v>
+      </c>
+      <c r="H33" s="49" t="s">
+        <v>86</v>
       </c>
       <c r="I33" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="K33" s="37" t="s">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="L33" s="37">
         <v>1</v>
@@ -5799,187 +5871,187 @@
         <v>5</v>
       </c>
       <c r="N33" s="37">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="O33" s="59" t="s">
         <v>136</v>
       </c>
       <c r="P33" s="38">
-        <v>0.1336</v>
-      </c>
-      <c r="Q33" s="38">
+        <v>1E-3</v>
+      </c>
+      <c r="Q33" s="50">
         <f>P33*N33</f>
-        <v>1.3359999999999999</v>
-      </c>
-      <c r="R33" s="37"/>
+        <v>0.1</v>
+      </c>
+      <c r="R33" s="76"/>
       <c r="S33" s="55"/>
     </row>
-    <row r="34" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="72">
-        <f t="shared" ref="B34" si="13">ROW(B34) - ROW($B$9)</f>
+      <c r="B34" s="46">
+        <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
       <c r="C34" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="D34" s="49" t="s">
-        <v>188</v>
-      </c>
-      <c r="E34" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="F34" s="49" t="s">
+      <c r="D34" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="F34" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="G34" s="49" t="s">
-        <v>190</v>
-      </c>
-      <c r="H34" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="I34" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J34" s="49" t="s">
-        <v>192</v>
-      </c>
-      <c r="K34" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="L34" s="49">
-        <v>2</v>
-      </c>
-      <c r="M34" s="49">
-        <f t="shared" ref="M34" si="14">L34*5</f>
+      <c r="G34" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="H34" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="I34" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="K34" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L34" s="37">
+        <v>1</v>
+      </c>
+      <c r="M34" s="37">
+        <f>L34*5</f>
+        <v>5</v>
+      </c>
+      <c r="N34" s="37">
         <v>10</v>
       </c>
-      <c r="N34" s="49">
-        <v>20</v>
-      </c>
-      <c r="O34" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P34" s="50">
-        <v>4.8300000000000003E-2</v>
-      </c>
-      <c r="Q34" s="50">
-        <f t="shared" ref="Q34" si="15">P34*N34</f>
-        <v>0.96600000000000008</v>
-      </c>
-      <c r="R34" s="49"/>
+      <c r="O34" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P34" s="38">
+        <v>0.1336</v>
+      </c>
+      <c r="Q34" s="38">
+        <f>P34*N34</f>
+        <v>1.3359999999999999</v>
+      </c>
+      <c r="R34" s="37"/>
       <c r="S34" s="55"/>
     </row>
     <row r="35" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="46">
-        <f>ROW(B35) - ROW($B$9)</f>
+      <c r="B35" s="72">
+        <f t="shared" ref="B35" si="13">ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="67" t="s">
+      <c r="C35" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="D35" s="37" t="s">
+      <c r="D35" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="E35" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="F35" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="G35" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="H35" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="I35" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="K35" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L35" s="49">
+        <v>2</v>
+      </c>
+      <c r="M35" s="49">
+        <f t="shared" ref="M35" si="14">L35*5</f>
+        <v>10</v>
+      </c>
+      <c r="N35" s="49">
+        <v>20</v>
+      </c>
+      <c r="O35" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P35" s="50">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="Q35" s="50">
+        <f t="shared" ref="Q35" si="15">P35*N35</f>
+        <v>0.96600000000000008</v>
+      </c>
+      <c r="R35" s="49"/>
+      <c r="S35" s="55"/>
+    </row>
+    <row r="36" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="46">
+        <f>ROW(B36) - ROW($B$9)</f>
+        <v>27</v>
+      </c>
+      <c r="C36" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="D36" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="E35" s="37" t="s">
+      <c r="E36" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="F35" s="37" t="s">
+      <c r="F36" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="G35" s="37" t="s">
+      <c r="G36" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="H35" s="37" t="s">
+      <c r="H36" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="I35" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J35" s="37" t="s">
+      <c r="I36" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J36" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="K35" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L35" s="37">
-        <v>1</v>
-      </c>
-      <c r="M35" s="37">
-        <f>L35*5</f>
+      <c r="K36" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L36" s="37">
+        <v>1</v>
+      </c>
+      <c r="M36" s="37">
+        <f>L36*5</f>
         <v>5</v>
       </c>
-      <c r="N35" s="37">
+      <c r="N36" s="37">
         <v>10</v>
       </c>
-      <c r="O35" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P35" s="38">
+      <c r="O36" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P36" s="38">
         <v>6.4600000000000005E-2</v>
       </c>
-      <c r="Q35" s="38">
-        <f>P35*N35</f>
+      <c r="Q36" s="38">
+        <f>P36*N36</f>
         <v>0.64600000000000002</v>
       </c>
-      <c r="R35" s="37"/>
-      <c r="S35" s="55"/>
-    </row>
-    <row r="36" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="56"/>
-      <c r="B36" s="46">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="C36" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="E36" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="F36" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="G36" s="49" t="s">
-        <v>83</v>
-      </c>
-      <c r="H36" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="I36" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J36" s="49" t="s">
-        <v>114</v>
-      </c>
-      <c r="K36" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L36" s="49">
-        <v>1</v>
-      </c>
-      <c r="M36" s="49">
-        <f t="shared" ref="M36" si="16">L36*5</f>
-        <v>5</v>
-      </c>
-      <c r="N36" s="49">
-        <v>10</v>
-      </c>
-      <c r="O36" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P36" s="50">
-        <v>0.2079</v>
-      </c>
-      <c r="Q36" s="50">
-        <f t="shared" ref="Q36" si="17">P36*N36</f>
-        <v>2.0790000000000002</v>
-      </c>
-      <c r="R36" s="49"/>
+      <c r="R36" s="37"/>
       <c r="S36" s="55"/>
     </row>
     <row r="37" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
@@ -5989,28 +6061,28 @@
         <v>28</v>
       </c>
       <c r="C37" s="68" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D37" s="49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E37" s="49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F37" s="49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G37" s="49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H37" s="49" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I37" s="49" t="s">
         <v>134</v>
       </c>
       <c r="J37" s="49" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K37" s="37" t="s">
         <v>134</v>
@@ -6019,112 +6091,114 @@
         <v>1</v>
       </c>
       <c r="M37" s="49">
-        <f t="shared" ref="M37" si="18">L37*5</f>
+        <f t="shared" ref="M37" si="16">L37*5</f>
         <v>5</v>
       </c>
       <c r="N37" s="49">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O37" s="60" t="s">
         <v>136</v>
       </c>
       <c r="P37" s="50">
-        <v>0.54569999999999996</v>
+        <v>0.2079</v>
       </c>
       <c r="Q37" s="50">
-        <f t="shared" ref="Q37" si="19">P37*N37</f>
-        <v>3.2741999999999996</v>
+        <f t="shared" ref="Q37" si="17">P37*N37</f>
+        <v>2.0790000000000002</v>
       </c>
       <c r="R37" s="49"/>
       <c r="S37" s="55"/>
     </row>
-    <row r="38" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="56"/>
       <c r="B38" s="46">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="E38" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="F38" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G38" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="H38" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="I38" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J38" s="37" t="s">
-        <v>116</v>
+      <c r="C38" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="F38" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="G38" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="H38" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="I38" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J38" s="49" t="s">
+        <v>115</v>
       </c>
       <c r="K38" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L38" s="37">
-        <v>1</v>
-      </c>
-      <c r="M38" s="37">
-        <f>L38*5</f>
+      <c r="L38" s="49">
+        <v>1</v>
+      </c>
+      <c r="M38" s="49">
+        <f t="shared" ref="M38" si="18">L38*5</f>
         <v>5</v>
       </c>
-      <c r="N38" s="37">
+      <c r="N38" s="49">
         <v>6</v>
       </c>
-      <c r="O38" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P38" s="38">
-        <v>2.8589000000000002</v>
-      </c>
-      <c r="Q38" s="38">
-        <f>P38*N38</f>
-        <v>17.153400000000001</v>
-      </c>
-      <c r="R38" s="37"/>
-      <c r="S38" s="39"/>
-    </row>
-    <row r="39" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O38" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P38" s="50">
+        <v>0.54569999999999996</v>
+      </c>
+      <c r="Q38" s="50">
+        <f t="shared" ref="Q38" si="19">P38*N38</f>
+        <v>3.2741999999999996</v>
+      </c>
+      <c r="R38" s="49"/>
+      <c r="S38" s="55"/>
+    </row>
+    <row r="39" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="56"/>
       <c r="B39" s="46">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C39" s="67" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>143</v>
+        <v>36</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>225</v>
+        <v>55</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="I39" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J39" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="K39" s="37"/>
+        <v>116</v>
+      </c>
+      <c r="K39" s="37" t="s">
+        <v>134</v>
+      </c>
       <c r="L39" s="37">
         <v>1</v>
       </c>
@@ -6133,17 +6207,17 @@
         <v>5</v>
       </c>
       <c r="N39" s="37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O39" s="59" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="P39" s="38">
-        <v>4.67</v>
+        <v>2.8589000000000002</v>
       </c>
       <c r="Q39" s="38">
         <f>P39*N39</f>
-        <v>23.35</v>
+        <v>17.153400000000001</v>
       </c>
       <c r="R39" s="37"/>
       <c r="S39" s="39"/>
@@ -6155,13 +6229,13 @@
         <v>31</v>
       </c>
       <c r="C40" s="67" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D40" s="37" t="s">
         <v>143</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F40" s="37" t="s">
         <v>134</v>
@@ -6187,80 +6261,134 @@
         <v>5</v>
       </c>
       <c r="N40" s="37">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O40" s="59" t="s">
         <v>147</v>
       </c>
       <c r="P40" s="38">
-        <v>0.35</v>
-      </c>
-      <c r="Q40" s="71">
+        <v>4.67</v>
+      </c>
+      <c r="Q40" s="38">
         <f>P40*N40</f>
-        <v>0.35</v>
+        <v>23.35</v>
       </c>
       <c r="R40" s="37"/>
       <c r="S40" s="39"/>
     </row>
-    <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1"/>
-      <c r="B41" s="40"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="44"/>
-      <c r="G41" s="45"/>
-      <c r="H41" s="44"/>
-      <c r="I41" s="45"/>
-      <c r="J41" s="44"/>
-      <c r="K41" s="45"/>
-      <c r="L41" s="45"/>
-      <c r="M41" s="45"/>
-      <c r="N41" s="95" t="s">
+    <row r="41" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="56"/>
+      <c r="B41" s="46">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C41" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="F41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="G41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="I41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="K41" s="37"/>
+      <c r="L41" s="37">
+        <v>1</v>
+      </c>
+      <c r="M41" s="37">
+        <f>L41*5</f>
         <v>5</v>
       </c>
-      <c r="O41" s="96"/>
-      <c r="P41" s="96"/>
-      <c r="Q41" s="47">
-        <f>SUM(Q10:Q40)</f>
-        <v>64.005400000000009</v>
-      </c>
-      <c r="R41" s="97"/>
-      <c r="S41" s="98"/>
+      <c r="N41" s="37">
+        <v>1</v>
+      </c>
+      <c r="O41" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="P41" s="38">
+        <v>0.35</v>
+      </c>
+      <c r="Q41" s="71">
+        <f>P41*N41</f>
+        <v>0.35</v>
+      </c>
+      <c r="R41" s="37"/>
+      <c r="S41" s="39"/>
     </row>
     <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
       <c r="N42" s="95" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O42" s="96"/>
       <c r="P42" s="96"/>
-      <c r="Q42" s="48">
-        <f>Q41/5</f>
-        <v>12.801080000000002</v>
-      </c>
-      <c r="R42" s="99"/>
-      <c r="S42" s="100"/>
+      <c r="Q42" s="47">
+        <f>SUM(Q10:Q41)</f>
+        <v>64.105400000000003</v>
+      </c>
+      <c r="R42" s="97"/>
+      <c r="S42" s="98"/>
+    </row>
+    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="95" t="s">
+        <v>6</v>
+      </c>
+      <c r="O43" s="96"/>
+      <c r="P43" s="96"/>
+      <c r="Q43" s="48">
+        <f>Q42/5</f>
+        <v>12.82108</v>
+      </c>
+      <c r="R43" s="99"/>
+      <c r="S43" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S42"/>
     <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S43"/>
+    <mergeCell ref="N43:P43"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O11" r:id="rId1"/>
@@ -6277,33 +6405,34 @@
     <hyperlink ref="O30" r:id="rId12"/>
     <hyperlink ref="O26" r:id="rId13"/>
     <hyperlink ref="O31" r:id="rId14"/>
-    <hyperlink ref="O36" r:id="rId15"/>
-    <hyperlink ref="O37" r:id="rId16"/>
-    <hyperlink ref="O38" r:id="rId17"/>
+    <hyperlink ref="O37" r:id="rId15"/>
+    <hyperlink ref="O38" r:id="rId16"/>
+    <hyperlink ref="O39" r:id="rId17"/>
     <hyperlink ref="O10" r:id="rId18"/>
     <hyperlink ref="O14" r:id="rId19"/>
     <hyperlink ref="O23" r:id="rId20"/>
     <hyperlink ref="O25" r:id="rId21"/>
     <hyperlink ref="O29" r:id="rId22"/>
     <hyperlink ref="O32" r:id="rId23"/>
-    <hyperlink ref="O33" r:id="rId24"/>
-    <hyperlink ref="O34" r:id="rId25"/>
-    <hyperlink ref="O35" r:id="rId26"/>
+    <hyperlink ref="O34" r:id="rId24"/>
+    <hyperlink ref="O35" r:id="rId25"/>
+    <hyperlink ref="O36" r:id="rId26"/>
     <hyperlink ref="O17" r:id="rId27"/>
     <hyperlink ref="O28" r:id="rId28"/>
     <hyperlink ref="O24" r:id="rId29"/>
-    <hyperlink ref="O39" r:id="rId30"/>
-    <hyperlink ref="O40" r:id="rId31"/>
+    <hyperlink ref="O40" r:id="rId30"/>
+    <hyperlink ref="O41" r:id="rId31"/>
+    <hyperlink ref="O33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId32"/>
-  <drawing r:id="rId33"/>
+  <pageSetup orientation="portrait" r:id="rId33"/>
+  <drawing r:id="rId34"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -6681,7 +6810,7 @@
     <row r="12" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="56"/>
       <c r="B12" s="46">
-        <f t="shared" ref="B12:B40" si="0">ROW(B12) - ROW($B$9)</f>
+        <f t="shared" ref="B12:B41" si="0">ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
       <c r="C12" s="67" t="s">
@@ -6715,7 +6844,7 @@
         <v>2</v>
       </c>
       <c r="M12" s="37">
-        <f t="shared" ref="M12:M40" si="1">L12*50</f>
+        <f t="shared" ref="M12:M41" si="1">L12*50</f>
         <v>100</v>
       </c>
       <c r="N12" s="37">
@@ -7796,7 +7925,7 @@
     <row r="32" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="56"/>
       <c r="B32" s="72">
-        <f t="shared" ref="B32" si="8">ROW(B32) - ROW($B$9)</f>
+        <f t="shared" ref="B32:B33" si="8">ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
       <c r="C32" s="87" t="s">
@@ -7850,259 +7979,259 @@
       </c>
       <c r="S32" s="94"/>
     </row>
-    <row r="33" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="56"/>
       <c r="B33" s="46">
-        <f>ROW(B33) - ROW($B$9)</f>
+        <f t="shared" si="8"/>
         <v>24</v>
       </c>
-      <c r="C33" s="68" t="s">
+      <c r="C33" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="49" t="s">
+        <v>228</v>
+      </c>
+      <c r="E33" s="85" t="s">
+        <v>229</v>
+      </c>
+      <c r="F33" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="G33" s="85" t="s">
+        <v>230</v>
+      </c>
+      <c r="H33" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J33" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="K33" s="37" t="s">
+        <v>232</v>
+      </c>
+      <c r="L33" s="37">
+        <v>1</v>
+      </c>
+      <c r="M33" s="37">
+        <f>L33*50</f>
+        <v>50</v>
+      </c>
+      <c r="N33" s="37">
+        <v>100</v>
+      </c>
+      <c r="O33" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P33" s="38">
+        <v>1E-3</v>
+      </c>
+      <c r="Q33" s="50">
+        <f>P33*N33</f>
+        <v>0.1</v>
+      </c>
+      <c r="R33" s="76"/>
+      <c r="S33" s="55"/>
+    </row>
+    <row r="34" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A34" s="56"/>
+      <c r="B34" s="46">
+        <f>ROW(B34) - ROW($B$9)</f>
+        <v>25</v>
+      </c>
+      <c r="C34" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="D33" s="37" t="s">
+      <c r="D34" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="37" t="s">
+      <c r="E34" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="F33" s="37" t="s">
+      <c r="F34" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="G33" s="37" t="s">
+      <c r="G34" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="H33" s="37" t="s">
+      <c r="H34" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I33" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J33" s="37" t="s">
+      <c r="I34" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="K33" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L33" s="37">
-        <v>1</v>
-      </c>
-      <c r="M33" s="37">
+      <c r="K34" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="L34" s="37">
+        <v>1</v>
+      </c>
+      <c r="M34" s="37">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N33" s="37">
+      <c r="N34" s="37">
         <v>55</v>
       </c>
-      <c r="O33" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P33" s="38">
+      <c r="O34" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P34" s="38">
         <v>0.1336</v>
       </c>
-      <c r="Q33" s="38">
-        <f>P33*N33</f>
+      <c r="Q34" s="38">
+        <f>P34*N34</f>
         <v>7.3479999999999999</v>
       </c>
-      <c r="R33" s="37"/>
-      <c r="S33" s="55"/>
-    </row>
-    <row r="34" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A34" s="56"/>
-      <c r="B34" s="72">
-        <f t="shared" ref="B34" si="9">ROW(B34) - ROW($B$9)</f>
-        <v>25</v>
-      </c>
-      <c r="C34" s="68" t="s">
+      <c r="R34" s="37"/>
+      <c r="S34" s="55"/>
+    </row>
+    <row r="35" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A35" s="56"/>
+      <c r="B35" s="72">
+        <f t="shared" ref="B35" si="9">ROW(B35) - ROW($B$9)</f>
+        <v>26</v>
+      </c>
+      <c r="C35" s="68" t="s">
         <v>187</v>
       </c>
-      <c r="D34" s="49" t="s">
+      <c r="D35" s="49" t="s">
         <v>188</v>
       </c>
-      <c r="E34" s="49" t="s">
+      <c r="E35" s="49" t="s">
         <v>189</v>
       </c>
-      <c r="F34" s="49" t="s">
+      <c r="F35" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="G34" s="49" t="s">
+      <c r="G35" s="49" t="s">
         <v>190</v>
       </c>
-      <c r="H34" s="49" t="s">
+      <c r="H35" s="49" t="s">
         <v>191</v>
       </c>
-      <c r="I34" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J34" s="49" t="s">
+      <c r="I35" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J35" s="49" t="s">
         <v>192</v>
       </c>
-      <c r="K34" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="L34" s="49">
+      <c r="K35" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L35" s="49">
         <v>2</v>
       </c>
-      <c r="M34" s="37">
+      <c r="M35" s="37">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="N34" s="49">
+      <c r="N35" s="49">
         <v>110</v>
       </c>
-      <c r="O34" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P34" s="50">
+      <c r="O35" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P35" s="50">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="Q34" s="50">
-        <f t="shared" ref="Q34" si="10">P34*N34</f>
+      <c r="Q35" s="50">
+        <f t="shared" ref="Q35" si="10">P35*N35</f>
         <v>4.5540000000000003</v>
       </c>
-      <c r="R34" s="49"/>
-      <c r="S34" s="55"/>
-    </row>
-    <row r="35" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
-      <c r="A35" s="56"/>
-      <c r="B35" s="46">
-        <f>ROW(B35) - ROW($B$9)</f>
-        <v>26</v>
-      </c>
-      <c r="C35" s="67" t="s">
-        <v>187</v>
-      </c>
-      <c r="D35" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="E35" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="F35" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="H35" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="I35" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J35" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="K35" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="L35" s="37">
-        <v>1</v>
-      </c>
-      <c r="M35" s="37">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="N35" s="37">
-        <v>60</v>
-      </c>
-      <c r="O35" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P35" s="38">
-        <v>6.4600000000000005E-2</v>
-      </c>
-      <c r="Q35" s="38">
-        <f>P35*N35</f>
-        <v>3.8760000000000003</v>
-      </c>
-      <c r="R35" s="37"/>
+      <c r="R35" s="49"/>
       <c r="S35" s="55"/>
     </row>
-    <row r="36" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" s="58" customFormat="1" ht="36" x14ac:dyDescent="0.25">
       <c r="A36" s="56"/>
       <c r="B36" s="46">
-        <f t="shared" si="0"/>
+        <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="E36" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="F36" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="G36" s="49" t="s">
-        <v>83</v>
-      </c>
-      <c r="H36" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="I36" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="J36" s="49" t="s">
-        <v>114</v>
+      <c r="C36" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="D36" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="E36" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="F36" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G36" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="H36" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I36" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J36" s="37" t="s">
+        <v>196</v>
       </c>
       <c r="K36" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L36" s="49">
+      <c r="L36" s="37">
         <v>1</v>
       </c>
       <c r="M36" s="37">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N36" s="49">
-        <v>55</v>
-      </c>
-      <c r="O36" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="P36" s="50">
-        <v>0.14460000000000001</v>
-      </c>
-      <c r="Q36" s="50">
-        <f t="shared" ref="Q36:Q37" si="11">P36*N36</f>
-        <v>7.9530000000000003</v>
-      </c>
-      <c r="R36" s="49"/>
+      <c r="N36" s="37">
+        <v>60</v>
+      </c>
+      <c r="O36" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="P36" s="38">
+        <v>6.4600000000000005E-2</v>
+      </c>
+      <c r="Q36" s="38">
+        <f>P36*N36</f>
+        <v>3.8760000000000003</v>
+      </c>
+      <c r="R36" s="37"/>
       <c r="S36" s="55"/>
     </row>
-    <row r="37" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="56"/>
       <c r="B37" s="46">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C37" s="68" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D37" s="49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E37" s="49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F37" s="49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G37" s="49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H37" s="49" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I37" s="49" t="s">
         <v>134</v>
       </c>
       <c r="J37" s="49" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K37" s="37" t="s">
         <v>134</v>
@@ -8115,108 +8244,110 @@
         <v>50</v>
       </c>
       <c r="N37" s="49">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="O37" s="60" t="s">
         <v>136</v>
       </c>
       <c r="P37" s="50">
-        <v>0.4073</v>
+        <v>0.14460000000000001</v>
       </c>
       <c r="Q37" s="50">
-        <f t="shared" si="11"/>
-        <v>21.179600000000001</v>
+        <f t="shared" ref="Q37:Q38" si="11">P37*N37</f>
+        <v>7.9530000000000003</v>
       </c>
       <c r="R37" s="49"/>
       <c r="S37" s="55"/>
     </row>
-    <row r="38" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" s="58" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A38" s="56"/>
       <c r="B38" s="46">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="E38" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="F38" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G38" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="H38" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="I38" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J38" s="37" t="s">
-        <v>116</v>
+      <c r="C38" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="F38" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="G38" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="H38" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="I38" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="J38" s="49" t="s">
+        <v>115</v>
       </c>
       <c r="K38" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="L38" s="37">
+      <c r="L38" s="49">
         <v>1</v>
       </c>
       <c r="M38" s="37">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="N38" s="37">
+      <c r="N38" s="49">
         <v>52</v>
       </c>
-      <c r="O38" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="P38" s="38">
-        <v>2.7953000000000001</v>
-      </c>
-      <c r="Q38" s="38">
-        <f>P38*N38</f>
-        <v>145.35560000000001</v>
-      </c>
-      <c r="R38" s="37"/>
-      <c r="S38" s="39"/>
-    </row>
-    <row r="39" spans="1:19" s="58" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O38" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="P38" s="50">
+        <v>0.4073</v>
+      </c>
+      <c r="Q38" s="50">
+        <f t="shared" si="11"/>
+        <v>21.179600000000001</v>
+      </c>
+      <c r="R38" s="49"/>
+      <c r="S38" s="55"/>
+    </row>
+    <row r="39" spans="1:19" s="58" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="56"/>
       <c r="B39" s="46">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C39" s="67" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>143</v>
+        <v>36</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>225</v>
+        <v>55</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="H39" s="37" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="I39" s="37" t="s">
         <v>134</v>
       </c>
       <c r="J39" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="K39" s="37"/>
+        <v>116</v>
+      </c>
+      <c r="K39" s="37" t="s">
+        <v>134</v>
+      </c>
       <c r="L39" s="37">
         <v>1</v>
       </c>
@@ -8225,17 +8356,17 @@
         <v>50</v>
       </c>
       <c r="N39" s="37">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="O39" s="59" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="P39" s="38">
-        <v>4.67</v>
+        <v>2.7953000000000001</v>
       </c>
       <c r="Q39" s="38">
         <f>P39*N39</f>
-        <v>233.5</v>
+        <v>145.35560000000001</v>
       </c>
       <c r="R39" s="37"/>
       <c r="S39" s="39"/>
@@ -8247,13 +8378,13 @@
         <v>31</v>
       </c>
       <c r="C40" s="67" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D40" s="37" t="s">
         <v>143</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F40" s="37" t="s">
         <v>134</v>
@@ -8285,74 +8416,128 @@
         <v>147</v>
       </c>
       <c r="P40" s="38">
-        <v>0.35</v>
-      </c>
-      <c r="Q40" s="71">
+        <v>4.67</v>
+      </c>
+      <c r="Q40" s="38">
         <f>P40*N40</f>
-        <v>17.5</v>
+        <v>233.5</v>
       </c>
       <c r="R40" s="37"/>
       <c r="S40" s="39"/>
     </row>
-    <row r="41" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1"/>
-      <c r="B41" s="40"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="44"/>
-      <c r="G41" s="45"/>
-      <c r="H41" s="44"/>
-      <c r="I41" s="45"/>
-      <c r="J41" s="44"/>
-      <c r="K41" s="45"/>
-      <c r="L41" s="45"/>
-      <c r="M41" s="45"/>
-      <c r="N41" s="95" t="s">
-        <v>5</v>
-      </c>
-      <c r="O41" s="96"/>
-      <c r="P41" s="96"/>
-      <c r="Q41" s="47">
-        <f>SUM(Q10:Q40)</f>
-        <v>515.23210000000006</v>
-      </c>
-      <c r="R41" s="97"/>
-      <c r="S41" s="98"/>
+    <row r="41" spans="1:19" s="58" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="56"/>
+      <c r="B41" s="46">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C41" s="67" t="s">
+        <v>145</v>
+      </c>
+      <c r="D41" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="F41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="G41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="I41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="J41" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="K41" s="37"/>
+      <c r="L41" s="37">
+        <v>1</v>
+      </c>
+      <c r="M41" s="37">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="N41" s="37">
+        <v>50</v>
+      </c>
+      <c r="O41" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="P41" s="38">
+        <v>0.35</v>
+      </c>
+      <c r="Q41" s="71">
+        <f>P41*N41</f>
+        <v>17.5</v>
+      </c>
+      <c r="R41" s="37"/>
+      <c r="S41" s="39"/>
     </row>
     <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
       <c r="N42" s="95" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O42" s="96"/>
       <c r="P42" s="96"/>
-      <c r="Q42" s="48">
-        <f>Q41/50</f>
-        <v>10.304642000000001</v>
-      </c>
-      <c r="R42" s="99"/>
-      <c r="S42" s="100"/>
+      <c r="Q42" s="47">
+        <f>SUM(Q10:Q41)</f>
+        <v>515.33210000000008</v>
+      </c>
+      <c r="R42" s="97"/>
+      <c r="S42" s="98"/>
+    </row>
+    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="95" t="s">
+        <v>6</v>
+      </c>
+      <c r="O43" s="96"/>
+      <c r="P43" s="96"/>
+      <c r="Q43" s="48">
+        <f>Q42/50</f>
+        <v>10.306642000000002</v>
+      </c>
+      <c r="R43" s="99"/>
+      <c r="S43" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S42"/>
     <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S43"/>
+    <mergeCell ref="N43:P43"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O11" r:id="rId1"/>
@@ -8369,27 +8554,28 @@
     <hyperlink ref="O30" r:id="rId12"/>
     <hyperlink ref="O26" r:id="rId13"/>
     <hyperlink ref="O31" r:id="rId14"/>
-    <hyperlink ref="O36" r:id="rId15"/>
-    <hyperlink ref="O37" r:id="rId16"/>
-    <hyperlink ref="O38" r:id="rId17"/>
+    <hyperlink ref="O37" r:id="rId15"/>
+    <hyperlink ref="O38" r:id="rId16"/>
+    <hyperlink ref="O39" r:id="rId17"/>
     <hyperlink ref="O10" r:id="rId18"/>
     <hyperlink ref="O14" r:id="rId19"/>
     <hyperlink ref="O23" r:id="rId20"/>
     <hyperlink ref="O25" r:id="rId21"/>
     <hyperlink ref="O29" r:id="rId22"/>
     <hyperlink ref="O32" r:id="rId23"/>
-    <hyperlink ref="O33" r:id="rId24"/>
-    <hyperlink ref="O34" r:id="rId25"/>
-    <hyperlink ref="O35" r:id="rId26"/>
+    <hyperlink ref="O34" r:id="rId24"/>
+    <hyperlink ref="O35" r:id="rId25"/>
+    <hyperlink ref="O36" r:id="rId26"/>
     <hyperlink ref="O28" r:id="rId27"/>
     <hyperlink ref="O17" r:id="rId28"/>
-    <hyperlink ref="O39" r:id="rId29"/>
-    <hyperlink ref="O40" r:id="rId30"/>
+    <hyperlink ref="O40" r:id="rId29"/>
+    <hyperlink ref="O41" r:id="rId30"/>
     <hyperlink ref="O24" r:id="rId31"/>
+    <hyperlink ref="O33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId32"/>
-  <drawing r:id="rId33"/>
+  <pageSetup orientation="portrait" r:id="rId33"/>
+  <drawing r:id="rId34"/>
 </worksheet>
 </file>
 
